--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="M12" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N12" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.63</v>
+        <v>1.9</v>
       </c>
       <c r="M13" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="N13" t="n">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.25</v>
+        <v>1.63</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="N14" t="n">
-        <v>3.3</v>
+        <v>5.7</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AB14" t="n">
         <v>1.75</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.9</v>
+        <v>2.35</v>
       </c>
       <c r="M15" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="N15" t="n">
-        <v>4.3</v>
+        <v>2.85</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.5</v>
+        <v>7.4</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="N16" t="n">
-        <v>3</v>
+        <v>1.45</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,16 +2370,16 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.3</v>
+        <v>1.63</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.62</v>
+        <v>2.25</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="M17" t="n">
-        <v>4.15</v>
+        <v>5.9</v>
       </c>
       <c r="N17" t="n">
-        <v>6.1</v>
+        <v>12</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,16 +2489,16 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,61 +2563,61 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="M18" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="N18" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AC18" t="n">
         <v>2.3</v>
       </c>
-      <c r="M18" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N18" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>0</v>
-      </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>7.4</v>
+        <v>2.3</v>
       </c>
       <c r="M20" t="n">
-        <v>4.4</v>
+        <v>3.45</v>
       </c>
       <c r="N20" t="n">
-        <v>1.45</v>
+        <v>3.05</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,16 +2846,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.25</v>
+        <v>1.9</v>
       </c>
       <c r="M21" t="n">
-        <v>5.9</v>
+        <v>3.45</v>
       </c>
       <c r="N21" t="n">
-        <v>12</v>
+        <v>4.3</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,16 +2965,16 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="AB21" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="M22" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="N22" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.63</v>
+        <v>2.3</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.25</v>
+        <v>1.62</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.3</v>
+        <v>1.63</v>
       </c>
       <c r="M11" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="N11" t="n">
-        <v>3.1</v>
+        <v>5.7</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.63</v>
+        <v>2.3</v>
       </c>
       <c r="M14" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="N14" t="n">
-        <v>5.7</v>
+        <v>3.1</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="M21" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="N21" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.65</v>
+        <v>2.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.2</v>
+        <v>1.62</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="M22" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="N22" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.3</v>
+        <v>1.65</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.62</v>
+        <v>2.2</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.63</v>
+        <v>2.25</v>
       </c>
       <c r="M11" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="N11" t="n">
-        <v>5.7</v>
+        <v>3.3</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,7 +1775,7 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AB11" t="n">
         <v>1.75</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.25</v>
+        <v>1.63</v>
       </c>
       <c r="M12" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="N12" t="n">
-        <v>3.3</v>
+        <v>5.7</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,7 +1894,7 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AB12" t="n">
         <v>1.75</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="M13" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N13" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="M14" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="N14" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2209,7 +2209,7 @@
         <v>2.35</v>
       </c>
       <c r="M15" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="N15" t="n">
         <v>2.85</v>
@@ -2251,16 +2251,16 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>7.4</v>
+        <v>2.5</v>
       </c>
       <c r="M16" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="N16" t="n">
-        <v>1.45</v>
+        <v>3</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,16 +2370,16 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.63</v>
+        <v>2.3</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.25</v>
+        <v>1.62</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.55</v>
+        <v>2.3</v>
       </c>
       <c r="M18" t="n">
-        <v>4.15</v>
+        <v>3.45</v>
       </c>
       <c r="N18" t="n">
-        <v>6.1</v>
+        <v>3.05</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,16 +2608,16 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.53</v>
+        <v>1.78</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.35</v>
+        <v>7.4</v>
       </c>
       <c r="M19" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="N19" t="n">
-        <v>2.85</v>
+        <v>1.45</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,16 +2727,16 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="M20" t="n">
         <v>3.45</v>
       </c>
       <c r="N20" t="n">
-        <v>3.05</v>
+        <v>4.3</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.5</v>
+        <v>1.55</v>
       </c>
       <c r="M21" t="n">
-        <v>3.1</v>
+        <v>4.15</v>
       </c>
       <c r="N21" t="n">
-        <v>3</v>
+        <v>6.1</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,16 +2965,16 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AC21" t="n">
         <v>2.3</v>
       </c>
-      <c r="AB21" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.9</v>
+        <v>2.35</v>
       </c>
       <c r="M22" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="N22" t="n">
-        <v>4.3</v>
+        <v>2.85</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.25</v>
+        <v>1.63</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="N11" t="n">
-        <v>3.3</v>
+        <v>5.7</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,7 +1775,7 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AB11" t="n">
         <v>1.75</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.63</v>
+        <v>1.9</v>
       </c>
       <c r="M12" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="N12" t="n">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="M13" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="M14" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N14" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.35</v>
+        <v>7.4</v>
       </c>
       <c r="M15" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="N15" t="n">
-        <v>2.85</v>
+        <v>1.45</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,16 +2251,16 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="N16" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.3</v>
+        <v>1.78</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.25</v>
+        <v>2.35</v>
       </c>
       <c r="M17" t="n">
-        <v>5.9</v>
+        <v>3.7</v>
       </c>
       <c r="N17" t="n">
-        <v>12</v>
+        <v>2.85</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,16 +2489,16 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.36</v>
+        <v>1.7</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="M18" t="n">
         <v>3.45</v>
       </c>
       <c r="N18" t="n">
-        <v>3.05</v>
+        <v>4.3</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>7.4</v>
+        <v>2.5</v>
       </c>
       <c r="M19" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="N19" t="n">
-        <v>1.45</v>
+        <v>3</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,16 +2727,16 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.63</v>
+        <v>2.3</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.25</v>
+        <v>1.62</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.9</v>
+        <v>2.35</v>
       </c>
       <c r="M20" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="N20" t="n">
-        <v>4.3</v>
+        <v>2.85</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.35</v>
+        <v>1.25</v>
       </c>
       <c r="M22" t="n">
-        <v>3.55</v>
+        <v>5.9</v>
       </c>
       <c r="N22" t="n">
-        <v>2.85</v>
+        <v>12</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,16 +3084,16 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.63</v>
+        <v>1.36</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.25</v>
+        <v>8</v>
       </c>
       <c r="M8" t="n">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="N8" t="n">
-        <v>15</v>
+        <v>1.45</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1424,10 +1424,10 @@
         <v>2.35</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>8</v>
+        <v>1.25</v>
       </c>
       <c r="M9" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="N9" t="n">
-        <v>1.45</v>
+        <v>15</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1543,10 +1543,10 @@
         <v>2.35</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.63</v>
+        <v>1.9</v>
       </c>
       <c r="M11" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="N11" t="n">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="M12" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N12" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.3</v>
+        <v>1.63</v>
       </c>
       <c r="M14" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="N14" t="n">
-        <v>3.1</v>
+        <v>5.7</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>7.4</v>
+        <v>1.9</v>
       </c>
       <c r="M15" t="n">
-        <v>4.4</v>
+        <v>3.45</v>
       </c>
       <c r="N15" t="n">
-        <v>1.45</v>
+        <v>4.3</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,16 +2251,16 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="M16" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="N16" t="n">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.35</v>
+        <v>1.25</v>
       </c>
       <c r="M17" t="n">
-        <v>3.7</v>
+        <v>5.9</v>
       </c>
       <c r="N17" t="n">
-        <v>2.85</v>
+        <v>12</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,16 +2489,16 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.05</v>
+        <v>3.1</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.9</v>
+        <v>1.55</v>
       </c>
       <c r="M18" t="n">
-        <v>3.45</v>
+        <v>4.15</v>
       </c>
       <c r="N18" t="n">
-        <v>4.3</v>
+        <v>6.1</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,16 +2608,16 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="M19" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="N19" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,16 +2727,16 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC19" t="n">
         <v>2.3</v>
       </c>
-      <c r="AB19" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>0</v>
-      </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="M20" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="N20" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.63</v>
+        <v>2.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.25</v>
+        <v>1.62</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.55</v>
+        <v>7.4</v>
       </c>
       <c r="M21" t="n">
-        <v>4.15</v>
+        <v>4.4</v>
       </c>
       <c r="N21" t="n">
-        <v>6.1</v>
+        <v>1.45</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,16 +2965,16 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.25</v>
+        <v>2.3</v>
       </c>
       <c r="M22" t="n">
-        <v>5.9</v>
+        <v>3.45</v>
       </c>
       <c r="N22" t="n">
-        <v>12</v>
+        <v>3.05</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,16 +3084,16 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.36</v>
+        <v>1.78</v>
       </c>
       <c r="AB22" t="n">
-        <v>3.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI23"/>
+  <dimension ref="A1:AI24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="M6" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="N6" t="n">
-        <v>3.92</v>
+        <v>3.85</v>
       </c>
       <c r="O6" t="n">
         <v>2.79</v>
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>8</v>
+        <v>4.2</v>
       </c>
       <c r="M8" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>1.45</v>
+        <v>1.95</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1412,16 +1412,16 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.58</v>
+        <v>2.62</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.35</v>
+        <v>1.44</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1442,7 +1442,7 @@
         <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>45987.61458333334</v>
+        <v>45987.60416666666</v>
       </c>
     </row>
     <row r="9">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.25</v>
+        <v>5.1</v>
       </c>
       <c r="M9" t="n">
-        <v>5.2</v>
+        <v>4.1</v>
       </c>
       <c r="N9" t="n">
-        <v>15</v>
+        <v>1.6</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1543,10 +1543,10 @@
         <v>2.35</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1570,12 +1570,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.85</v>
+        <v>1.32</v>
       </c>
       <c r="M10" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="N10" t="n">
-        <v>3.8</v>
+        <v>9</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,16 +1656,16 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1680,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>45987.625</v>
+        <v>45987.61458333334</v>
       </c>
     </row>
     <row r="11">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="M11" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="N11" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
-        <v>45987.69791666666</v>
+        <v>45987.625</v>
       </c>
     </row>
     <row r="12">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.3</v>
+        <v>1.63</v>
       </c>
       <c r="M12" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="N12" t="n">
-        <v>3.1</v>
+        <v>5.7</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N13" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.63</v>
+        <v>2.25</v>
       </c>
       <c r="M14" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>5.7</v>
+        <v>3.3</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AB14" t="n">
         <v>1.75</v>
@@ -2165,12 +2165,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2212,7 +2212,7 @@
         <v>3.45</v>
       </c>
       <c r="N15" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.65</v>
+        <v>2.12</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2275,7 +2275,7 @@
         <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>45987.70833333334</v>
+        <v>45987.69791666666</v>
       </c>
     </row>
     <row r="16">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.35</v>
+        <v>1.26</v>
       </c>
       <c r="M16" t="n">
-        <v>3.55</v>
+        <v>6</v>
       </c>
       <c r="N16" t="n">
-        <v>2.85</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,16 +2370,16 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.63</v>
+        <v>1.36</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.25</v>
+        <v>2.5</v>
       </c>
       <c r="M17" t="n">
-        <v>5.9</v>
+        <v>3.1</v>
       </c>
       <c r="N17" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,16 +2489,16 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.36</v>
+        <v>2.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.1</v>
+        <v>1.62</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.55</v>
+        <v>6.9</v>
       </c>
       <c r="M18" t="n">
-        <v>4.15</v>
+        <v>5</v>
       </c>
       <c r="N18" t="n">
-        <v>6.1</v>
+        <v>1.38</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,16 +2608,16 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.35</v>
+        <v>2.07</v>
       </c>
       <c r="M19" t="n">
-        <v>3.7</v>
+        <v>3.56</v>
       </c>
       <c r="N19" t="n">
-        <v>2.85</v>
+        <v>3.27</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="M20" t="n">
-        <v>3.1</v>
+        <v>3.51</v>
       </c>
       <c r="N20" t="n">
-        <v>3</v>
+        <v>2.47</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.3</v>
+        <v>1.63</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.62</v>
+        <v>2.25</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>7.4</v>
+        <v>1.43</v>
       </c>
       <c r="M21" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="N21" t="n">
-        <v>1.45</v>
+        <v>6.6</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,16 +2965,16 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.3</v>
+        <v>1.71</v>
       </c>
       <c r="M22" t="n">
-        <v>3.45</v>
+        <v>3.92</v>
       </c>
       <c r="N22" t="n">
-        <v>3.05</v>
+        <v>4.33</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3117,116 +3117,235 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Atlético Madrid</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Inter Milan</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" s="3" t="n">
+        <v>45987.70833333334</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>45987</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Brazil Serie A</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Bragantino</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>Fortaleza</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="inlineStr">
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI23" s="3" t="n">
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="3" t="n">
         <v>45987.79166666666</v>
       </c>
     </row>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>5.1</v>
+        <v>1.32</v>
       </c>
       <c r="M9" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="N9" t="n">
-        <v>1.6</v>
+        <v>9</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1543,10 +1543,10 @@
         <v>2.35</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.32</v>
+        <v>5.1</v>
       </c>
       <c r="M10" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="N10" t="n">
-        <v>9</v>
+        <v>1.6</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1662,10 +1662,10 @@
         <v>2.35</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.63</v>
+        <v>1.9</v>
       </c>
       <c r="M12" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="N12" t="n">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.3</v>
+        <v>1.63</v>
       </c>
       <c r="M13" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="N13" t="n">
-        <v>3.1</v>
+        <v>5.7</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N14" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="M15" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N15" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.26</v>
+        <v>6.9</v>
       </c>
       <c r="M16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N16" t="n">
-        <v>8.800000000000001</v>
+        <v>1.38</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,16 +2370,16 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.76</v>
+        <v>2.15</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,61 +2444,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.5</v>
+        <v>1.26</v>
       </c>
       <c r="M17" t="n">
+        <v>6</v>
+      </c>
+      <c r="N17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AB17" t="n">
         <v>3.1</v>
       </c>
-      <c r="N17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>6.9</v>
+        <v>2.5</v>
       </c>
       <c r="M18" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>1.38</v>
+        <v>3</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,16 +2608,16 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.63</v>
+        <v>2.3</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.25</v>
+        <v>1.62</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.07</v>
+        <v>1.43</v>
       </c>
       <c r="M19" t="n">
-        <v>3.56</v>
+        <v>4.6</v>
       </c>
       <c r="N19" t="n">
-        <v>3.27</v>
+        <v>6.6</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="AC19" t="n">
         <v>2.3</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.63</v>
+        <v>2.07</v>
       </c>
       <c r="M20" t="n">
-        <v>3.51</v>
+        <v>3.56</v>
       </c>
       <c r="N20" t="n">
-        <v>2.47</v>
+        <v>3.27</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,16 +2846,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.43</v>
+        <v>2.29</v>
       </c>
       <c r="M21" t="n">
-        <v>4.6</v>
+        <v>3.39</v>
       </c>
       <c r="N21" t="n">
-        <v>6.6</v>
+        <v>2.95</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,16 +2965,16 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.53</v>
+        <v>1.79</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.29</v>
+        <v>2.63</v>
       </c>
       <c r="M23" t="n">
-        <v>3.39</v>
+        <v>3.51</v>
       </c>
       <c r="N23" t="n">
-        <v>2.95</v>
+        <v>2.47</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.79</v>
+        <v>1.63</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.32</v>
+        <v>5.1</v>
       </c>
       <c r="M9" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="N9" t="n">
-        <v>9</v>
+        <v>1.6</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1543,10 +1543,10 @@
         <v>2.35</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5.1</v>
+        <v>1.32</v>
       </c>
       <c r="M10" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="N10" t="n">
-        <v>1.6</v>
+        <v>9</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1662,10 +1662,10 @@
         <v>2.35</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="M12" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N12" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.63</v>
+        <v>1.9</v>
       </c>
       <c r="M13" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="N13" t="n">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.3</v>
+        <v>1.63</v>
       </c>
       <c r="M14" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="N14" t="n">
-        <v>3.1</v>
+        <v>5.7</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.26</v>
+        <v>2.29</v>
       </c>
       <c r="M17" t="n">
-        <v>6</v>
+        <v>3.39</v>
       </c>
       <c r="N17" t="n">
-        <v>8.800000000000001</v>
+        <v>2.95</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,16 +2489,16 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.36</v>
+        <v>1.79</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.1</v>
+        <v>1.95</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.5</v>
+        <v>1.71</v>
       </c>
       <c r="M18" t="n">
-        <v>3.1</v>
+        <v>3.92</v>
       </c>
       <c r="N18" t="n">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.3</v>
+        <v>1.65</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.62</v>
+        <v>2.2</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.43</v>
+        <v>2.5</v>
       </c>
       <c r="M19" t="n">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="N19" t="n">
-        <v>6.6</v>
+        <v>3</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,16 +2727,16 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.53</v>
+        <v>2.3</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.45</v>
+        <v>1.62</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.07</v>
+        <v>2.63</v>
       </c>
       <c r="M20" t="n">
-        <v>3.56</v>
+        <v>3.51</v>
       </c>
       <c r="N20" t="n">
-        <v>3.27</v>
+        <v>2.47</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,16 +2846,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.29</v>
+        <v>1.43</v>
       </c>
       <c r="M21" t="n">
-        <v>3.39</v>
+        <v>4.6</v>
       </c>
       <c r="N21" t="n">
-        <v>2.95</v>
+        <v>6.6</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,16 +2965,16 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.79</v>
+        <v>1.53</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.71</v>
+        <v>2.07</v>
       </c>
       <c r="M22" t="n">
-        <v>3.92</v>
+        <v>3.56</v>
       </c>
       <c r="N22" t="n">
-        <v>4.33</v>
+        <v>3.27</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,16 +3084,16 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.63</v>
+        <v>1.26</v>
       </c>
       <c r="M23" t="n">
-        <v>3.51</v>
+        <v>6</v>
       </c>
       <c r="N23" t="n">
-        <v>2.47</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,16 +3203,16 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.63</v>
+        <v>1.36</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>6.9</v>
+        <v>1.71</v>
       </c>
       <c r="M16" t="n">
-        <v>5</v>
+        <v>3.92</v>
       </c>
       <c r="N16" t="n">
-        <v>1.38</v>
+        <v>4.33</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,16 +2370,16 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.29</v>
+        <v>2.63</v>
       </c>
       <c r="M17" t="n">
-        <v>3.39</v>
+        <v>3.51</v>
       </c>
       <c r="N17" t="n">
-        <v>2.95</v>
+        <v>2.47</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.79</v>
+        <v>1.63</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.71</v>
+        <v>6.9</v>
       </c>
       <c r="M18" t="n">
-        <v>3.92</v>
+        <v>5</v>
       </c>
       <c r="N18" t="n">
-        <v>4.33</v>
+        <v>1.38</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,16 +2608,16 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD18" t="n">
         <v>1.65</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>0</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="M19" t="n">
-        <v>3.1</v>
+        <v>3.39</v>
       </c>
       <c r="N19" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.3</v>
+        <v>1.79</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.63</v>
+        <v>1.43</v>
       </c>
       <c r="M20" t="n">
-        <v>3.51</v>
+        <v>4.6</v>
       </c>
       <c r="N20" t="n">
-        <v>2.47</v>
+        <v>6.6</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,16 +2846,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.43</v>
+        <v>2.5</v>
       </c>
       <c r="M21" t="n">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="N21" t="n">
-        <v>6.6</v>
+        <v>3</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,16 +2965,16 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.53</v>
+        <v>2.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.45</v>
+        <v>1.62</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>5.1</v>
+        <v>1.32</v>
       </c>
       <c r="M9" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="N9" t="n">
-        <v>1.6</v>
+        <v>9</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1543,10 +1543,10 @@
         <v>2.35</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.32</v>
+        <v>5.1</v>
       </c>
       <c r="M10" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="N10" t="n">
-        <v>9</v>
+        <v>1.6</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1662,10 +1662,10 @@
         <v>2.35</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="M12" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="N12" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="M13" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="M15" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N15" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.71</v>
+        <v>1.43</v>
       </c>
       <c r="M16" t="n">
-        <v>3.92</v>
+        <v>4.6</v>
       </c>
       <c r="N16" t="n">
-        <v>4.33</v>
+        <v>6.6</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,16 +2370,16 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>6.9</v>
+        <v>2.07</v>
       </c>
       <c r="M18" t="n">
-        <v>5</v>
+        <v>3.56</v>
       </c>
       <c r="N18" t="n">
-        <v>1.38</v>
+        <v>3.27</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,16 +2608,16 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.29</v>
+        <v>1.71</v>
       </c>
       <c r="M19" t="n">
-        <v>3.39</v>
+        <v>3.92</v>
       </c>
       <c r="N19" t="n">
-        <v>2.95</v>
+        <v>4.33</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.43</v>
+        <v>2.5</v>
       </c>
       <c r="M20" t="n">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="N20" t="n">
-        <v>6.6</v>
+        <v>3</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,16 +2846,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.53</v>
+        <v>2.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.45</v>
+        <v>1.62</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.5</v>
+        <v>6.9</v>
       </c>
       <c r="M21" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="N21" t="n">
-        <v>3</v>
+        <v>1.38</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,16 +2965,16 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.3</v>
+        <v>1.63</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.62</v>
+        <v>2.25</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.07</v>
+        <v>2.29</v>
       </c>
       <c r="M22" t="n">
-        <v>3.56</v>
+        <v>3.39</v>
       </c>
       <c r="N22" t="n">
-        <v>3.27</v>
+        <v>2.95</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,16 +3084,16 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="M12" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N12" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N13" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.43</v>
+        <v>2.63</v>
       </c>
       <c r="M16" t="n">
-        <v>4.6</v>
+        <v>3.51</v>
       </c>
       <c r="N16" t="n">
-        <v>6.6</v>
+        <v>2.47</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,16 +2370,16 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.63</v>
+        <v>1.43</v>
       </c>
       <c r="M17" t="n">
-        <v>3.51</v>
+        <v>4.6</v>
       </c>
       <c r="N17" t="n">
-        <v>2.47</v>
+        <v>6.6</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,16 +2489,16 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.71</v>
+        <v>6.9</v>
       </c>
       <c r="M19" t="n">
-        <v>3.92</v>
+        <v>5</v>
       </c>
       <c r="N19" t="n">
-        <v>4.33</v>
+        <v>1.38</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,16 +2727,16 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD19" t="n">
         <v>1.65</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,61 +2801,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.5</v>
+        <v>1.26</v>
       </c>
       <c r="M20" t="n">
+        <v>6</v>
+      </c>
+      <c r="N20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AB20" t="n">
         <v>3.1</v>
       </c>
-      <c r="N20" t="n">
-        <v>3</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>6.9</v>
+        <v>2.5</v>
       </c>
       <c r="M21" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="N21" t="n">
-        <v>1.38</v>
+        <v>3</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,16 +2965,16 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.63</v>
+        <v>2.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.25</v>
+        <v>1.62</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.26</v>
+        <v>1.71</v>
       </c>
       <c r="M23" t="n">
-        <v>6</v>
+        <v>3.92</v>
       </c>
       <c r="N23" t="n">
-        <v>8.800000000000001</v>
+        <v>4.33</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,16 +3203,16 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="AB23" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.9</v>
+        <v>1.63</v>
       </c>
       <c r="M13" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="N13" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.63</v>
+        <v>1.9</v>
       </c>
       <c r="M14" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="N14" t="n">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.63</v>
+        <v>2.07</v>
       </c>
       <c r="M16" t="n">
-        <v>3.51</v>
+        <v>3.56</v>
       </c>
       <c r="N16" t="n">
-        <v>2.47</v>
+        <v>3.27</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,16 +2370,16 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.07</v>
+        <v>2.5</v>
       </c>
       <c r="M18" t="n">
-        <v>3.56</v>
+        <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>3.27</v>
+        <v>3</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,16 +2608,16 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="M21" t="n">
-        <v>3.1</v>
+        <v>3.51</v>
       </c>
       <c r="N21" t="n">
-        <v>3</v>
+        <v>2.47</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.3</v>
+        <v>1.63</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.62</v>
+        <v>2.25</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="M12" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N12" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="M14" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.07</v>
+        <v>1.26</v>
       </c>
       <c r="M16" t="n">
-        <v>3.56</v>
+        <v>6</v>
       </c>
       <c r="N16" t="n">
-        <v>3.27</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,16 +2370,16 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.05</v>
+        <v>3.1</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.3</v>
+        <v>1.76</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.43</v>
+        <v>1.71</v>
       </c>
       <c r="M17" t="n">
-        <v>4.6</v>
+        <v>3.92</v>
       </c>
       <c r="N17" t="n">
-        <v>6.6</v>
+        <v>4.33</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,16 +2489,16 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="M18" t="n">
-        <v>3.1</v>
+        <v>3.39</v>
       </c>
       <c r="N18" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.3</v>
+        <v>1.79</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>6.9</v>
+        <v>2.07</v>
       </c>
       <c r="M19" t="n">
-        <v>5</v>
+        <v>3.56</v>
       </c>
       <c r="N19" t="n">
-        <v>1.38</v>
+        <v>3.27</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,16 +2727,16 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.26</v>
+        <v>2.63</v>
       </c>
       <c r="M20" t="n">
-        <v>6</v>
+        <v>3.51</v>
       </c>
       <c r="N20" t="n">
-        <v>8.800000000000001</v>
+        <v>2.47</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,16 +2846,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="AB20" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.63</v>
+        <v>6.9</v>
       </c>
       <c r="M21" t="n">
-        <v>3.51</v>
+        <v>5</v>
       </c>
       <c r="N21" t="n">
-        <v>2.47</v>
+        <v>1.38</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2971,10 +2971,10 @@
         <v>2.25</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="M22" t="n">
-        <v>3.39</v>
+        <v>3.1</v>
       </c>
       <c r="N22" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.79</v>
+        <v>2.3</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.71</v>
+        <v>1.43</v>
       </c>
       <c r="M23" t="n">
-        <v>3.92</v>
+        <v>4.6</v>
       </c>
       <c r="N23" t="n">
-        <v>4.33</v>
+        <v>6.6</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,16 +3203,16 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="M12" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N12" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N14" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.26</v>
+        <v>1.71</v>
       </c>
       <c r="M16" t="n">
-        <v>6</v>
+        <v>3.92</v>
       </c>
       <c r="N16" t="n">
-        <v>8.800000000000001</v>
+        <v>4.33</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,16 +2370,16 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.71</v>
+        <v>1.26</v>
       </c>
       <c r="M17" t="n">
-        <v>3.92</v>
+        <v>6</v>
       </c>
       <c r="N17" t="n">
-        <v>4.33</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,16 +2489,16 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.65</v>
+        <v>1.36</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="M18" t="n">
-        <v>3.39</v>
+        <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.79</v>
+        <v>2.3</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>6.9</v>
+        <v>1.43</v>
       </c>
       <c r="M21" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="N21" t="n">
-        <v>1.38</v>
+        <v>6.6</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,16 +2965,16 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.5</v>
+        <v>6.9</v>
       </c>
       <c r="M22" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="N22" t="n">
-        <v>3</v>
+        <v>1.38</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,16 +3084,16 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.3</v>
+        <v>1.63</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.62</v>
+        <v>2.25</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.43</v>
+        <v>2.29</v>
       </c>
       <c r="M23" t="n">
-        <v>4.6</v>
+        <v>3.39</v>
       </c>
       <c r="N23" t="n">
-        <v>6.6</v>
+        <v>2.95</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,16 +3203,16 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.53</v>
+        <v>1.79</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.32</v>
+        <v>5.1</v>
       </c>
       <c r="M9" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="N9" t="n">
-        <v>9</v>
+        <v>1.6</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1543,10 +1543,10 @@
         <v>2.35</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5.1</v>
+        <v>1.32</v>
       </c>
       <c r="M10" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="N10" t="n">
-        <v>1.6</v>
+        <v>9</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1662,10 +1662,10 @@
         <v>2.35</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.25</v>
+        <v>1.63</v>
       </c>
       <c r="M12" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="N12" t="n">
-        <v>3.3</v>
+        <v>5.7</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,7 +1894,7 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AB12" t="n">
         <v>1.75</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.63</v>
+        <v>2.25</v>
       </c>
       <c r="M13" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>5.7</v>
+        <v>3.3</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,7 +2013,7 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AB13" t="n">
         <v>1.75</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="M14" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N14" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="M15" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="N15" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.71</v>
+        <v>2.5</v>
       </c>
       <c r="M16" t="n">
-        <v>3.92</v>
+        <v>3.1</v>
       </c>
       <c r="N16" t="n">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.65</v>
+        <v>2.3</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.2</v>
+        <v>1.62</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.26</v>
+        <v>2.63</v>
       </c>
       <c r="M17" t="n">
-        <v>6</v>
+        <v>3.51</v>
       </c>
       <c r="N17" t="n">
-        <v>8.800000000000001</v>
+        <v>2.47</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,16 +2489,16 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.5</v>
+        <v>1.43</v>
       </c>
       <c r="M18" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="N18" t="n">
-        <v>3</v>
+        <v>6.6</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,16 +2608,16 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AC18" t="n">
         <v>2.3</v>
       </c>
-      <c r="AB18" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>0</v>
-      </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.07</v>
+        <v>6.9</v>
       </c>
       <c r="M19" t="n">
-        <v>3.56</v>
+        <v>5</v>
       </c>
       <c r="N19" t="n">
-        <v>3.27</v>
+        <v>1.38</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,16 +2727,16 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.63</v>
+        <v>2.07</v>
       </c>
       <c r="M20" t="n">
-        <v>3.51</v>
+        <v>3.56</v>
       </c>
       <c r="N20" t="n">
-        <v>2.47</v>
+        <v>3.27</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,16 +2846,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.43</v>
+        <v>1.71</v>
       </c>
       <c r="M21" t="n">
-        <v>4.6</v>
+        <v>3.92</v>
       </c>
       <c r="N21" t="n">
-        <v>6.6</v>
+        <v>4.33</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,16 +2965,16 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>6.9</v>
+        <v>2.29</v>
       </c>
       <c r="M22" t="n">
-        <v>5</v>
+        <v>3.39</v>
       </c>
       <c r="N22" t="n">
-        <v>1.38</v>
+        <v>2.95</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,16 +3084,16 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.63</v>
+        <v>1.79</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.29</v>
+        <v>1.26</v>
       </c>
       <c r="M23" t="n">
-        <v>3.39</v>
+        <v>6</v>
       </c>
       <c r="N23" t="n">
-        <v>2.95</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,16 +3203,16 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.79</v>
+        <v>1.36</v>
       </c>
       <c r="AB23" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AD23" t="n">
         <v>1.95</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.63</v>
+        <v>1.9</v>
       </c>
       <c r="M12" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="N12" t="n">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.25</v>
+        <v>1.63</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="N13" t="n">
-        <v>3.3</v>
+        <v>5.7</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,7 +2013,7 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AB13" t="n">
         <v>1.75</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="M15" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N15" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.5</v>
+        <v>1.43</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="N16" t="n">
-        <v>3</v>
+        <v>6.6</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,16 +2370,16 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AC16" t="n">
         <v>2.3</v>
       </c>
-      <c r="AB16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.63</v>
+        <v>2.29</v>
       </c>
       <c r="M17" t="n">
-        <v>3.51</v>
+        <v>3.39</v>
       </c>
       <c r="N17" t="n">
-        <v>2.47</v>
+        <v>2.95</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.63</v>
+        <v>1.79</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.43</v>
+        <v>2.63</v>
       </c>
       <c r="M18" t="n">
-        <v>4.6</v>
+        <v>3.51</v>
       </c>
       <c r="N18" t="n">
-        <v>6.6</v>
+        <v>2.47</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,16 +2608,16 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>6.9</v>
+        <v>1.71</v>
       </c>
       <c r="M19" t="n">
-        <v>5</v>
+        <v>3.92</v>
       </c>
       <c r="N19" t="n">
-        <v>1.38</v>
+        <v>4.33</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,16 +2727,16 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.07</v>
+        <v>2.5</v>
       </c>
       <c r="M20" t="n">
-        <v>3.56</v>
+        <v>3.1</v>
       </c>
       <c r="N20" t="n">
-        <v>3.27</v>
+        <v>3</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,16 +2846,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.71</v>
+        <v>2.07</v>
       </c>
       <c r="M21" t="n">
-        <v>3.92</v>
+        <v>3.56</v>
       </c>
       <c r="N21" t="n">
-        <v>4.33</v>
+        <v>3.27</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,16 +2965,16 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.29</v>
+        <v>1.26</v>
       </c>
       <c r="M22" t="n">
-        <v>3.39</v>
+        <v>6</v>
       </c>
       <c r="N22" t="n">
-        <v>2.95</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,16 +3084,16 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.79</v>
+        <v>1.36</v>
       </c>
       <c r="AB22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AD22" t="n">
         <v>1.95</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.26</v>
+        <v>6.9</v>
       </c>
       <c r="M23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N23" t="n">
-        <v>8.800000000000001</v>
+        <v>1.38</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,16 +3203,16 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="AB23" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.76</v>
+        <v>2.15</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>5.1</v>
+        <v>1.32</v>
       </c>
       <c r="M9" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="N9" t="n">
-        <v>1.6</v>
+        <v>9</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1543,10 +1543,10 @@
         <v>2.35</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.32</v>
+        <v>5.1</v>
       </c>
       <c r="M10" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="N10" t="n">
-        <v>9</v>
+        <v>1.6</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1662,10 +1662,10 @@
         <v>2.35</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.63</v>
+        <v>2.25</v>
       </c>
       <c r="M13" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>5.7</v>
+        <v>3.3</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,7 +2013,7 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AB13" t="n">
         <v>1.75</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.3</v>
+        <v>1.63</v>
       </c>
       <c r="M14" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="N14" t="n">
-        <v>3.1</v>
+        <v>5.7</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="M15" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N15" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.43</v>
+        <v>2.29</v>
       </c>
       <c r="M16" t="n">
-        <v>4.6</v>
+        <v>3.39</v>
       </c>
       <c r="N16" t="n">
-        <v>6.6</v>
+        <v>2.95</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,16 +2370,16 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.53</v>
+        <v>1.79</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.29</v>
+        <v>6.9</v>
       </c>
       <c r="M17" t="n">
-        <v>3.39</v>
+        <v>5</v>
       </c>
       <c r="N17" t="n">
-        <v>2.95</v>
+        <v>1.38</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,16 +2489,16 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.79</v>
+        <v>1.63</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="M18" t="n">
-        <v>3.51</v>
+        <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>2.47</v>
+        <v>3</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.63</v>
+        <v>2.3</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.25</v>
+        <v>1.62</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.71</v>
+        <v>1.43</v>
       </c>
       <c r="M19" t="n">
-        <v>3.92</v>
+        <v>4.6</v>
       </c>
       <c r="N19" t="n">
-        <v>4.33</v>
+        <v>6.6</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,16 +2727,16 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,61 +2801,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.5</v>
+        <v>1.26</v>
       </c>
       <c r="M20" t="n">
+        <v>6</v>
+      </c>
+      <c r="N20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AB20" t="n">
         <v>3.1</v>
       </c>
-      <c r="N20" t="n">
-        <v>3</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.07</v>
+        <v>1.71</v>
       </c>
       <c r="M21" t="n">
-        <v>3.56</v>
+        <v>3.92</v>
       </c>
       <c r="N21" t="n">
-        <v>3.27</v>
+        <v>4.33</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,16 +2965,16 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.26</v>
+        <v>2.63</v>
       </c>
       <c r="M22" t="n">
-        <v>6</v>
+        <v>3.51</v>
       </c>
       <c r="N22" t="n">
-        <v>8.800000000000001</v>
+        <v>2.47</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,16 +3084,16 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="AB22" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>6.9</v>
+        <v>2.07</v>
       </c>
       <c r="M23" t="n">
-        <v>5</v>
+        <v>3.56</v>
       </c>
       <c r="N23" t="n">
-        <v>1.38</v>
+        <v>3.27</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,16 +3203,16 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.32</v>
+        <v>5.1</v>
       </c>
       <c r="M9" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="N9" t="n">
-        <v>9</v>
+        <v>1.6</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1543,10 +1543,10 @@
         <v>2.35</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5.1</v>
+        <v>1.32</v>
       </c>
       <c r="M10" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="N10" t="n">
-        <v>1.6</v>
+        <v>9</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1662,10 +1662,10 @@
         <v>2.35</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="M12" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N12" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N13" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="M16" t="n">
-        <v>3.39</v>
+        <v>3.1</v>
       </c>
       <c r="N16" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.79</v>
+        <v>2.3</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,61 +2563,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.5</v>
+        <v>1.26</v>
       </c>
       <c r="M18" t="n">
+        <v>6</v>
+      </c>
+      <c r="N18" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AB18" t="n">
         <v>3.1</v>
       </c>
-      <c r="N18" t="n">
-        <v>3</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.43</v>
+        <v>2.29</v>
       </c>
       <c r="M19" t="n">
-        <v>4.6</v>
+        <v>3.39</v>
       </c>
       <c r="N19" t="n">
-        <v>6.6</v>
+        <v>2.95</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,16 +2727,16 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.53</v>
+        <v>1.79</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.26</v>
+        <v>1.71</v>
       </c>
       <c r="M20" t="n">
-        <v>6</v>
+        <v>3.92</v>
       </c>
       <c r="N20" t="n">
-        <v>8.800000000000001</v>
+        <v>4.33</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,16 +2846,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="AB20" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.71</v>
+        <v>2.63</v>
       </c>
       <c r="M21" t="n">
-        <v>3.92</v>
+        <v>3.51</v>
       </c>
       <c r="N21" t="n">
-        <v>4.33</v>
+        <v>2.47</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.63</v>
+        <v>1.43</v>
       </c>
       <c r="M22" t="n">
-        <v>3.51</v>
+        <v>4.6</v>
       </c>
       <c r="N22" t="n">
-        <v>2.47</v>
+        <v>6.6</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,16 +3084,16 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="M12" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N12" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="M13" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.63</v>
+        <v>1.9</v>
       </c>
       <c r="M14" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="N14" t="n">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.3</v>
+        <v>1.63</v>
       </c>
       <c r="M15" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="N15" t="n">
-        <v>3.1</v>
+        <v>5.7</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.5</v>
+        <v>1.43</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="N16" t="n">
-        <v>3</v>
+        <v>6.6</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,16 +2370,16 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AC16" t="n">
         <v>2.3</v>
       </c>
-      <c r="AB16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>6.9</v>
+        <v>1.71</v>
       </c>
       <c r="M17" t="n">
-        <v>5</v>
+        <v>3.92</v>
       </c>
       <c r="N17" t="n">
-        <v>1.38</v>
+        <v>4.33</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,16 +2489,16 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.26</v>
+        <v>2.63</v>
       </c>
       <c r="M18" t="n">
-        <v>6</v>
+        <v>3.51</v>
       </c>
       <c r="N18" t="n">
-        <v>8.800000000000001</v>
+        <v>2.47</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,16 +2608,16 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.71</v>
+        <v>6.9</v>
       </c>
       <c r="M20" t="n">
-        <v>3.92</v>
+        <v>5</v>
       </c>
       <c r="N20" t="n">
-        <v>4.33</v>
+        <v>1.38</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,16 +2846,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD20" t="n">
         <v>1.65</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.63</v>
+        <v>2.07</v>
       </c>
       <c r="M21" t="n">
-        <v>3.51</v>
+        <v>3.56</v>
       </c>
       <c r="N21" t="n">
-        <v>2.47</v>
+        <v>3.27</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,16 +2965,16 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.43</v>
+        <v>1.26</v>
       </c>
       <c r="M22" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="N22" t="n">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,16 +3084,16 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.3</v>
+        <v>1.76</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.07</v>
+        <v>2.5</v>
       </c>
       <c r="M23" t="n">
-        <v>3.56</v>
+        <v>3.1</v>
       </c>
       <c r="N23" t="n">
-        <v>3.27</v>
+        <v>3</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,16 +3203,16 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.3</v>
+        <v>1.63</v>
       </c>
       <c r="M12" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="N12" t="n">
-        <v>3.1</v>
+        <v>5.7</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N13" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="M14" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.63</v>
+        <v>1.9</v>
       </c>
       <c r="M15" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="N15" t="n">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.71</v>
+        <v>2.07</v>
       </c>
       <c r="M17" t="n">
-        <v>3.92</v>
+        <v>3.56</v>
       </c>
       <c r="N17" t="n">
-        <v>4.33</v>
+        <v>3.27</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,16 +2489,16 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.63</v>
+        <v>2.29</v>
       </c>
       <c r="M18" t="n">
-        <v>3.51</v>
+        <v>3.39</v>
       </c>
       <c r="N18" t="n">
-        <v>2.47</v>
+        <v>2.95</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.63</v>
+        <v>1.79</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="M19" t="n">
-        <v>3.39</v>
+        <v>3.1</v>
       </c>
       <c r="N19" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.79</v>
+        <v>2.3</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>6.9</v>
+        <v>1.71</v>
       </c>
       <c r="M20" t="n">
-        <v>5</v>
+        <v>3.92</v>
       </c>
       <c r="N20" t="n">
-        <v>1.38</v>
+        <v>4.33</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,16 +2846,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.07</v>
+        <v>1.26</v>
       </c>
       <c r="M21" t="n">
-        <v>3.56</v>
+        <v>6</v>
       </c>
       <c r="N21" t="n">
-        <v>3.27</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,16 +2965,16 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.05</v>
+        <v>3.1</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.3</v>
+        <v>1.76</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.26</v>
+        <v>6.9</v>
       </c>
       <c r="M22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N22" t="n">
-        <v>8.800000000000001</v>
+        <v>1.38</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,16 +3084,16 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="AB22" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.76</v>
+        <v>2.15</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="M23" t="n">
-        <v>3.1</v>
+        <v>3.51</v>
       </c>
       <c r="N23" t="n">
-        <v>3</v>
+        <v>2.47</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.3</v>
+        <v>1.63</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.62</v>
+        <v>2.25</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="M6" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="N6" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="O6" t="n">
         <v>2.79</v>
@@ -1180,10 +1180,10 @@
         <v>2.49</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AC6" t="n">
         <v>4.35</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>5.1</v>
+        <v>1.32</v>
       </c>
       <c r="M9" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="N9" t="n">
-        <v>1.6</v>
+        <v>9</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1543,10 +1543,10 @@
         <v>2.35</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.32</v>
+        <v>5.1</v>
       </c>
       <c r="M10" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="N10" t="n">
-        <v>9</v>
+        <v>1.6</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1662,10 +1662,10 @@
         <v>2.35</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.63</v>
+        <v>2.25</v>
       </c>
       <c r="M12" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="N12" t="n">
-        <v>5.7</v>
+        <v>3.3</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,7 +1894,7 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AB12" t="n">
         <v>1.75</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.3</v>
+        <v>1.63</v>
       </c>
       <c r="M13" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="N13" t="n">
-        <v>3.1</v>
+        <v>5.7</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N14" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.43</v>
+        <v>2.5</v>
       </c>
       <c r="M16" t="n">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="N16" t="n">
-        <v>6.6</v>
+        <v>3</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,16 +2370,16 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.53</v>
+        <v>2.3</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.45</v>
+        <v>1.62</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.07</v>
+        <v>2.29</v>
       </c>
       <c r="M17" t="n">
-        <v>3.56</v>
+        <v>3.39</v>
       </c>
       <c r="N17" t="n">
-        <v>3.27</v>
+        <v>2.95</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,16 +2489,16 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.29</v>
+        <v>2.07</v>
       </c>
       <c r="M18" t="n">
-        <v>3.39</v>
+        <v>3.56</v>
       </c>
       <c r="N18" t="n">
-        <v>2.95</v>
+        <v>3.27</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,16 +2608,16 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.5</v>
+        <v>1.43</v>
       </c>
       <c r="M19" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="N19" t="n">
-        <v>3</v>
+        <v>6.6</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,16 +2727,16 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AC19" t="n">
         <v>2.3</v>
       </c>
-      <c r="AB19" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>0</v>
-      </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.71</v>
+        <v>6.9</v>
       </c>
       <c r="M20" t="n">
-        <v>3.92</v>
+        <v>5</v>
       </c>
       <c r="N20" t="n">
-        <v>4.33</v>
+        <v>1.38</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,16 +2846,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD20" t="n">
         <v>1.65</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.26</v>
+        <v>2.63</v>
       </c>
       <c r="M21" t="n">
-        <v>6</v>
+        <v>3.51</v>
       </c>
       <c r="N21" t="n">
-        <v>8.800000000000001</v>
+        <v>2.47</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,16 +2965,16 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="AB21" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>6.9</v>
+        <v>1.71</v>
       </c>
       <c r="M22" t="n">
-        <v>5</v>
+        <v>3.92</v>
       </c>
       <c r="N22" t="n">
-        <v>1.38</v>
+        <v>4.33</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,16 +3084,16 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.63</v>
+        <v>1.26</v>
       </c>
       <c r="M23" t="n">
-        <v>3.51</v>
+        <v>6</v>
       </c>
       <c r="N23" t="n">
-        <v>2.47</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,16 +3203,16 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.63</v>
+        <v>1.36</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.32</v>
+        <v>5.1</v>
       </c>
       <c r="M9" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="N9" t="n">
-        <v>9</v>
+        <v>1.6</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1543,10 +1543,10 @@
         <v>2.35</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5.1</v>
+        <v>1.32</v>
       </c>
       <c r="M10" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="N10" t="n">
-        <v>1.6</v>
+        <v>9</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1662,10 +1662,10 @@
         <v>2.35</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="M12" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N12" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="M14" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1</v>
+        <v>3.51</v>
       </c>
       <c r="N16" t="n">
-        <v>3</v>
+        <v>2.47</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.3</v>
+        <v>1.63</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.62</v>
+        <v>2.25</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.29</v>
+        <v>6.9</v>
       </c>
       <c r="M17" t="n">
-        <v>3.39</v>
+        <v>5</v>
       </c>
       <c r="N17" t="n">
-        <v>2.95</v>
+        <v>1.38</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,16 +2489,16 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.79</v>
+        <v>1.63</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.07</v>
+        <v>1.26</v>
       </c>
       <c r="M18" t="n">
-        <v>3.56</v>
+        <v>6</v>
       </c>
       <c r="N18" t="n">
-        <v>3.27</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,16 +2608,16 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.05</v>
+        <v>3.1</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.3</v>
+        <v>1.76</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.43</v>
+        <v>2.5</v>
       </c>
       <c r="M19" t="n">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="N19" t="n">
-        <v>6.6</v>
+        <v>3</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,16 +2727,16 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.53</v>
+        <v>2.3</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.45</v>
+        <v>1.62</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>6.9</v>
+        <v>2.29</v>
       </c>
       <c r="M20" t="n">
-        <v>5</v>
+        <v>3.39</v>
       </c>
       <c r="N20" t="n">
-        <v>1.38</v>
+        <v>2.95</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,16 +2846,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.63</v>
+        <v>1.79</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.63</v>
+        <v>1.71</v>
       </c>
       <c r="M21" t="n">
-        <v>3.51</v>
+        <v>3.92</v>
       </c>
       <c r="N21" t="n">
-        <v>2.47</v>
+        <v>4.33</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.71</v>
+        <v>2.07</v>
       </c>
       <c r="M22" t="n">
-        <v>3.92</v>
+        <v>3.56</v>
       </c>
       <c r="N22" t="n">
-        <v>4.33</v>
+        <v>3.27</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,16 +3084,16 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.26</v>
+        <v>1.43</v>
       </c>
       <c r="M23" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="N23" t="n">
-        <v>8.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,16 +3203,16 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AB23" t="n">
-        <v>3.1</v>
+        <v>2.45</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.76</v>
+        <v>2.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>5.1</v>
+        <v>1.32</v>
       </c>
       <c r="M9" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="N9" t="n">
-        <v>1.6</v>
+        <v>9</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1543,10 +1543,10 @@
         <v>2.35</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.32</v>
+        <v>5.1</v>
       </c>
       <c r="M10" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="N10" t="n">
-        <v>9</v>
+        <v>1.6</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1662,10 +1662,10 @@
         <v>2.35</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="M11" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="N11" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="M12" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="N12" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.63</v>
+        <v>2.25</v>
       </c>
       <c r="M13" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>5.7</v>
+        <v>3.3</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,7 +2013,7 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AB13" t="n">
         <v>1.75</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.25</v>
+        <v>1.63</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="N14" t="n">
-        <v>3.3</v>
+        <v>5.7</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AB14" t="n">
         <v>1.75</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="M15" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N15" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="M16" t="n">
-        <v>3.51</v>
+        <v>3.1</v>
       </c>
       <c r="N16" t="n">
-        <v>2.47</v>
+        <v>3</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.63</v>
+        <v>2.3</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.25</v>
+        <v>1.62</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>6.9</v>
+        <v>1.43</v>
       </c>
       <c r="M17" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="N17" t="n">
-        <v>1.38</v>
+        <v>6.6</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,16 +2489,16 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.26</v>
+        <v>2.63</v>
       </c>
       <c r="M18" t="n">
-        <v>6</v>
+        <v>3.51</v>
       </c>
       <c r="N18" t="n">
-        <v>8.800000000000001</v>
+        <v>2.47</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,16 +2608,16 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.5</v>
+        <v>2.07</v>
       </c>
       <c r="M19" t="n">
-        <v>3.1</v>
+        <v>3.56</v>
       </c>
       <c r="N19" t="n">
-        <v>3</v>
+        <v>3.27</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,16 +2727,16 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC19" t="n">
         <v>2.3</v>
       </c>
-      <c r="AB19" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>0</v>
-      </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.71</v>
+        <v>6.9</v>
       </c>
       <c r="M21" t="n">
-        <v>3.92</v>
+        <v>5</v>
       </c>
       <c r="N21" t="n">
-        <v>4.33</v>
+        <v>1.38</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,16 +2965,16 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD21" t="n">
         <v>1.65</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.07</v>
+        <v>1.26</v>
       </c>
       <c r="M22" t="n">
-        <v>3.56</v>
+        <v>6</v>
       </c>
       <c r="N22" t="n">
-        <v>3.27</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,16 +3084,16 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.05</v>
+        <v>3.1</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.3</v>
+        <v>1.76</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.43</v>
+        <v>1.71</v>
       </c>
       <c r="M23" t="n">
-        <v>4.6</v>
+        <v>3.92</v>
       </c>
       <c r="N23" t="n">
-        <v>6.6</v>
+        <v>4.33</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,16 +3203,16 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.32</v>
+        <v>5.1</v>
       </c>
       <c r="M9" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="N9" t="n">
-        <v>9</v>
+        <v>1.6</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1543,10 +1543,10 @@
         <v>2.35</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5.1</v>
+        <v>1.32</v>
       </c>
       <c r="M10" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="N10" t="n">
-        <v>1.6</v>
+        <v>9</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1662,10 +1662,10 @@
         <v>2.35</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.25</v>
+        <v>1.63</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="N13" t="n">
-        <v>3.3</v>
+        <v>5.7</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,7 +2013,7 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AB13" t="n">
         <v>1.75</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.63</v>
+        <v>2.25</v>
       </c>
       <c r="M14" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>5.7</v>
+        <v>3.3</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AB14" t="n">
         <v>1.75</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.5</v>
+        <v>6.9</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="N16" t="n">
-        <v>3</v>
+        <v>1.38</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,16 +2370,16 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.3</v>
+        <v>1.63</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.62</v>
+        <v>2.25</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.43</v>
+        <v>2.29</v>
       </c>
       <c r="M17" t="n">
-        <v>4.6</v>
+        <v>3.39</v>
       </c>
       <c r="N17" t="n">
-        <v>6.6</v>
+        <v>2.95</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,16 +2489,16 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.53</v>
+        <v>1.79</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="M18" t="n">
-        <v>3.51</v>
+        <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>2.47</v>
+        <v>3</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.63</v>
+        <v>2.3</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.25</v>
+        <v>1.62</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.07</v>
+        <v>2.63</v>
       </c>
       <c r="M19" t="n">
-        <v>3.56</v>
+        <v>3.51</v>
       </c>
       <c r="N19" t="n">
-        <v>3.27</v>
+        <v>2.47</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,16 +2727,16 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.29</v>
+        <v>1.43</v>
       </c>
       <c r="M20" t="n">
-        <v>3.39</v>
+        <v>4.6</v>
       </c>
       <c r="N20" t="n">
-        <v>2.95</v>
+        <v>6.6</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,16 +2846,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.79</v>
+        <v>1.53</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>6.9</v>
+        <v>1.71</v>
       </c>
       <c r="M21" t="n">
-        <v>5</v>
+        <v>3.92</v>
       </c>
       <c r="N21" t="n">
-        <v>1.38</v>
+        <v>4.33</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,16 +2965,16 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.71</v>
+        <v>2.07</v>
       </c>
       <c r="M23" t="n">
-        <v>3.92</v>
+        <v>3.56</v>
       </c>
       <c r="N23" t="n">
-        <v>4.33</v>
+        <v>3.27</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,16 +3203,16 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.9</v>
+        <v>1.63</v>
       </c>
       <c r="M12" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="N12" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.63</v>
+        <v>1.9</v>
       </c>
       <c r="M13" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="N13" t="n">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N14" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="M15" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N15" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>6.9</v>
+        <v>1.26</v>
       </c>
       <c r="M16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N16" t="n">
-        <v>1.38</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,16 +2370,16 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.63</v>
+        <v>1.36</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.15</v>
+        <v>1.76</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.29</v>
+        <v>6.9</v>
       </c>
       <c r="M17" t="n">
-        <v>3.39</v>
+        <v>5</v>
       </c>
       <c r="N17" t="n">
-        <v>2.95</v>
+        <v>1.38</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,16 +2489,16 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.79</v>
+        <v>1.63</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.63</v>
+        <v>1.43</v>
       </c>
       <c r="M19" t="n">
-        <v>3.51</v>
+        <v>4.6</v>
       </c>
       <c r="N19" t="n">
-        <v>2.47</v>
+        <v>6.6</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,16 +2727,16 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.43</v>
+        <v>2.63</v>
       </c>
       <c r="M20" t="n">
-        <v>4.6</v>
+        <v>3.51</v>
       </c>
       <c r="N20" t="n">
-        <v>6.6</v>
+        <v>2.47</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,16 +2846,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.26</v>
+        <v>2.07</v>
       </c>
       <c r="M22" t="n">
-        <v>6</v>
+        <v>3.56</v>
       </c>
       <c r="N22" t="n">
-        <v>8.800000000000001</v>
+        <v>3.27</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,16 +3084,16 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.36</v>
+        <v>1.7</v>
       </c>
       <c r="AB22" t="n">
-        <v>3.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.76</v>
+        <v>2.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.07</v>
+        <v>2.29</v>
       </c>
       <c r="M23" t="n">
-        <v>3.56</v>
+        <v>3.39</v>
       </c>
       <c r="N23" t="n">
-        <v>3.27</v>
+        <v>2.95</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,16 +3203,16 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>5.1</v>
+        <v>1.32</v>
       </c>
       <c r="M9" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="N9" t="n">
-        <v>1.6</v>
+        <v>9</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1543,10 +1543,10 @@
         <v>2.35</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.32</v>
+        <v>5.1</v>
       </c>
       <c r="M10" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="N10" t="n">
-        <v>9</v>
+        <v>1.6</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1662,10 +1662,10 @@
         <v>2.35</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.63</v>
+        <v>2.3</v>
       </c>
       <c r="M12" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="N12" t="n">
-        <v>5.7</v>
+        <v>3.1</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.9</v>
+        <v>1.63</v>
       </c>
       <c r="M13" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="N13" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="M14" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="N14" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.26</v>
+        <v>1.71</v>
       </c>
       <c r="M16" t="n">
-        <v>6</v>
+        <v>3.92</v>
       </c>
       <c r="N16" t="n">
-        <v>8.800000000000001</v>
+        <v>4.33</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,16 +2370,16 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>6.9</v>
+        <v>2.63</v>
       </c>
       <c r="M17" t="n">
-        <v>5</v>
+        <v>3.51</v>
       </c>
       <c r="N17" t="n">
-        <v>1.38</v>
+        <v>2.47</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2495,10 +2495,10 @@
         <v>2.25</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,61 +2563,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.5</v>
+        <v>1.26</v>
       </c>
       <c r="M18" t="n">
+        <v>6</v>
+      </c>
+      <c r="N18" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AB18" t="n">
         <v>3.1</v>
       </c>
-      <c r="N18" t="n">
-        <v>3</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.43</v>
+        <v>2.07</v>
       </c>
       <c r="M19" t="n">
-        <v>4.6</v>
+        <v>3.56</v>
       </c>
       <c r="N19" t="n">
-        <v>6.6</v>
+        <v>3.27</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="AC19" t="n">
         <v>2.3</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.63</v>
+        <v>2.29</v>
       </c>
       <c r="M20" t="n">
-        <v>3.51</v>
+        <v>3.39</v>
       </c>
       <c r="N20" t="n">
-        <v>2.47</v>
+        <v>2.95</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.63</v>
+        <v>1.79</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.71</v>
+        <v>6.9</v>
       </c>
       <c r="M21" t="n">
-        <v>3.92</v>
+        <v>5</v>
       </c>
       <c r="N21" t="n">
-        <v>4.33</v>
+        <v>1.38</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,16 +2965,16 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD21" t="n">
         <v>1.65</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.07</v>
+        <v>2.5</v>
       </c>
       <c r="M22" t="n">
-        <v>3.56</v>
+        <v>3.1</v>
       </c>
       <c r="N22" t="n">
-        <v>3.27</v>
+        <v>3</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,16 +3084,16 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.29</v>
+        <v>1.43</v>
       </c>
       <c r="M23" t="n">
-        <v>3.39</v>
+        <v>4.6</v>
       </c>
       <c r="N23" t="n">
-        <v>2.95</v>
+        <v>6.6</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,16 +3203,16 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.79</v>
+        <v>1.53</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.32</v>
+        <v>5.1</v>
       </c>
       <c r="M9" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="N9" t="n">
-        <v>9</v>
+        <v>1.6</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1543,10 +1543,10 @@
         <v>2.35</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5.1</v>
+        <v>1.32</v>
       </c>
       <c r="M10" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="N10" t="n">
-        <v>1.6</v>
+        <v>9</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1662,10 +1662,10 @@
         <v>2.35</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="M12" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="N12" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.63</v>
+        <v>2.25</v>
       </c>
       <c r="M13" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>5.7</v>
+        <v>3.3</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,7 +2013,7 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AB13" t="n">
         <v>1.75</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.9</v>
+        <v>1.63</v>
       </c>
       <c r="M14" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="N14" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="M15" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N15" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.71</v>
+        <v>1.26</v>
       </c>
       <c r="M16" t="n">
-        <v>3.92</v>
+        <v>6</v>
       </c>
       <c r="N16" t="n">
-        <v>4.33</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,16 +2370,16 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.65</v>
+        <v>1.36</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.63</v>
+        <v>6.9</v>
       </c>
       <c r="M17" t="n">
-        <v>3.51</v>
+        <v>5</v>
       </c>
       <c r="N17" t="n">
-        <v>2.47</v>
+        <v>1.38</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2495,10 +2495,10 @@
         <v>2.25</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.26</v>
+        <v>1.71</v>
       </c>
       <c r="M18" t="n">
-        <v>6</v>
+        <v>3.92</v>
       </c>
       <c r="N18" t="n">
-        <v>8.800000000000001</v>
+        <v>4.33</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,16 +2608,16 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.07</v>
+        <v>2.5</v>
       </c>
       <c r="M19" t="n">
-        <v>3.56</v>
+        <v>3.1</v>
       </c>
       <c r="N19" t="n">
-        <v>3.27</v>
+        <v>3</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,16 +2727,16 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>6.9</v>
+        <v>2.63</v>
       </c>
       <c r="M21" t="n">
-        <v>5</v>
+        <v>3.51</v>
       </c>
       <c r="N21" t="n">
-        <v>1.38</v>
+        <v>2.47</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2971,10 +2971,10 @@
         <v>2.25</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.5</v>
+        <v>1.43</v>
       </c>
       <c r="M22" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="N22" t="n">
-        <v>3</v>
+        <v>6.6</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,16 +3084,16 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AC22" t="n">
         <v>2.3</v>
       </c>
-      <c r="AB22" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>0</v>
-      </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.43</v>
+        <v>2.07</v>
       </c>
       <c r="M23" t="n">
-        <v>4.6</v>
+        <v>3.56</v>
       </c>
       <c r="N23" t="n">
-        <v>6.6</v>
+        <v>3.27</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="AC23" t="n">
         <v>2.3</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI24"/>
+  <dimension ref="A1:AI25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1382,34 +1382,34 @@
         <v>1.95</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y8" t="n">
         <v>1.56</v>
@@ -1424,22 +1424,22 @@
         <v>1.44</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45987.60416666666</v>
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,76 +1492,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>5.1</v>
+        <v>3.3</v>
       </c>
       <c r="M9" t="n">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="N9" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.58</v>
+        <v>2.75</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.35</v>
+        <v>1.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>45987.61458333334</v>
+        <v>45987.60416666666</v>
       </c>
     </row>
     <row r="10">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.75</v>
+        <v>5.1</v>
       </c>
       <c r="M11" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="N11" t="n">
-        <v>3.95</v>
+        <v>1.6</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
-        <v>45987.625</v>
+        <v>45987.61458333334</v>
       </c>
     </row>
     <row r="12">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="M12" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="N12" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.12</v>
+        <v>1.65</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.72</v>
+        <v>2.1</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1918,7 +1918,7 @@
         <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>45987.69791666666</v>
+        <v>45987.625</v>
       </c>
     </row>
     <row r="13">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N13" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="M15" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N15" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2284,12 +2284,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.26</v>
+        <v>2.3</v>
       </c>
       <c r="M16" t="n">
-        <v>6</v>
+        <v>3.35</v>
       </c>
       <c r="N16" t="n">
-        <v>8.800000000000001</v>
+        <v>3.1</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,16 +2370,16 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.36</v>
+        <v>2.15</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -2394,7 +2394,7 @@
         <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>45987.70833333334</v>
+        <v>45987.69791666666</v>
       </c>
     </row>
     <row r="17">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>6.9</v>
+        <v>2.07</v>
       </c>
       <c r="M17" t="n">
-        <v>5</v>
+        <v>3.56</v>
       </c>
       <c r="N17" t="n">
-        <v>1.38</v>
+        <v>3.27</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,16 +2489,16 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.71</v>
+        <v>1.43</v>
       </c>
       <c r="M18" t="n">
-        <v>3.92</v>
+        <v>4.6</v>
       </c>
       <c r="N18" t="n">
-        <v>4.33</v>
+        <v>6.6</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,16 +2608,16 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="M19" t="n">
-        <v>3.1</v>
+        <v>3.51</v>
       </c>
       <c r="N19" t="n">
-        <v>3</v>
+        <v>2.47</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.3</v>
+        <v>1.63</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.62</v>
+        <v>2.25</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.29</v>
+        <v>6.9</v>
       </c>
       <c r="M20" t="n">
-        <v>3.39</v>
+        <v>5</v>
       </c>
       <c r="N20" t="n">
-        <v>2.95</v>
+        <v>1.38</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,16 +2846,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.79</v>
+        <v>1.63</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.63</v>
+        <v>2.29</v>
       </c>
       <c r="M21" t="n">
-        <v>3.51</v>
+        <v>3.39</v>
       </c>
       <c r="N21" t="n">
-        <v>2.47</v>
+        <v>2.95</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.63</v>
+        <v>1.79</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.43</v>
+        <v>1.26</v>
       </c>
       <c r="M22" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="N22" t="n">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,16 +3084,16 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.3</v>
+        <v>1.76</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.07</v>
+        <v>2.5</v>
       </c>
       <c r="M23" t="n">
-        <v>3.56</v>
+        <v>3.1</v>
       </c>
       <c r="N23" t="n">
-        <v>3.27</v>
+        <v>3</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,16 +3203,16 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -3236,116 +3236,235 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sporting CP</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Club Brugge</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="N24" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="3" t="n">
+        <v>45987.70833333334</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>45987</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Brazil Serie A</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Bragantino</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>Fortaleza</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="inlineStr">
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI24" s="3" t="n">
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" s="3" t="n">
         <v>45987.79166666666</v>
       </c>
     </row>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="M6" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="O6" t="n">
-        <v>2.79</v>
+        <v>2.5</v>
       </c>
       <c r="P6" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.4</v>
+        <v>4.65</v>
       </c>
       <c r="R6" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="S6" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="T6" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="U6" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="V6" t="n">
         <v>8.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.49</v>
+        <v>2.59</v>
       </c>
       <c r="AA6" t="n">
         <v>2.25</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45987.45833333334</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,49 +1611,49 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.32</v>
+        <v>5.1</v>
       </c>
       <c r="M10" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="N10" t="n">
-        <v>9</v>
+        <v>1.6</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA10" t="n">
         <v>1.58</v>
@@ -1662,22 +1662,22 @@
         <v>2.35</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.1</v>
+        <v>2.49</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45987.61458333334</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,49 +1730,49 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>5.1</v>
+        <v>1.32</v>
       </c>
       <c r="M11" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="N11" t="n">
-        <v>1.6</v>
+        <v>9</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA11" t="n">
         <v>1.58</v>
@@ -1781,22 +1781,22 @@
         <v>2.35</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45987.61458333334</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.63</v>
+        <v>2.3</v>
       </c>
       <c r="M14" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="N14" t="n">
-        <v>5.7</v>
+        <v>3.1</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.25</v>
+        <v>1.63</v>
       </c>
       <c r="M15" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="N15" t="n">
-        <v>3.3</v>
+        <v>5.7</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AB15" t="n">
         <v>1.75</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="M16" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N16" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.07</v>
+        <v>1.43</v>
       </c>
       <c r="M17" t="n">
-        <v>3.56</v>
+        <v>4.6</v>
       </c>
       <c r="N17" t="n">
-        <v>3.27</v>
+        <v>6.6</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="AC17" t="n">
         <v>2.3</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.43</v>
+        <v>2.63</v>
       </c>
       <c r="M18" t="n">
-        <v>4.6</v>
+        <v>3.51</v>
       </c>
       <c r="N18" t="n">
-        <v>6.6</v>
+        <v>2.47</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,16 +2608,16 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.63</v>
+        <v>2.07</v>
       </c>
       <c r="M19" t="n">
-        <v>3.51</v>
+        <v>3.56</v>
       </c>
       <c r="N19" t="n">
-        <v>2.47</v>
+        <v>3.27</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,16 +2727,16 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>6.9</v>
+        <v>1.26</v>
       </c>
       <c r="M20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N20" t="n">
-        <v>1.38</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,16 +2846,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.63</v>
+        <v>1.36</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.15</v>
+        <v>1.76</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.29</v>
+        <v>6.9</v>
       </c>
       <c r="M21" t="n">
-        <v>3.39</v>
+        <v>5</v>
       </c>
       <c r="N21" t="n">
-        <v>2.95</v>
+        <v>1.38</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,16 +2965,16 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.79</v>
+        <v>1.63</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.26</v>
+        <v>2.29</v>
       </c>
       <c r="M22" t="n">
-        <v>6</v>
+        <v>3.39</v>
       </c>
       <c r="N22" t="n">
-        <v>8.800000000000001</v>
+        <v>2.95</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,16 +3084,16 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.36</v>
+        <v>1.79</v>
       </c>
       <c r="AB22" t="n">
-        <v>3.1</v>
+        <v>1.95</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.5</v>
+        <v>1.71</v>
       </c>
       <c r="M23" t="n">
-        <v>3.1</v>
+        <v>3.92</v>
       </c>
       <c r="N23" t="n">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.3</v>
+        <v>1.65</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.62</v>
+        <v>2.2</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.71</v>
+        <v>2.5</v>
       </c>
       <c r="M24" t="n">
-        <v>3.92</v>
+        <v>3.1</v>
       </c>
       <c r="N24" t="n">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.65</v>
+        <v>2.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.2</v>
+        <v>1.62</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -1138,25 +1138,25 @@
         <v>2</v>
       </c>
       <c r="M6" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="N6" t="n">
-        <v>3.5</v>
+        <v>3.91</v>
       </c>
       <c r="O6" t="n">
-        <v>2.5</v>
+        <v>2.76</v>
       </c>
       <c r="P6" t="n">
         <v>1.84</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.65</v>
+        <v>4.89</v>
       </c>
       <c r="R6" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="S6" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="T6" t="n">
         <v>3.2</v>
@@ -1165,10 +1165,10 @@
         <v>1.27</v>
       </c>
       <c r="V6" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
         <v>1.06</v>
@@ -1183,13 +1183,13 @@
         <v>2.25</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AC6" t="n">
         <v>4.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE6" t="n">
         <v>1.95</v>
@@ -1198,10 +1198,10 @@
         <v>1.74</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45987.45833333334</v>
@@ -1373,31 +1373,31 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="N8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="O8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="P8" t="n">
         <v>1.95</v>
       </c>
-      <c r="O8" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.82</v>
-      </c>
       <c r="Q8" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="R8" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="S8" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="T8" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="U8" t="n">
         <v>1.22</v>
@@ -1409,37 +1409,37 @@
         <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AA8" t="n">
         <v>2.62</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AC8" t="n">
         <v>5.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45987.60416666666</v>
@@ -1492,31 +1492,31 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="M9" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="N9" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="O9" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="P9" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
         <v>1.64</v>
       </c>
       <c r="S9" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="T9" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="U9" t="n">
         <v>1.28</v>
@@ -1525,40 +1525,40 @@
         <v>8.800000000000001</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.37</v>
+        <v>2.2</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="AB9" t="n">
         <v>1.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45987.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,49 +1611,49 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5.1</v>
+        <v>1.32</v>
       </c>
       <c r="M10" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="N10" t="n">
-        <v>1.6</v>
+        <v>9</v>
       </c>
       <c r="O10" t="n">
-        <v>5.15</v>
+        <v>1.79</v>
       </c>
       <c r="P10" t="n">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.08</v>
+        <v>6.95</v>
       </c>
       <c r="R10" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>3.42</v>
+        <v>4</v>
       </c>
       <c r="T10" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="U10" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="V10" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="AA10" t="n">
         <v>1.58</v>
@@ -1662,22 +1662,22 @@
         <v>2.35</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.49</v>
+        <v>2.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.25</v>
+        <v>1.17</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.18</v>
+        <v>3.2</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45987.61458333334</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,49 +1730,49 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.32</v>
+        <v>5.1</v>
       </c>
       <c r="M11" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="N11" t="n">
-        <v>9</v>
+        <v>1.6</v>
       </c>
       <c r="O11" t="n">
-        <v>1.79</v>
+        <v>5.15</v>
       </c>
       <c r="P11" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.95</v>
+        <v>2.08</v>
       </c>
       <c r="R11" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>3.42</v>
       </c>
       <c r="T11" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="U11" t="n">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="V11" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="W11" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="AA11" t="n">
         <v>1.58</v>
@@ -1781,22 +1781,22 @@
         <v>2.35</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.1</v>
+        <v>2.49</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.17</v>
+        <v>2.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.2</v>
+        <v>1.18</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45987.61458333334</v>
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="M12" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="N12" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.9</v>
+        <v>2.33</v>
       </c>
       <c r="M13" t="n">
-        <v>3.45</v>
+        <v>3.22</v>
       </c>
       <c r="N13" t="n">
-        <v>4.2</v>
+        <v>3.05</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="M14" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N14" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="M15" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="N15" t="n">
-        <v>5.7</v>
+        <v>5.42</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="M16" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="N16" t="n">
-        <v>3.3</v>
+        <v>3.48</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.43</v>
+        <v>1.26</v>
       </c>
       <c r="M17" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="N17" t="n">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,16 +2489,16 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.3</v>
+        <v>1.76</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.07</v>
+        <v>1.43</v>
       </c>
       <c r="M19" t="n">
-        <v>3.56</v>
+        <v>4.6</v>
       </c>
       <c r="N19" t="n">
-        <v>3.27</v>
+        <v>6.6</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="AC19" t="n">
         <v>2.3</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.26</v>
+        <v>2.07</v>
       </c>
       <c r="M20" t="n">
-        <v>6</v>
+        <v>3.56</v>
       </c>
       <c r="N20" t="n">
-        <v>8.800000000000001</v>
+        <v>3.27</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,16 +2846,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.36</v>
+        <v>1.7</v>
       </c>
       <c r="AB20" t="n">
-        <v>3.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.76</v>
+        <v>2.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>6.9</v>
+        <v>1.71</v>
       </c>
       <c r="M21" t="n">
-        <v>5</v>
+        <v>3.92</v>
       </c>
       <c r="N21" t="n">
-        <v>1.38</v>
+        <v>4.33</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,16 +2965,16 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.71</v>
+        <v>6.9</v>
       </c>
       <c r="M23" t="n">
-        <v>3.92</v>
+        <v>5</v>
       </c>
       <c r="N23" t="n">
-        <v>4.33</v>
+        <v>1.38</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,16 +3203,16 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD23" t="n">
         <v>1.65</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="M24" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="N24" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3325,7 +3325,7 @@
         <v>2.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="M6" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="N6" t="n">
-        <v>3.91</v>
+        <v>4</v>
       </c>
       <c r="O6" t="n">
         <v>2.76</v>
@@ -1183,7 +1183,7 @@
         <v>2.25</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AC6" t="n">
         <v>4.4</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.33</v>
+        <v>1.6</v>
       </c>
       <c r="M13" t="n">
-        <v>3.22</v>
+        <v>3.7</v>
       </c>
       <c r="N13" t="n">
-        <v>3.05</v>
+        <v>5.42</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA13" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.85</v>
+        <v>2.06</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="N14" t="n">
-        <v>4.5</v>
+        <v>3.48</v>
       </c>
       <c r="O14" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.6</v>
+        <v>2.33</v>
       </c>
       <c r="M15" t="n">
-        <v>3.7</v>
+        <v>3.22</v>
       </c>
       <c r="N15" t="n">
-        <v>5.42</v>
+        <v>3.05</v>
       </c>
       <c r="O15" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
       <c r="M16" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="N16" t="n">
-        <v>3.48</v>
+        <v>4.5</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.26</v>
+        <v>2.07</v>
       </c>
       <c r="M17" t="n">
-        <v>6</v>
+        <v>3.56</v>
       </c>
       <c r="N17" t="n">
-        <v>8.800000000000001</v>
+        <v>3.27</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,16 +2489,16 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.36</v>
+        <v>1.7</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.76</v>
+        <v>2.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.63</v>
+        <v>1.26</v>
       </c>
       <c r="M18" t="n">
-        <v>3.51</v>
+        <v>6</v>
       </c>
       <c r="N18" t="n">
-        <v>2.47</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,16 +2608,16 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.63</v>
+        <v>1.36</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.43</v>
+        <v>2.63</v>
       </c>
       <c r="M19" t="n">
-        <v>4.6</v>
+        <v>3.51</v>
       </c>
       <c r="N19" t="n">
-        <v>6.6</v>
+        <v>2.47</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,16 +2727,16 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.07</v>
+        <v>1.71</v>
       </c>
       <c r="M20" t="n">
-        <v>3.56</v>
+        <v>3.92</v>
       </c>
       <c r="N20" t="n">
-        <v>3.27</v>
+        <v>4.33</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,16 +2846,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.71</v>
+        <v>2.29</v>
       </c>
       <c r="M21" t="n">
-        <v>3.92</v>
+        <v>3.39</v>
       </c>
       <c r="N21" t="n">
-        <v>4.33</v>
+        <v>2.95</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.29</v>
+        <v>6.9</v>
       </c>
       <c r="M22" t="n">
-        <v>3.39</v>
+        <v>5</v>
       </c>
       <c r="N22" t="n">
-        <v>2.95</v>
+        <v>1.38</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,16 +3084,16 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.79</v>
+        <v>1.63</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>6.9</v>
+        <v>1.43</v>
       </c>
       <c r="M23" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="N23" t="n">
-        <v>1.38</v>
+        <v>6.6</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,16 +3203,16 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,49 +1611,49 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.32</v>
+        <v>5.1</v>
       </c>
       <c r="M10" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="N10" t="n">
-        <v>9</v>
+        <v>1.6</v>
       </c>
       <c r="O10" t="n">
-        <v>1.79</v>
+        <v>5.15</v>
       </c>
       <c r="P10" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.95</v>
+        <v>2.08</v>
       </c>
       <c r="R10" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>3.42</v>
       </c>
       <c r="T10" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="U10" t="n">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="V10" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="W10" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="X10" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="AA10" t="n">
         <v>1.58</v>
@@ -1662,22 +1662,22 @@
         <v>2.35</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.1</v>
+        <v>2.49</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.17</v>
+        <v>2.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.2</v>
+        <v>1.18</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45987.61458333334</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,49 +1730,49 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>5.1</v>
+        <v>1.32</v>
       </c>
       <c r="M11" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="N11" t="n">
-        <v>1.6</v>
+        <v>9</v>
       </c>
       <c r="O11" t="n">
-        <v>5.15</v>
+        <v>1.79</v>
       </c>
       <c r="P11" t="n">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.08</v>
+        <v>6.95</v>
       </c>
       <c r="R11" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="S11" t="n">
-        <v>3.42</v>
+        <v>4</v>
       </c>
       <c r="T11" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="U11" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="V11" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="AA11" t="n">
         <v>1.58</v>
@@ -1781,22 +1781,22 @@
         <v>2.35</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.49</v>
+        <v>2.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.25</v>
+        <v>1.17</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.18</v>
+        <v>3.2</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45987.61458333334</v>
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="M12" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="N12" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.6</v>
+        <v>2.06</v>
       </c>
       <c r="M13" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="N13" t="n">
-        <v>5.42</v>
+        <v>3.48</v>
       </c>
       <c r="O13" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.06</v>
+        <v>2.33</v>
       </c>
       <c r="M14" t="n">
-        <v>3.55</v>
+        <v>3.22</v>
       </c>
       <c r="N14" t="n">
-        <v>3.48</v>
+        <v>3.05</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.33</v>
+        <v>1.85</v>
       </c>
       <c r="M15" t="n">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="N15" t="n">
-        <v>3.05</v>
+        <v>4.5</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,58 +2325,58 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="M16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N16" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>5</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC16" t="n">
         <v>3.4</v>
-      </c>
-      <c r="N16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O16" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V16" t="n">
-        <v>7</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.38</v>
       </c>
       <c r="AD16" t="n">
         <v>1.24</v>
@@ -2385,13 +2385,13 @@
         <v>1.85</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.91</v>
+        <v>2.16</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.07</v>
+        <v>1.26</v>
       </c>
       <c r="M17" t="n">
-        <v>3.56</v>
+        <v>6</v>
       </c>
       <c r="N17" t="n">
-        <v>3.27</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,16 +2489,16 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.05</v>
+        <v>3.1</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.3</v>
+        <v>1.76</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.26</v>
+        <v>1.43</v>
       </c>
       <c r="M18" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="N18" t="n">
-        <v>8.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,16 +2608,16 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.1</v>
+        <v>2.45</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.76</v>
+        <v>2.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.63</v>
+        <v>6.9</v>
       </c>
       <c r="M19" t="n">
-        <v>3.51</v>
+        <v>5</v>
       </c>
       <c r="N19" t="n">
-        <v>2.47</v>
+        <v>1.38</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2733,10 +2733,10 @@
         <v>2.25</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.71</v>
+        <v>2.63</v>
       </c>
       <c r="M20" t="n">
-        <v>3.92</v>
+        <v>3.51</v>
       </c>
       <c r="N20" t="n">
-        <v>4.33</v>
+        <v>2.47</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.29</v>
+        <v>1.71</v>
       </c>
       <c r="M21" t="n">
-        <v>3.39</v>
+        <v>3.92</v>
       </c>
       <c r="N21" t="n">
-        <v>2.95</v>
+        <v>4.33</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>6.9</v>
+        <v>2.29</v>
       </c>
       <c r="M22" t="n">
-        <v>5</v>
+        <v>3.39</v>
       </c>
       <c r="N22" t="n">
-        <v>1.38</v>
+        <v>2.95</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,16 +3084,16 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.63</v>
+        <v>1.79</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.43</v>
+        <v>2.57</v>
       </c>
       <c r="M23" t="n">
-        <v>4.6</v>
+        <v>3.04</v>
       </c>
       <c r="N23" t="n">
-        <v>6.6</v>
+        <v>2.8</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,16 +3203,16 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.53</v>
+        <v>2.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.45</v>
+        <v>1.61</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.57</v>
+        <v>2.07</v>
       </c>
       <c r="M24" t="n">
-        <v>3.04</v>
+        <v>3.56</v>
       </c>
       <c r="N24" t="n">
-        <v>2.8</v>
+        <v>3.27</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,16 +3322,16 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC24" t="n">
         <v>2.3</v>
       </c>
-      <c r="AB24" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>0</v>
-      </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1144,13 +1144,13 @@
         <v>4</v>
       </c>
       <c r="O6" t="n">
-        <v>2.76</v>
+        <v>2.5</v>
       </c>
       <c r="P6" t="n">
         <v>1.84</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.89</v>
+        <v>4.6</v>
       </c>
       <c r="R6" t="n">
         <v>1.52</v>
@@ -1177,7 +1177,7 @@
         <v>1.39</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="AA6" t="n">
         <v>2.25</v>
@@ -1195,13 +1195,13 @@
         <v>1.95</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45987.45833333334</v>
@@ -1376,46 +1376,46 @@
         <v>4</v>
       </c>
       <c r="M8" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="N8" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="O8" t="n">
-        <v>4.4</v>
+        <v>5.25</v>
       </c>
       <c r="P8" t="n">
         <v>1.95</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="R8" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="S8" t="n">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="T8" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="U8" t="n">
         <v>1.22</v>
       </c>
       <c r="V8" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="W8" t="n">
         <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AA8" t="n">
         <v>2.62</v>
@@ -1424,10 +1424,10 @@
         <v>1.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AE8" t="n">
         <v>2.25</v>
@@ -1436,10 +1436,10 @@
         <v>1.57</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45987.60416666666</v>
@@ -1507,25 +1507,25 @@
         <v>1.91</v>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="R9" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="S9" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="T9" t="n">
         <v>3.7</v>
       </c>
       <c r="U9" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="V9" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="W9" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
         <v>1.08</v>
@@ -1537,13 +1537,13 @@
         <v>2.2</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.38</v>
+        <v>2.95</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="AD9" t="n">
         <v>1.09</v>
@@ -1626,34 +1626,34 @@
         <v>2.38</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="R10" t="n">
         <v>1.31</v>
       </c>
       <c r="S10" t="n">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="T10" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="U10" t="n">
         <v>1.59</v>
       </c>
       <c r="V10" t="n">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="W10" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="AA10" t="n">
         <v>1.58</v>
@@ -1662,19 +1662,19 @@
         <v>2.35</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="AD10" t="n">
         <v>1.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.25</v>
+        <v>1.25</v>
       </c>
       <c r="AH10" t="n">
         <v>1.18</v>
@@ -1739,28 +1739,28 @@
         <v>9</v>
       </c>
       <c r="O11" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="P11" t="n">
         <v>2.63</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.95</v>
+        <v>7</v>
       </c>
       <c r="R11" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>3.58</v>
       </c>
       <c r="T11" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="U11" t="n">
         <v>1.66</v>
       </c>
       <c r="V11" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="W11" t="n">
         <v>1.16</v>
@@ -1772,7 +1772,7 @@
         <v>1.17</v>
       </c>
       <c r="Z11" t="n">
-        <v>5</v>
+        <v>4.65</v>
       </c>
       <c r="AA11" t="n">
         <v>1.58</v>
@@ -1793,7 +1793,7 @@
         <v>1.95</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AH11" t="n">
         <v>3.2</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.06</v>
+        <v>2.44</v>
       </c>
       <c r="M13" t="n">
-        <v>3.55</v>
+        <v>3.31</v>
       </c>
       <c r="N13" t="n">
-        <v>3.48</v>
+        <v>2.8</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.33</v>
+        <v>2.07</v>
       </c>
       <c r="M14" t="n">
-        <v>3.22</v>
+        <v>3.35</v>
       </c>
       <c r="N14" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AA14" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AB14" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE14" t="n">
         <v>1.8</v>
       </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0</v>
-      </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>3.63</v>
       </c>
       <c r="N15" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="O15" t="n">
-        <v>2.43</v>
+        <v>2.21</v>
       </c>
       <c r="P15" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="S15" t="n">
-        <v>2.85</v>
+        <v>2.69</v>
       </c>
       <c r="T15" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="U15" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="V15" t="n">
         <v>7</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.03</v>
+        <v>1.87</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="AD15" t="n">
         <v>1.24</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.91</v>
+        <v>2.17</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.6</v>
+        <v>1.81</v>
       </c>
       <c r="M16" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="N16" t="n">
-        <v>5.42</v>
+        <v>4.4</v>
       </c>
       <c r="O16" t="n">
-        <v>2.21</v>
+        <v>2.4</v>
       </c>
       <c r="P16" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q16" t="n">
-        <v>5</v>
+        <v>5.11</v>
       </c>
       <c r="R16" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S16" t="n">
-        <v>2.69</v>
+        <v>2.85</v>
       </c>
       <c r="T16" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="U16" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="V16" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="W16" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="AD16" t="n">
         <v>1.24</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.16</v>
+        <v>1.91</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.26</v>
+        <v>6.9</v>
       </c>
       <c r="M17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N17" t="n">
-        <v>8.800000000000001</v>
+        <v>1.38</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.76</v>
+        <v>2.15</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,55 +2563,55 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.43</v>
+        <v>2.07</v>
       </c>
       <c r="M18" t="n">
-        <v>4.6</v>
+        <v>3.56</v>
       </c>
       <c r="N18" t="n">
-        <v>6.6</v>
+        <v>3.27</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="AC18" t="n">
         <v>2.3</v>
@@ -2620,16 +2620,16 @@
         <v>1.6</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>6.9</v>
+        <v>1.26</v>
       </c>
       <c r="M19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N19" t="n">
-        <v>1.38</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>5.13</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.63</v>
+        <v>1.36</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.15</v>
+        <v>1.76</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P20" t="n">
         <v>2.63</v>
       </c>
-      <c r="M20" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="N20" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.71</v>
+        <v>2.63</v>
       </c>
       <c r="M21" t="n">
-        <v>3.92</v>
+        <v>3.51</v>
       </c>
       <c r="N21" t="n">
-        <v>4.33</v>
+        <v>2.47</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3048,40 +3048,40 @@
         <v>2.95</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA22" t="n">
         <v>1.79</v>
@@ -3090,22 +3090,22 @@
         <v>1.95</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.57</v>
+        <v>1.71</v>
       </c>
       <c r="M23" t="n">
-        <v>3.04</v>
+        <v>3.92</v>
       </c>
       <c r="N23" t="n">
-        <v>2.8</v>
+        <v>4.33</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA23" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC23" t="n">
         <v>2.3</v>
       </c>
-      <c r="AB23" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>0</v>
-      </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.07</v>
+        <v>2.52</v>
       </c>
       <c r="M24" t="n">
-        <v>3.56</v>
+        <v>3.13</v>
       </c>
       <c r="N24" t="n">
-        <v>3.27</v>
+        <v>2.83</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.7</v>
+        <v>2.28</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.05</v>
+        <v>1.55</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.6</v>
+        <v>1.17</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O8" t="n">
         <v>4</v>
       </c>
-      <c r="M8" t="n">
+      <c r="P8" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q8" t="n">
         <v>2.9</v>
       </c>
-      <c r="N8" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="O8" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.7</v>
-      </c>
       <c r="R8" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="S8" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="T8" t="n">
         <v>3.7</v>
       </c>
       <c r="U8" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="V8" t="n">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W8" t="n">
         <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.62</v>
+        <v>2.95</v>
       </c>
       <c r="AB8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG8" t="n">
         <v>1.4</v>
       </c>
-      <c r="AC8" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AH8" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45987.60416666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="M9" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="N9" t="n">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="O9" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="P9" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="R9" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="S9" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="T9" t="n">
         <v>3.7</v>
       </c>
       <c r="U9" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="V9" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="W9" t="n">
         <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.95</v>
+        <v>2.62</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45987.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,49 +1611,49 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5.1</v>
+        <v>1.32</v>
       </c>
       <c r="M10" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="N10" t="n">
-        <v>1.6</v>
+        <v>9</v>
       </c>
       <c r="O10" t="n">
-        <v>5.15</v>
+        <v>1.75</v>
       </c>
       <c r="P10" t="n">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.12</v>
+        <v>7</v>
       </c>
       <c r="R10" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="S10" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="T10" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="U10" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="V10" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="W10" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
         <v>1.17</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="AA10" t="n">
         <v>1.58</v>
@@ -1662,22 +1662,22 @@
         <v>2.35</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.18</v>
+        <v>3.2</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45987.61458333334</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,49 +1730,49 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.32</v>
+        <v>5.1</v>
       </c>
       <c r="M11" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="N11" t="n">
-        <v>9</v>
+        <v>1.6</v>
       </c>
       <c r="O11" t="n">
-        <v>1.75</v>
+        <v>5.15</v>
       </c>
       <c r="P11" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="Q11" t="n">
-        <v>7</v>
+        <v>2.12</v>
       </c>
       <c r="R11" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="S11" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="T11" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="U11" t="n">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="V11" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="W11" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
         <v>1.17</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.65</v>
+        <v>4.6</v>
       </c>
       <c r="AA11" t="n">
         <v>1.58</v>
@@ -1781,22 +1781,22 @@
         <v>2.35</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.2</v>
+        <v>1.18</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45987.61458333334</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.07</v>
+        <v>1.61</v>
       </c>
       <c r="M14" t="n">
-        <v>3.35</v>
+        <v>3.63</v>
       </c>
       <c r="N14" t="n">
-        <v>3.45</v>
+        <v>5.8</v>
       </c>
       <c r="O14" t="n">
-        <v>2.75</v>
+        <v>2.21</v>
       </c>
       <c r="P14" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="S14" t="n">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="T14" t="n">
-        <v>2.89</v>
+        <v>2.95</v>
       </c>
       <c r="U14" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V14" t="n">
         <v>7</v>
       </c>
       <c r="W14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X14" t="n">
         <v>1.05</v>
       </c>
-      <c r="X14" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.99</v>
+        <v>3.12</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.65</v>
+        <v>2.17</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,31 +2206,31 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.61</v>
+        <v>1.81</v>
       </c>
       <c r="M15" t="n">
-        <v>3.63</v>
+        <v>3.45</v>
       </c>
       <c r="N15" t="n">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="O15" t="n">
-        <v>2.21</v>
+        <v>2.4</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q15" t="n">
-        <v>5</v>
+        <v>5.11</v>
       </c>
       <c r="R15" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S15" t="n">
-        <v>2.69</v>
+        <v>2.85</v>
       </c>
       <c r="T15" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="U15" t="n">
         <v>1.35</v>
@@ -2239,40 +2239,40 @@
         <v>7</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X15" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="AD15" t="n">
         <v>1.24</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.17</v>
+        <v>1.91</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,34 +2325,34 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.81</v>
+        <v>2.07</v>
       </c>
       <c r="M16" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N16" t="n">
         <v>3.45</v>
       </c>
-      <c r="N16" t="n">
-        <v>4.4</v>
-      </c>
       <c r="O16" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="P16" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.11</v>
+        <v>3.75</v>
       </c>
       <c r="R16" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="S16" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="T16" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="U16" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V16" t="n">
         <v>7</v>
@@ -2361,13 +2361,13 @@
         <v>1.05</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
         <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="AA16" t="n">
         <v>1.98</v>
@@ -2376,22 +2376,22 @@
         <v>1.77</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>6.9</v>
+        <v>2.07</v>
       </c>
       <c r="M17" t="n">
-        <v>5</v>
+        <v>3.56</v>
       </c>
       <c r="N17" t="n">
-        <v>1.38</v>
+        <v>3.27</v>
       </c>
       <c r="O17" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V17" t="n">
         <v>5.75</v>
       </c>
-      <c r="P17" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="V17" t="n">
-        <v>4.8</v>
-      </c>
       <c r="W17" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="X17" t="n">
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="Z17" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.1</v>
+        <v>2.29</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.11</v>
+        <v>1.71</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.07</v>
+        <v>2.29</v>
       </c>
       <c r="M18" t="n">
-        <v>3.56</v>
+        <v>3.39</v>
       </c>
       <c r="N18" t="n">
-        <v>3.27</v>
+        <v>2.95</v>
       </c>
       <c r="O18" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="P18" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="R18" t="n">
         <v>1.35</v>
       </c>
       <c r="S18" t="n">
-        <v>3.18</v>
+        <v>2.98</v>
       </c>
       <c r="T18" t="n">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="U18" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="V18" t="n">
-        <v>5.75</v>
+        <v>6.3</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.3</v>
+        <v>2.93</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.6</v>
+        <v>1.34</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.29</v>
+        <v>2.14</v>
       </c>
       <c r="AG18" t="n">
         <v>1.3</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R19" t="n">
         <v>1.26</v>
       </c>
-      <c r="M19" t="n">
-        <v>6</v>
-      </c>
-      <c r="N19" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>5.13</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.18</v>
-      </c>
       <c r="S19" t="n">
-        <v>4.5</v>
+        <v>3.66</v>
       </c>
       <c r="T19" t="n">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="U19" t="n">
-        <v>1.89</v>
+        <v>1.67</v>
       </c>
       <c r="V19" t="n">
-        <v>3.84</v>
+        <v>4.8</v>
       </c>
       <c r="W19" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="Z19" t="n">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.1</v>
+        <v>2.45</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.76</v>
+        <v>2.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,43 +2801,43 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.43</v>
+        <v>1.71</v>
       </c>
       <c r="M20" t="n">
-        <v>4.6</v>
+        <v>3.92</v>
       </c>
       <c r="N20" t="n">
-        <v>6.6</v>
+        <v>4.33</v>
       </c>
       <c r="O20" t="n">
-        <v>1.83</v>
+        <v>2.21</v>
       </c>
       <c r="P20" t="n">
-        <v>2.63</v>
+        <v>2.39</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="R20" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="S20" t="n">
-        <v>3.66</v>
+        <v>3.7</v>
       </c>
       <c r="T20" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="U20" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="V20" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
         <v>1.15</v>
@@ -2846,28 +2846,28 @@
         <v>5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="AC20" t="n">
         <v>2.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.7</v>
+        <v>2.21</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.29</v>
+        <v>1.26</v>
       </c>
       <c r="M22" t="n">
-        <v>3.39</v>
+        <v>6</v>
       </c>
       <c r="N22" t="n">
-        <v>2.95</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>2.8</v>
+        <v>1.68</v>
       </c>
       <c r="P22" t="n">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.45</v>
+        <v>5.13</v>
       </c>
       <c r="R22" t="n">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="S22" t="n">
-        <v>2.98</v>
+        <v>4.5</v>
       </c>
       <c r="T22" t="n">
-        <v>2.7</v>
+        <v>1.94</v>
       </c>
       <c r="U22" t="n">
-        <v>1.47</v>
+        <v>1.89</v>
       </c>
       <c r="V22" t="n">
-        <v>6.3</v>
+        <v>3.84</v>
       </c>
       <c r="W22" t="n">
-        <v>1.09</v>
+        <v>1.24</v>
       </c>
       <c r="X22" t="n">
         <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.24</v>
+        <v>1.05</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.85</v>
+        <v>6.6</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.79</v>
+        <v>1.36</v>
       </c>
       <c r="AB22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AD22" t="n">
         <v>1.95</v>
       </c>
-      <c r="AC22" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AE22" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.64</v>
+        <v>3.4</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.71</v>
+        <v>6.9</v>
       </c>
       <c r="M23" t="n">
-        <v>3.92</v>
+        <v>5</v>
       </c>
       <c r="N23" t="n">
-        <v>4.33</v>
+        <v>1.38</v>
       </c>
       <c r="O23" t="n">
-        <v>2.21</v>
+        <v>5.75</v>
       </c>
       <c r="P23" t="n">
-        <v>2.39</v>
+        <v>2.63</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.5</v>
+        <v>1.82</v>
       </c>
       <c r="R23" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S23" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T23" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="U23" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="V23" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="W23" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X23" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Z23" t="n">
         <v>5</v>
       </c>
       <c r="AA23" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD23" t="n">
         <v>1.65</v>
       </c>
-      <c r="AB23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AE23" t="n">
-        <v>1.54</v>
+        <v>1.7</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.21</v>
+        <v>1.11</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3405,40 +3405,40 @@
         <v>3.31</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA25" t="n">
         <v>1.85</v>
@@ -3447,22 +3447,22 @@
         <v>1.85</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45987.79166666666</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.44</v>
+        <v>1.61</v>
       </c>
       <c r="M13" t="n">
-        <v>3.31</v>
+        <v>3.63</v>
       </c>
       <c r="N13" t="n">
-        <v>2.8</v>
+        <v>5.8</v>
       </c>
       <c r="O13" t="n">
-        <v>2.96</v>
+        <v>2.21</v>
       </c>
       <c r="P13" t="n">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.81</v>
+        <v>5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="S13" t="n">
-        <v>2.94</v>
+        <v>2.69</v>
       </c>
       <c r="T13" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="U13" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="V13" t="n">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AC13" t="n">
         <v>3.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.57</v>
+        <v>2.17</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.61</v>
+        <v>2.44</v>
       </c>
       <c r="M14" t="n">
-        <v>3.63</v>
+        <v>3.31</v>
       </c>
       <c r="N14" t="n">
-        <v>5.8</v>
+        <v>2.8</v>
       </c>
       <c r="O14" t="n">
-        <v>2.21</v>
+        <v>2.96</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="Q14" t="n">
-        <v>5</v>
+        <v>3.81</v>
       </c>
       <c r="R14" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="S14" t="n">
-        <v>2.69</v>
+        <v>2.94</v>
       </c>
       <c r="T14" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="U14" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="V14" t="n">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="W14" t="n">
         <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AC14" t="n">
         <v>3.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.17</v>
+        <v>1.57</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,34 +2206,34 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.81</v>
+        <v>2.07</v>
       </c>
       <c r="M15" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N15" t="n">
         <v>3.45</v>
       </c>
-      <c r="N15" t="n">
-        <v>4.4</v>
-      </c>
       <c r="O15" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="P15" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.11</v>
+        <v>3.75</v>
       </c>
       <c r="R15" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="S15" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="T15" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="U15" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V15" t="n">
         <v>7</v>
@@ -2242,13 +2242,13 @@
         <v>1.05</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
         <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="AA15" t="n">
         <v>1.98</v>
@@ -2257,22 +2257,22 @@
         <v>1.77</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,34 +2325,34 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.07</v>
+        <v>1.81</v>
       </c>
       <c r="M16" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="N16" t="n">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="O16" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="P16" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.75</v>
+        <v>5.11</v>
       </c>
       <c r="R16" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="S16" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="T16" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="U16" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V16" t="n">
         <v>7</v>
@@ -2361,13 +2361,13 @@
         <v>1.05</v>
       </c>
       <c r="X16" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
         <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="AA16" t="n">
         <v>1.98</v>
@@ -2376,22 +2376,22 @@
         <v>1.77</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,55 +2444,55 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.07</v>
+        <v>1.43</v>
       </c>
       <c r="M17" t="n">
-        <v>3.56</v>
+        <v>4.6</v>
       </c>
       <c r="N17" t="n">
-        <v>3.27</v>
+        <v>6.6</v>
       </c>
       <c r="O17" t="n">
-        <v>2.65</v>
+        <v>1.83</v>
       </c>
       <c r="P17" t="n">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="S17" t="n">
-        <v>3.18</v>
+        <v>3.66</v>
       </c>
       <c r="T17" t="n">
-        <v>2.54</v>
+        <v>2.2</v>
       </c>
       <c r="U17" t="n">
-        <v>1.51</v>
+        <v>1.67</v>
       </c>
       <c r="V17" t="n">
-        <v>5.75</v>
+        <v>4.8</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="AC17" t="n">
         <v>2.3</v>
@@ -2504,13 +2504,13 @@
         <v>1.62</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.71</v>
+        <v>2.7</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.29</v>
+        <v>2.52</v>
       </c>
       <c r="M18" t="n">
-        <v>3.39</v>
+        <v>3.13</v>
       </c>
       <c r="N18" t="n">
-        <v>2.95</v>
+        <v>2.83</v>
       </c>
       <c r="O18" t="n">
-        <v>2.8</v>
+        <v>3.26</v>
       </c>
       <c r="P18" t="n">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.45</v>
+        <v>3.51</v>
       </c>
       <c r="R18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V18" t="n">
+        <v>8</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG18" t="n">
         <v>1.35</v>
       </c>
-      <c r="S18" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U18" t="n">
+      <c r="AH18" t="n">
         <v>1.47</v>
-      </c>
-      <c r="V18" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.64</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,34 +2682,34 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.43</v>
+        <v>6.9</v>
       </c>
       <c r="M19" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="N19" t="n">
-        <v>6.6</v>
+        <v>1.38</v>
       </c>
       <c r="O19" t="n">
-        <v>1.83</v>
+        <v>5.75</v>
       </c>
       <c r="P19" t="n">
         <v>2.63</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.5</v>
+        <v>1.82</v>
       </c>
       <c r="R19" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S19" t="n">
-        <v>3.66</v>
+        <v>3.75</v>
       </c>
       <c r="T19" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="U19" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="V19" t="n">
         <v>4.8</v>
@@ -2718,37 +2718,37 @@
         <v>1.16</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Z19" t="n">
         <v>5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.7</v>
+        <v>1.11</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.71</v>
+        <v>2.63</v>
       </c>
       <c r="M20" t="n">
-        <v>3.92</v>
+        <v>3.51</v>
       </c>
       <c r="N20" t="n">
-        <v>4.33</v>
+        <v>2.47</v>
       </c>
       <c r="O20" t="n">
-        <v>2.21</v>
+        <v>3.2</v>
       </c>
       <c r="P20" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="R20" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="S20" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="T20" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="U20" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="V20" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X20" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z20" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.21</v>
+        <v>1.51</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.63</v>
+        <v>1.26</v>
       </c>
       <c r="M21" t="n">
-        <v>3.51</v>
+        <v>6</v>
       </c>
       <c r="N21" t="n">
-        <v>2.47</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>3.2</v>
+        <v>1.68</v>
       </c>
       <c r="P21" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.8</v>
+        <v>5.13</v>
       </c>
       <c r="R21" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="S21" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="T21" t="n">
-        <v>2.4</v>
+        <v>1.94</v>
       </c>
       <c r="U21" t="n">
-        <v>1.53</v>
+        <v>1.89</v>
       </c>
       <c r="V21" t="n">
-        <v>5.5</v>
+        <v>3.84</v>
       </c>
       <c r="W21" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.19</v>
+        <v>1.05</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.63</v>
+        <v>1.36</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.7</v>
+        <v>1.76</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.5</v>
+        <v>1.95</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.51</v>
+        <v>3.4</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.26</v>
+        <v>2.29</v>
       </c>
       <c r="M22" t="n">
-        <v>6</v>
+        <v>3.39</v>
       </c>
       <c r="N22" t="n">
-        <v>8.800000000000001</v>
+        <v>2.95</v>
       </c>
       <c r="O22" t="n">
-        <v>1.68</v>
+        <v>2.8</v>
       </c>
       <c r="P22" t="n">
-        <v>2.88</v>
+        <v>2.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.13</v>
+        <v>3.45</v>
       </c>
       <c r="R22" t="n">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="S22" t="n">
-        <v>4.5</v>
+        <v>2.98</v>
       </c>
       <c r="T22" t="n">
-        <v>1.94</v>
+        <v>2.7</v>
       </c>
       <c r="U22" t="n">
-        <v>1.89</v>
+        <v>1.47</v>
       </c>
       <c r="V22" t="n">
-        <v>3.84</v>
+        <v>6.3</v>
       </c>
       <c r="W22" t="n">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
       <c r="X22" t="n">
         <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.05</v>
+        <v>1.24</v>
       </c>
       <c r="Z22" t="n">
-        <v>6.6</v>
+        <v>3.85</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.36</v>
+        <v>1.79</v>
       </c>
       <c r="AB22" t="n">
-        <v>3.1</v>
+        <v>1.95</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.76</v>
+        <v>2.93</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.95</v>
+        <v>1.34</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>3.4</v>
+        <v>1.64</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>6.9</v>
+        <v>1.71</v>
       </c>
       <c r="M23" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="N23" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V23" t="n">
         <v>5</v>
       </c>
-      <c r="N23" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="O23" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="V23" t="n">
-        <v>4.8</v>
-      </c>
       <c r="W23" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Z23" t="n">
         <v>5</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.7</v>
+        <v>1.54</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.11</v>
+        <v>2.21</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.52</v>
+        <v>2.07</v>
       </c>
       <c r="M24" t="n">
-        <v>3.13</v>
+        <v>3.56</v>
       </c>
       <c r="N24" t="n">
-        <v>2.83</v>
+        <v>3.27</v>
       </c>
       <c r="O24" t="n">
-        <v>3.26</v>
+        <v>2.65</v>
       </c>
       <c r="P24" t="n">
-        <v>1.92</v>
+        <v>2.38</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.51</v>
+        <v>3.7</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="S24" t="n">
-        <v>2.42</v>
+        <v>3.18</v>
       </c>
       <c r="T24" t="n">
-        <v>3.28</v>
+        <v>2.54</v>
       </c>
       <c r="U24" t="n">
-        <v>1.29</v>
+        <v>1.51</v>
       </c>
       <c r="V24" t="n">
-        <v>8</v>
+        <v>5.75</v>
       </c>
       <c r="W24" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="X24" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.75</v>
+        <v>3.9</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.28</v>
+        <v>1.7</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.55</v>
+        <v>2.05</v>
       </c>
       <c r="AC24" t="n">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.17</v>
+        <v>1.6</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.78</v>
+        <v>2.29</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.47</v>
+        <v>1.71</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45987.70833333334</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1144,7 +1144,7 @@
         <v>4</v>
       </c>
       <c r="O6" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="P6" t="n">
         <v>1.84</v>
@@ -1186,7 +1186,7 @@
         <v>1.57</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.4</v>
+        <v>3.96</v>
       </c>
       <c r="AD6" t="n">
         <v>1.18</v>
@@ -1198,10 +1198,10 @@
         <v>1.75</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45987.45833333334</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="M8" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="N8" t="n">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="O8" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="P8" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="R8" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="S8" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="T8" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="U8" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="V8" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="W8" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X8" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.95</v>
+        <v>2.62</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG8" t="n">
         <v>1.4</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45987.60416666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O9" t="n">
         <v>4</v>
       </c>
-      <c r="M9" t="n">
+      <c r="P9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q9" t="n">
         <v>2.9</v>
       </c>
-      <c r="N9" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="O9" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.7</v>
-      </c>
       <c r="R9" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="S9" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="T9" t="n">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="U9" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="V9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W9" t="n">
         <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AB9" t="n">
         <v>1.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45987.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,49 +1611,49 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.32</v>
+        <v>5.1</v>
       </c>
       <c r="M10" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="N10" t="n">
-        <v>9</v>
+        <v>1.6</v>
       </c>
       <c r="O10" t="n">
-        <v>1.75</v>
+        <v>5.15</v>
       </c>
       <c r="P10" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="Q10" t="n">
-        <v>7</v>
+        <v>2.12</v>
       </c>
       <c r="R10" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="S10" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="T10" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="U10" t="n">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="V10" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="W10" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X10" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
         <v>1.17</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.65</v>
+        <v>4.6</v>
       </c>
       <c r="AA10" t="n">
         <v>1.58</v>
@@ -1662,22 +1662,22 @@
         <v>2.35</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.2</v>
+        <v>1.18</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45987.61458333334</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,49 +1730,49 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>5.1</v>
+        <v>1.32</v>
       </c>
       <c r="M11" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="N11" t="n">
-        <v>1.6</v>
+        <v>9</v>
       </c>
       <c r="O11" t="n">
-        <v>5.15</v>
+        <v>1.75</v>
       </c>
       <c r="P11" t="n">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.12</v>
+        <v>7</v>
       </c>
       <c r="R11" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="S11" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="T11" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="U11" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="V11" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="W11" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
         <v>1.17</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="AA11" t="n">
         <v>1.58</v>
@@ -1781,22 +1781,22 @@
         <v>2.35</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.18</v>
+        <v>3.2</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45987.61458333334</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.61</v>
+        <v>2.18</v>
       </c>
       <c r="M13" t="n">
-        <v>3.63</v>
+        <v>3.5</v>
       </c>
       <c r="N13" t="n">
-        <v>5.8</v>
+        <v>3.5</v>
       </c>
       <c r="O13" t="n">
-        <v>2.21</v>
+        <v>2.75</v>
       </c>
       <c r="P13" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q13" t="n">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="R13" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S13" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="T13" t="n">
-        <v>2.95</v>
+        <v>2.89</v>
       </c>
       <c r="U13" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V13" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.87</v>
+        <v>2.03</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AD13" t="n">
         <v>1.24</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.17</v>
+        <v>1.65</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.44</v>
+        <v>1.63</v>
       </c>
       <c r="M14" t="n">
-        <v>3.31</v>
+        <v>3.68</v>
       </c>
       <c r="N14" t="n">
-        <v>2.8</v>
+        <v>5.51</v>
       </c>
       <c r="O14" t="n">
-        <v>2.96</v>
+        <v>2.2</v>
       </c>
       <c r="P14" t="n">
-        <v>2.01</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.81</v>
+        <v>5</v>
       </c>
       <c r="R14" t="n">
         <v>1.37</v>
       </c>
       <c r="S14" t="n">
-        <v>2.94</v>
+        <v>2.65</v>
       </c>
       <c r="T14" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="U14" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="W14" t="n">
         <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
         <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="AC14" t="n">
         <v>3.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,34 +2206,34 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.07</v>
+        <v>1.8</v>
       </c>
       <c r="M15" t="n">
-        <v>3.35</v>
+        <v>3.42</v>
       </c>
       <c r="N15" t="n">
-        <v>3.45</v>
+        <v>4.25</v>
       </c>
       <c r="O15" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="P15" t="n">
         <v>2.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="R15" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S15" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="T15" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="U15" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V15" t="n">
         <v>7</v>
@@ -2245,34 +2245,34 @@
         <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AD15" t="n">
         <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AG15" t="n">
         <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.81</v>
+        <v>2.35</v>
       </c>
       <c r="M16" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N16" t="n">
-        <v>4.4</v>
+        <v>2.95</v>
       </c>
       <c r="O16" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="P16" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.11</v>
+        <v>3.85</v>
       </c>
       <c r="R16" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S16" t="n">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="T16" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="U16" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V16" t="n">
         <v>7</v>
       </c>
       <c r="W16" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.43</v>
+        <v>2.29</v>
       </c>
       <c r="M17" t="n">
-        <v>4.6</v>
+        <v>3.39</v>
       </c>
       <c r="N17" t="n">
-        <v>6.6</v>
+        <v>2.95</v>
       </c>
       <c r="O17" t="n">
-        <v>1.83</v>
+        <v>2.8</v>
       </c>
       <c r="P17" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.5</v>
+        <v>3.45</v>
       </c>
       <c r="R17" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="S17" t="n">
-        <v>3.66</v>
+        <v>2.98</v>
       </c>
       <c r="T17" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="U17" t="n">
-        <v>1.67</v>
+        <v>1.47</v>
       </c>
       <c r="V17" t="n">
-        <v>4.8</v>
+        <v>6.3</v>
       </c>
       <c r="W17" t="n">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="Z17" t="n">
-        <v>5</v>
+        <v>3.85</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.53</v>
+        <v>1.79</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.3</v>
+        <v>2.93</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.6</v>
+        <v>1.34</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.7</v>
+        <v>1.64</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.52</v>
+        <v>1.26</v>
       </c>
       <c r="M18" t="n">
-        <v>3.13</v>
+        <v>6</v>
       </c>
       <c r="N18" t="n">
-        <v>2.83</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>3.26</v>
+        <v>1.68</v>
       </c>
       <c r="P18" t="n">
-        <v>1.92</v>
+        <v>2.88</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.51</v>
+        <v>5.13</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="S18" t="n">
-        <v>2.42</v>
+        <v>4.5</v>
       </c>
       <c r="T18" t="n">
-        <v>3.28</v>
+        <v>1.94</v>
       </c>
       <c r="U18" t="n">
-        <v>1.29</v>
+        <v>1.89</v>
       </c>
       <c r="V18" t="n">
-        <v>8</v>
+        <v>3.84</v>
       </c>
       <c r="W18" t="n">
-        <v>1.02</v>
+        <v>1.24</v>
       </c>
       <c r="X18" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.4</v>
+        <v>1.05</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.75</v>
+        <v>6.6</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.28</v>
+        <v>1.36</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.55</v>
+        <v>3.1</v>
       </c>
       <c r="AC18" t="n">
-        <v>4</v>
+        <v>1.76</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.17</v>
+        <v>1.95</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.78</v>
+        <v>2.4</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.35</v>
+        <v>1.14</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.47</v>
+        <v>3.4</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>6.9</v>
+        <v>2.6</v>
       </c>
       <c r="M19" t="n">
-        <v>5</v>
+        <v>3.04</v>
       </c>
       <c r="N19" t="n">
-        <v>1.38</v>
+        <v>2.8</v>
       </c>
       <c r="O19" t="n">
-        <v>5.75</v>
+        <v>3.1</v>
       </c>
       <c r="P19" t="n">
-        <v>2.63</v>
+        <v>1.92</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.82</v>
+        <v>3.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="S19" t="n">
-        <v>3.75</v>
+        <v>2.6</v>
       </c>
       <c r="T19" t="n">
-        <v>2.12</v>
+        <v>3.15</v>
       </c>
       <c r="U19" t="n">
-        <v>1.69</v>
+        <v>1.3</v>
       </c>
       <c r="V19" t="n">
-        <v>4.8</v>
+        <v>8</v>
       </c>
       <c r="W19" t="n">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="Z19" t="n">
-        <v>5</v>
+        <v>2.64</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.63</v>
+        <v>2.28</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.25</v>
+        <v>1.61</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.15</v>
+        <v>4.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.65</v>
+        <v>1.2</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.1</v>
+        <v>1.81</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.11</v>
+        <v>1.44</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.63</v>
+        <v>2.07</v>
       </c>
       <c r="M20" t="n">
-        <v>3.51</v>
+        <v>3.56</v>
       </c>
       <c r="N20" t="n">
-        <v>2.47</v>
+        <v>3.27</v>
       </c>
       <c r="O20" t="n">
-        <v>3.2</v>
+        <v>2.65</v>
       </c>
       <c r="P20" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="R20" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S20" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="T20" t="n">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="U20" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="V20" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="W20" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X20" t="n">
         <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.6</v>
+        <v>2.29</v>
       </c>
       <c r="AG20" t="n">
         <v>1.3</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.51</v>
+        <v>1.71</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N21" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R21" t="n">
         <v>1.26</v>
       </c>
-      <c r="M21" t="n">
-        <v>6</v>
-      </c>
-      <c r="N21" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>5.13</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.18</v>
-      </c>
       <c r="S21" t="n">
-        <v>4.5</v>
+        <v>3.66</v>
       </c>
       <c r="T21" t="n">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="U21" t="n">
-        <v>1.89</v>
+        <v>1.67</v>
       </c>
       <c r="V21" t="n">
-        <v>3.84</v>
+        <v>4.8</v>
       </c>
       <c r="W21" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="Z21" t="n">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AB21" t="n">
-        <v>3.1</v>
+        <v>2.45</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.76</v>
+        <v>2.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AH21" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.29</v>
+        <v>1.71</v>
       </c>
       <c r="M22" t="n">
-        <v>3.39</v>
+        <v>3.92</v>
       </c>
       <c r="N22" t="n">
-        <v>2.95</v>
+        <v>4.33</v>
       </c>
       <c r="O22" t="n">
-        <v>2.8</v>
+        <v>2.21</v>
       </c>
       <c r="P22" t="n">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="S22" t="n">
-        <v>2.98</v>
+        <v>3.7</v>
       </c>
       <c r="T22" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="U22" t="n">
-        <v>1.47</v>
+        <v>1.64</v>
       </c>
       <c r="V22" t="n">
-        <v>6.3</v>
+        <v>5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.85</v>
+        <v>5</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.93</v>
+        <v>2.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.34</v>
+        <v>1.53</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.64</v>
+        <v>2.21</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.71</v>
+        <v>2.63</v>
       </c>
       <c r="M23" t="n">
-        <v>3.92</v>
+        <v>3.51</v>
       </c>
       <c r="N23" t="n">
-        <v>4.33</v>
+        <v>2.47</v>
       </c>
       <c r="O23" t="n">
-        <v>2.21</v>
+        <v>3.2</v>
       </c>
       <c r="P23" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="R23" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="S23" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="T23" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="U23" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="V23" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X23" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z23" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.21</v>
+        <v>1.51</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.07</v>
+        <v>6.9</v>
       </c>
       <c r="M24" t="n">
-        <v>3.56</v>
+        <v>5</v>
       </c>
       <c r="N24" t="n">
-        <v>3.27</v>
+        <v>1.38</v>
       </c>
       <c r="O24" t="n">
-        <v>2.65</v>
+        <v>5.75</v>
       </c>
       <c r="P24" t="n">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.7</v>
+        <v>1.82</v>
       </c>
       <c r="R24" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="S24" t="n">
-        <v>3.18</v>
+        <v>3.75</v>
       </c>
       <c r="T24" t="n">
-        <v>2.54</v>
+        <v>2.12</v>
       </c>
       <c r="U24" t="n">
-        <v>1.51</v>
+        <v>1.69</v>
       </c>
       <c r="V24" t="n">
-        <v>5.75</v>
+        <v>4.8</v>
       </c>
       <c r="W24" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="X24" t="n">
         <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="AA24" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE24" t="n">
         <v>1.7</v>
       </c>
-      <c r="AB24" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AF24" t="n">
-        <v>2.29</v>
+        <v>2.1</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.71</v>
+        <v>1.11</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45987.70833333334</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="M6" t="n">
         <v>2.9</v>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="O6" t="n">
         <v>2.75</v>
@@ -1168,10 +1168,10 @@
         <v>9.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y6" t="n">
         <v>1.39</v>
@@ -1183,7 +1183,7 @@
         <v>2.25</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AC6" t="n">
         <v>3.96</v>
@@ -1198,10 +1198,10 @@
         <v>1.75</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45987.45833333334</v>
@@ -1376,31 +1376,31 @@
         <v>4</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="N8" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="O8" t="n">
-        <v>5.25</v>
+        <v>4.4</v>
       </c>
       <c r="P8" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="Q8" t="n">
         <v>2.7</v>
       </c>
       <c r="R8" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="S8" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="T8" t="n">
-        <v>3.45</v>
+        <v>3.72</v>
       </c>
       <c r="U8" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="V8" t="n">
         <v>11</v>
@@ -1409,25 +1409,25 @@
         <v>1.04</v>
       </c>
       <c r="X8" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.1</v>
+        <v>2.29</v>
       </c>
       <c r="AA8" t="n">
         <v>2.62</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AE8" t="n">
         <v>2.25</v>
@@ -1436,10 +1436,10 @@
         <v>1.57</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45987.60416666666</v>
@@ -1492,16 +1492,16 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="M9" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="N9" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="O9" t="n">
-        <v>4</v>
+        <v>4.66</v>
       </c>
       <c r="P9" t="n">
         <v>1.91</v>
@@ -1516,7 +1516,7 @@
         <v>2.2</v>
       </c>
       <c r="T9" t="n">
-        <v>3.68</v>
+        <v>3.75</v>
       </c>
       <c r="U9" t="n">
         <v>1.2</v>
@@ -1525,16 +1525,16 @@
         <v>12</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AA9" t="n">
         <v>2.7</v>
@@ -1546,7 +1546,7 @@
         <v>5.75</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AE9" t="n">
         <v>2.2</v>
@@ -1555,10 +1555,10 @@
         <v>1.62</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45987.60416666666</v>
@@ -1632,28 +1632,28 @@
         <v>1.31</v>
       </c>
       <c r="S10" t="n">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
       <c r="T10" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="U10" t="n">
         <v>1.59</v>
       </c>
       <c r="V10" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="W10" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AA10" t="n">
         <v>1.58</v>
@@ -1665,7 +1665,7 @@
         <v>2.45</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AE10" t="n">
         <v>1.62</v>
@@ -1748,19 +1748,19 @@
         <v>7</v>
       </c>
       <c r="R11" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S11" t="n">
         <v>3.58</v>
       </c>
       <c r="T11" t="n">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="U11" t="n">
         <v>1.66</v>
       </c>
       <c r="V11" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="W11" t="n">
         <v>1.16</v>
@@ -1793,10 +1793,10 @@
         <v>1.95</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.2</v>
+        <v>3.01</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45987.61458333334</v>
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="M12" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="N12" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.18</v>
+        <v>1.63</v>
       </c>
       <c r="M13" t="n">
-        <v>3.5</v>
+        <v>3.68</v>
       </c>
       <c r="N13" t="n">
-        <v>3.5</v>
+        <v>5.51</v>
       </c>
       <c r="O13" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="P13" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="S13" t="n">
         <v>2.65</v>
       </c>
       <c r="T13" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="U13" t="n">
         <v>1.36</v>
       </c>
       <c r="V13" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
         <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF13" t="n">
         <v>1.8</v>
       </c>
-      <c r="AF13" t="n">
-        <v>1.93</v>
-      </c>
       <c r="AG13" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.65</v>
+        <v>2.2</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,31 +2087,31 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.63</v>
+        <v>2.35</v>
       </c>
       <c r="M14" t="n">
-        <v>3.68</v>
+        <v>3.35</v>
       </c>
       <c r="N14" t="n">
-        <v>5.51</v>
+        <v>2.95</v>
       </c>
       <c r="O14" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="Q14" t="n">
-        <v>5</v>
+        <v>3.85</v>
       </c>
       <c r="R14" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="S14" t="n">
         <v>2.65</v>
       </c>
       <c r="T14" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U14" t="n">
         <v>1.36</v>
@@ -2123,37 +2123,37 @@
         <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AC14" t="n">
         <v>3.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.8</v>
+        <v>2.18</v>
       </c>
       <c r="M15" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="N15" t="n">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="O15" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="P15" t="n">
         <v>2.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="R15" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="T15" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="U15" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V15" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="W15" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AA15" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AB15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE15" t="n">
         <v>1.8</v>
       </c>
-      <c r="AC15" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AF15" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AG15" t="n">
         <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.35</v>
+        <v>1.8</v>
       </c>
       <c r="M16" t="n">
-        <v>3.35</v>
+        <v>3.42</v>
       </c>
       <c r="N16" t="n">
-        <v>2.95</v>
+        <v>4.25</v>
       </c>
       <c r="O16" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="P16" t="n">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="R16" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="S16" t="n">
-        <v>2.65</v>
+        <v>2.85</v>
       </c>
       <c r="T16" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="U16" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V16" t="n">
         <v>7</v>
       </c>
       <c r="W16" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X16" t="n">
         <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB16" t="n">
         <v>1.8</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AF16" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG16" t="n">
         <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.29</v>
+        <v>1.26</v>
       </c>
       <c r="M17" t="n">
-        <v>3.39</v>
+        <v>6</v>
       </c>
       <c r="N17" t="n">
-        <v>2.95</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>2.8</v>
+        <v>1.68</v>
       </c>
       <c r="P17" t="n">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.45</v>
+        <v>5.13</v>
       </c>
       <c r="R17" t="n">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="S17" t="n">
-        <v>2.98</v>
+        <v>4.5</v>
       </c>
       <c r="T17" t="n">
-        <v>2.7</v>
+        <v>1.94</v>
       </c>
       <c r="U17" t="n">
-        <v>1.47</v>
+        <v>1.89</v>
       </c>
       <c r="V17" t="n">
-        <v>6.3</v>
+        <v>3.84</v>
       </c>
       <c r="W17" t="n">
-        <v>1.09</v>
+        <v>1.24</v>
       </c>
       <c r="X17" t="n">
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.24</v>
+        <v>1.05</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.85</v>
+        <v>7.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.79</v>
+        <v>1.36</v>
       </c>
       <c r="AB17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AD17" t="n">
         <v>1.95</v>
       </c>
-      <c r="AC17" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AE17" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.64</v>
+        <v>3.4</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.26</v>
+        <v>2.07</v>
       </c>
       <c r="M18" t="n">
-        <v>6</v>
+        <v>3.56</v>
       </c>
       <c r="N18" t="n">
-        <v>8.800000000000001</v>
+        <v>3.27</v>
       </c>
       <c r="O18" t="n">
-        <v>1.68</v>
+        <v>2.8</v>
       </c>
       <c r="P18" t="n">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.13</v>
+        <v>3.7</v>
       </c>
       <c r="R18" t="n">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="S18" t="n">
-        <v>4.5</v>
+        <v>3.18</v>
       </c>
       <c r="T18" t="n">
-        <v>1.94</v>
+        <v>2.56</v>
       </c>
       <c r="U18" t="n">
-        <v>1.89</v>
+        <v>1.48</v>
       </c>
       <c r="V18" t="n">
-        <v>3.84</v>
+        <v>5.75</v>
       </c>
       <c r="W18" t="n">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="Z18" t="n">
-        <v>6.6</v>
+        <v>3.9</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.36</v>
+        <v>1.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.76</v>
+        <v>2.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.4</v>
+        <v>1.65</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.6</v>
+        <v>1.71</v>
       </c>
       <c r="M19" t="n">
-        <v>3.04</v>
+        <v>3.92</v>
       </c>
       <c r="N19" t="n">
-        <v>2.8</v>
+        <v>4.33</v>
       </c>
       <c r="O19" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="P19" t="n">
-        <v>1.92</v>
+        <v>2.39</v>
       </c>
       <c r="Q19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S19" t="n">
         <v>3.5</v>
       </c>
-      <c r="R19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.6</v>
-      </c>
       <c r="T19" t="n">
-        <v>3.15</v>
+        <v>2.3</v>
       </c>
       <c r="U19" t="n">
-        <v>1.3</v>
+        <v>1.59</v>
       </c>
       <c r="V19" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="X19" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.64</v>
+        <v>5.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.28</v>
+        <v>1.65</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.61</v>
+        <v>2.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.2</v>
+        <v>1.53</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.89</v>
+        <v>1.54</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.81</v>
+        <v>2.3</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.07</v>
+        <v>2.6</v>
       </c>
       <c r="M20" t="n">
-        <v>3.56</v>
+        <v>3.04</v>
       </c>
       <c r="N20" t="n">
-        <v>3.27</v>
+        <v>2.8</v>
       </c>
       <c r="O20" t="n">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="P20" t="n">
-        <v>2.38</v>
+        <v>1.92</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="R20" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="S20" t="n">
-        <v>3.18</v>
+        <v>2.6</v>
       </c>
       <c r="T20" t="n">
-        <v>2.54</v>
+        <v>3.15</v>
       </c>
       <c r="U20" t="n">
-        <v>1.51</v>
+        <v>1.3</v>
       </c>
       <c r="V20" t="n">
-        <v>5.75</v>
+        <v>8</v>
       </c>
       <c r="W20" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.9</v>
+        <v>2.64</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.7</v>
+        <v>2.28</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.05</v>
+        <v>1.61</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.62</v>
+        <v>1.89</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.29</v>
+        <v>1.81</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.71</v>
+        <v>1.44</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.43</v>
+        <v>2.63</v>
       </c>
       <c r="M21" t="n">
-        <v>4.6</v>
+        <v>3.51</v>
       </c>
       <c r="N21" t="n">
-        <v>6.6</v>
+        <v>2.47</v>
       </c>
       <c r="O21" t="n">
-        <v>1.83</v>
+        <v>3.2</v>
       </c>
       <c r="P21" t="n">
-        <v>2.63</v>
+        <v>2.23</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.5</v>
+        <v>2.8</v>
       </c>
       <c r="R21" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="S21" t="n">
-        <v>3.66</v>
+        <v>3.3</v>
       </c>
       <c r="T21" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="U21" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="V21" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="W21" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y21" t="n">
         <v>1.16</v>
       </c>
-      <c r="X21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.15</v>
-      </c>
       <c r="Z21" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.2</v>
+        <v>2.49</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.7</v>
+        <v>1.44</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.71</v>
+        <v>2.29</v>
       </c>
       <c r="M22" t="n">
-        <v>3.92</v>
+        <v>3.39</v>
       </c>
       <c r="N22" t="n">
-        <v>4.33</v>
+        <v>2.95</v>
       </c>
       <c r="O22" t="n">
-        <v>2.21</v>
+        <v>2.8</v>
       </c>
       <c r="P22" t="n">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.5</v>
+        <v>3.45</v>
       </c>
       <c r="R22" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V22" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y22" t="n">
         <v>1.24</v>
       </c>
-      <c r="S22" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="V22" t="n">
-        <v>5</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.15</v>
-      </c>
       <c r="Z22" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="AA22" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AE22" t="n">
         <v>1.65</v>
       </c>
-      <c r="AB22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.54</v>
-      </c>
       <c r="AF22" t="n">
-        <v>2.38</v>
+        <v>2.14</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.21</v>
+        <v>1.62</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.63</v>
+        <v>1.43</v>
       </c>
       <c r="M23" t="n">
-        <v>3.51</v>
+        <v>4.6</v>
       </c>
       <c r="N23" t="n">
-        <v>2.47</v>
+        <v>6.6</v>
       </c>
       <c r="O23" t="n">
-        <v>3.2</v>
+        <v>1.83</v>
       </c>
       <c r="P23" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="Q23" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V23" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH23" t="n">
         <v>2.8</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V23" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.51</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3286,13 +3286,13 @@
         <v>1.38</v>
       </c>
       <c r="O24" t="n">
-        <v>5.75</v>
+        <v>5.32</v>
       </c>
       <c r="P24" t="n">
-        <v>2.63</v>
+        <v>2.52</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="R24" t="n">
         <v>1.25</v>
@@ -3301,7 +3301,7 @@
         <v>3.75</v>
       </c>
       <c r="T24" t="n">
-        <v>2.12</v>
+        <v>2.21</v>
       </c>
       <c r="U24" t="n">
         <v>1.69</v>
@@ -3319,7 +3319,7 @@
         <v>1.1</v>
       </c>
       <c r="Z24" t="n">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="AA24" t="n">
         <v>1.63</v>
@@ -3337,7 +3337,7 @@
         <v>1.7</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG24" t="n">
         <v>1.18</v>
@@ -3405,19 +3405,19 @@
         <v>3.31</v>
       </c>
       <c r="O25" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="P25" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.8</v>
+        <v>4.05</v>
       </c>
       <c r="R25" t="n">
         <v>1.38</v>
       </c>
       <c r="S25" t="n">
-        <v>2.81</v>
+        <v>3.08</v>
       </c>
       <c r="T25" t="n">
         <v>2.69</v>
@@ -3432,7 +3432,7 @@
         <v>1.06</v>
       </c>
       <c r="X25" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
         <v>1.29</v>
@@ -3447,7 +3447,7 @@
         <v>1.85</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AD25" t="n">
         <v>1.3</v>
@@ -3459,7 +3459,7 @@
         <v>2.05</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AH25" t="n">
         <v>1.73</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5.1</v>
+        <v>1.34</v>
       </c>
       <c r="M10" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="N10" t="n">
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="O10" t="n">
-        <v>5.15</v>
+        <v>1.83</v>
       </c>
       <c r="P10" t="n">
-        <v>2.38</v>
+        <v>2.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.12</v>
+        <v>6.4</v>
       </c>
       <c r="R10" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="S10" t="n">
-        <v>3.42</v>
+        <v>3.75</v>
       </c>
       <c r="T10" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="U10" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="V10" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="W10" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.62</v>
+        <v>1.81</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.18</v>
+        <v>3.2</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45987.61458333334</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.32</v>
+        <v>5.3</v>
       </c>
       <c r="M11" t="n">
-        <v>5</v>
+        <v>4.22</v>
       </c>
       <c r="N11" t="n">
-        <v>9</v>
+        <v>1.61</v>
       </c>
       <c r="O11" t="n">
-        <v>1.75</v>
+        <v>5.15</v>
       </c>
       <c r="P11" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="Q11" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="S11" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="T11" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="U11" t="n">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="V11" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="W11" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.65</v>
+        <v>4.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.01</v>
+        <v>1.18</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45987.61458333334</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.63</v>
+        <v>2.17</v>
       </c>
       <c r="M13" t="n">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="N13" t="n">
-        <v>5.51</v>
+        <v>3.25</v>
       </c>
       <c r="O13" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q13" t="n">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="R13" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S13" t="n">
         <v>2.65</v>
       </c>
       <c r="T13" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="U13" t="n">
         <v>1.36</v>
       </c>
       <c r="V13" t="n">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
         <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AD13" t="n">
         <v>1.25</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2087,31 +2087,31 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="M14" t="n">
         <v>3.35</v>
       </c>
       <c r="N14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T14" t="n">
         <v>2.95</v>
-      </c>
-      <c r="O14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3</v>
       </c>
       <c r="U14" t="n">
         <v>1.36</v>
@@ -2120,19 +2120,19 @@
         <v>7</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X14" t="n">
         <v>1.06</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z14" t="n">
         <v>3.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="AB14" t="n">
         <v>1.8</v>
@@ -2141,19 +2141,19 @@
         <v>3.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AE14" t="n">
         <v>1.75</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AG14" t="n">
         <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.18</v>
+        <v>1.68</v>
       </c>
       <c r="M15" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N15" t="n">
-        <v>3.5</v>
+        <v>5.25</v>
       </c>
       <c r="O15" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="P15" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>2.65</v>
+        <v>2.97</v>
       </c>
       <c r="T15" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="U15" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="V15" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
         <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.65</v>
+        <v>2.2</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2325,16 +2325,16 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="M16" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="N16" t="n">
-        <v>4.25</v>
+        <v>4.52</v>
       </c>
       <c r="O16" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="P16" t="n">
         <v>2.15</v>
@@ -2343,16 +2343,16 @@
         <v>4.6</v>
       </c>
       <c r="R16" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="S16" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="T16" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="U16" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V16" t="n">
         <v>7</v>
@@ -2364,19 +2364,19 @@
         <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="AA16" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="AD16" t="n">
         <v>1.25</v>
@@ -2388,10 +2388,10 @@
         <v>1.85</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.91</v>
+        <v>2.07</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.26</v>
+        <v>2.26</v>
       </c>
       <c r="M17" t="n">
-        <v>6</v>
+        <v>3.45</v>
       </c>
       <c r="N17" t="n">
-        <v>8.800000000000001</v>
+        <v>2.89</v>
       </c>
       <c r="O17" t="n">
-        <v>1.68</v>
+        <v>2.7</v>
       </c>
       <c r="P17" t="n">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.13</v>
+        <v>3.7</v>
       </c>
       <c r="R17" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="S17" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="T17" t="n">
-        <v>1.94</v>
+        <v>2.56</v>
       </c>
       <c r="U17" t="n">
-        <v>1.89</v>
+        <v>1.52</v>
       </c>
       <c r="V17" t="n">
-        <v>3.84</v>
+        <v>5.8</v>
       </c>
       <c r="W17" t="n">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="Z17" t="n">
-        <v>7.5</v>
+        <v>3.9</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.36</v>
+        <v>1.76</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.76</v>
+        <v>2.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.14</v>
+        <v>1.4</v>
       </c>
       <c r="AH17" t="n">
-        <v>3.4</v>
+        <v>1.65</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.07</v>
+        <v>2.6</v>
       </c>
       <c r="M18" t="n">
-        <v>3.56</v>
+        <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>3.27</v>
+        <v>2.71</v>
       </c>
       <c r="O18" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="P18" t="n">
-        <v>2.38</v>
+        <v>1.92</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="S18" t="n">
-        <v>3.18</v>
+        <v>2.42</v>
       </c>
       <c r="T18" t="n">
-        <v>2.56</v>
+        <v>3.3</v>
       </c>
       <c r="U18" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="V18" t="n">
-        <v>5.75</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.9</v>
+        <v>2.75</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.05</v>
+        <v>1.6</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.3</v>
+        <v>4.31</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.29</v>
+        <v>1.8</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.71</v>
+        <v>2.3</v>
       </c>
       <c r="M19" t="n">
-        <v>3.92</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>4.33</v>
+        <v>3.25</v>
       </c>
       <c r="O19" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="P19" t="n">
-        <v>2.39</v>
+        <v>2.33</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.5</v>
+        <v>3.65</v>
       </c>
       <c r="R19" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="S19" t="n">
-        <v>3.5</v>
+        <v>3.02</v>
       </c>
       <c r="T19" t="n">
-        <v>2.3</v>
+        <v>2.67</v>
       </c>
       <c r="U19" t="n">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="V19" t="n">
-        <v>5</v>
+        <v>6.3</v>
       </c>
       <c r="W19" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X19" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.5</v>
+        <v>3.56</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.53</v>
+        <v>1.35</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.54</v>
+        <v>1.67</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.6</v>
+        <v>7.5</v>
       </c>
       <c r="M20" t="n">
-        <v>3.04</v>
+        <v>4.85</v>
       </c>
       <c r="N20" t="n">
-        <v>2.8</v>
+        <v>1.38</v>
       </c>
       <c r="O20" t="n">
-        <v>3.1</v>
+        <v>5.75</v>
       </c>
       <c r="P20" t="n">
-        <v>1.92</v>
+        <v>2.63</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.5</v>
+        <v>1.82</v>
       </c>
       <c r="R20" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="S20" t="n">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="T20" t="n">
-        <v>3.15</v>
+        <v>2.21</v>
       </c>
       <c r="U20" t="n">
-        <v>1.3</v>
+        <v>1.69</v>
       </c>
       <c r="V20" t="n">
-        <v>8</v>
+        <v>4.8</v>
       </c>
       <c r="W20" t="n">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="X20" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.64</v>
+        <v>5.05</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.28</v>
+        <v>1.46</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.61</v>
+        <v>2.55</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.4</v>
+        <v>2.35</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.2</v>
+        <v>1.63</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.81</v>
+        <v>2.05</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.44</v>
+        <v>1.11</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.63</v>
+        <v>1.3</v>
       </c>
       <c r="M21" t="n">
-        <v>3.51</v>
+        <v>6.2</v>
       </c>
       <c r="N21" t="n">
-        <v>2.47</v>
+        <v>9.02</v>
       </c>
       <c r="O21" t="n">
-        <v>3.2</v>
+        <v>1.68</v>
       </c>
       <c r="P21" t="n">
-        <v>2.23</v>
+        <v>2.88</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.8</v>
+        <v>5.03</v>
       </c>
       <c r="R21" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="S21" t="n">
-        <v>3.3</v>
+        <v>4.7</v>
       </c>
       <c r="T21" t="n">
-        <v>2.4</v>
+        <v>1.94</v>
       </c>
       <c r="U21" t="n">
-        <v>1.53</v>
+        <v>1.84</v>
       </c>
       <c r="V21" t="n">
-        <v>5.3</v>
+        <v>3.84</v>
       </c>
       <c r="W21" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.63</v>
+        <v>1.36</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.25</v>
+        <v>3.29</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.47</v>
+        <v>1.95</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.49</v>
+        <v>2.28</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.44</v>
+        <v>3.4</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.29</v>
+        <v>1.43</v>
       </c>
       <c r="M22" t="n">
-        <v>3.39</v>
+        <v>4.8</v>
       </c>
       <c r="N22" t="n">
-        <v>2.95</v>
+        <v>6.85</v>
       </c>
       <c r="O22" t="n">
-        <v>2.8</v>
+        <v>1.83</v>
       </c>
       <c r="P22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V22" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC22" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q22" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V22" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.93</v>
-      </c>
       <c r="AD22" t="n">
-        <v>1.34</v>
+        <v>1.6</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.62</v>
+        <v>2.67</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.43</v>
+        <v>2.62</v>
       </c>
       <c r="M23" t="n">
-        <v>4.6</v>
+        <v>3.56</v>
       </c>
       <c r="N23" t="n">
-        <v>6.6</v>
+        <v>2.56</v>
       </c>
       <c r="O23" t="n">
-        <v>1.83</v>
+        <v>3.2</v>
       </c>
       <c r="P23" t="n">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="Q23" t="n">
-        <v>5.5</v>
+        <v>3.06</v>
       </c>
       <c r="R23" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="S23" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="T23" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V23" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB23" t="n">
         <v>2.2</v>
       </c>
-      <c r="U23" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="V23" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.45</v>
-      </c>
       <c r="AC23" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.16</v>
+        <v>2.64</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.8</v>
+        <v>1.44</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>6.9</v>
+        <v>1.68</v>
       </c>
       <c r="M24" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N24" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="O24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V24" t="n">
         <v>5</v>
       </c>
-      <c r="N24" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="O24" t="n">
-        <v>5.32</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="V24" t="n">
-        <v>4.8</v>
-      </c>
       <c r="W24" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="Z24" t="n">
-        <v>5.05</v>
+        <v>4.55</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.05</v>
+        <v>2.36</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.11</v>
+        <v>2.24</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45987.70833333334</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.34</v>
+        <v>5.3</v>
       </c>
       <c r="M10" t="n">
-        <v>5</v>
+        <v>4.22</v>
       </c>
       <c r="N10" t="n">
-        <v>8</v>
+        <v>1.61</v>
       </c>
       <c r="O10" t="n">
-        <v>1.83</v>
+        <v>5.15</v>
       </c>
       <c r="P10" t="n">
-        <v>2.8</v>
+        <v>2.38</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.4</v>
+        <v>2</v>
       </c>
       <c r="R10" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="S10" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="T10" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="U10" t="n">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="V10" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="W10" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X10" t="n">
         <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.6</v>
+        <v>4.3</v>
       </c>
       <c r="AA10" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AD10" t="n">
         <v>1.5</v>
       </c>
-      <c r="AB10" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AC10" t="n">
+      <c r="AE10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF10" t="n">
         <v>2.25</v>
       </c>
-      <c r="AD10" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AG10" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.2</v>
+        <v>1.18</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45987.61458333334</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>5.3</v>
+        <v>1.34</v>
       </c>
       <c r="M11" t="n">
-        <v>4.22</v>
+        <v>5</v>
       </c>
       <c r="N11" t="n">
-        <v>1.61</v>
+        <v>8</v>
       </c>
       <c r="O11" t="n">
-        <v>5.15</v>
+        <v>1.83</v>
       </c>
       <c r="P11" t="n">
-        <v>2.38</v>
+        <v>2.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>6.4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="S11" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="T11" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="U11" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="V11" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="W11" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X11" t="n">
         <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.32</v>
+        <v>2.55</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.62</v>
+        <v>1.81</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.18</v>
+        <v>3.2</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45987.61458333334</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.17</v>
+        <v>1.68</v>
       </c>
       <c r="M13" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N13" t="n">
-        <v>3.25</v>
+        <v>5.25</v>
       </c>
       <c r="O13" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="P13" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="R13" t="n">
         <v>1.36</v>
       </c>
       <c r="S13" t="n">
-        <v>2.65</v>
+        <v>2.97</v>
       </c>
       <c r="T13" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="U13" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="V13" t="n">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="W13" t="n">
         <v>1.05</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
         <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.65</v>
+        <v>2.2</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.68</v>
+        <v>2.17</v>
       </c>
       <c r="M15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q15" t="n">
         <v>3.75</v>
-      </c>
-      <c r="N15" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="O15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>5</v>
       </c>
       <c r="R15" t="n">
         <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>2.97</v>
+        <v>2.65</v>
       </c>
       <c r="T15" t="n">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="U15" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="V15" t="n">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="W15" t="n">
         <v>1.05</v>
       </c>
       <c r="X15" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
         <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AA15" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.26</v>
+        <v>7.5</v>
       </c>
       <c r="M17" t="n">
-        <v>3.45</v>
+        <v>4.85</v>
       </c>
       <c r="N17" t="n">
-        <v>2.89</v>
+        <v>1.38</v>
       </c>
       <c r="O17" t="n">
-        <v>2.7</v>
+        <v>5.75</v>
       </c>
       <c r="P17" t="n">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.7</v>
+        <v>1.82</v>
       </c>
       <c r="R17" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="T17" t="n">
-        <v>2.56</v>
+        <v>2.21</v>
       </c>
       <c r="U17" t="n">
-        <v>1.52</v>
+        <v>1.69</v>
       </c>
       <c r="V17" t="n">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="W17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH17" t="n">
         <v>1.11</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.65</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="M19" t="n">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="N19" t="n">
-        <v>3.25</v>
+        <v>2.56</v>
       </c>
       <c r="O19" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="P19" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.65</v>
+        <v>3.06</v>
       </c>
       <c r="R19" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="S19" t="n">
-        <v>3.02</v>
+        <v>3.45</v>
       </c>
       <c r="T19" t="n">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="U19" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="V19" t="n">
-        <v>6.3</v>
+        <v>5.3</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X19" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.56</v>
+        <v>4.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.15</v>
+        <v>2.64</v>
       </c>
       <c r="AG19" t="n">
         <v>1.3</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>7.5</v>
+        <v>1.68</v>
       </c>
       <c r="M20" t="n">
-        <v>4.85</v>
+        <v>4.1</v>
       </c>
       <c r="N20" t="n">
-        <v>1.38</v>
+        <v>4.86</v>
       </c>
       <c r="O20" t="n">
-        <v>5.75</v>
+        <v>2.2</v>
       </c>
       <c r="P20" t="n">
-        <v>2.63</v>
+        <v>2.39</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.82</v>
+        <v>4.5</v>
       </c>
       <c r="R20" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S20" t="n">
         <v>3.9</v>
       </c>
       <c r="T20" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="U20" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="V20" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.05</v>
+        <v>4.55</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.05</v>
+        <v>2.36</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.11</v>
+        <v>2.24</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V21" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG21" t="n">
         <v>1.3</v>
       </c>
-      <c r="M21" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="N21" t="n">
-        <v>9.02</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>5.03</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S21" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="V21" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AH21" t="n">
-        <v>3.4</v>
+        <v>1.62</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.43</v>
+        <v>2.26</v>
       </c>
       <c r="M22" t="n">
-        <v>4.8</v>
+        <v>3.45</v>
       </c>
       <c r="N22" t="n">
-        <v>6.85</v>
+        <v>2.89</v>
       </c>
       <c r="O22" t="n">
-        <v>1.83</v>
+        <v>2.7</v>
       </c>
       <c r="P22" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.73</v>
+        <v>3.7</v>
       </c>
       <c r="R22" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V22" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y22" t="n">
         <v>1.22</v>
       </c>
-      <c r="S22" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V22" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.12</v>
-      </c>
       <c r="Z22" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.48</v>
+        <v>1.76</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AE22" t="n">
         <v>1.62</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.67</v>
+        <v>1.65</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.62</v>
+        <v>1.43</v>
       </c>
       <c r="M23" t="n">
-        <v>3.56</v>
+        <v>4.8</v>
       </c>
       <c r="N23" t="n">
-        <v>2.56</v>
+        <v>6.85</v>
       </c>
       <c r="O23" t="n">
-        <v>3.2</v>
+        <v>1.83</v>
       </c>
       <c r="P23" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V23" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC23" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q23" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V23" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y23" t="n">
+      <c r="AD23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG23" t="n">
         <v>1.2</v>
       </c>
-      <c r="Z23" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH23" t="n">
-        <v>1.44</v>
+        <v>2.67</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M24" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="N24" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="O24" t="n">
         <v>1.68</v>
       </c>
-      <c r="M24" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="N24" t="n">
-        <v>4.86</v>
-      </c>
-      <c r="O24" t="n">
-        <v>2.2</v>
-      </c>
       <c r="P24" t="n">
-        <v>2.39</v>
+        <v>2.88</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.5</v>
+        <v>5.03</v>
       </c>
       <c r="R24" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="S24" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="T24" t="n">
-        <v>2.3</v>
+        <v>1.94</v>
       </c>
       <c r="U24" t="n">
-        <v>1.64</v>
+        <v>1.84</v>
       </c>
       <c r="V24" t="n">
-        <v>5</v>
+        <v>3.84</v>
       </c>
       <c r="W24" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="X24" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.55</v>
+        <v>6.6</v>
       </c>
       <c r="AA24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE24" t="n">
         <v>1.57</v>
       </c>
-      <c r="AB24" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.56</v>
-      </c>
       <c r="AF24" t="n">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.24</v>
+        <v>3.4</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3405,34 +3405,34 @@
         <v>3.31</v>
       </c>
       <c r="O25" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="P25" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="R25" t="n">
         <v>1.38</v>
       </c>
       <c r="S25" t="n">
-        <v>3.08</v>
+        <v>2.81</v>
       </c>
       <c r="T25" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="U25" t="n">
         <v>1.41</v>
       </c>
       <c r="V25" t="n">
-        <v>6.25</v>
+        <v>6.7</v>
       </c>
       <c r="W25" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y25" t="n">
         <v>1.29</v>
@@ -3447,7 +3447,7 @@
         <v>1.85</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AD25" t="n">
         <v>1.3</v>
@@ -3459,7 +3459,7 @@
         <v>2.05</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AH25" t="n">
         <v>1.73</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1135,28 +1135,28 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="M6" t="n">
         <v>2.9</v>
       </c>
       <c r="N6" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="O6" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="P6" t="n">
         <v>1.84</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="R6" t="n">
         <v>1.52</v>
       </c>
       <c r="S6" t="n">
-        <v>2.27</v>
+        <v>2.51</v>
       </c>
       <c r="T6" t="n">
         <v>3.2</v>
@@ -1165,10 +1165,10 @@
         <v>1.27</v>
       </c>
       <c r="V6" t="n">
-        <v>9.5</v>
+        <v>8.1</v>
       </c>
       <c r="W6" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
         <v>1.08</v>
@@ -1177,13 +1177,13 @@
         <v>1.39</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="AA6" t="n">
         <v>2.25</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AC6" t="n">
         <v>3.96</v>
@@ -1198,10 +1198,10 @@
         <v>1.75</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45987.45833333334</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="M8" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="N8" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="O8" t="n">
-        <v>4.4</v>
+        <v>4.56</v>
       </c>
       <c r="P8" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="Q8" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="V8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA8" t="n">
         <v>2.7</v>
       </c>
-      <c r="R8" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V8" t="n">
-        <v>11</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.62</v>
-      </c>
       <c r="AB8" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.3</v>
+        <v>5.45</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AF8" t="n">
         <v>1.57</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45987.60416666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="M9" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="N9" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="O9" t="n">
-        <v>4.66</v>
+        <v>5.05</v>
       </c>
       <c r="P9" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="R9" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="S9" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="T9" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="U9" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="V9" t="n">
-        <v>12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W9" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.75</v>
+        <v>5.3</v>
       </c>
       <c r="AD9" t="n">
         <v>1.11</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45987.60416666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,28 +2206,28 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.17</v>
+        <v>1.7</v>
       </c>
       <c r="M15" t="n">
         <v>3.5</v>
       </c>
       <c r="N15" t="n">
-        <v>3.25</v>
+        <v>4.52</v>
       </c>
       <c r="O15" t="n">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="P15" t="n">
         <v>2.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="R15" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="S15" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="T15" t="n">
         <v>2.89</v>
@@ -2236,43 +2236,43 @@
         <v>1.36</v>
       </c>
       <c r="V15" t="n">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="W15" t="n">
         <v>1.05</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="AD15" t="n">
         <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.65</v>
+        <v>2.07</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,28 +2325,28 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.7</v>
+        <v>2.17</v>
       </c>
       <c r="M16" t="n">
         <v>3.5</v>
       </c>
       <c r="N16" t="n">
-        <v>4.52</v>
+        <v>3.25</v>
       </c>
       <c r="O16" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="P16" t="n">
         <v>2.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="R16" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="S16" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="T16" t="n">
         <v>2.89</v>
@@ -2355,43 +2355,43 @@
         <v>1.36</v>
       </c>
       <c r="V16" t="n">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="W16" t="n">
         <v>1.05</v>
       </c>
       <c r="X16" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AD16" t="n">
         <v>1.25</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.07</v>
+        <v>1.65</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>7.5</v>
+        <v>1.3</v>
       </c>
       <c r="M17" t="n">
-        <v>4.85</v>
+        <v>6.2</v>
       </c>
       <c r="N17" t="n">
-        <v>1.38</v>
+        <v>9.02</v>
       </c>
       <c r="O17" t="n">
-        <v>5.75</v>
+        <v>1.68</v>
       </c>
       <c r="P17" t="n">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.82</v>
+        <v>5.03</v>
       </c>
       <c r="R17" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="S17" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="T17" t="n">
-        <v>2.21</v>
+        <v>1.94</v>
       </c>
       <c r="U17" t="n">
-        <v>1.69</v>
+        <v>1.84</v>
       </c>
       <c r="V17" t="n">
-        <v>4.8</v>
+        <v>3.84</v>
       </c>
       <c r="W17" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.05</v>
+        <v>6.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.55</v>
+        <v>3.29</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.35</v>
+        <v>1.9</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.63</v>
+        <v>1.95</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.05</v>
+        <v>2.28</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.11</v>
+        <v>3.4</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="M18" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="N18" t="n">
-        <v>2.71</v>
+        <v>3.25</v>
       </c>
       <c r="O18" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="P18" t="n">
-        <v>1.92</v>
+        <v>2.33</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="R18" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="S18" t="n">
-        <v>2.42</v>
+        <v>3.02</v>
       </c>
       <c r="T18" t="n">
-        <v>3.3</v>
+        <v>2.67</v>
       </c>
       <c r="U18" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V18" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG18" t="n">
         <v>1.3</v>
       </c>
-      <c r="V18" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AH18" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.62</v>
+        <v>7.5</v>
       </c>
       <c r="M19" t="n">
-        <v>3.56</v>
+        <v>4.85</v>
       </c>
       <c r="N19" t="n">
-        <v>2.56</v>
+        <v>1.38</v>
       </c>
       <c r="O19" t="n">
-        <v>3.2</v>
+        <v>5.75</v>
       </c>
       <c r="P19" t="n">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.06</v>
+        <v>1.82</v>
       </c>
       <c r="R19" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="S19" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="T19" t="n">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="U19" t="n">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="V19" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="W19" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.5</v>
+        <v>5.05</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.64</v>
+        <v>2.05</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.44</v>
+        <v>1.11</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.68</v>
+        <v>2.26</v>
       </c>
       <c r="M20" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="N20" t="n">
-        <v>4.86</v>
+        <v>2.89</v>
       </c>
       <c r="O20" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="P20" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="R20" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="S20" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="T20" t="n">
-        <v>2.3</v>
+        <v>2.56</v>
       </c>
       <c r="U20" t="n">
-        <v>1.64</v>
+        <v>1.52</v>
       </c>
       <c r="V20" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="W20" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X20" t="n">
         <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.55</v>
+        <v>3.9</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.57</v>
+        <v>1.76</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.24</v>
+        <v>1.65</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.3</v>
+        <v>1.43</v>
       </c>
       <c r="M21" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="N21" t="n">
-        <v>3.25</v>
+        <v>6.85</v>
       </c>
       <c r="O21" t="n">
-        <v>2.8</v>
+        <v>1.83</v>
       </c>
       <c r="P21" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.65</v>
+        <v>4.73</v>
       </c>
       <c r="R21" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="S21" t="n">
-        <v>3.02</v>
+        <v>3.85</v>
       </c>
       <c r="T21" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V21" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH21" t="n">
         <v>2.67</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V21" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.62</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.26</v>
+        <v>1.68</v>
       </c>
       <c r="M22" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="N22" t="n">
-        <v>2.89</v>
+        <v>4.86</v>
       </c>
       <c r="O22" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="P22" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="S22" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="T22" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="U22" t="n">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="V22" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X22" t="n">
         <v>1.04</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.9</v>
+        <v>4.55</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.76</v>
+        <v>1.57</v>
       </c>
       <c r="AB22" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.65</v>
+        <v>2.24</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.43</v>
+        <v>2.62</v>
       </c>
       <c r="M23" t="n">
-        <v>4.8</v>
+        <v>3.56</v>
       </c>
       <c r="N23" t="n">
-        <v>6.85</v>
+        <v>2.56</v>
       </c>
       <c r="O23" t="n">
-        <v>1.83</v>
+        <v>3.2</v>
       </c>
       <c r="P23" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T23" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q23" t="n">
-        <v>4.73</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.12</v>
-      </c>
       <c r="U23" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V23" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA23" t="n">
         <v>1.67</v>
       </c>
-      <c r="V23" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AB23" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.2</v>
+        <v>2.64</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.67</v>
+        <v>1.44</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="O24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U24" t="n">
         <v>1.3</v>
       </c>
-      <c r="M24" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="N24" t="n">
-        <v>9.02</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>5.03</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S24" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.84</v>
-      </c>
       <c r="V24" t="n">
-        <v>3.84</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W24" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.05</v>
+        <v>1.41</v>
       </c>
       <c r="Z24" t="n">
-        <v>6.6</v>
+        <v>2.75</v>
       </c>
       <c r="AA24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG24" t="n">
         <v>1.36</v>
       </c>
-      <c r="AB24" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AH24" t="n">
-        <v>3.4</v>
+        <v>1.44</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3405,13 +3405,13 @@
         <v>3.31</v>
       </c>
       <c r="O25" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="P25" t="n">
         <v>2.2</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.8</v>
+        <v>3.92</v>
       </c>
       <c r="R25" t="n">
         <v>1.38</v>
@@ -3420,34 +3420,34 @@
         <v>2.81</v>
       </c>
       <c r="T25" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="U25" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="V25" t="n">
-        <v>6.7</v>
+        <v>6.25</v>
       </c>
       <c r="W25" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X25" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AB25" t="n">
         <v>1.85</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.2</v>
+        <v>3.26</v>
       </c>
       <c r="AD25" t="n">
         <v>1.3</v>
@@ -3456,13 +3456,13 @@
         <v>1.7</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45987.79166666666</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="M12" t="n">
-        <v>3.75</v>
+        <v>3.36</v>
       </c>
       <c r="N12" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,34 +1968,34 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="M13" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N13" t="n">
-        <v>5.25</v>
+        <v>4.52</v>
       </c>
       <c r="O13" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q13" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="R13" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="U13" t="n">
         <v>1.36</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.39</v>
       </c>
       <c r="V13" t="n">
         <v>7</v>
@@ -2004,25 +2004,25 @@
         <v>1.05</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="AA13" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE13" t="n">
         <v>1.85</v>
@@ -2031,10 +2031,10 @@
         <v>1.85</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,28 +2206,28 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.7</v>
+        <v>2.17</v>
       </c>
       <c r="M15" t="n">
         <v>3.5</v>
       </c>
       <c r="N15" t="n">
-        <v>4.52</v>
+        <v>3.25</v>
       </c>
       <c r="O15" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="P15" t="n">
         <v>2.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="R15" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="T15" t="n">
         <v>2.89</v>
@@ -2236,43 +2236,43 @@
         <v>1.36</v>
       </c>
       <c r="V15" t="n">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="W15" t="n">
         <v>1.05</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AD15" t="n">
         <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.07</v>
+        <v>1.65</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.17</v>
+        <v>1.68</v>
       </c>
       <c r="M16" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N16" t="n">
-        <v>3.25</v>
+        <v>5.25</v>
       </c>
       <c r="O16" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="P16" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="R16" t="n">
         <v>1.36</v>
       </c>
       <c r="S16" t="n">
-        <v>2.65</v>
+        <v>2.97</v>
       </c>
       <c r="T16" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="U16" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="V16" t="n">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="W16" t="n">
         <v>1.05</v>
       </c>
       <c r="X16" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y16" t="n">
         <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.65</v>
+        <v>2.2</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.3</v>
+        <v>2.62</v>
       </c>
       <c r="M17" t="n">
-        <v>6.2</v>
+        <v>3.56</v>
       </c>
       <c r="N17" t="n">
-        <v>9.02</v>
+        <v>2.56</v>
       </c>
       <c r="O17" t="n">
-        <v>1.68</v>
+        <v>3.2</v>
       </c>
       <c r="P17" t="n">
-        <v>2.88</v>
+        <v>2.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.03</v>
+        <v>3.06</v>
       </c>
       <c r="R17" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="S17" t="n">
-        <v>4.7</v>
+        <v>3.45</v>
       </c>
       <c r="T17" t="n">
-        <v>1.94</v>
+        <v>2.4</v>
       </c>
       <c r="U17" t="n">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="V17" t="n">
-        <v>3.84</v>
+        <v>5.3</v>
       </c>
       <c r="W17" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="Z17" t="n">
-        <v>6.6</v>
+        <v>4.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.29</v>
+        <v>2.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.28</v>
+        <v>2.64</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AH17" t="n">
-        <v>3.4</v>
+        <v>1.44</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="M18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T18" t="n">
         <v>2.3</v>
       </c>
-      <c r="M18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N18" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O18" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.67</v>
-      </c>
       <c r="U18" t="n">
-        <v>1.47</v>
+        <v>1.64</v>
       </c>
       <c r="V18" t="n">
-        <v>6.3</v>
+        <v>5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.56</v>
+        <v>4.55</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.35</v>
+        <v>1.53</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.15</v>
+        <v>2.36</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.62</v>
+        <v>2.24</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>7.5</v>
+        <v>1.43</v>
       </c>
       <c r="M19" t="n">
-        <v>4.85</v>
+        <v>4.8</v>
       </c>
       <c r="N19" t="n">
-        <v>1.38</v>
+        <v>6.85</v>
       </c>
       <c r="O19" t="n">
-        <v>5.75</v>
+        <v>1.83</v>
       </c>
       <c r="P19" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.82</v>
+        <v>4.73</v>
       </c>
       <c r="R19" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S19" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="T19" t="n">
-        <v>2.21</v>
+        <v>2.12</v>
       </c>
       <c r="U19" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="V19" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="W19" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.11</v>
+        <v>2.67</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.26</v>
+        <v>1.3</v>
       </c>
       <c r="M20" t="n">
-        <v>3.45</v>
+        <v>6.2</v>
       </c>
       <c r="N20" t="n">
-        <v>2.89</v>
+        <v>9.02</v>
       </c>
       <c r="O20" t="n">
-        <v>2.7</v>
+        <v>1.68</v>
       </c>
       <c r="P20" t="n">
-        <v>2.38</v>
+        <v>2.88</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.7</v>
+        <v>5.03</v>
       </c>
       <c r="R20" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="S20" t="n">
-        <v>3.3</v>
+        <v>4.7</v>
       </c>
       <c r="T20" t="n">
-        <v>2.56</v>
+        <v>1.94</v>
       </c>
       <c r="U20" t="n">
-        <v>1.52</v>
+        <v>1.84</v>
       </c>
       <c r="V20" t="n">
-        <v>5.8</v>
+        <v>3.84</v>
       </c>
       <c r="W20" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="X20" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.9</v>
+        <v>6.6</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.76</v>
+        <v>1.36</v>
       </c>
       <c r="AB20" t="n">
-        <v>2</v>
+        <v>3.29</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.4</v>
+        <v>1.14</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.65</v>
+        <v>3.4</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.43</v>
+        <v>2.26</v>
       </c>
       <c r="M21" t="n">
-        <v>4.8</v>
+        <v>3.45</v>
       </c>
       <c r="N21" t="n">
-        <v>6.85</v>
+        <v>2.89</v>
       </c>
       <c r="O21" t="n">
-        <v>1.83</v>
+        <v>2.7</v>
       </c>
       <c r="P21" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.73</v>
+        <v>3.7</v>
       </c>
       <c r="R21" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V21" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y21" t="n">
         <v>1.22</v>
       </c>
-      <c r="S21" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V21" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.12</v>
-      </c>
       <c r="Z21" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.48</v>
+        <v>1.76</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AE21" t="n">
         <v>1.62</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.67</v>
+        <v>1.65</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.68</v>
+        <v>2.3</v>
       </c>
       <c r="M22" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="N22" t="n">
-        <v>4.86</v>
+        <v>3.25</v>
       </c>
       <c r="O22" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="P22" t="n">
-        <v>2.39</v>
+        <v>2.33</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.5</v>
+        <v>3.65</v>
       </c>
       <c r="R22" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="S22" t="n">
-        <v>3.9</v>
+        <v>3.02</v>
       </c>
       <c r="T22" t="n">
-        <v>2.3</v>
+        <v>2.67</v>
       </c>
       <c r="U22" t="n">
-        <v>1.64</v>
+        <v>1.47</v>
       </c>
       <c r="V22" t="n">
-        <v>5</v>
+        <v>6.3</v>
       </c>
       <c r="W22" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X22" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.55</v>
+        <v>3.56</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.53</v>
+        <v>1.35</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.36</v>
+        <v>2.15</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.24</v>
+        <v>1.62</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.62</v>
+        <v>7.5</v>
       </c>
       <c r="M23" t="n">
-        <v>3.56</v>
+        <v>4.85</v>
       </c>
       <c r="N23" t="n">
-        <v>2.56</v>
+        <v>1.38</v>
       </c>
       <c r="O23" t="n">
-        <v>3.2</v>
+        <v>5.75</v>
       </c>
       <c r="P23" t="n">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.06</v>
+        <v>1.82</v>
       </c>
       <c r="R23" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="S23" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="T23" t="n">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="U23" t="n">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="V23" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="W23" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.5</v>
+        <v>5.05</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.64</v>
+        <v>2.05</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.44</v>
+        <v>1.11</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45987.70833333334</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1144,19 +1144,19 @@
         <v>4</v>
       </c>
       <c r="O6" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="P6" t="n">
         <v>1.84</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="R6" t="n">
         <v>1.52</v>
       </c>
       <c r="S6" t="n">
-        <v>2.51</v>
+        <v>2.27</v>
       </c>
       <c r="T6" t="n">
         <v>3.2</v>
@@ -1174,7 +1174,7 @@
         <v>1.08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Z6" t="n">
         <v>2.59</v>
@@ -1189,7 +1189,7 @@
         <v>3.96</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE6" t="n">
         <v>1.95</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="M8" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="N8" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="O8" t="n">
+        <v>5</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S8" t="n">
         <v>2.3</v>
       </c>
-      <c r="O8" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.15</v>
-      </c>
       <c r="T8" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="U8" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="V8" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="W8" t="n">
         <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.45</v>
+        <v>5.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AF8" t="n">
         <v>1.57</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45987.60416666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,34 +1492,34 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="N9" t="n">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="O9" t="n">
-        <v>5.05</v>
+        <v>4.56</v>
       </c>
       <c r="P9" t="n">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="R9" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="S9" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="T9" t="n">
-        <v>3.6</v>
+        <v>3.78</v>
       </c>
       <c r="U9" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="V9" t="n">
         <v>8.800000000000001</v>
@@ -1528,31 +1528,31 @@
         <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AG9" t="n">
         <v>1.4</v>
@@ -1611,40 +1611,40 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="M10" t="n">
-        <v>4.22</v>
+        <v>4.1</v>
       </c>
       <c r="N10" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="O10" t="n">
-        <v>5.15</v>
+        <v>5</v>
       </c>
       <c r="P10" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="R10" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
       <c r="T10" t="n">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
       <c r="U10" t="n">
         <v>1.59</v>
       </c>
       <c r="V10" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="W10" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X10" t="n">
         <v>1.03</v>
@@ -1653,13 +1653,13 @@
         <v>1.15</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="AC10" t="n">
         <v>2.45</v>
@@ -1668,16 +1668,16 @@
         <v>1.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.25</v>
+        <v>2.37</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45987.61458333334</v>
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="M11" t="n">
         <v>5</v>
       </c>
       <c r="N11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O11" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="P11" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="R11" t="n">
         <v>1.27</v>
       </c>
       <c r="S11" t="n">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="T11" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="U11" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="V11" t="n">
-        <v>5.2</v>
+        <v>4.95</v>
       </c>
       <c r="W11" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AF11" t="n">
         <v>1.95</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45987.61458333334</v>
@@ -1968,61 +1968,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="M13" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="N13" t="n">
-        <v>4.52</v>
+        <v>4.4</v>
       </c>
       <c r="O13" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="P13" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.6</v>
+        <v>5.27</v>
       </c>
       <c r="R13" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S13" t="n">
         <v>2.8</v>
       </c>
       <c r="T13" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="U13" t="n">
         <v>1.36</v>
       </c>
       <c r="V13" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
         <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE13" t="n">
         <v>1.85</v>
@@ -2031,10 +2031,10 @@
         <v>1.85</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.45</v>
+        <v>1.61</v>
       </c>
       <c r="M14" t="n">
-        <v>3.35</v>
+        <v>3.63</v>
       </c>
       <c r="N14" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>5</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="T14" t="n">
         <v>2.8</v>
       </c>
-      <c r="O14" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.95</v>
-      </c>
       <c r="U14" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="V14" t="n">
         <v>7</v>
       </c>
       <c r="W14" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
         <v>3.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.01</v>
+        <v>1.87</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AC14" t="n">
         <v>3.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.53</v>
+        <v>2.15</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.17</v>
+        <v>2.44</v>
       </c>
       <c r="M15" t="n">
-        <v>3.5</v>
+        <v>3.31</v>
       </c>
       <c r="N15" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="O15" t="n">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="P15" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="R15" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S15" t="n">
         <v>2.65</v>
       </c>
       <c r="T15" t="n">
-        <v>2.89</v>
+        <v>2.93</v>
       </c>
       <c r="U15" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="V15" t="n">
         <v>7.3</v>
       </c>
       <c r="W15" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC15" t="n">
         <v>3.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.68</v>
+        <v>2.07</v>
       </c>
       <c r="M16" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="N16" t="n">
-        <v>5.25</v>
+        <v>3.45</v>
       </c>
       <c r="O16" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="P16" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="R16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U16" t="n">
         <v>1.36</v>
       </c>
-      <c r="S16" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.39</v>
-      </c>
       <c r="V16" t="n">
-        <v>7</v>
+        <v>6.95</v>
       </c>
       <c r="W16" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
         <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.3</v>
+        <v>2.99</v>
       </c>
       <c r="AA16" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.2</v>
+        <v>1.71</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,70 +2444,70 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="M17" t="n">
-        <v>3.56</v>
+        <v>3.13</v>
       </c>
       <c r="N17" t="n">
-        <v>2.56</v>
+        <v>2.83</v>
       </c>
       <c r="O17" t="n">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="P17" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.06</v>
+        <v>3.19</v>
       </c>
       <c r="R17" t="n">
-        <v>1.27</v>
+        <v>1.51</v>
       </c>
       <c r="S17" t="n">
-        <v>3.45</v>
+        <v>2.39</v>
       </c>
       <c r="T17" t="n">
-        <v>2.4</v>
+        <v>3.28</v>
       </c>
       <c r="U17" t="n">
-        <v>1.53</v>
+        <v>1.29</v>
       </c>
       <c r="V17" t="n">
-        <v>5.3</v>
+        <v>8.1</v>
       </c>
       <c r="W17" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.5</v>
+        <v>2.81</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.67</v>
+        <v>2.28</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.2</v>
+        <v>1.55</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.7</v>
+        <v>4.46</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.52</v>
+        <v>1.91</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.64</v>
+        <v>1.8</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH17" t="n">
         <v>1.44</v>
@@ -2563,31 +2563,31 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="M18" t="n">
-        <v>4.1</v>
+        <v>3.92</v>
       </c>
       <c r="N18" t="n">
-        <v>4.86</v>
+        <v>4.33</v>
       </c>
       <c r="O18" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T18" t="n">
         <v>2.2</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.3</v>
       </c>
       <c r="U18" t="n">
         <v>1.64</v>
@@ -2602,16 +2602,16 @@
         <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.55</v>
+        <v>5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AC18" t="n">
         <v>2.3</v>
@@ -2620,16 +2620,16 @@
         <v>1.53</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.43</v>
+        <v>2.63</v>
       </c>
       <c r="M19" t="n">
-        <v>4.8</v>
+        <v>3.51</v>
       </c>
       <c r="N19" t="n">
-        <v>6.85</v>
+        <v>2.47</v>
       </c>
       <c r="O19" t="n">
-        <v>1.83</v>
+        <v>3.2</v>
       </c>
       <c r="P19" t="n">
         <v>2.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.73</v>
+        <v>3</v>
       </c>
       <c r="R19" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="S19" t="n">
-        <v>3.85</v>
+        <v>3.36</v>
       </c>
       <c r="T19" t="n">
-        <v>2.12</v>
+        <v>2.4</v>
       </c>
       <c r="U19" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="V19" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="Z19" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.48</v>
+        <v>1.63</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.67</v>
+        <v>1.44</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AG20" t="n">
         <v>1.3</v>
       </c>
-      <c r="M20" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="N20" t="n">
-        <v>9.02</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>5.03</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S20" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="V20" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AH20" t="n">
-        <v>3.4</v>
+        <v>1.62</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.26</v>
+        <v>6.9</v>
       </c>
       <c r="M21" t="n">
-        <v>3.45</v>
+        <v>5</v>
       </c>
       <c r="N21" t="n">
-        <v>2.89</v>
+        <v>1.38</v>
       </c>
       <c r="O21" t="n">
-        <v>2.7</v>
+        <v>7.29</v>
       </c>
       <c r="P21" t="n">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.7</v>
+        <v>1.85</v>
       </c>
       <c r="R21" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="S21" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="T21" t="n">
-        <v>2.56</v>
+        <v>2.23</v>
       </c>
       <c r="U21" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="V21" t="n">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="W21" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AH21" t="n">
         <v>1.11</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.65</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.3</v>
+        <v>2.07</v>
       </c>
       <c r="M22" t="n">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="N22" t="n">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="O22" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="P22" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="R22" t="n">
         <v>1.35</v>
       </c>
       <c r="S22" t="n">
-        <v>3.02</v>
+        <v>3.18</v>
       </c>
       <c r="T22" t="n">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="U22" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="V22" t="n">
-        <v>6.3</v>
+        <v>5.75</v>
       </c>
       <c r="W22" t="n">
         <v>1.1</v>
       </c>
       <c r="X22" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.56</v>
+        <v>3.9</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AB22" t="n">
         <v>2.05</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.35</v>
+        <v>1.6</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AG22" t="n">
         <v>1.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M23" t="n">
+        <v>6</v>
+      </c>
+      <c r="N23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="V23" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z23" t="n">
         <v>7.5</v>
       </c>
-      <c r="M23" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="N23" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="O23" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="V23" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>5.05</v>
-      </c>
       <c r="AA23" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.55</v>
+        <v>3.1</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.35</v>
+        <v>1.76</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.63</v>
+        <v>1.95</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.11</v>
+        <v>3.4</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.6</v>
+        <v>1.43</v>
       </c>
       <c r="M24" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="N24" t="n">
-        <v>2.71</v>
+        <v>6.6</v>
       </c>
       <c r="O24" t="n">
-        <v>3.1</v>
+        <v>1.83</v>
       </c>
       <c r="P24" t="n">
-        <v>1.92</v>
+        <v>2.63</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="S24" t="n">
-        <v>2.42</v>
+        <v>3.85</v>
       </c>
       <c r="T24" t="n">
-        <v>3.3</v>
+        <v>2.21</v>
       </c>
       <c r="U24" t="n">
-        <v>1.3</v>
+        <v>1.67</v>
       </c>
       <c r="V24" t="n">
-        <v>8.699999999999999</v>
+        <v>4.7</v>
       </c>
       <c r="W24" t="n">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="X24" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.41</v>
+        <v>1.12</v>
       </c>
       <c r="Z24" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH24" t="n">
         <v>2.75</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.44</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3423,7 +3423,7 @@
         <v>2.8</v>
       </c>
       <c r="U25" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="V25" t="n">
         <v>6.25</v>
@@ -3432,16 +3432,16 @@
         <v>1.06</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y25" t="n">
         <v>1.25</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AB25" t="n">
         <v>1.85</v>
@@ -3459,10 +3459,10 @@
         <v>2</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45987.79166666666</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,49 +1611,49 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5.1</v>
+        <v>1.32</v>
       </c>
       <c r="M10" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="N10" t="n">
-        <v>1.6</v>
+        <v>9</v>
       </c>
       <c r="O10" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>7</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V10" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z10" t="n">
         <v>5</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="V10" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4.6</v>
       </c>
       <c r="AA10" t="n">
         <v>1.58</v>
@@ -1662,22 +1662,22 @@
         <v>2.35</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.26</v>
+        <v>1.95</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.37</v>
+        <v>1.18</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.13</v>
+        <v>3.1</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45987.61458333334</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,49 +1730,49 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.32</v>
+        <v>5.1</v>
       </c>
       <c r="M11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O11" t="n">
         <v>5</v>
       </c>
-      <c r="N11" t="n">
-        <v>9</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.74</v>
-      </c>
       <c r="P11" t="n">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="Q11" t="n">
-        <v>7</v>
+        <v>2.06</v>
       </c>
       <c r="R11" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="S11" t="n">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="T11" t="n">
-        <v>2.28</v>
+        <v>2.43</v>
       </c>
       <c r="U11" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="V11" t="n">
-        <v>4.95</v>
+        <v>5.2</v>
       </c>
       <c r="W11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y11" t="n">
         <v>1.15</v>
       </c>
-      <c r="X11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.18</v>
-      </c>
       <c r="Z11" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AA11" t="n">
         <v>1.58</v>
@@ -1781,22 +1781,22 @@
         <v>2.35</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.95</v>
+        <v>2.26</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.18</v>
+        <v>2.37</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.1</v>
+        <v>1.13</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45987.61458333334</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.81</v>
+        <v>1.61</v>
       </c>
       <c r="M13" t="n">
-        <v>3.45</v>
+        <v>3.63</v>
       </c>
       <c r="N13" t="n">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="O13" t="n">
-        <v>2.37</v>
+        <v>2.15</v>
       </c>
       <c r="P13" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.27</v>
+        <v>5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="T13" t="n">
         <v>2.8</v>
       </c>
-      <c r="T13" t="n">
-        <v>2.88</v>
-      </c>
       <c r="U13" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="V13" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="W13" t="n">
         <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
         <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG13" t="n">
         <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.61</v>
+        <v>2.44</v>
       </c>
       <c r="M14" t="n">
-        <v>3.63</v>
+        <v>3.31</v>
       </c>
       <c r="N14" t="n">
-        <v>5.8</v>
+        <v>2.8</v>
       </c>
       <c r="O14" t="n">
-        <v>2.15</v>
+        <v>3.05</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="Q14" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S14" t="n">
-        <v>2.98</v>
+        <v>2.65</v>
       </c>
       <c r="T14" t="n">
-        <v>2.8</v>
+        <v>2.93</v>
       </c>
       <c r="U14" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="V14" t="n">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z14" t="n">
         <v>3.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.15</v>
+        <v>1.53</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,49 +2206,49 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.44</v>
+        <v>1.81</v>
       </c>
       <c r="M15" t="n">
-        <v>3.31</v>
+        <v>3.45</v>
       </c>
       <c r="N15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S15" t="n">
         <v>2.8</v>
       </c>
-      <c r="O15" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.65</v>
-      </c>
       <c r="T15" t="n">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="U15" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V15" t="n">
-        <v>7.3</v>
+        <v>6.8</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
         <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AA15" t="n">
         <v>1.98</v>
@@ -2257,22 +2257,22 @@
         <v>1.77</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AF15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH15" t="n">
         <v>2</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.53</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.52</v>
+        <v>1.43</v>
       </c>
       <c r="M17" t="n">
-        <v>3.13</v>
+        <v>4.6</v>
       </c>
       <c r="N17" t="n">
-        <v>2.83</v>
+        <v>6.6</v>
       </c>
       <c r="O17" t="n">
-        <v>3.32</v>
+        <v>1.83</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>2.63</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.19</v>
+        <v>5.5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.51</v>
+        <v>1.22</v>
       </c>
       <c r="S17" t="n">
-        <v>2.39</v>
+        <v>3.85</v>
       </c>
       <c r="T17" t="n">
-        <v>3.28</v>
+        <v>2.21</v>
       </c>
       <c r="U17" t="n">
-        <v>1.29</v>
+        <v>1.67</v>
       </c>
       <c r="V17" t="n">
-        <v>8.1</v>
+        <v>4.7</v>
       </c>
       <c r="W17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X17" t="n">
         <v>1.02</v>
       </c>
-      <c r="X17" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y17" t="n">
-        <v>1.4</v>
+        <v>1.12</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.81</v>
+        <v>4.75</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.28</v>
+        <v>1.53</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.55</v>
+        <v>2.45</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.46</v>
+        <v>2.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.17</v>
+        <v>1.6</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.8</v>
+        <v>2.19</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.44</v>
+        <v>2.75</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.71</v>
+        <v>2.63</v>
       </c>
       <c r="M18" t="n">
-        <v>3.92</v>
+        <v>3.51</v>
       </c>
       <c r="N18" t="n">
-        <v>4.33</v>
+        <v>2.47</v>
       </c>
       <c r="O18" t="n">
-        <v>2.14</v>
+        <v>3.2</v>
       </c>
       <c r="P18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC18" t="n">
         <v>2.45</v>
       </c>
-      <c r="Q18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="V18" t="n">
-        <v>5</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AD18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE18" t="n">
         <v>1.53</v>
       </c>
-      <c r="AE18" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AF18" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.27</v>
+        <v>1.44</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,70 +2682,70 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.63</v>
+        <v>2.52</v>
       </c>
       <c r="M19" t="n">
-        <v>3.51</v>
+        <v>3.13</v>
       </c>
       <c r="N19" t="n">
-        <v>2.47</v>
+        <v>2.83</v>
       </c>
       <c r="O19" t="n">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="P19" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="Q19" t="n">
-        <v>3</v>
+        <v>3.19</v>
       </c>
       <c r="R19" t="n">
-        <v>1.32</v>
+        <v>1.51</v>
       </c>
       <c r="S19" t="n">
-        <v>3.36</v>
+        <v>2.39</v>
       </c>
       <c r="T19" t="n">
-        <v>2.4</v>
+        <v>3.28</v>
       </c>
       <c r="U19" t="n">
-        <v>1.57</v>
+        <v>1.29</v>
       </c>
       <c r="V19" t="n">
-        <v>5.5</v>
+        <v>8.1</v>
       </c>
       <c r="W19" t="n">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.19</v>
+        <v>1.4</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.5</v>
+        <v>2.81</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.63</v>
+        <v>2.28</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.25</v>
+        <v>1.55</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.45</v>
+        <v>4.46</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH19" t="n">
         <v>1.44</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.43</v>
+        <v>1.71</v>
       </c>
       <c r="M24" t="n">
-        <v>4.6</v>
+        <v>3.92</v>
       </c>
       <c r="N24" t="n">
-        <v>6.6</v>
+        <v>4.33</v>
       </c>
       <c r="O24" t="n">
-        <v>1.83</v>
+        <v>2.14</v>
       </c>
       <c r="P24" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="Q24" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="R24" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S24" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="T24" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="U24" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="V24" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="AC24" t="n">
         <v>2.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.19</v>
+        <v>2.32</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.75</v>
+        <v>2.27</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45987.70833333334</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -847,7 +847,7 @@
         <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
-        <v>45987.41666666666</v>
+        <v>45987.375</v>
       </c>
     </row>
     <row r="4">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,49 +1611,49 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.32</v>
+        <v>5.1</v>
       </c>
       <c r="M10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O10" t="n">
         <v>5</v>
       </c>
-      <c r="N10" t="n">
-        <v>9</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.74</v>
-      </c>
       <c r="P10" t="n">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="Q10" t="n">
-        <v>7</v>
+        <v>2.06</v>
       </c>
       <c r="R10" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="T10" t="n">
-        <v>2.28</v>
+        <v>2.43</v>
       </c>
       <c r="U10" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="V10" t="n">
-        <v>4.95</v>
+        <v>5.2</v>
       </c>
       <c r="W10" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y10" t="n">
         <v>1.15</v>
       </c>
-      <c r="X10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.18</v>
-      </c>
       <c r="Z10" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AA10" t="n">
         <v>1.58</v>
@@ -1662,22 +1662,22 @@
         <v>2.35</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.95</v>
+        <v>2.26</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.18</v>
+        <v>2.37</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.1</v>
+        <v>1.13</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45987.61458333334</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,49 +1730,49 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>5.1</v>
+        <v>1.32</v>
       </c>
       <c r="M11" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="N11" t="n">
-        <v>1.6</v>
+        <v>9</v>
       </c>
       <c r="O11" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>7</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V11" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z11" t="n">
         <v>5</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="V11" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4.6</v>
       </c>
       <c r="AA11" t="n">
         <v>1.58</v>
@@ -1781,22 +1781,22 @@
         <v>2.35</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.26</v>
+        <v>1.95</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.37</v>
+        <v>1.18</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.13</v>
+        <v>3.1</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45987.61458333334</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.61</v>
+        <v>1.81</v>
       </c>
       <c r="M13" t="n">
-        <v>3.63</v>
+        <v>3.45</v>
       </c>
       <c r="N13" t="n">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="O13" t="n">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="Q13" t="n">
-        <v>5</v>
+        <v>5.27</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S13" t="n">
-        <v>2.98</v>
+        <v>2.8</v>
       </c>
       <c r="T13" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="U13" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="V13" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="W13" t="n">
         <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
         <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG13" t="n">
         <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,49 +2087,49 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.44</v>
+        <v>2.07</v>
       </c>
       <c r="M14" t="n">
-        <v>3.31</v>
+        <v>3.35</v>
       </c>
       <c r="N14" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O14" t="n">
         <v>2.8</v>
       </c>
-      <c r="O14" t="n">
-        <v>3.05</v>
-      </c>
       <c r="P14" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="R14" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="S14" t="n">
         <v>2.65</v>
       </c>
       <c r="T14" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="U14" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>7.3</v>
+        <v>6.95</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.3</v>
+        <v>2.99</v>
       </c>
       <c r="AA14" t="n">
         <v>1.98</v>
@@ -2141,19 +2141,19 @@
         <v>3.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,49 +2206,49 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.81</v>
+        <v>2.44</v>
       </c>
       <c r="M15" t="n">
-        <v>3.45</v>
+        <v>3.31</v>
       </c>
       <c r="N15" t="n">
-        <v>4.4</v>
+        <v>2.8</v>
       </c>
       <c r="O15" t="n">
-        <v>2.37</v>
+        <v>3.05</v>
       </c>
       <c r="P15" t="n">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.27</v>
+        <v>3.4</v>
       </c>
       <c r="R15" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="S15" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="T15" t="n">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="U15" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="V15" t="n">
-        <v>6.8</v>
+        <v>7.3</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
         <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AA15" t="n">
         <v>1.98</v>
@@ -2257,22 +2257,22 @@
         <v>1.77</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.07</v>
+        <v>1.61</v>
       </c>
       <c r="M16" t="n">
-        <v>3.35</v>
+        <v>3.63</v>
       </c>
       <c r="N16" t="n">
-        <v>3.45</v>
+        <v>5.8</v>
       </c>
       <c r="O16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>5</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="T16" t="n">
         <v>2.8</v>
       </c>
-      <c r="P16" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.95</v>
-      </c>
       <c r="U16" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="V16" t="n">
-        <v>6.95</v>
+        <v>7</v>
       </c>
       <c r="W16" t="n">
         <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
         <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.99</v>
+        <v>3.3</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AG16" t="n">
         <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.71</v>
+        <v>2.15</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.43</v>
+        <v>1.71</v>
       </c>
       <c r="M17" t="n">
-        <v>4.6</v>
+        <v>3.92</v>
       </c>
       <c r="N17" t="n">
-        <v>6.6</v>
+        <v>4.33</v>
       </c>
       <c r="O17" t="n">
-        <v>1.83</v>
+        <v>2.14</v>
       </c>
       <c r="P17" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="R17" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="T17" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="U17" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="V17" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="AC17" t="n">
         <v>2.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.19</v>
+        <v>2.32</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.75</v>
+        <v>2.27</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.63</v>
+        <v>2.29</v>
       </c>
       <c r="M18" t="n">
-        <v>3.51</v>
+        <v>3.39</v>
       </c>
       <c r="N18" t="n">
-        <v>2.47</v>
+        <v>2.95</v>
       </c>
       <c r="O18" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="P18" t="n">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="Q18" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="R18" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="S18" t="n">
-        <v>3.36</v>
+        <v>3.15</v>
       </c>
       <c r="T18" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="U18" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="V18" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="W18" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.5</v>
+        <v>3.65</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.63</v>
+        <v>1.79</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AG18" t="n">
         <v>1.3</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.52</v>
+        <v>6.9</v>
       </c>
       <c r="M19" t="n">
-        <v>3.13</v>
+        <v>5</v>
       </c>
       <c r="N19" t="n">
-        <v>2.83</v>
+        <v>1.38</v>
       </c>
       <c r="O19" t="n">
-        <v>3.32</v>
+        <v>7.29</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>2.63</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.19</v>
+        <v>1.85</v>
       </c>
       <c r="R19" t="n">
-        <v>1.51</v>
+        <v>1.22</v>
       </c>
       <c r="S19" t="n">
-        <v>2.39</v>
+        <v>3.75</v>
       </c>
       <c r="T19" t="n">
-        <v>3.28</v>
+        <v>2.23</v>
       </c>
       <c r="U19" t="n">
-        <v>1.29</v>
+        <v>1.68</v>
       </c>
       <c r="V19" t="n">
-        <v>8.1</v>
+        <v>4.5</v>
       </c>
       <c r="W19" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X19" t="n">
         <v>1.02</v>
       </c>
-      <c r="X19" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y19" t="n">
-        <v>1.4</v>
+        <v>1.14</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.81</v>
+        <v>5</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.28</v>
+        <v>1.63</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.55</v>
+        <v>2.25</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.46</v>
+        <v>2.15</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.17</v>
+        <v>1.65</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.91</v>
+        <v>1.76</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.36</v>
+        <v>2.95</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.44</v>
+        <v>1.11</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.29</v>
+        <v>1.43</v>
       </c>
       <c r="M20" t="n">
-        <v>3.39</v>
+        <v>4.6</v>
       </c>
       <c r="N20" t="n">
-        <v>2.95</v>
+        <v>6.6</v>
       </c>
       <c r="O20" t="n">
-        <v>2.8</v>
+        <v>1.83</v>
       </c>
       <c r="P20" t="n">
-        <v>2.14</v>
+        <v>2.63</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.3</v>
+        <v>5.5</v>
       </c>
       <c r="R20" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="S20" t="n">
-        <v>3.15</v>
+        <v>3.85</v>
       </c>
       <c r="T20" t="n">
-        <v>2.6</v>
+        <v>2.21</v>
       </c>
       <c r="U20" t="n">
-        <v>1.47</v>
+        <v>1.67</v>
       </c>
       <c r="V20" t="n">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="W20" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="X20" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.65</v>
+        <v>4.75</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.79</v>
+        <v>1.53</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.62</v>
+        <v>2.75</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M21" t="n">
+        <v>6</v>
+      </c>
+      <c r="N21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q21" t="n">
         <v>6.9</v>
       </c>
-      <c r="M21" t="n">
-        <v>5</v>
-      </c>
-      <c r="N21" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="O21" t="n">
-        <v>7.29</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1.85</v>
-      </c>
       <c r="R21" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="S21" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="T21" t="n">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>1.68</v>
+        <v>1.91</v>
       </c>
       <c r="V21" t="n">
-        <v>4.5</v>
+        <v>3.84</v>
       </c>
       <c r="W21" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG21" t="n">
         <v>1.14</v>
       </c>
-      <c r="Z21" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>2.95</v>
-      </c>
       <c r="AH21" t="n">
-        <v>1.11</v>
+        <v>3.4</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.26</v>
+        <v>2.52</v>
       </c>
       <c r="M23" t="n">
-        <v>6</v>
+        <v>3.13</v>
       </c>
       <c r="N23" t="n">
-        <v>8.800000000000001</v>
+        <v>2.83</v>
       </c>
       <c r="O23" t="n">
-        <v>1.73</v>
+        <v>3.32</v>
       </c>
       <c r="P23" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="n">
-        <v>6.9</v>
+        <v>3.19</v>
       </c>
       <c r="R23" t="n">
-        <v>1.19</v>
+        <v>1.51</v>
       </c>
       <c r="S23" t="n">
-        <v>4.4</v>
+        <v>2.39</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>3.28</v>
       </c>
       <c r="U23" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V23" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE23" t="n">
         <v>1.91</v>
       </c>
-      <c r="V23" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA23" t="n">
+      <c r="AF23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG23" t="n">
         <v>1.36</v>
       </c>
-      <c r="AB23" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AH23" t="n">
-        <v>3.4</v>
+        <v>1.44</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.71</v>
+        <v>2.63</v>
       </c>
       <c r="M24" t="n">
-        <v>3.92</v>
+        <v>3.51</v>
       </c>
       <c r="N24" t="n">
-        <v>4.33</v>
+        <v>2.47</v>
       </c>
       <c r="O24" t="n">
-        <v>2.14</v>
+        <v>3.2</v>
       </c>
       <c r="P24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC24" t="n">
         <v>2.45</v>
       </c>
-      <c r="Q24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="V24" t="n">
-        <v>5</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AD24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE24" t="n">
         <v>1.53</v>
       </c>
-      <c r="AE24" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AF24" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.27</v>
+        <v>1.44</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45987.70833333334</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -1135,16 +1135,16 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="M6" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="O6" t="n">
-        <v>2.65</v>
+        <v>2.77</v>
       </c>
       <c r="P6" t="n">
         <v>1.84</v>
@@ -1174,7 +1174,7 @@
         <v>1.08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Z6" t="n">
         <v>2.59</v>
@@ -1183,7 +1183,7 @@
         <v>2.25</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AC6" t="n">
         <v>3.96</v>
@@ -1198,7 +1198,7 @@
         <v>1.75</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AH6" t="n">
         <v>1.63</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,49 +1611,49 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5.1</v>
+        <v>1.32</v>
       </c>
       <c r="M10" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="N10" t="n">
-        <v>1.6</v>
+        <v>9</v>
       </c>
       <c r="O10" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>7</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V10" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z10" t="n">
         <v>5</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="V10" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4.6</v>
       </c>
       <c r="AA10" t="n">
         <v>1.58</v>
@@ -1662,22 +1662,22 @@
         <v>2.35</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.26</v>
+        <v>1.95</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.37</v>
+        <v>1.18</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.13</v>
+        <v>3.1</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45987.61458333334</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,49 +1730,49 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.32</v>
+        <v>5.1</v>
       </c>
       <c r="M11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O11" t="n">
         <v>5</v>
       </c>
-      <c r="N11" t="n">
-        <v>9</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.74</v>
-      </c>
       <c r="P11" t="n">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="Q11" t="n">
-        <v>7</v>
+        <v>2.06</v>
       </c>
       <c r="R11" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="S11" t="n">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="T11" t="n">
-        <v>2.28</v>
+        <v>2.43</v>
       </c>
       <c r="U11" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="V11" t="n">
-        <v>4.95</v>
+        <v>5.2</v>
       </c>
       <c r="W11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y11" t="n">
         <v>1.15</v>
       </c>
-      <c r="X11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.18</v>
-      </c>
       <c r="Z11" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AA11" t="n">
         <v>1.58</v>
@@ -1781,22 +1781,22 @@
         <v>2.35</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.95</v>
+        <v>2.26</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.18</v>
+        <v>2.37</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.1</v>
+        <v>1.13</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45987.61458333334</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.07</v>
+        <v>1.61</v>
       </c>
       <c r="M14" t="n">
-        <v>3.35</v>
+        <v>3.63</v>
       </c>
       <c r="N14" t="n">
-        <v>3.45</v>
+        <v>5.8</v>
       </c>
       <c r="O14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>5</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="T14" t="n">
         <v>2.8</v>
       </c>
-      <c r="P14" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.95</v>
-      </c>
       <c r="U14" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="V14" t="n">
-        <v>6.95</v>
+        <v>7</v>
       </c>
       <c r="W14" t="n">
         <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
         <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.99</v>
+        <v>3.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AG14" t="n">
         <v>1.25</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.71</v>
+        <v>2.15</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,49 +2206,49 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.44</v>
+        <v>2.07</v>
       </c>
       <c r="M15" t="n">
-        <v>3.31</v>
+        <v>3.35</v>
       </c>
       <c r="N15" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O15" t="n">
         <v>2.8</v>
       </c>
-      <c r="O15" t="n">
-        <v>3.05</v>
-      </c>
       <c r="P15" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="R15" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
         <v>2.65</v>
       </c>
       <c r="T15" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="U15" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V15" t="n">
-        <v>7.3</v>
+        <v>6.95</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.3</v>
+        <v>2.99</v>
       </c>
       <c r="AA15" t="n">
         <v>1.98</v>
@@ -2260,19 +2260,19 @@
         <v>3.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AF15" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.61</v>
+        <v>2.44</v>
       </c>
       <c r="M16" t="n">
-        <v>3.63</v>
+        <v>3.31</v>
       </c>
       <c r="N16" t="n">
-        <v>5.8</v>
+        <v>2.8</v>
       </c>
       <c r="O16" t="n">
-        <v>2.15</v>
+        <v>3.05</v>
       </c>
       <c r="P16" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="Q16" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S16" t="n">
-        <v>2.98</v>
+        <v>2.65</v>
       </c>
       <c r="T16" t="n">
-        <v>2.8</v>
+        <v>2.93</v>
       </c>
       <c r="U16" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="V16" t="n">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z16" t="n">
         <v>3.3</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.15</v>
+        <v>1.53</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.71</v>
+        <v>1.43</v>
       </c>
       <c r="M17" t="n">
-        <v>3.92</v>
+        <v>4.6</v>
       </c>
       <c r="N17" t="n">
-        <v>4.33</v>
+        <v>6.6</v>
       </c>
       <c r="O17" t="n">
-        <v>2.14</v>
+        <v>1.83</v>
       </c>
       <c r="P17" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB17" t="n">
         <v>2.45</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="V17" t="n">
-        <v>5</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.2</v>
       </c>
       <c r="AC17" t="n">
         <v>2.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.32</v>
+        <v>2.19</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.27</v>
+        <v>2.75</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.29</v>
+        <v>2.52</v>
       </c>
       <c r="M18" t="n">
-        <v>3.39</v>
+        <v>3.13</v>
       </c>
       <c r="N18" t="n">
-        <v>2.95</v>
+        <v>2.83</v>
       </c>
       <c r="O18" t="n">
-        <v>2.8</v>
+        <v>3.32</v>
       </c>
       <c r="P18" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.3</v>
+        <v>3.19</v>
       </c>
       <c r="R18" t="n">
-        <v>1.35</v>
+        <v>1.51</v>
       </c>
       <c r="S18" t="n">
-        <v>3.15</v>
+        <v>2.39</v>
       </c>
       <c r="T18" t="n">
-        <v>2.6</v>
+        <v>3.28</v>
       </c>
       <c r="U18" t="n">
-        <v>1.47</v>
+        <v>1.29</v>
       </c>
       <c r="V18" t="n">
-        <v>6.2</v>
+        <v>8.1</v>
       </c>
       <c r="W18" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="X18" t="n">
         <v>1.05</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.65</v>
+        <v>2.81</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.79</v>
+        <v>2.28</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.95</v>
+        <v>1.55</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.88</v>
+        <v>4.46</v>
       </c>
       <c r="AD18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG18" t="n">
         <v>1.36</v>
       </c>
-      <c r="AE18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH18" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>6.9</v>
+        <v>2.07</v>
       </c>
       <c r="M19" t="n">
-        <v>5</v>
+        <v>3.56</v>
       </c>
       <c r="N19" t="n">
-        <v>1.38</v>
+        <v>3.27</v>
       </c>
       <c r="O19" t="n">
-        <v>7.29</v>
+        <v>2.5</v>
       </c>
       <c r="P19" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.85</v>
+        <v>3.7</v>
       </c>
       <c r="R19" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="S19" t="n">
-        <v>3.75</v>
+        <v>3.18</v>
       </c>
       <c r="T19" t="n">
-        <v>2.23</v>
+        <v>2.54</v>
       </c>
       <c r="U19" t="n">
-        <v>1.68</v>
+        <v>1.51</v>
       </c>
       <c r="V19" t="n">
-        <v>4.5</v>
+        <v>5.75</v>
       </c>
       <c r="W19" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="X19" t="n">
         <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="Z19" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AD19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH19" t="n">
         <v>1.65</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.11</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.43</v>
+        <v>1.71</v>
       </c>
       <c r="M20" t="n">
-        <v>4.6</v>
+        <v>3.92</v>
       </c>
       <c r="N20" t="n">
-        <v>6.6</v>
+        <v>4.33</v>
       </c>
       <c r="O20" t="n">
-        <v>1.83</v>
+        <v>2.14</v>
       </c>
       <c r="P20" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="R20" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S20" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="T20" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="U20" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="V20" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="AC20" t="n">
         <v>2.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.19</v>
+        <v>2.32</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.75</v>
+        <v>2.27</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,61 +2920,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.26</v>
+        <v>2.63</v>
       </c>
       <c r="M21" t="n">
-        <v>6</v>
+        <v>3.51</v>
       </c>
       <c r="N21" t="n">
-        <v>8.800000000000001</v>
+        <v>2.47</v>
       </c>
       <c r="O21" t="n">
-        <v>1.73</v>
+        <v>3.2</v>
       </c>
       <c r="P21" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>6.9</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="S21" t="n">
-        <v>4.4</v>
+        <v>3.36</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="U21" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="V21" t="n">
-        <v>3.84</v>
+        <v>5.5</v>
       </c>
       <c r="W21" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.05</v>
+        <v>1.19</v>
       </c>
       <c r="Z21" t="n">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="AB21" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.76</v>
+        <v>2.45</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="AE21" t="n">
         <v>1.53</v>
@@ -2983,10 +2983,10 @@
         <v>2.4</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AH21" t="n">
-        <v>3.4</v>
+        <v>1.44</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.07</v>
+        <v>6.9</v>
       </c>
       <c r="M22" t="n">
-        <v>3.56</v>
+        <v>5</v>
       </c>
       <c r="N22" t="n">
-        <v>3.27</v>
+        <v>1.38</v>
       </c>
       <c r="O22" t="n">
-        <v>2.5</v>
+        <v>7.29</v>
       </c>
       <c r="P22" t="n">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.7</v>
+        <v>1.85</v>
       </c>
       <c r="R22" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="S22" t="n">
-        <v>3.18</v>
+        <v>3.75</v>
       </c>
       <c r="T22" t="n">
-        <v>2.54</v>
+        <v>2.23</v>
       </c>
       <c r="U22" t="n">
-        <v>1.51</v>
+        <v>1.68</v>
       </c>
       <c r="V22" t="n">
-        <v>5.75</v>
+        <v>4.5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="X22" t="n">
         <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AB22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF22" t="n">
         <v>2.05</v>
       </c>
-      <c r="AC22" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AG22" t="n">
-        <v>1.3</v>
+        <v>2.95</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.65</v>
+        <v>1.11</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.52</v>
+        <v>1.26</v>
       </c>
       <c r="M23" t="n">
-        <v>3.13</v>
+        <v>6</v>
       </c>
       <c r="N23" t="n">
-        <v>2.83</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O23" t="n">
-        <v>3.32</v>
+        <v>1.73</v>
       </c>
       <c r="P23" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T23" t="n">
         <v>2</v>
       </c>
-      <c r="Q23" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3.28</v>
-      </c>
       <c r="U23" t="n">
-        <v>1.29</v>
+        <v>1.91</v>
       </c>
       <c r="V23" t="n">
-        <v>8.1</v>
+        <v>3.84</v>
       </c>
       <c r="W23" t="n">
-        <v>1.02</v>
+        <v>1.24</v>
       </c>
       <c r="X23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y23" t="n">
         <v>1.05</v>
       </c>
-      <c r="Y23" t="n">
-        <v>1.4</v>
-      </c>
       <c r="Z23" t="n">
-        <v>2.81</v>
+        <v>7.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.28</v>
+        <v>1.36</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.55</v>
+        <v>3.1</v>
       </c>
       <c r="AC23" t="n">
-        <v>4.46</v>
+        <v>1.76</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.17</v>
+        <v>1.95</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.44</v>
+        <v>3.4</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.63</v>
+        <v>2.29</v>
       </c>
       <c r="M24" t="n">
-        <v>3.51</v>
+        <v>3.39</v>
       </c>
       <c r="N24" t="n">
-        <v>2.47</v>
+        <v>2.95</v>
       </c>
       <c r="O24" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="P24" t="n">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="Q24" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="R24" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="S24" t="n">
-        <v>3.36</v>
+        <v>3.15</v>
       </c>
       <c r="T24" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="U24" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="V24" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="W24" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.5</v>
+        <v>3.65</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.63</v>
+        <v>1.79</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AG24" t="n">
         <v>1.3</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45987.70833333334</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="M6" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="N6" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O6" t="n">
         <v>2.77</v>
@@ -1183,7 +1183,7 @@
         <v>2.25</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AC6" t="n">
         <v>3.96</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="N8" t="n">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="O8" t="n">
-        <v>5</v>
+        <v>4.56</v>
       </c>
       <c r="P8" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="S8" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="T8" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="U8" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="V8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W8" t="n">
         <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.25</v>
+        <v>5.35</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45987.60416666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,67 +1492,67 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="M9" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="N9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="O9" t="n">
+        <v>5</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S9" t="n">
         <v>2.3</v>
       </c>
-      <c r="O9" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.15</v>
-      </c>
       <c r="T9" t="n">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="U9" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="V9" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="W9" t="n">
         <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="AB9" t="n">
         <v>1.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG9" t="n">
         <v>1.4</v>
@@ -1620,7 +1620,7 @@
         <v>9</v>
       </c>
       <c r="O10" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="P10" t="n">
         <v>2.62</v>
@@ -1632,16 +1632,16 @@
         <v>1.27</v>
       </c>
       <c r="S10" t="n">
-        <v>3.58</v>
+        <v>3.85</v>
       </c>
       <c r="T10" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="U10" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="V10" t="n">
-        <v>4.95</v>
+        <v>4.9</v>
       </c>
       <c r="W10" t="n">
         <v>1.15</v>
@@ -1650,7 +1650,7 @@
         <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z10" t="n">
         <v>5</v>
@@ -1671,13 +1671,13 @@
         <v>1.83</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AG10" t="n">
         <v>1.18</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45987.61458333334</v>
@@ -1742,7 +1742,7 @@
         <v>5</v>
       </c>
       <c r="P11" t="n">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="Q11" t="n">
         <v>2.06</v>
@@ -1754,13 +1754,13 @@
         <v>3.42</v>
       </c>
       <c r="T11" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="U11" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="V11" t="n">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="W11" t="n">
         <v>1.13</v>
@@ -1772,7 +1772,7 @@
         <v>1.15</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AA11" t="n">
         <v>1.58</v>
@@ -1787,16 +1787,16 @@
         <v>1.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.26</v>
+        <v>2.12</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45987.61458333334</v>
@@ -1858,40 +1858,40 @@
         <v>3.2</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA12" t="n">
         <v>1.65</v>
@@ -1900,22 +1900,22 @@
         <v>2.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45987.625</v>
@@ -1977,13 +1977,13 @@
         <v>4.4</v>
       </c>
       <c r="O13" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="P13" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.27</v>
+        <v>4.6</v>
       </c>
       <c r="R13" t="n">
         <v>1.42</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.61</v>
+        <v>2.07</v>
       </c>
       <c r="M14" t="n">
-        <v>3.63</v>
+        <v>3.35</v>
       </c>
       <c r="N14" t="n">
-        <v>5.8</v>
+        <v>3.45</v>
       </c>
       <c r="O14" t="n">
-        <v>2.15</v>
+        <v>2.58</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="Q14" t="n">
-        <v>5</v>
+        <v>3.85</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S14" t="n">
-        <v>2.98</v>
+        <v>2.65</v>
       </c>
       <c r="T14" t="n">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="U14" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>7</v>
+        <v>6.95</v>
       </c>
       <c r="W14" t="n">
         <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
         <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.15</v>
+        <v>1.71</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.07</v>
+        <v>1.61</v>
       </c>
       <c r="M15" t="n">
-        <v>3.35</v>
+        <v>3.63</v>
       </c>
       <c r="N15" t="n">
-        <v>3.45</v>
+        <v>5.8</v>
       </c>
       <c r="O15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>5</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T15" t="n">
         <v>2.8</v>
       </c>
-      <c r="P15" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.95</v>
-      </c>
       <c r="U15" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="V15" t="n">
-        <v>6.95</v>
+        <v>7</v>
       </c>
       <c r="W15" t="n">
         <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
         <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.99</v>
+        <v>3.49</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AG15" t="n">
         <v>1.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.71</v>
+        <v>2.15</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2334,7 +2334,7 @@
         <v>2.8</v>
       </c>
       <c r="O16" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="P16" t="n">
         <v>2.14</v>
@@ -2343,19 +2343,19 @@
         <v>3.4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="S16" t="n">
         <v>2.65</v>
       </c>
       <c r="T16" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="U16" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V16" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="W16" t="n">
         <v>1.03</v>
@@ -2376,13 +2376,13 @@
         <v>1.77</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="AD16" t="n">
         <v>1.29</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AF16" t="n">
         <v>2</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,55 +2444,55 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.43</v>
+        <v>2.07</v>
       </c>
       <c r="M17" t="n">
-        <v>4.6</v>
+        <v>3.56</v>
       </c>
       <c r="N17" t="n">
-        <v>6.6</v>
+        <v>3.27</v>
       </c>
       <c r="O17" t="n">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="P17" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.5</v>
+        <v>3.7</v>
       </c>
       <c r="R17" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="S17" t="n">
-        <v>3.85</v>
+        <v>3.18</v>
       </c>
       <c r="T17" t="n">
-        <v>2.21</v>
+        <v>2.54</v>
       </c>
       <c r="U17" t="n">
-        <v>1.67</v>
+        <v>1.51</v>
       </c>
       <c r="V17" t="n">
-        <v>4.7</v>
+        <v>5.75</v>
       </c>
       <c r="W17" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="X17" t="n">
         <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.75</v>
+        <v>3.9</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.53</v>
+        <v>1.79</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.45</v>
+        <v>1.91</v>
       </c>
       <c r="AC17" t="n">
         <v>2.3</v>
@@ -2501,16 +2501,16 @@
         <v>1.6</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.75</v>
+        <v>1.65</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.52</v>
+        <v>1.43</v>
       </c>
       <c r="M18" t="n">
-        <v>3.13</v>
+        <v>4.6</v>
       </c>
       <c r="N18" t="n">
-        <v>2.83</v>
+        <v>6.6</v>
       </c>
       <c r="O18" t="n">
-        <v>3.32</v>
+        <v>1.83</v>
       </c>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>2.63</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.19</v>
+        <v>5.5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.51</v>
+        <v>1.26</v>
       </c>
       <c r="S18" t="n">
-        <v>2.39</v>
+        <v>3.66</v>
       </c>
       <c r="T18" t="n">
-        <v>3.28</v>
+        <v>2.22</v>
       </c>
       <c r="U18" t="n">
-        <v>1.29</v>
+        <v>1.68</v>
       </c>
       <c r="V18" t="n">
-        <v>8.1</v>
+        <v>4.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="X18" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.4</v>
+        <v>1.12</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.81</v>
+        <v>4.8</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.28</v>
+        <v>1.53</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.55</v>
+        <v>2.45</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.46</v>
+        <v>2.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.17</v>
+        <v>1.6</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.8</v>
+        <v>2.18</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.44</v>
+        <v>2.92</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.07</v>
+        <v>1.71</v>
       </c>
       <c r="M19" t="n">
-        <v>3.56</v>
+        <v>3.92</v>
       </c>
       <c r="N19" t="n">
-        <v>3.27</v>
+        <v>4.33</v>
       </c>
       <c r="O19" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="P19" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="R19" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="S19" t="n">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="T19" t="n">
-        <v>2.54</v>
+        <v>2.3</v>
       </c>
       <c r="U19" t="n">
-        <v>1.51</v>
+        <v>1.64</v>
       </c>
       <c r="V19" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.9</v>
+        <v>4.55</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AC19" t="n">
         <v>2.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.71</v>
+        <v>2.29</v>
       </c>
       <c r="M20" t="n">
-        <v>3.92</v>
+        <v>3.39</v>
       </c>
       <c r="N20" t="n">
-        <v>4.33</v>
+        <v>2.95</v>
       </c>
       <c r="O20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P20" t="n">
         <v>2.14</v>
       </c>
-      <c r="P20" t="n">
-        <v>2.45</v>
-      </c>
       <c r="Q20" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="R20" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="S20" t="n">
-        <v>3.5</v>
+        <v>3.02</v>
       </c>
       <c r="T20" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="U20" t="n">
-        <v>1.64</v>
+        <v>1.47</v>
       </c>
       <c r="V20" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="X20" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="Z20" t="n">
-        <v>5</v>
+        <v>3.65</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.27</v>
+        <v>1.62</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,49 +2920,49 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.63</v>
+        <v>6.9</v>
       </c>
       <c r="M21" t="n">
-        <v>3.51</v>
+        <v>5</v>
       </c>
       <c r="N21" t="n">
-        <v>2.47</v>
+        <v>1.38</v>
       </c>
       <c r="O21" t="n">
-        <v>3.2</v>
+        <v>5.03</v>
       </c>
       <c r="P21" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="Q21" t="n">
-        <v>3</v>
+        <v>1.82</v>
       </c>
       <c r="R21" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="S21" t="n">
-        <v>3.36</v>
+        <v>3.75</v>
       </c>
       <c r="T21" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="U21" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="V21" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="W21" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.5</v>
+        <v>4.95</v>
       </c>
       <c r="AA21" t="n">
         <v>1.63</v>
@@ -2971,22 +2971,22 @@
         <v>2.25</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.4</v>
+        <v>2.02</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.3</v>
+        <v>2.95</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.44</v>
+        <v>1.11</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,49 +3039,49 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>6.9</v>
+        <v>2.63</v>
       </c>
       <c r="M22" t="n">
-        <v>5</v>
+        <v>3.51</v>
       </c>
       <c r="N22" t="n">
-        <v>1.38</v>
+        <v>2.47</v>
       </c>
       <c r="O22" t="n">
-        <v>7.29</v>
+        <v>2.97</v>
       </c>
       <c r="P22" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.85</v>
+        <v>3</v>
       </c>
       <c r="R22" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="S22" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="T22" t="n">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="U22" t="n">
-        <v>1.68</v>
+        <v>1.54</v>
       </c>
       <c r="V22" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z22" t="n">
         <v>4.5</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>5</v>
       </c>
       <c r="AA22" t="n">
         <v>1.63</v>
@@ -3090,22 +3090,22 @@
         <v>2.25</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.76</v>
+        <v>1.48</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.95</v>
+        <v>1.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.11</v>
+        <v>1.44</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3167,7 +3167,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="O23" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="P23" t="n">
         <v>2.9</v>
@@ -3176,16 +3176,16 @@
         <v>6.9</v>
       </c>
       <c r="R23" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="S23" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T23" t="n">
         <v>2</v>
       </c>
       <c r="U23" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="V23" t="n">
         <v>3.84</v>
@@ -3215,13 +3215,13 @@
         <v>1.95</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AF23" t="n">
         <v>2.4</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AH23" t="n">
         <v>3.4</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.29</v>
+        <v>2.52</v>
       </c>
       <c r="M24" t="n">
-        <v>3.39</v>
+        <v>3.13</v>
       </c>
       <c r="N24" t="n">
-        <v>2.95</v>
+        <v>2.83</v>
       </c>
       <c r="O24" t="n">
-        <v>2.8</v>
+        <v>3.34</v>
       </c>
       <c r="P24" t="n">
-        <v>2.14</v>
+        <v>1.91</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.35</v>
+        <v>1.51</v>
       </c>
       <c r="S24" t="n">
-        <v>3.15</v>
+        <v>2.39</v>
       </c>
       <c r="T24" t="n">
-        <v>2.6</v>
+        <v>3.28</v>
       </c>
       <c r="U24" t="n">
-        <v>1.47</v>
+        <v>1.29</v>
       </c>
       <c r="V24" t="n">
-        <v>6.2</v>
+        <v>8.1</v>
       </c>
       <c r="W24" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="X24" t="n">
         <v>1.05</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.24</v>
+        <v>1.39</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.65</v>
+        <v>2.81</v>
       </c>
       <c r="AA24" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AF24" t="n">
         <v>1.79</v>
       </c>
-      <c r="AB24" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD24" t="n">
+      <c r="AG24" t="n">
         <v>1.36</v>
       </c>
-      <c r="AE24" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH24" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3411,19 +3411,19 @@
         <v>2.2</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.92</v>
+        <v>3.8</v>
       </c>
       <c r="R25" t="n">
         <v>1.38</v>
       </c>
       <c r="S25" t="n">
-        <v>2.81</v>
+        <v>3.08</v>
       </c>
       <c r="T25" t="n">
         <v>2.8</v>
       </c>
       <c r="U25" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="V25" t="n">
         <v>6.25</v>
@@ -3432,13 +3432,13 @@
         <v>1.06</v>
       </c>
       <c r="X25" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y25" t="n">
         <v>1.25</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.5</v>
+        <v>3.64</v>
       </c>
       <c r="AA25" t="n">
         <v>1.85</v>
@@ -3453,10 +3453,10 @@
         <v>1.3</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AF25" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AG25" t="n">
         <v>1.3</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,49 +1611,49 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.32</v>
+        <v>5.1</v>
       </c>
       <c r="M10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O10" t="n">
         <v>5</v>
       </c>
-      <c r="N10" t="n">
-        <v>9</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.78</v>
-      </c>
       <c r="P10" t="n">
-        <v>2.62</v>
+        <v>2.32</v>
       </c>
       <c r="Q10" t="n">
-        <v>7</v>
+        <v>2.06</v>
       </c>
       <c r="R10" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>3.85</v>
+        <v>3.42</v>
       </c>
       <c r="T10" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="U10" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="V10" t="n">
-        <v>4.9</v>
+        <v>5.25</v>
       </c>
       <c r="W10" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y10" t="n">
         <v>1.15</v>
       </c>
-      <c r="X10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.17</v>
-      </c>
       <c r="Z10" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="AA10" t="n">
         <v>1.58</v>
@@ -1662,22 +1662,22 @@
         <v>2.35</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.83</v>
+        <v>1.64</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.94</v>
+        <v>2.12</v>
       </c>
       <c r="AG10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH10" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>3.2</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45987.61458333334</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,49 +1730,49 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>5.1</v>
+        <v>1.32</v>
       </c>
       <c r="M11" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="N11" t="n">
-        <v>1.6</v>
+        <v>9</v>
       </c>
       <c r="O11" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>7</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="V11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z11" t="n">
         <v>5</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V11" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4.3</v>
       </c>
       <c r="AA11" t="n">
         <v>1.58</v>
@@ -1781,22 +1781,22 @@
         <v>2.35</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.12</v>
+        <v>1.94</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.25</v>
+        <v>1.18</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.18</v>
+        <v>3.2</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45987.61458333334</v>
@@ -1849,28 +1849,28 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="M12" t="n">
-        <v>3.36</v>
+        <v>3.62</v>
       </c>
       <c r="N12" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O12" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="P12" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.5</v>
+        <v>4.04</v>
       </c>
       <c r="R12" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S12" t="n">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="T12" t="n">
         <v>2.3</v>
@@ -1879,7 +1879,7 @@
         <v>1.55</v>
       </c>
       <c r="V12" t="n">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="W12" t="n">
         <v>1.11</v>
@@ -1888,19 +1888,19 @@
         <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z12" t="n">
         <v>4.6</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AD12" t="n">
         <v>1.5</v>
@@ -1909,13 +1909,13 @@
         <v>1.53</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45987.625</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.43</v>
+        <v>2.29</v>
       </c>
       <c r="M18" t="n">
-        <v>4.6</v>
+        <v>3.39</v>
       </c>
       <c r="N18" t="n">
-        <v>6.6</v>
+        <v>2.95</v>
       </c>
       <c r="O18" t="n">
-        <v>1.83</v>
+        <v>2.8</v>
       </c>
       <c r="P18" t="n">
-        <v>2.63</v>
+        <v>2.14</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.5</v>
+        <v>3.3</v>
       </c>
       <c r="R18" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="S18" t="n">
-        <v>3.66</v>
+        <v>3.02</v>
       </c>
       <c r="T18" t="n">
-        <v>2.22</v>
+        <v>2.6</v>
       </c>
       <c r="U18" t="n">
-        <v>1.68</v>
+        <v>1.47</v>
       </c>
       <c r="V18" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.8</v>
+        <v>3.65</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.53</v>
+        <v>1.79</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.18</v>
+        <v>2.27</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.92</v>
+        <v>1.62</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.71</v>
+        <v>2.63</v>
       </c>
       <c r="M19" t="n">
-        <v>3.92</v>
+        <v>3.51</v>
       </c>
       <c r="N19" t="n">
-        <v>4.33</v>
+        <v>2.47</v>
       </c>
       <c r="O19" t="n">
-        <v>2.14</v>
+        <v>2.97</v>
       </c>
       <c r="P19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="V19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC19" t="n">
         <v>2.45</v>
       </c>
-      <c r="Q19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="V19" t="n">
-        <v>5</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AD19" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.29</v>
+        <v>6.9</v>
       </c>
       <c r="M20" t="n">
-        <v>3.39</v>
+        <v>5</v>
       </c>
       <c r="N20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="O20" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AG20" t="n">
         <v>2.95</v>
       </c>
-      <c r="O20" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V20" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH20" t="n">
-        <v>1.62</v>
+        <v>1.11</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>6.9</v>
+        <v>1.43</v>
       </c>
       <c r="M21" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="N21" t="n">
-        <v>1.38</v>
+        <v>6.6</v>
       </c>
       <c r="O21" t="n">
-        <v>5.03</v>
+        <v>1.83</v>
       </c>
       <c r="P21" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.82</v>
+        <v>5.5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="S21" t="n">
-        <v>3.75</v>
+        <v>3.66</v>
       </c>
       <c r="T21" t="n">
-        <v>2.33</v>
+        <v>2.22</v>
       </c>
       <c r="U21" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="V21" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="W21" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X21" t="n">
         <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.95</v>
+        <v>4.8</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.95</v>
+        <v>1.2</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.11</v>
+        <v>2.92</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.63</v>
+        <v>1.26</v>
       </c>
       <c r="M22" t="n">
-        <v>3.51</v>
+        <v>6</v>
       </c>
       <c r="N22" t="n">
-        <v>2.47</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>2.97</v>
+        <v>1.68</v>
       </c>
       <c r="P22" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="Q22" t="n">
-        <v>3</v>
+        <v>6.9</v>
       </c>
       <c r="R22" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="S22" t="n">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="T22" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
-        <v>1.54</v>
+        <v>1.89</v>
       </c>
       <c r="V22" t="n">
-        <v>5.5</v>
+        <v>3.84</v>
       </c>
       <c r="W22" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="X22" t="n">
         <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.19</v>
+        <v>1.05</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.63</v>
+        <v>1.36</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.45</v>
+        <v>1.76</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.55</v>
+        <v>1.95</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="AF22" t="n">
         <v>2.4</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.44</v>
+        <v>3.4</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.26</v>
+        <v>1.71</v>
       </c>
       <c r="M23" t="n">
-        <v>6</v>
+        <v>3.92</v>
       </c>
       <c r="N23" t="n">
-        <v>8.800000000000001</v>
+        <v>4.33</v>
       </c>
       <c r="O23" t="n">
-        <v>1.68</v>
+        <v>2.14</v>
       </c>
       <c r="P23" t="n">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="Q23" t="n">
-        <v>6.9</v>
+        <v>4.2</v>
       </c>
       <c r="R23" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="S23" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="U23" t="n">
-        <v>1.89</v>
+        <v>1.64</v>
       </c>
       <c r="V23" t="n">
-        <v>3.84</v>
+        <v>5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="Z23" t="n">
-        <v>7.5</v>
+        <v>4.55</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="AB23" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.76</v>
+        <v>2.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="AH23" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45987.70833333334</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -1135,22 +1135,22 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="M6" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>3.91</v>
       </c>
       <c r="O6" t="n">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="P6" t="n">
         <v>1.84</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="R6" t="n">
         <v>1.52</v>
@@ -1174,22 +1174,22 @@
         <v>1.08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.96</v>
+        <v>4.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE6" t="n">
         <v>1.95</v>
@@ -1198,10 +1198,10 @@
         <v>1.75</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45987.45833333334</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="M8" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="O8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q8" t="n">
         <v>2.75</v>
       </c>
-      <c r="N8" t="n">
+      <c r="R8" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="S8" t="n">
         <v>2.3</v>
       </c>
-      <c r="O8" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.16</v>
-      </c>
       <c r="T8" t="n">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
       <c r="U8" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="V8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W8" t="n">
         <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.35</v>
+        <v>5.3</v>
       </c>
       <c r="AD8" t="n">
         <v>1.13</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45987.60416666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="N9" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="O9" t="n">
-        <v>5</v>
+        <v>4.56</v>
       </c>
       <c r="P9" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="R9" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="S9" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="T9" t="n">
-        <v>3.7</v>
+        <v>3.76</v>
       </c>
       <c r="U9" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="V9" t="n">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
         <v>1.08</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG9" t="n">
         <v>1.4</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45987.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5.1</v>
+        <v>1.34</v>
       </c>
       <c r="M10" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="N10" t="n">
-        <v>1.6</v>
+        <v>8.6</v>
       </c>
       <c r="O10" t="n">
-        <v>5</v>
+        <v>1.79</v>
       </c>
       <c r="P10" t="n">
-        <v>2.32</v>
+        <v>2.62</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.06</v>
+        <v>7</v>
       </c>
       <c r="R10" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S10" t="n">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="T10" t="n">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="U10" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="V10" t="n">
-        <v>5.25</v>
+        <v>4.95</v>
       </c>
       <c r="W10" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="X10" t="n">
         <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.25</v>
+        <v>1.18</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.18</v>
+        <v>3.57</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45987.61458333334</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
+        <v>5</v>
+      </c>
+      <c r="M11" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O11" t="n">
+        <v>5</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="R11" t="n">
         <v>1.32</v>
       </c>
-      <c r="M11" t="n">
-        <v>5</v>
-      </c>
-      <c r="N11" t="n">
-        <v>9</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>7</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.27</v>
-      </c>
       <c r="S11" t="n">
-        <v>3.85</v>
+        <v>3.36</v>
       </c>
       <c r="T11" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="U11" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="V11" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="W11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y11" t="n">
         <v>1.15</v>
       </c>
-      <c r="X11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.17</v>
-      </c>
       <c r="Z11" t="n">
-        <v>5</v>
+        <v>4.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.94</v>
+        <v>2.25</v>
       </c>
       <c r="AG11" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>3.2</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45987.61458333334</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="M13" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="N13" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="O13" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="P13" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="S13" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="T13" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="U13" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="V13" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="W13" t="n">
         <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
         <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.2</v>
+        <v>3.49</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG13" t="n">
         <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.07</v>
+        <v>1.77</v>
       </c>
       <c r="M14" t="n">
-        <v>3.35</v>
+        <v>3.56</v>
       </c>
       <c r="N14" t="n">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="O14" t="n">
-        <v>2.58</v>
+        <v>2.42</v>
       </c>
       <c r="P14" t="n">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.85</v>
+        <v>4.55</v>
       </c>
       <c r="R14" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="T14" t="n">
-        <v>2.95</v>
+        <v>3.07</v>
       </c>
       <c r="U14" t="n">
         <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>6.95</v>
+        <v>6.8</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y14" t="n">
         <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.77</v>
+        <v>1.89</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.71</v>
+        <v>2.04</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.61</v>
+        <v>2.18</v>
       </c>
       <c r="M15" t="n">
-        <v>3.63</v>
+        <v>3.35</v>
       </c>
       <c r="N15" t="n">
-        <v>5.8</v>
+        <v>3.24</v>
       </c>
       <c r="O15" t="n">
-        <v>2.15</v>
+        <v>2.58</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="Q15" t="n">
-        <v>5</v>
+        <v>3.85</v>
       </c>
       <c r="R15" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="T15" t="n">
         <v>2.8</v>
       </c>
       <c r="U15" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="V15" t="n">
-        <v>7</v>
+        <v>6.95</v>
       </c>
       <c r="W15" t="n">
         <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.49</v>
+        <v>3.25</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.87</v>
+        <v>2.03</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2325,31 +2325,31 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="M16" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="N16" t="n">
         <v>2.8</v>
       </c>
       <c r="O16" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="R16" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S16" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="T16" t="n">
-        <v>2.9</v>
+        <v>3.01</v>
       </c>
       <c r="U16" t="n">
         <v>1.36</v>
@@ -2358,7 +2358,7 @@
         <v>7.2</v>
       </c>
       <c r="W16" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
         <v>1.06</v>
@@ -2367,31 +2367,31 @@
         <v>1.28</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.45</v>
+        <v>3.58</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AF16" t="n">
         <v>2</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.07</v>
+        <v>2.65</v>
       </c>
       <c r="M17" t="n">
-        <v>3.56</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>3.27</v>
+        <v>2.7</v>
       </c>
       <c r="O17" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="P17" t="n">
-        <v>2.38</v>
+        <v>1.99</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="R17" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U17" t="n">
         <v>1.28</v>
       </c>
-      <c r="S17" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.51</v>
-      </c>
       <c r="V17" t="n">
-        <v>5.75</v>
+        <v>8</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.9</v>
+        <v>2.61</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.79</v>
+        <v>2.35</v>
       </c>
       <c r="AB17" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE17" t="n">
         <v>1.91</v>
       </c>
-      <c r="AC17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AF17" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="M18" t="n">
-        <v>3.39</v>
+        <v>3.55</v>
       </c>
       <c r="N18" t="n">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="O18" t="n">
         <v>2.8</v>
@@ -2578,7 +2578,7 @@
         <v>2.14</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="R18" t="n">
         <v>1.35</v>
@@ -2587,10 +2587,10 @@
         <v>3.02</v>
       </c>
       <c r="T18" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="U18" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="V18" t="n">
         <v>6.5</v>
@@ -2602,13 +2602,13 @@
         <v>1.05</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AB18" t="n">
         <v>1.95</v>
@@ -2626,10 +2626,10 @@
         <v>2.27</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M19" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="N19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P19" t="n">
         <v>2.63</v>
       </c>
-      <c r="M19" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="N19" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="O19" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.4</v>
-      </c>
       <c r="Q19" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S19" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="T19" t="n">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="U19" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="V19" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="W19" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y19" t="n">
         <v>1.12</v>
       </c>
-      <c r="X19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.19</v>
-      </c>
       <c r="Z19" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AB19" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AC19" t="n">
         <v>2.25</v>
       </c>
-      <c r="AC19" t="n">
-        <v>2.45</v>
-      </c>
       <c r="AD19" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.4</v>
+        <v>2.16</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.44</v>
+        <v>2.75</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>6.9</v>
+        <v>1.68</v>
       </c>
       <c r="M20" t="n">
+        <v>4</v>
+      </c>
+      <c r="N20" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V20" t="n">
         <v>5</v>
       </c>
-      <c r="N20" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="O20" t="n">
-        <v>5.03</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="R20" t="n">
+      <c r="W20" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AG20" t="n">
         <v>1.22</v>
       </c>
-      <c r="S20" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V20" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>2.95</v>
-      </c>
       <c r="AH20" t="n">
-        <v>1.11</v>
+        <v>2.27</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.43</v>
+        <v>2.42</v>
       </c>
       <c r="M21" t="n">
-        <v>4.6</v>
+        <v>3.35</v>
       </c>
       <c r="N21" t="n">
-        <v>6.6</v>
+        <v>2.6</v>
       </c>
       <c r="O21" t="n">
-        <v>1.83</v>
+        <v>3.2</v>
       </c>
       <c r="P21" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="Q21" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V21" t="n">
         <v>5.5</v>
       </c>
-      <c r="R21" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="V21" t="n">
+      <c r="W21" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z21" t="n">
         <v>4.5</v>
       </c>
-      <c r="W21" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>4.8</v>
-      </c>
       <c r="AA21" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AB21" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC21" t="n">
         <v>2.45</v>
       </c>
-      <c r="AC21" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AD21" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.7</v>
+        <v>1.51</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.18</v>
+        <v>2.64</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.92</v>
+        <v>1.44</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.26</v>
+        <v>2.2</v>
       </c>
       <c r="M22" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="N22" t="n">
-        <v>8.800000000000001</v>
+        <v>3.2</v>
       </c>
       <c r="O22" t="n">
-        <v>1.68</v>
+        <v>2.5</v>
       </c>
       <c r="P22" t="n">
-        <v>2.9</v>
+        <v>2.38</v>
       </c>
       <c r="Q22" t="n">
-        <v>6.9</v>
+        <v>3.7</v>
       </c>
       <c r="R22" t="n">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="S22" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="T22" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V22" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AB22" t="n">
         <v>2</v>
       </c>
-      <c r="U22" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="V22" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>3.1</v>
-      </c>
       <c r="AC22" t="n">
-        <v>1.76</v>
+        <v>2.84</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.08</v>
+        <v>1.32</v>
       </c>
       <c r="AH22" t="n">
-        <v>3.4</v>
+        <v>1.71</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.71</v>
+        <v>1.3</v>
       </c>
       <c r="M23" t="n">
-        <v>3.92</v>
+        <v>5.5</v>
       </c>
       <c r="N23" t="n">
-        <v>4.33</v>
+        <v>6.8</v>
       </c>
       <c r="O23" t="n">
-        <v>2.14</v>
+        <v>1.68</v>
       </c>
       <c r="P23" t="n">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.2</v>
+        <v>5.75</v>
       </c>
       <c r="R23" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="S23" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="T23" t="n">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="U23" t="n">
-        <v>1.64</v>
+        <v>1.84</v>
       </c>
       <c r="V23" t="n">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="W23" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="X23" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.55</v>
+        <v>7.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.65</v>
+        <v>1.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.2</v>
+        <v>3.14</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="AE23" t="n">
         <v>1.57</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.52</v>
+        <v>7.5</v>
       </c>
       <c r="M24" t="n">
-        <v>3.13</v>
+        <v>5</v>
       </c>
       <c r="N24" t="n">
-        <v>2.83</v>
+        <v>1.4</v>
       </c>
       <c r="O24" t="n">
-        <v>3.34</v>
+        <v>5.75</v>
       </c>
       <c r="P24" t="n">
-        <v>1.91</v>
+        <v>2.63</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.5</v>
+        <v>1.85</v>
       </c>
       <c r="R24" t="n">
-        <v>1.51</v>
+        <v>1.22</v>
       </c>
       <c r="S24" t="n">
-        <v>2.39</v>
+        <v>3.85</v>
       </c>
       <c r="T24" t="n">
-        <v>3.28</v>
+        <v>2.23</v>
       </c>
       <c r="U24" t="n">
-        <v>1.29</v>
+        <v>1.68</v>
       </c>
       <c r="V24" t="n">
-        <v>8.1</v>
+        <v>4.85</v>
       </c>
       <c r="W24" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X24" t="n">
         <v>1.02</v>
       </c>
-      <c r="X24" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y24" t="n">
-        <v>1.39</v>
+        <v>1.15</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.81</v>
+        <v>5</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.28</v>
+        <v>1.47</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.55</v>
+        <v>2.46</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.46</v>
+        <v>2.25</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.17</v>
+        <v>1.69</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.92</v>
+        <v>1.73</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.79</v>
+        <v>2.05</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.36</v>
+        <v>2.9</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.44</v>
+        <v>1.11</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3396,16 +3396,16 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="M25" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="N25" t="n">
-        <v>3.31</v>
+        <v>3.4</v>
       </c>
       <c r="O25" t="n">
-        <v>2.69</v>
+        <v>2.55</v>
       </c>
       <c r="P25" t="n">
         <v>2.2</v>
@@ -3414,49 +3414,49 @@
         <v>3.8</v>
       </c>
       <c r="R25" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S25" t="n">
-        <v>3.08</v>
+        <v>2.95</v>
       </c>
       <c r="T25" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="U25" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="V25" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X25" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.64</v>
+        <v>3.44</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.26</v>
+        <v>3.07</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AG25" t="n">
         <v>1.3</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1141,10 +1141,10 @@
         <v>2.8</v>
       </c>
       <c r="N6" t="n">
-        <v>3.91</v>
+        <v>3.85</v>
       </c>
       <c r="O6" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="P6" t="n">
         <v>1.84</v>
@@ -1156,7 +1156,7 @@
         <v>1.52</v>
       </c>
       <c r="S6" t="n">
-        <v>2.27</v>
+        <v>2.51</v>
       </c>
       <c r="T6" t="n">
         <v>3.2</v>
@@ -1171,37 +1171,37 @@
         <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.5</v>
+        <v>3.96</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE6" t="n">
         <v>1.95</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45987.45833333334</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="M8" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="N8" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="O8" t="n">
-        <v>4.4</v>
+        <v>4.56</v>
       </c>
       <c r="P8" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="R8" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="S8" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="T8" t="n">
-        <v>3.72</v>
+        <v>3.76</v>
       </c>
       <c r="U8" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="V8" t="n">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W8" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X8" t="n">
         <v>1.08</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AD8" t="n">
         <v>1.13</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG8" t="n">
         <v>1.4</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45987.60416666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="M9" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="O9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q9" t="n">
         <v>2.75</v>
       </c>
-      <c r="N9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="O9" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3.05</v>
-      </c>
       <c r="R9" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="S9" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="T9" t="n">
-        <v>3.76</v>
+        <v>3.72</v>
       </c>
       <c r="U9" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="V9" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="W9" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
         <v>1.08</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AD9" t="n">
         <v>1.13</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG9" t="n">
         <v>1.4</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45987.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.34</v>
+        <v>5</v>
       </c>
       <c r="M10" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O10" t="n">
         <v>5</v>
       </c>
-      <c r="N10" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.79</v>
-      </c>
       <c r="P10" t="n">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="Q10" t="n">
-        <v>7</v>
+        <v>2.07</v>
       </c>
       <c r="R10" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="S10" t="n">
-        <v>3.58</v>
+        <v>3.36</v>
       </c>
       <c r="T10" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="U10" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="V10" t="n">
-        <v>4.95</v>
+        <v>5.1</v>
       </c>
       <c r="W10" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="X10" t="n">
         <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.6</v>
+        <v>4.25</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AG10" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH10" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>3.57</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45987.61458333334</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M11" t="n">
         <v>5</v>
       </c>
-      <c r="M11" t="n">
-        <v>4.16</v>
-      </c>
       <c r="N11" t="n">
-        <v>1.6</v>
+        <v>8.6</v>
       </c>
       <c r="O11" t="n">
-        <v>5</v>
+        <v>1.79</v>
       </c>
       <c r="P11" t="n">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.07</v>
+        <v>7</v>
       </c>
       <c r="R11" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="S11" t="n">
-        <v>3.36</v>
+        <v>3.58</v>
       </c>
       <c r="T11" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="U11" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="V11" t="n">
-        <v>5.1</v>
+        <v>4.95</v>
       </c>
       <c r="W11" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="X11" t="n">
         <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.25</v>
+        <v>4.6</v>
       </c>
       <c r="AA11" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD11" t="n">
         <v>1.57</v>
       </c>
-      <c r="AB11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AE11" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.18</v>
+        <v>3.57</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45987.61458333334</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.77</v>
+        <v>2.18</v>
       </c>
       <c r="M14" t="n">
-        <v>3.56</v>
+        <v>3.35</v>
       </c>
       <c r="N14" t="n">
-        <v>3.95</v>
+        <v>3.24</v>
       </c>
       <c r="O14" t="n">
-        <v>2.42</v>
+        <v>2.58</v>
       </c>
       <c r="P14" t="n">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.55</v>
+        <v>3.85</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S14" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T14" t="n">
         <v>2.8</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.07</v>
       </c>
       <c r="U14" t="n">
         <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>6.8</v>
+        <v>6.95</v>
       </c>
       <c r="W14" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.04</v>
+        <v>1.65</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="M15" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N15" t="n">
-        <v>3.24</v>
+        <v>2.8</v>
       </c>
       <c r="O15" t="n">
-        <v>2.58</v>
+        <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.85</v>
+        <v>3.58</v>
       </c>
       <c r="R15" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S15" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="T15" t="n">
-        <v>2.8</v>
+        <v>3.01</v>
       </c>
       <c r="U15" t="n">
         <v>1.36</v>
       </c>
       <c r="V15" t="n">
-        <v>6.95</v>
+        <v>7.2</v>
       </c>
       <c r="W15" t="n">
         <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AB15" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE15" t="n">
         <v>1.75</v>
       </c>
-      <c r="AC15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AF15" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.45</v>
+        <v>1.77</v>
       </c>
       <c r="M16" t="n">
-        <v>3.3</v>
+        <v>3.56</v>
       </c>
       <c r="N16" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S16" t="n">
         <v>2.8</v>
       </c>
-      <c r="O16" t="n">
-        <v>3</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.69</v>
-      </c>
       <c r="T16" t="n">
-        <v>3.01</v>
+        <v>3.07</v>
       </c>
       <c r="U16" t="n">
         <v>1.36</v>
       </c>
       <c r="V16" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X16" t="n">
         <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.58</v>
+        <v>3.35</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AF16" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.47</v>
+        <v>2.04</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.65</v>
+        <v>7.5</v>
       </c>
       <c r="M17" t="n">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="N17" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="O17" t="n">
-        <v>3.3</v>
+        <v>5.75</v>
       </c>
       <c r="P17" t="n">
-        <v>1.99</v>
+        <v>2.63</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.5</v>
+        <v>1.85</v>
       </c>
       <c r="R17" t="n">
-        <v>1.49</v>
+        <v>1.22</v>
       </c>
       <c r="S17" t="n">
-        <v>2.42</v>
+        <v>3.85</v>
       </c>
       <c r="T17" t="n">
-        <v>3.3</v>
+        <v>2.23</v>
       </c>
       <c r="U17" t="n">
-        <v>1.28</v>
+        <v>1.68</v>
       </c>
       <c r="V17" t="n">
-        <v>8</v>
+        <v>4.85</v>
       </c>
       <c r="W17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X17" t="n">
         <v>1.02</v>
       </c>
-      <c r="X17" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y17" t="n">
-        <v>1.4</v>
+        <v>1.15</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.61</v>
+        <v>5</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.35</v>
+        <v>1.47</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.59</v>
+        <v>2.46</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.1</v>
+        <v>2.25</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.17</v>
+        <v>1.69</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.35</v>
+        <v>2.9</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.45</v>
+        <v>1.11</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.31</v>
+        <v>1.68</v>
       </c>
       <c r="M18" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="N18" t="n">
-        <v>3.05</v>
+        <v>4.33</v>
       </c>
       <c r="O18" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="P18" t="n">
-        <v>2.14</v>
+        <v>2.45</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="R18" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="S18" t="n">
-        <v>3.02</v>
+        <v>3.7</v>
       </c>
       <c r="T18" t="n">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="U18" t="n">
-        <v>1.45</v>
+        <v>1.61</v>
       </c>
       <c r="V18" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="X18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.8</v>
+        <v>4.55</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AF18" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH18" t="n">
         <v>2.27</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.65</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.68</v>
+        <v>2.42</v>
       </c>
       <c r="M20" t="n">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="N20" t="n">
-        <v>4.33</v>
+        <v>2.6</v>
       </c>
       <c r="O20" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="P20" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.2</v>
+        <v>3.18</v>
       </c>
       <c r="R20" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="S20" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="T20" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="U20" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="V20" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X20" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AC20" t="n">
         <v>2.45</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.32</v>
+        <v>2.64</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.27</v>
+        <v>1.44</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.42</v>
+        <v>1.3</v>
       </c>
       <c r="M21" t="n">
-        <v>3.35</v>
+        <v>5.5</v>
       </c>
       <c r="N21" t="n">
-        <v>2.6</v>
+        <v>6.8</v>
       </c>
       <c r="O21" t="n">
-        <v>3.2</v>
+        <v>1.68</v>
       </c>
       <c r="P21" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.18</v>
+        <v>5.75</v>
       </c>
       <c r="R21" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="S21" t="n">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="T21" t="n">
-        <v>2.4</v>
+        <v>1.92</v>
       </c>
       <c r="U21" t="n">
-        <v>1.57</v>
+        <v>1.84</v>
       </c>
       <c r="V21" t="n">
-        <v>5.5</v>
+        <v>3.7</v>
       </c>
       <c r="W21" t="n">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.19</v>
+        <v>1.05</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.66</v>
+        <v>1.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.35</v>
+        <v>3.14</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.45</v>
+        <v>1.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.47</v>
+        <v>1.91</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.64</v>
+        <v>2.4</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.44</v>
+        <v>3.4</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.2</v>
+        <v>2.65</v>
       </c>
       <c r="M22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O22" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q22" t="n">
         <v>3.5</v>
       </c>
-      <c r="N22" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>3.7</v>
-      </c>
       <c r="R22" t="n">
-        <v>1.29</v>
+        <v>1.49</v>
       </c>
       <c r="S22" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T22" t="n">
         <v>3.3</v>
       </c>
-      <c r="T22" t="n">
-        <v>2.52</v>
-      </c>
       <c r="U22" t="n">
-        <v>1.52</v>
+        <v>1.28</v>
       </c>
       <c r="V22" t="n">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.9</v>
+        <v>2.61</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.76</v>
+        <v>2.35</v>
       </c>
       <c r="AB22" t="n">
-        <v>2</v>
+        <v>1.59</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.84</v>
+        <v>4.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.71</v>
+        <v>1.45</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.3</v>
+        <v>2.31</v>
       </c>
       <c r="M23" t="n">
-        <v>5.5</v>
+        <v>3.55</v>
       </c>
       <c r="N23" t="n">
-        <v>6.8</v>
+        <v>3.05</v>
       </c>
       <c r="O23" t="n">
-        <v>1.68</v>
+        <v>2.8</v>
       </c>
       <c r="P23" t="n">
-        <v>2.9</v>
+        <v>2.14</v>
       </c>
       <c r="Q23" t="n">
-        <v>5.75</v>
+        <v>3.65</v>
       </c>
       <c r="R23" t="n">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="S23" t="n">
-        <v>4.5</v>
+        <v>3.02</v>
       </c>
       <c r="T23" t="n">
-        <v>1.92</v>
+        <v>2.55</v>
       </c>
       <c r="U23" t="n">
-        <v>1.84</v>
+        <v>1.45</v>
       </c>
       <c r="V23" t="n">
-        <v>3.7</v>
+        <v>6.5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.05</v>
+        <v>1.26</v>
       </c>
       <c r="Z23" t="n">
-        <v>7.5</v>
+        <v>3.8</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="AB23" t="n">
-        <v>3.14</v>
+        <v>1.95</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.9</v>
+        <v>2.88</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.91</v>
+        <v>1.36</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="AH23" t="n">
-        <v>3.4</v>
+        <v>1.65</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>7.5</v>
+        <v>2.2</v>
       </c>
       <c r="M24" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="N24" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="O24" t="n">
-        <v>5.75</v>
+        <v>2.5</v>
       </c>
       <c r="P24" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.85</v>
+        <v>3.7</v>
       </c>
       <c r="R24" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="S24" t="n">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="T24" t="n">
-        <v>2.23</v>
+        <v>2.52</v>
       </c>
       <c r="U24" t="n">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="V24" t="n">
-        <v>4.85</v>
+        <v>5.8</v>
       </c>
       <c r="W24" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="X24" t="n">
         <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="Z24" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.47</v>
+        <v>1.76</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.46</v>
+        <v>2</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.25</v>
+        <v>2.84</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.69</v>
+        <v>1.4</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.9</v>
+        <v>1.32</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.11</v>
+        <v>1.71</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3396,64 +3396,64 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="M25" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N25" t="n">
         <v>3.5</v>
       </c>
-      <c r="N25" t="n">
-        <v>3.4</v>
-      </c>
       <c r="O25" t="n">
-        <v>2.55</v>
+        <v>2.44</v>
       </c>
       <c r="P25" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="Q25" t="n">
         <v>3.8</v>
       </c>
       <c r="R25" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S25" t="n">
-        <v>2.95</v>
+        <v>3.21</v>
       </c>
       <c r="T25" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="U25" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="V25" t="n">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="W25" t="n">
         <v>1.07</v>
       </c>
       <c r="X25" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.07</v>
+        <v>2.85</v>
       </c>
       <c r="AD25" t="n">
         <v>1.33</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AF25" t="n">
         <v>2.05</v>
@@ -3462,7 +3462,7 @@
         <v>1.3</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45987.79166666666</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="M6" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="N6" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="O6" t="n">
         <v>2.78</v>
@@ -1180,10 +1180,10 @@
         <v>2.59</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AC6" t="n">
         <v>3.96</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="M8" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="N8" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="O8" t="n">
-        <v>4.56</v>
+        <v>4.95</v>
       </c>
       <c r="P8" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="R8" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="S8" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="T8" t="n">
-        <v>3.76</v>
+        <v>3.5</v>
       </c>
       <c r="U8" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="V8" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="W8" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X8" t="n">
         <v>1.08</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.36</v>
+        <v>2.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.4</v>
+        <v>5.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45987.60416666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="M9" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="N9" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="O9" t="n">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="P9" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="R9" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="S9" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="T9" t="n">
-        <v>3.72</v>
+        <v>3.75</v>
       </c>
       <c r="U9" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="V9" t="n">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W9" t="n">
         <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.3</v>
+        <v>5.35</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45987.60416666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="M13" t="n">
-        <v>3.8</v>
+        <v>3.56</v>
       </c>
       <c r="N13" t="n">
-        <v>4.7</v>
+        <v>3.95</v>
       </c>
       <c r="O13" t="n">
-        <v>2.15</v>
+        <v>2.42</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="Q13" t="n">
-        <v>5</v>
+        <v>4.55</v>
       </c>
       <c r="R13" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="T13" t="n">
-        <v>2.85</v>
+        <v>3.07</v>
       </c>
       <c r="U13" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="V13" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
         <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.49</v>
+        <v>3.08</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.18</v>
+        <v>1.67</v>
       </c>
       <c r="M14" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="N14" t="n">
-        <v>3.24</v>
+        <v>4.7</v>
       </c>
       <c r="O14" t="n">
-        <v>2.58</v>
+        <v>2.15</v>
       </c>
       <c r="P14" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.85</v>
+        <v>5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="S14" t="n">
-        <v>2.65</v>
+        <v>2.73</v>
       </c>
       <c r="T14" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="U14" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="V14" t="n">
-        <v>6.95</v>
+        <v>7</v>
       </c>
       <c r="W14" t="n">
         <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.25</v>
+        <v>3.49</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="M15" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N15" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T15" t="n">
         <v>2.8</v>
-      </c>
-      <c r="O15" t="n">
-        <v>3</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3.01</v>
       </c>
       <c r="U15" t="n">
         <v>1.36</v>
       </c>
       <c r="V15" t="n">
-        <v>7.2</v>
+        <v>6.95</v>
       </c>
       <c r="W15" t="n">
         <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AF15" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.77</v>
+        <v>2.45</v>
       </c>
       <c r="M16" t="n">
-        <v>3.56</v>
+        <v>3.3</v>
       </c>
       <c r="N16" t="n">
-        <v>3.95</v>
+        <v>2.8</v>
       </c>
       <c r="O16" t="n">
-        <v>2.42</v>
+        <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.55</v>
+        <v>3.58</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S16" t="n">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="T16" t="n">
-        <v>3.07</v>
+        <v>3.01</v>
       </c>
       <c r="U16" t="n">
         <v>1.36</v>
       </c>
       <c r="V16" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="W16" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
         <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.35</v>
+        <v>3.58</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.04</v>
+        <v>1.47</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>7.5</v>
+        <v>1.37</v>
       </c>
       <c r="M17" t="n">
-        <v>5</v>
+        <v>4.85</v>
       </c>
       <c r="N17" t="n">
-        <v>1.4</v>
+        <v>7.2</v>
       </c>
       <c r="O17" t="n">
-        <v>5.75</v>
+        <v>1.83</v>
       </c>
       <c r="P17" t="n">
         <v>2.63</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.85</v>
+        <v>5.5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="S17" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T17" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="U17" t="n">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
       <c r="V17" t="n">
-        <v>4.85</v>
+        <v>4.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="Z17" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="AC17" t="n">
         <v>2.25</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.11</v>
+        <v>2.75</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.68</v>
+        <v>2.65</v>
       </c>
       <c r="M18" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="N18" t="n">
-        <v>4.33</v>
+        <v>2.7</v>
       </c>
       <c r="O18" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="P18" t="n">
-        <v>2.45</v>
+        <v>1.99</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="S18" t="n">
-        <v>3.7</v>
+        <v>2.42</v>
       </c>
       <c r="T18" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="U18" t="n">
-        <v>1.61</v>
+        <v>1.28</v>
       </c>
       <c r="V18" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W18" t="n">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="X18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.15</v>
+        <v>1.4</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.55</v>
+        <v>2.61</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.55</v>
+        <v>2.35</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.4</v>
+        <v>1.59</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.45</v>
+        <v>4.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.53</v>
+        <v>1.17</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.32</v>
+        <v>1.8</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.27</v>
+        <v>1.45</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="M19" t="n">
-        <v>4.85</v>
+        <v>5.5</v>
       </c>
       <c r="N19" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="O19" t="n">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="P19" t="n">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="R19" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="S19" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="T19" t="n">
-        <v>2.21</v>
+        <v>1.92</v>
       </c>
       <c r="U19" t="n">
-        <v>1.59</v>
+        <v>1.84</v>
       </c>
       <c r="V19" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="W19" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.8</v>
+        <v>7.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.62</v>
+        <v>3.14</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.66</v>
+        <v>1.91</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.42</v>
+        <v>1.68</v>
       </c>
       <c r="M20" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="N20" t="n">
-        <v>2.6</v>
+        <v>4.33</v>
       </c>
       <c r="O20" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="P20" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V20" t="n">
+        <v>5</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB20" t="n">
         <v>2.4</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V20" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.35</v>
       </c>
       <c r="AC20" t="n">
         <v>2.45</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.64</v>
+        <v>2.32</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.44</v>
+        <v>2.27</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="M21" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="N21" t="n">
-        <v>6.8</v>
+        <v>3.2</v>
       </c>
       <c r="O21" t="n">
-        <v>1.68</v>
+        <v>2.5</v>
       </c>
       <c r="P21" t="n">
-        <v>2.9</v>
+        <v>2.38</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.75</v>
+        <v>3.7</v>
       </c>
       <c r="R21" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="S21" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="T21" t="n">
-        <v>1.92</v>
+        <v>2.52</v>
       </c>
       <c r="U21" t="n">
-        <v>1.84</v>
+        <v>1.52</v>
       </c>
       <c r="V21" t="n">
-        <v>3.7</v>
+        <v>5.8</v>
       </c>
       <c r="W21" t="n">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.05</v>
+        <v>1.21</v>
       </c>
       <c r="Z21" t="n">
-        <v>7.5</v>
+        <v>3.9</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.3</v>
+        <v>1.76</v>
       </c>
       <c r="AB21" t="n">
-        <v>3.14</v>
+        <v>2</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.9</v>
+        <v>2.84</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.91</v>
+        <v>1.4</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="AH21" t="n">
-        <v>3.4</v>
+        <v>1.71</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.65</v>
+        <v>2.31</v>
       </c>
       <c r="M22" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="N22" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="O22" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="P22" t="n">
-        <v>1.99</v>
+        <v>2.14</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="R22" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="S22" t="n">
-        <v>2.42</v>
+        <v>3.02</v>
       </c>
       <c r="T22" t="n">
-        <v>3.3</v>
+        <v>2.55</v>
       </c>
       <c r="U22" t="n">
-        <v>1.28</v>
+        <v>1.45</v>
       </c>
       <c r="V22" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="X22" t="n">
         <v>1.05</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.61</v>
+        <v>3.8</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.35</v>
+        <v>1.8</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.59</v>
+        <v>1.95</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.1</v>
+        <v>2.88</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.8</v>
+        <v>2.27</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.45</v>
+        <v>1.65</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.31</v>
+        <v>7.5</v>
       </c>
       <c r="M23" t="n">
-        <v>3.55</v>
+        <v>5</v>
       </c>
       <c r="N23" t="n">
-        <v>3.05</v>
+        <v>1.4</v>
       </c>
       <c r="O23" t="n">
-        <v>2.8</v>
+        <v>5.75</v>
       </c>
       <c r="P23" t="n">
-        <v>2.14</v>
+        <v>2.63</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.65</v>
+        <v>1.85</v>
       </c>
       <c r="R23" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="S23" t="n">
-        <v>3.02</v>
+        <v>3.85</v>
       </c>
       <c r="T23" t="n">
-        <v>2.55</v>
+        <v>2.23</v>
       </c>
       <c r="U23" t="n">
-        <v>1.45</v>
+        <v>1.68</v>
       </c>
       <c r="V23" t="n">
-        <v>6.5</v>
+        <v>4.85</v>
       </c>
       <c r="W23" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="X23" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.8</v>
+        <v>1.47</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.95</v>
+        <v>2.46</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.88</v>
+        <v>2.25</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.36</v>
+        <v>1.69</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.27</v>
+        <v>2.05</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.36</v>
+        <v>2.9</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.65</v>
+        <v>1.11</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="M24" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="N24" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O24" t="n">
         <v>3.2</v>
       </c>
-      <c r="O24" t="n">
-        <v>2.5</v>
-      </c>
       <c r="P24" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.7</v>
+        <v>3.18</v>
       </c>
       <c r="R24" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="S24" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="T24" t="n">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="U24" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="V24" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="AB24" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.84</v>
+        <v>2.45</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.2</v>
+        <v>2.64</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.71</v>
+        <v>1.44</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45987.70833333334</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="N8" t="n">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="O8" t="n">
-        <v>4.95</v>
+        <v>4.45</v>
       </c>
       <c r="P8" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="R8" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="S8" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="T8" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U8" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="V8" t="n">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W8" t="n">
         <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.25</v>
+        <v>5.35</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45987.60416666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="M9" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="N9" t="n">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="O9" t="n">
-        <v>4.45</v>
+        <v>4.95</v>
       </c>
       <c r="P9" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="R9" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="S9" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="T9" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U9" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="V9" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="W9" t="n">
         <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.35</v>
+        <v>5.25</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45987.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M10" t="n">
         <v>5</v>
       </c>
-      <c r="M10" t="n">
-        <v>4.16</v>
-      </c>
       <c r="N10" t="n">
-        <v>1.6</v>
+        <v>8.6</v>
       </c>
       <c r="O10" t="n">
-        <v>5</v>
+        <v>1.79</v>
       </c>
       <c r="P10" t="n">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.07</v>
+        <v>7</v>
       </c>
       <c r="R10" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="S10" t="n">
-        <v>3.36</v>
+        <v>3.58</v>
       </c>
       <c r="T10" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="U10" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="V10" t="n">
-        <v>5.1</v>
+        <v>4.95</v>
       </c>
       <c r="W10" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="X10" t="n">
         <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.25</v>
+        <v>4.6</v>
       </c>
       <c r="AA10" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD10" t="n">
         <v>1.57</v>
       </c>
-      <c r="AB10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AE10" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.18</v>
+        <v>3.57</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45987.61458333334</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.34</v>
+        <v>5</v>
       </c>
       <c r="M11" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O11" t="n">
         <v>5</v>
       </c>
-      <c r="N11" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.79</v>
-      </c>
       <c r="P11" t="n">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="Q11" t="n">
-        <v>7</v>
+        <v>2.07</v>
       </c>
       <c r="R11" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="S11" t="n">
-        <v>3.58</v>
+        <v>3.36</v>
       </c>
       <c r="T11" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="U11" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="V11" t="n">
-        <v>4.95</v>
+        <v>5.1</v>
       </c>
       <c r="W11" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="X11" t="n">
         <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.6</v>
+        <v>4.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AG11" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>3.57</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45987.61458333334</v>
@@ -1849,25 +1849,25 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="M12" t="n">
-        <v>3.62</v>
+        <v>3.36</v>
       </c>
       <c r="N12" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O12" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="P12" t="n">
         <v>2.26</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.04</v>
+        <v>3.92</v>
       </c>
       <c r="R12" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S12" t="n">
         <v>3.28</v>
@@ -1876,40 +1876,40 @@
         <v>2.3</v>
       </c>
       <c r="U12" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="V12" t="n">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="W12" t="n">
         <v>1.11</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
         <v>1.18</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AE12" t="n">
         <v>1.53</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="AG12" t="n">
         <v>1.26</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="M13" t="n">
-        <v>3.56</v>
+        <v>3.8</v>
       </c>
       <c r="N13" t="n">
-        <v>3.95</v>
+        <v>4.7</v>
       </c>
       <c r="O13" t="n">
-        <v>2.42</v>
+        <v>2.15</v>
       </c>
       <c r="P13" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.55</v>
+        <v>5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="S13" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="T13" t="n">
-        <v>3.07</v>
+        <v>2.85</v>
       </c>
       <c r="U13" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="V13" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
         <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.08</v>
+        <v>3.49</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.67</v>
+        <v>2.45</v>
       </c>
       <c r="M14" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>4.7</v>
+        <v>2.8</v>
       </c>
       <c r="O14" t="n">
+        <v>3</v>
+      </c>
+      <c r="P14" t="n">
         <v>2.15</v>
       </c>
-      <c r="P14" t="n">
-        <v>2.2</v>
-      </c>
       <c r="Q14" t="n">
-        <v>5</v>
+        <v>3.58</v>
       </c>
       <c r="R14" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="S14" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="T14" t="n">
-        <v>2.85</v>
+        <v>3.01</v>
       </c>
       <c r="U14" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="W14" t="n">
         <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.49</v>
+        <v>3.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.15</v>
+        <v>1.47</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.18</v>
+        <v>1.77</v>
       </c>
       <c r="M15" t="n">
-        <v>3.35</v>
+        <v>3.56</v>
       </c>
       <c r="N15" t="n">
-        <v>3.24</v>
+        <v>3.95</v>
       </c>
       <c r="O15" t="n">
-        <v>2.58</v>
+        <v>2.42</v>
       </c>
       <c r="P15" t="n">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.85</v>
+        <v>4.55</v>
       </c>
       <c r="R15" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="T15" t="n">
-        <v>2.8</v>
+        <v>3.07</v>
       </c>
       <c r="U15" t="n">
         <v>1.36</v>
       </c>
       <c r="V15" t="n">
-        <v>6.95</v>
+        <v>6.8</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.65</v>
+        <v>2.04</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="M16" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N16" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T16" t="n">
         <v>2.8</v>
-      </c>
-      <c r="O16" t="n">
-        <v>3</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.01</v>
       </c>
       <c r="U16" t="n">
         <v>1.36</v>
       </c>
       <c r="V16" t="n">
-        <v>7.2</v>
+        <v>6.95</v>
       </c>
       <c r="W16" t="n">
         <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AF16" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.37</v>
+        <v>2.42</v>
       </c>
       <c r="M17" t="n">
-        <v>4.85</v>
+        <v>3.35</v>
       </c>
       <c r="N17" t="n">
-        <v>7.2</v>
+        <v>2.6</v>
       </c>
       <c r="O17" t="n">
-        <v>1.83</v>
+        <v>3.2</v>
       </c>
       <c r="P17" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="Q17" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V17" t="n">
         <v>5.5</v>
       </c>
-      <c r="R17" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="V17" t="n">
+      <c r="W17" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z17" t="n">
         <v>4.5</v>
       </c>
-      <c r="W17" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>5.8</v>
-      </c>
       <c r="AA17" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.62</v>
+        <v>2.35</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.66</v>
+        <v>1.47</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.7</v>
+        <v>1.51</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.16</v>
+        <v>2.64</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.75</v>
+        <v>1.44</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.65</v>
+        <v>2.31</v>
       </c>
       <c r="M18" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="N18" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="O18" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="P18" t="n">
-        <v>1.99</v>
+        <v>2.14</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="R18" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="S18" t="n">
-        <v>2.42</v>
+        <v>3.02</v>
       </c>
       <c r="T18" t="n">
-        <v>3.3</v>
+        <v>2.55</v>
       </c>
       <c r="U18" t="n">
-        <v>1.28</v>
+        <v>1.45</v>
       </c>
       <c r="V18" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="X18" t="n">
         <v>1.05</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.61</v>
+        <v>3.8</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.35</v>
+        <v>1.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.59</v>
+        <v>1.95</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.1</v>
+        <v>2.88</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.8</v>
+        <v>2.27</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.45</v>
+        <v>1.65</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="M19" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>6.8</v>
+        <v>3.2</v>
       </c>
       <c r="O19" t="n">
-        <v>1.68</v>
+        <v>2.5</v>
       </c>
       <c r="P19" t="n">
-        <v>2.9</v>
+        <v>2.38</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.75</v>
+        <v>3.7</v>
       </c>
       <c r="R19" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="S19" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="T19" t="n">
-        <v>1.92</v>
+        <v>2.52</v>
       </c>
       <c r="U19" t="n">
-        <v>1.84</v>
+        <v>1.52</v>
       </c>
       <c r="V19" t="n">
-        <v>3.7</v>
+        <v>5.8</v>
       </c>
       <c r="W19" t="n">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.05</v>
+        <v>1.21</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.5</v>
+        <v>3.9</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.3</v>
+        <v>1.76</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.14</v>
+        <v>2</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.9</v>
+        <v>2.84</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.91</v>
+        <v>1.4</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.4</v>
+        <v>1.71</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.68</v>
+        <v>2.65</v>
       </c>
       <c r="M20" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="N20" t="n">
-        <v>4.33</v>
+        <v>2.7</v>
       </c>
       <c r="O20" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="P20" t="n">
-        <v>2.45</v>
+        <v>1.99</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="R20" t="n">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="S20" t="n">
-        <v>3.7</v>
+        <v>2.42</v>
       </c>
       <c r="T20" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="U20" t="n">
-        <v>1.61</v>
+        <v>1.28</v>
       </c>
       <c r="V20" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W20" t="n">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="X20" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.15</v>
+        <v>1.4</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.55</v>
+        <v>2.61</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.55</v>
+        <v>2.35</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.4</v>
+        <v>1.59</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.45</v>
+        <v>4.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.53</v>
+        <v>1.17</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.32</v>
+        <v>1.8</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.27</v>
+        <v>1.45</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.2</v>
+        <v>1.37</v>
       </c>
       <c r="M21" t="n">
-        <v>3.5</v>
+        <v>4.85</v>
       </c>
       <c r="N21" t="n">
-        <v>3.2</v>
+        <v>7.2</v>
       </c>
       <c r="O21" t="n">
-        <v>2.5</v>
+        <v>1.83</v>
       </c>
       <c r="P21" t="n">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="S21" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="T21" t="n">
-        <v>2.52</v>
+        <v>2.21</v>
       </c>
       <c r="U21" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="V21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z21" t="n">
         <v>5.8</v>
       </c>
-      <c r="W21" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AA21" t="n">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>2</v>
+        <v>2.62</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.84</v>
+        <v>2.25</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.4</v>
+        <v>1.66</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.71</v>
+        <v>2.75</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.31</v>
+        <v>1.68</v>
       </c>
       <c r="M22" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="N22" t="n">
-        <v>3.05</v>
+        <v>4.33</v>
       </c>
       <c r="O22" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="P22" t="n">
-        <v>2.14</v>
+        <v>2.45</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="R22" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>3.02</v>
+        <v>3.7</v>
       </c>
       <c r="T22" t="n">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="U22" t="n">
-        <v>1.45</v>
+        <v>1.61</v>
       </c>
       <c r="V22" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="X22" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.8</v>
+        <v>4.55</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AF22" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH22" t="n">
         <v>2.27</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.65</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.42</v>
+        <v>1.3</v>
       </c>
       <c r="M24" t="n">
-        <v>3.35</v>
+        <v>5.5</v>
       </c>
       <c r="N24" t="n">
-        <v>2.6</v>
+        <v>6.8</v>
       </c>
       <c r="O24" t="n">
-        <v>3.2</v>
+        <v>1.68</v>
       </c>
       <c r="P24" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.18</v>
+        <v>5.75</v>
       </c>
       <c r="R24" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="S24" t="n">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="T24" t="n">
-        <v>2.4</v>
+        <v>1.92</v>
       </c>
       <c r="U24" t="n">
-        <v>1.57</v>
+        <v>1.84</v>
       </c>
       <c r="V24" t="n">
-        <v>5.5</v>
+        <v>3.7</v>
       </c>
       <c r="W24" t="n">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="X24" t="n">
         <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.19</v>
+        <v>1.05</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.66</v>
+        <v>1.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.35</v>
+        <v>3.14</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.45</v>
+        <v>1.9</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.47</v>
+        <v>1.91</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.64</v>
+        <v>2.4</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.44</v>
+        <v>3.4</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45987.70833333334</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -659,22 +659,22 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -778,22 +778,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1144,40 +1144,40 @@
         <v>4</v>
       </c>
       <c r="O6" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="P6" t="n">
-        <v>1.84</v>
+        <v>1.96</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="R6" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="S6" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="T6" t="n">
         <v>3.2</v>
       </c>
       <c r="U6" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="V6" t="n">
-        <v>8.1</v>
+        <v>9.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="AA6" t="n">
         <v>2.25</v>
@@ -1186,22 +1186,22 @@
         <v>1.57</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.96</v>
+        <v>4.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45987.45833333334</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="M8" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="O8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q8" t="n">
         <v>2.75</v>
       </c>
-      <c r="N8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O8" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3.05</v>
-      </c>
       <c r="R8" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="S8" t="n">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="T8" t="n">
         <v>3.75</v>
       </c>
       <c r="U8" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="V8" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="W8" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X8" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.35</v>
+        <v>5.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.35</v>
+        <v>1.7</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45987.60416666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O9" t="n">
         <v>4</v>
       </c>
-      <c r="M9" t="n">
+      <c r="P9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q9" t="n">
         <v>2.9</v>
       </c>
-      <c r="N9" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="O9" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.78</v>
-      </c>
       <c r="R9" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="S9" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="T9" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U9" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="V9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W9" t="n">
         <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.25</v>
+        <v>5.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45987.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.34</v>
+        <v>5.1</v>
       </c>
       <c r="M10" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="N10" t="n">
-        <v>8.6</v>
+        <v>1.6</v>
       </c>
       <c r="O10" t="n">
-        <v>1.79</v>
+        <v>4.31</v>
       </c>
       <c r="P10" t="n">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="Q10" t="n">
-        <v>7</v>
+        <v>2.06</v>
       </c>
       <c r="R10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG10" t="n">
         <v>1.27</v>
       </c>
-      <c r="S10" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V10" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AH10" t="n">
-        <v>3.57</v>
+        <v>1.19</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45987.61458333334</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M11" t="n">
         <v>5</v>
       </c>
-      <c r="M11" t="n">
-        <v>4.16</v>
-      </c>
       <c r="N11" t="n">
-        <v>1.6</v>
+        <v>9</v>
       </c>
       <c r="O11" t="n">
-        <v>5</v>
+        <v>1.77</v>
       </c>
       <c r="P11" t="n">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.07</v>
+        <v>7</v>
       </c>
       <c r="R11" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="S11" t="n">
-        <v>3.36</v>
+        <v>3.58</v>
       </c>
       <c r="T11" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="U11" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="V11" t="n">
-        <v>5.1</v>
+        <v>4.95</v>
       </c>
       <c r="W11" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
         <v>1.15</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.25</v>
+        <v>1.99</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.26</v>
+        <v>1.08</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.18</v>
+        <v>3.1</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45987.61458333334</v>
@@ -1858,25 +1858,25 @@
         <v>3.2</v>
       </c>
       <c r="O12" t="n">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="P12" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S12" t="n">
         <v>3.28</v>
       </c>
       <c r="T12" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="U12" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="V12" t="n">
         <v>5</v>
@@ -1891,7 +1891,7 @@
         <v>1.18</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="AA12" t="n">
         <v>1.65</v>
@@ -1900,16 +1900,16 @@
         <v>2.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AE12" t="n">
         <v>1.53</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="AG12" t="n">
         <v>1.26</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="M13" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="N13" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="O13" t="n">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q13" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="R13" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="S13" t="n">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="T13" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="U13" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="V13" t="n">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG13" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z13" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH13" t="n">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2087,64 +2087,64 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="N14" t="n">
         <v>2.8</v>
       </c>
       <c r="O14" t="n">
-        <v>3</v>
+        <v>3.26</v>
       </c>
       <c r="P14" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.58</v>
+        <v>3.2</v>
       </c>
       <c r="R14" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="T14" t="n">
-        <v>3.01</v>
+        <v>2.8</v>
       </c>
       <c r="U14" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V14" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
         <v>1.06</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.58</v>
+        <v>3.63</v>
       </c>
       <c r="AD14" t="n">
         <v>1.25</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AF14" t="n">
         <v>2</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="M15" t="n">
-        <v>3.56</v>
+        <v>3.63</v>
       </c>
       <c r="N15" t="n">
-        <v>3.95</v>
+        <v>5.8</v>
       </c>
       <c r="O15" t="n">
-        <v>2.42</v>
+        <v>2.26</v>
       </c>
       <c r="P15" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.55</v>
+        <v>4.9</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="S15" t="n">
-        <v>2.8</v>
+        <v>2.98</v>
       </c>
       <c r="T15" t="n">
-        <v>3.07</v>
+        <v>2.9</v>
       </c>
       <c r="U15" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="V15" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="W15" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
         <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.04</v>
+        <v>1.87</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2325,19 +2325,19 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.18</v>
+        <v>2.07</v>
       </c>
       <c r="M16" t="n">
         <v>3.35</v>
       </c>
       <c r="N16" t="n">
-        <v>3.24</v>
+        <v>3.45</v>
       </c>
       <c r="O16" t="n">
-        <v>2.58</v>
+        <v>2.75</v>
       </c>
       <c r="P16" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="Q16" t="n">
         <v>3.85</v>
@@ -2349,13 +2349,13 @@
         <v>2.65</v>
       </c>
       <c r="T16" t="n">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="U16" t="n">
         <v>1.36</v>
       </c>
       <c r="V16" t="n">
-        <v>6.95</v>
+        <v>7</v>
       </c>
       <c r="W16" t="n">
         <v>1.04</v>
@@ -2364,34 +2364,34 @@
         <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z16" t="n">
         <v>3.25</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.42</v>
+        <v>1.26</v>
       </c>
       <c r="M17" t="n">
-        <v>3.35</v>
+        <v>6</v>
       </c>
       <c r="N17" t="n">
-        <v>2.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>3.2</v>
+        <v>1.66</v>
       </c>
       <c r="P17" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.18</v>
+        <v>5.8</v>
       </c>
       <c r="R17" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="S17" t="n">
-        <v>3.45</v>
+        <v>4.55</v>
       </c>
       <c r="T17" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="V17" t="n">
-        <v>5.5</v>
+        <v>3.75</v>
       </c>
       <c r="W17" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="X17" t="n">
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.19</v>
+        <v>1.04</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.66</v>
+        <v>1.33</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.35</v>
+        <v>3.15</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.45</v>
+        <v>1.76</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.47</v>
+        <v>1.95</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.64</v>
+        <v>2.3</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.44</v>
+        <v>3.4</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.31</v>
+        <v>2.07</v>
       </c>
       <c r="M18" t="n">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="N18" t="n">
-        <v>3.05</v>
+        <v>3.27</v>
       </c>
       <c r="O18" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="P18" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="R18" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S18" t="n">
-        <v>3.02</v>
+        <v>3.32</v>
       </c>
       <c r="T18" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="U18" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="V18" t="n">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="W18" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X18" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="M19" t="n">
-        <v>3.5</v>
+        <v>3.51</v>
       </c>
       <c r="N19" t="n">
-        <v>3.2</v>
+        <v>2.47</v>
       </c>
       <c r="O19" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="P19" t="n">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="R19" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="S19" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="T19" t="n">
-        <v>2.52</v>
+        <v>2.39</v>
       </c>
       <c r="U19" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="V19" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="AB19" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.84</v>
+        <v>2.46</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.2</v>
+        <v>2.64</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.71</v>
+        <v>1.44</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.65</v>
+        <v>1.71</v>
       </c>
       <c r="M20" t="n">
-        <v>3.25</v>
+        <v>3.92</v>
       </c>
       <c r="N20" t="n">
-        <v>2.7</v>
+        <v>4.33</v>
       </c>
       <c r="O20" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="P20" t="n">
-        <v>1.99</v>
+        <v>2.45</v>
       </c>
       <c r="Q20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S20" t="n">
         <v>3.5</v>
       </c>
-      <c r="R20" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.42</v>
-      </c>
       <c r="T20" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="U20" t="n">
-        <v>1.28</v>
+        <v>1.64</v>
       </c>
       <c r="V20" t="n">
-        <v>8</v>
+        <v>5.05</v>
       </c>
       <c r="W20" t="n">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="X20" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.4</v>
+        <v>1.13</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.61</v>
+        <v>5</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.35</v>
+        <v>1.65</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.59</v>
+        <v>2.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.1</v>
+        <v>2.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.17</v>
+        <v>1.6</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.91</v>
+        <v>1.61</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.8</v>
+        <v>2.49</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.45</v>
+        <v>2.32</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.37</v>
+        <v>6.9</v>
       </c>
       <c r="M21" t="n">
-        <v>4.85</v>
+        <v>5</v>
       </c>
       <c r="N21" t="n">
-        <v>7.2</v>
+        <v>1.38</v>
       </c>
       <c r="O21" t="n">
+        <v>6</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q21" t="n">
         <v>1.83</v>
       </c>
-      <c r="P21" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>5.5</v>
-      </c>
       <c r="R21" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="S21" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="T21" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="U21" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="V21" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="W21" t="n">
         <v>1.17</v>
       </c>
       <c r="X21" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="Z21" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.75</v>
+        <v>1.13</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.68</v>
+        <v>2.29</v>
       </c>
       <c r="M22" t="n">
-        <v>4</v>
+        <v>3.39</v>
       </c>
       <c r="N22" t="n">
-        <v>4.33</v>
+        <v>2.95</v>
       </c>
       <c r="O22" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="P22" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="R22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V22" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y22" t="n">
         <v>1.25</v>
       </c>
-      <c r="S22" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V22" t="n">
-        <v>5</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.15</v>
-      </c>
       <c r="Z22" t="n">
-        <v>4.55</v>
+        <v>3.8</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.55</v>
+        <v>1.79</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.45</v>
+        <v>3.02</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.27</v>
+        <v>1.67</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>7.5</v>
+        <v>2.52</v>
       </c>
       <c r="M23" t="n">
-        <v>5</v>
+        <v>3.13</v>
       </c>
       <c r="N23" t="n">
-        <v>1.4</v>
+        <v>2.83</v>
       </c>
       <c r="O23" t="n">
-        <v>5.75</v>
+        <v>3.4</v>
       </c>
       <c r="P23" t="n">
-        <v>2.63</v>
+        <v>1.91</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.85</v>
+        <v>3.3</v>
       </c>
       <c r="R23" t="n">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="S23" t="n">
-        <v>3.85</v>
+        <v>2.57</v>
       </c>
       <c r="T23" t="n">
-        <v>2.23</v>
+        <v>3.3</v>
       </c>
       <c r="U23" t="n">
-        <v>1.68</v>
+        <v>1.28</v>
       </c>
       <c r="V23" t="n">
-        <v>4.85</v>
+        <v>8.5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.16</v>
+        <v>1.02</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.15</v>
+        <v>1.43</v>
       </c>
       <c r="Z23" t="n">
-        <v>5</v>
+        <v>2.75</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.47</v>
+        <v>2.28</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.46</v>
+        <v>1.55</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.25</v>
+        <v>4.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.69</v>
+        <v>1.17</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.73</v>
+        <v>2.01</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.05</v>
+        <v>1.81</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.9</v>
+        <v>1.31</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.11</v>
+        <v>1.39</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="M24" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="N24" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="O24" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="P24" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="R24" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG24" t="n">
         <v>1.18</v>
       </c>
-      <c r="S24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="V24" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AH24" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3396,16 +3396,16 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="M25" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="N25" t="n">
-        <v>3.5</v>
+        <v>3.31</v>
       </c>
       <c r="O25" t="n">
-        <v>2.44</v>
+        <v>2.55</v>
       </c>
       <c r="P25" t="n">
         <v>2.16</v>
@@ -3414,16 +3414,16 @@
         <v>3.8</v>
       </c>
       <c r="R25" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="S25" t="n">
-        <v>3.21</v>
+        <v>2.95</v>
       </c>
       <c r="T25" t="n">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="U25" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="V25" t="n">
         <v>5.9</v>
@@ -3438,13 +3438,13 @@
         <v>1.22</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.08</v>
+        <v>1.85</v>
       </c>
       <c r="AC25" t="n">
         <v>2.85</v>
@@ -3456,13 +3456,13 @@
         <v>1.67</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45987.79166666666</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,49 +1968,49 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.81</v>
+        <v>2.44</v>
       </c>
       <c r="M13" t="n">
-        <v>3.45</v>
+        <v>3.31</v>
       </c>
       <c r="N13" t="n">
-        <v>4.4</v>
+        <v>2.8</v>
       </c>
       <c r="O13" t="n">
-        <v>2.32</v>
+        <v>3.26</v>
       </c>
       <c r="P13" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="R13" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
         <v>2.65</v>
       </c>
       <c r="T13" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="U13" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V13" t="n">
-        <v>6.75</v>
+        <v>7.4</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.5</v>
+        <v>3.08</v>
       </c>
       <c r="AA13" t="n">
         <v>1.98</v>
@@ -2019,22 +2019,22 @@
         <v>1.77</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.35</v>
+        <v>3.63</v>
       </c>
       <c r="AD13" t="n">
         <v>1.25</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.99</v>
+        <v>1.47</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.44</v>
+        <v>1.61</v>
       </c>
       <c r="M14" t="n">
-        <v>3.31</v>
+        <v>3.63</v>
       </c>
       <c r="N14" t="n">
-        <v>2.8</v>
+        <v>5.8</v>
       </c>
       <c r="O14" t="n">
-        <v>3.26</v>
+        <v>2.26</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.2</v>
+        <v>4.9</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="S14" t="n">
-        <v>2.65</v>
+        <v>2.98</v>
       </c>
       <c r="T14" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="U14" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="V14" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.63</v>
+        <v>3.38</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.47</v>
+        <v>2.18</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.61</v>
+        <v>1.81</v>
       </c>
       <c r="M15" t="n">
-        <v>3.63</v>
+        <v>3.45</v>
       </c>
       <c r="N15" t="n">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="O15" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="P15" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="R15" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
-        <v>2.98</v>
+        <v>2.65</v>
       </c>
       <c r="T15" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="U15" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="V15" t="n">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="W15" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG15" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AH15" t="n">
-        <v>2.18</v>
+        <v>1.99</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.26</v>
+        <v>6.9</v>
       </c>
       <c r="M17" t="n">
+        <v>5</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="O17" t="n">
         <v>6</v>
       </c>
-      <c r="N17" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.66</v>
-      </c>
       <c r="P17" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.8</v>
+        <v>1.83</v>
       </c>
       <c r="R17" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S17" t="n">
-        <v>4.55</v>
+        <v>3.75</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="U17" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="V17" t="n">
-        <v>3.75</v>
+        <v>4.75</v>
       </c>
       <c r="W17" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="Z17" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.33</v>
+        <v>1.63</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.15</v>
+        <v>2.25</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.76</v>
+        <v>2.35</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.95</v>
+        <v>1.52</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AH17" t="n">
-        <v>3.4</v>
+        <v>1.13</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,55 +2563,55 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.07</v>
+        <v>1.71</v>
       </c>
       <c r="M18" t="n">
-        <v>3.56</v>
+        <v>3.92</v>
       </c>
       <c r="N18" t="n">
-        <v>3.27</v>
+        <v>4.33</v>
       </c>
       <c r="O18" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="P18" t="n">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="R18" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="S18" t="n">
-        <v>3.32</v>
+        <v>3.5</v>
       </c>
       <c r="T18" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="U18" t="n">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="V18" t="n">
-        <v>5.75</v>
+        <v>5.05</v>
       </c>
       <c r="W18" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="Z18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AC18" t="n">
         <v>2.3</v>
@@ -2620,16 +2620,16 @@
         <v>1.6</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.2</v>
+        <v>2.49</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.71</v>
+        <v>2.32</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.63</v>
+        <v>2.29</v>
       </c>
       <c r="M19" t="n">
-        <v>3.51</v>
+        <v>3.39</v>
       </c>
       <c r="N19" t="n">
-        <v>2.47</v>
+        <v>2.95</v>
       </c>
       <c r="O19" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="P19" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="R19" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="S19" t="n">
-        <v>3.45</v>
+        <v>3.02</v>
       </c>
       <c r="T19" t="n">
-        <v>2.39</v>
+        <v>2.62</v>
       </c>
       <c r="U19" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="V19" t="n">
-        <v>5.5</v>
+        <v>6.1</v>
       </c>
       <c r="W19" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.63</v>
+        <v>1.79</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.46</v>
+        <v>3.02</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.64</v>
+        <v>2.29</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.71</v>
+        <v>2.52</v>
       </c>
       <c r="M20" t="n">
-        <v>3.92</v>
+        <v>3.13</v>
       </c>
       <c r="N20" t="n">
-        <v>4.33</v>
+        <v>2.83</v>
       </c>
       <c r="O20" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="P20" t="n">
-        <v>2.45</v>
+        <v>1.91</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="R20" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U20" t="n">
         <v>1.28</v>
       </c>
-      <c r="S20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.64</v>
-      </c>
       <c r="V20" t="n">
-        <v>5.05</v>
+        <v>8.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="X20" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.13</v>
+        <v>1.43</v>
       </c>
       <c r="Z20" t="n">
-        <v>5</v>
+        <v>2.75</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.65</v>
+        <v>2.28</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.2</v>
+        <v>1.55</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.3</v>
+        <v>4.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.6</v>
+        <v>1.17</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.61</v>
+        <v>2.01</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.49</v>
+        <v>1.81</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.32</v>
+        <v>1.39</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>6.9</v>
+        <v>1.26</v>
       </c>
       <c r="M21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N21" t="n">
-        <v>1.38</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>6</v>
+        <v>1.66</v>
       </c>
       <c r="P21" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.83</v>
+        <v>5.8</v>
       </c>
       <c r="R21" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="S21" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V21" t="n">
         <v>3.75</v>
       </c>
-      <c r="T21" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V21" t="n">
-        <v>4.75</v>
-      </c>
       <c r="W21" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="Z21" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.25</v>
+        <v>3.15</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.35</v>
+        <v>1.76</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.52</v>
+        <v>1.95</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.13</v>
+        <v>3.4</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.29</v>
+        <v>2.63</v>
       </c>
       <c r="M22" t="n">
-        <v>3.39</v>
+        <v>3.51</v>
       </c>
       <c r="N22" t="n">
-        <v>2.95</v>
+        <v>2.47</v>
       </c>
       <c r="O22" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="P22" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="R22" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="S22" t="n">
-        <v>3.02</v>
+        <v>3.45</v>
       </c>
       <c r="T22" t="n">
-        <v>2.62</v>
+        <v>2.39</v>
       </c>
       <c r="U22" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="V22" t="n">
-        <v>6.1</v>
+        <v>5.5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X22" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AG22" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z22" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH22" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.52</v>
+        <v>2.07</v>
       </c>
       <c r="M23" t="n">
-        <v>3.13</v>
+        <v>3.56</v>
       </c>
       <c r="N23" t="n">
-        <v>2.83</v>
+        <v>3.27</v>
       </c>
       <c r="O23" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="P23" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V23" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB23" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q23" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V23" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AC23" t="n">
-        <v>4.1</v>
+        <v>2.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.17</v>
+        <v>1.6</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.01</v>
+        <v>1.64</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.81</v>
+        <v>2.2</v>
       </c>
       <c r="AG23" t="n">
         <v>1.31</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.39</v>
+        <v>1.71</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45987.70833333334</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,49 +1611,49 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5.1</v>
+        <v>1.32</v>
       </c>
       <c r="M10" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="N10" t="n">
-        <v>1.6</v>
+        <v>9</v>
       </c>
       <c r="O10" t="n">
-        <v>4.31</v>
+        <v>1.77</v>
       </c>
       <c r="P10" t="n">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.06</v>
+        <v>7</v>
       </c>
       <c r="R10" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="S10" t="n">
-        <v>3.36</v>
+        <v>3.58</v>
       </c>
       <c r="T10" t="n">
-        <v>2.39</v>
+        <v>2.28</v>
       </c>
       <c r="U10" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="V10" t="n">
-        <v>5.3</v>
+        <v>4.95</v>
       </c>
       <c r="W10" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.15</v>
+        <v>5</v>
       </c>
       <c r="AA10" t="n">
         <v>1.58</v>
@@ -1662,22 +1662,22 @@
         <v>2.35</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.25</v>
+        <v>1.99</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.27</v>
+        <v>1.08</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.19</v>
+        <v>3.1</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45987.61458333334</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,49 +1730,49 @@
         </is>
       </c>
       <c r="L11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O11" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R11" t="n">
         <v>1.32</v>
       </c>
-      <c r="M11" t="n">
-        <v>5</v>
-      </c>
-      <c r="N11" t="n">
-        <v>9</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>7</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.27</v>
-      </c>
       <c r="S11" t="n">
-        <v>3.58</v>
+        <v>3.36</v>
       </c>
       <c r="T11" t="n">
-        <v>2.28</v>
+        <v>2.39</v>
       </c>
       <c r="U11" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="V11" t="n">
-        <v>4.95</v>
+        <v>5.3</v>
       </c>
       <c r="W11" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z11" t="n">
-        <v>5</v>
+        <v>4.15</v>
       </c>
       <c r="AA11" t="n">
         <v>1.58</v>
@@ -1781,22 +1781,22 @@
         <v>2.35</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.99</v>
+        <v>2.25</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.1</v>
+        <v>1.19</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45987.61458333334</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,49 +1968,49 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.44</v>
+        <v>1.81</v>
       </c>
       <c r="M13" t="n">
-        <v>3.31</v>
+        <v>3.45</v>
       </c>
       <c r="N13" t="n">
-        <v>2.8</v>
+        <v>4.4</v>
       </c>
       <c r="O13" t="n">
-        <v>3.26</v>
+        <v>2.32</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S13" t="n">
         <v>2.65</v>
       </c>
       <c r="T13" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="U13" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V13" t="n">
-        <v>7.4</v>
+        <v>6.75</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.08</v>
+        <v>3.5</v>
       </c>
       <c r="AA13" t="n">
         <v>1.98</v>
@@ -2019,22 +2019,22 @@
         <v>1.77</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.63</v>
+        <v>3.35</v>
       </c>
       <c r="AD13" t="n">
         <v>1.25</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AF13" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.47</v>
+        <v>1.99</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,49 +2206,49 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.81</v>
+        <v>2.44</v>
       </c>
       <c r="M15" t="n">
-        <v>3.45</v>
+        <v>3.31</v>
       </c>
       <c r="N15" t="n">
-        <v>4.4</v>
+        <v>2.8</v>
       </c>
       <c r="O15" t="n">
-        <v>2.32</v>
+        <v>3.26</v>
       </c>
       <c r="P15" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="R15" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
         <v>2.65</v>
       </c>
       <c r="T15" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="U15" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V15" t="n">
-        <v>6.75</v>
+        <v>7.4</v>
       </c>
       <c r="W15" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.5</v>
+        <v>3.08</v>
       </c>
       <c r="AA15" t="n">
         <v>1.98</v>
@@ -2257,22 +2257,22 @@
         <v>1.77</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.35</v>
+        <v>3.63</v>
       </c>
       <c r="AD15" t="n">
         <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.99</v>
+        <v>1.47</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,49 +2444,49 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>6.9</v>
+        <v>2.63</v>
       </c>
       <c r="M17" t="n">
-        <v>5</v>
+        <v>3.51</v>
       </c>
       <c r="N17" t="n">
-        <v>1.38</v>
+        <v>2.47</v>
       </c>
       <c r="O17" t="n">
-        <v>6</v>
+        <v>3.25</v>
       </c>
       <c r="P17" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.83</v>
+        <v>3</v>
       </c>
       <c r="R17" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="S17" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="T17" t="n">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="U17" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="V17" t="n">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z17" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AA17" t="n">
         <v>1.63</v>
@@ -2495,22 +2495,22 @@
         <v>2.25</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.35</v>
+        <v>2.46</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.14</v>
+        <v>2.64</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.13</v>
+        <v>1.44</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.29</v>
+        <v>6.9</v>
       </c>
       <c r="M19" t="n">
-        <v>3.39</v>
+        <v>5</v>
       </c>
       <c r="N19" t="n">
-        <v>2.95</v>
+        <v>1.38</v>
       </c>
       <c r="O19" t="n">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="P19" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.3</v>
+        <v>1.83</v>
       </c>
       <c r="R19" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="S19" t="n">
-        <v>3.02</v>
+        <v>3.75</v>
       </c>
       <c r="T19" t="n">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="U19" t="n">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="V19" t="n">
-        <v>6.1</v>
+        <v>4.75</v>
       </c>
       <c r="W19" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="X19" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.79</v>
+        <v>1.63</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.02</v>
+        <v>2.35</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.29</v>
+        <v>2.14</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.67</v>
+        <v>1.13</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.26</v>
+        <v>2.29</v>
       </c>
       <c r="M21" t="n">
-        <v>6</v>
+        <v>3.39</v>
       </c>
       <c r="N21" t="n">
-        <v>8.800000000000001</v>
+        <v>2.95</v>
       </c>
       <c r="O21" t="n">
-        <v>1.66</v>
+        <v>2.8</v>
       </c>
       <c r="P21" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.8</v>
+        <v>3.3</v>
       </c>
       <c r="R21" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="S21" t="n">
-        <v>4.55</v>
+        <v>3.02</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>2.62</v>
       </c>
       <c r="U21" t="n">
-        <v>1.9</v>
+        <v>1.48</v>
       </c>
       <c r="V21" t="n">
-        <v>3.75</v>
+        <v>6.1</v>
       </c>
       <c r="W21" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y21" t="n">
         <v>1.25</v>
       </c>
-      <c r="X21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.04</v>
-      </c>
       <c r="Z21" t="n">
-        <v>7.5</v>
+        <v>3.8</v>
       </c>
       <c r="AA21" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AG21" t="n">
         <v>1.33</v>
       </c>
-      <c r="AB21" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AH21" t="n">
-        <v>3.4</v>
+        <v>1.67</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.63</v>
+        <v>1.26</v>
       </c>
       <c r="M22" t="n">
-        <v>3.51</v>
+        <v>6</v>
       </c>
       <c r="N22" t="n">
-        <v>2.47</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>3.25</v>
+        <v>1.66</v>
       </c>
       <c r="P22" t="n">
-        <v>2.15</v>
+        <v>2.7</v>
       </c>
       <c r="Q22" t="n">
-        <v>3</v>
+        <v>5.8</v>
       </c>
       <c r="R22" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="S22" t="n">
-        <v>3.45</v>
+        <v>4.55</v>
       </c>
       <c r="T22" t="n">
-        <v>2.39</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="V22" t="n">
-        <v>5.5</v>
+        <v>3.75</v>
       </c>
       <c r="W22" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="X22" t="n">
         <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.19</v>
+        <v>1.04</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.25</v>
+        <v>3.15</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.46</v>
+        <v>1.76</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.47</v>
+        <v>1.95</v>
       </c>
       <c r="AE22" t="n">
         <v>1.53</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.64</v>
+        <v>2.3</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.44</v>
+        <v>3.4</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45987.70833333334</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI25"/>
+  <dimension ref="A1:AI27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1135,22 +1135,22 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="M6" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="O6" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="P6" t="n">
         <v>1.96</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="R6" t="n">
         <v>1.44</v>
@@ -1171,25 +1171,25 @@
         <v>1.05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.63</v>
+        <v>2.35</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="AC6" t="n">
         <v>4.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AE6" t="n">
         <v>1.97</v>
@@ -1198,10 +1198,10 @@
         <v>1.62</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45987.45833333334</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O8" t="n">
         <v>4</v>
       </c>
-      <c r="M8" t="n">
+      <c r="P8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q8" t="n">
         <v>2.9</v>
       </c>
-      <c r="N8" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="O8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.75</v>
-      </c>
       <c r="R8" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S8" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="T8" t="n">
         <v>3.75</v>
       </c>
       <c r="U8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="V8" t="n">
+        <v>12</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH8" t="n">
         <v>1.25</v>
-      </c>
-      <c r="V8" t="n">
-        <v>11</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.22</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45987.60416666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="M9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="O9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q9" t="n">
         <v>2.75</v>
       </c>
-      <c r="N9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O9" t="n">
-        <v>4</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.9</v>
-      </c>
       <c r="R9" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="S9" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="T9" t="n">
         <v>3.75</v>
       </c>
       <c r="U9" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="V9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.4</v>
+        <v>5.25</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45987.60416666666</v>
@@ -1968,19 +1968,19 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="M13" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="N13" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O13" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="P13" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="Q13" t="n">
         <v>4.6</v>
@@ -2001,7 +2001,7 @@
         <v>6.75</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
         <v>1.02</v>
@@ -2016,7 +2016,7 @@
         <v>1.98</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AC13" t="n">
         <v>3.35</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.61</v>
+        <v>2.55</v>
       </c>
       <c r="M14" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC14" t="n">
         <v>3.63</v>
       </c>
-      <c r="N14" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="O14" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V14" t="n">
-        <v>7</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.38</v>
-      </c>
       <c r="AD14" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.18</v>
+        <v>1.5</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.44</v>
+        <v>2.12</v>
       </c>
       <c r="M15" t="n">
-        <v>3.31</v>
+        <v>3.35</v>
       </c>
       <c r="N15" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="O15" t="n">
-        <v>3.26</v>
+        <v>2.75</v>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
         <v>2.65</v>
       </c>
       <c r="T15" t="n">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="U15" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V15" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG15" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z15" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH15" t="n">
-        <v>1.47</v>
+        <v>1.64</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.07</v>
+        <v>1.48</v>
       </c>
       <c r="M16" t="n">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="N16" t="n">
-        <v>3.45</v>
+        <v>4.79</v>
       </c>
       <c r="O16" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="P16" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.85</v>
+        <v>5.78</v>
       </c>
       <c r="R16" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S16" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="T16" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="U16" t="n">
         <v>1.36</v>
       </c>
       <c r="V16" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="W16" t="n">
         <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.38</v>
+        <v>3.61</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.82</v>
+        <v>2.01</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.69</v>
+        <v>2.17</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.63</v>
+        <v>2.07</v>
       </c>
       <c r="M17" t="n">
-        <v>3.51</v>
+        <v>3.56</v>
       </c>
       <c r="N17" t="n">
-        <v>2.47</v>
+        <v>3.27</v>
       </c>
       <c r="O17" t="n">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="P17" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="Q17" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="R17" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S17" t="n">
-        <v>3.45</v>
+        <v>3.32</v>
       </c>
       <c r="T17" t="n">
-        <v>2.39</v>
+        <v>2.6</v>
       </c>
       <c r="U17" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="V17" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="W17" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.63</v>
+        <v>1.79</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.64</v>
+        <v>2.2</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.44</v>
+        <v>1.71</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,55 +2563,55 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.71</v>
+        <v>1.43</v>
       </c>
       <c r="M18" t="n">
-        <v>3.92</v>
+        <v>4.6</v>
       </c>
       <c r="N18" t="n">
-        <v>4.33</v>
+        <v>6.6</v>
       </c>
       <c r="O18" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="P18" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.2</v>
+        <v>6.5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="S18" t="n">
-        <v>3.5</v>
+        <v>3.66</v>
       </c>
       <c r="T18" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="U18" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="V18" t="n">
-        <v>5.05</v>
+        <v>4.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X18" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z18" t="n">
         <v>5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.65</v>
+        <v>1.49</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.2</v>
+        <v>2.51</v>
       </c>
       <c r="AC18" t="n">
         <v>2.3</v>
@@ -2620,16 +2620,16 @@
         <v>1.6</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.49</v>
+        <v>2.1</v>
       </c>
       <c r="AG18" t="n">
         <v>1.18</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.32</v>
+        <v>3</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>6.9</v>
+        <v>2.29</v>
       </c>
       <c r="M19" t="n">
-        <v>5</v>
+        <v>3.39</v>
       </c>
       <c r="N19" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R19" t="n">
         <v>1.38</v>
       </c>
-      <c r="O19" t="n">
-        <v>6</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.22</v>
-      </c>
       <c r="S19" t="n">
-        <v>3.75</v>
+        <v>3.02</v>
       </c>
       <c r="T19" t="n">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="U19" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V19" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE19" t="n">
         <v>1.67</v>
       </c>
-      <c r="V19" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AF19" t="n">
-        <v>2.14</v>
+        <v>2.29</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.13</v>
+        <v>1.67</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.52</v>
+        <v>1.26</v>
       </c>
       <c r="M20" t="n">
-        <v>3.13</v>
+        <v>6</v>
       </c>
       <c r="N20" t="n">
-        <v>2.83</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O20" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S20" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V20" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AH20" t="n">
         <v>3.4</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V20" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.39</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.29</v>
+        <v>6.9</v>
       </c>
       <c r="M21" t="n">
-        <v>3.39</v>
+        <v>5</v>
       </c>
       <c r="N21" t="n">
-        <v>2.95</v>
+        <v>1.38</v>
       </c>
       <c r="O21" t="n">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="P21" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.3</v>
+        <v>1.83</v>
       </c>
       <c r="R21" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="S21" t="n">
-        <v>3.02</v>
+        <v>3.75</v>
       </c>
       <c r="T21" t="n">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="U21" t="n">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="V21" t="n">
-        <v>6.1</v>
+        <v>4.75</v>
       </c>
       <c r="W21" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="X21" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.79</v>
+        <v>1.63</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.02</v>
+        <v>2.35</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.29</v>
+        <v>2.14</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.67</v>
+        <v>1.13</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.26</v>
+        <v>1.71</v>
       </c>
       <c r="M22" t="n">
-        <v>6</v>
+        <v>3.92</v>
       </c>
       <c r="N22" t="n">
-        <v>8.800000000000001</v>
+        <v>4.33</v>
       </c>
       <c r="O22" t="n">
-        <v>1.66</v>
+        <v>2.2</v>
       </c>
       <c r="P22" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="R22" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V22" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AG22" t="n">
         <v>1.18</v>
       </c>
-      <c r="S22" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="V22" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AH22" t="n">
-        <v>3.4</v>
+        <v>2.32</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.07</v>
+        <v>2.63</v>
       </c>
       <c r="M23" t="n">
-        <v>3.56</v>
+        <v>3.51</v>
       </c>
       <c r="N23" t="n">
-        <v>3.27</v>
+        <v>2.47</v>
       </c>
       <c r="O23" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="P23" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="R23" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S23" t="n">
-        <v>3.32</v>
+        <v>3.45</v>
       </c>
       <c r="T23" t="n">
-        <v>2.6</v>
+        <v>2.39</v>
       </c>
       <c r="U23" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="V23" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z23" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.79</v>
+        <v>1.63</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.2</v>
+        <v>2.64</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.71</v>
+        <v>1.44</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="O24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V24" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y24" t="n">
         <v>1.43</v>
       </c>
-      <c r="M24" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="N24" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.11</v>
-      </c>
       <c r="Z24" t="n">
-        <v>5</v>
+        <v>2.75</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.49</v>
+        <v>2.38</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.51</v>
+        <v>1.57</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.3</v>
+        <v>4.05</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.6</v>
+        <v>1.18</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.18</v>
+        <v>1.45</v>
       </c>
       <c r="AH24" t="n">
-        <v>3</v>
+        <v>1.44</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3355,117 +3355,355 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Chile Primera B</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>San Marcos</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Cobreloa</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M25" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" s="3" t="n">
+        <v>45987.75</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>45987</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Brazil Serie A</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Bragantino</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>Fortaleza</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="inlineStr">
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L25" t="n">
+      <c r="L26" t="n">
         <v>1.96</v>
       </c>
-      <c r="M25" t="n">
+      <c r="M26" t="n">
         <v>3.25</v>
       </c>
-      <c r="N25" t="n">
+      <c r="N26" t="n">
         <v>3.31</v>
       </c>
-      <c r="O25" t="n">
+      <c r="O26" t="n">
         <v>2.55</v>
       </c>
-      <c r="P25" t="n">
+      <c r="P26" t="n">
         <v>2.16</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="Q26" t="n">
         <v>3.8</v>
       </c>
-      <c r="R25" t="n">
+      <c r="R26" t="n">
         <v>1.38</v>
       </c>
-      <c r="S25" t="n">
+      <c r="S26" t="n">
         <v>2.95</v>
       </c>
-      <c r="T25" t="n">
+      <c r="T26" t="n">
         <v>2.7</v>
       </c>
-      <c r="U25" t="n">
+      <c r="U26" t="n">
         <v>1.41</v>
       </c>
-      <c r="V25" t="n">
+      <c r="V26" t="n">
         <v>5.9</v>
       </c>
-      <c r="W25" t="n">
+      <c r="W26" t="n">
         <v>1.07</v>
       </c>
-      <c r="X25" t="n">
+      <c r="X26" t="n">
         <v>1</v>
       </c>
-      <c r="Y25" t="n">
+      <c r="Y26" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z25" t="n">
+      <c r="Z26" t="n">
         <v>3.52</v>
       </c>
-      <c r="AA25" t="n">
+      <c r="AA26" t="n">
         <v>1.85</v>
       </c>
-      <c r="AB25" t="n">
+      <c r="AB26" t="n">
         <v>1.85</v>
       </c>
-      <c r="AC25" t="n">
+      <c r="AC26" t="n">
         <v>2.85</v>
       </c>
-      <c r="AD25" t="n">
+      <c r="AD26" t="n">
         <v>1.33</v>
       </c>
-      <c r="AE25" t="n">
+      <c r="AE26" t="n">
         <v>1.67</v>
       </c>
-      <c r="AF25" t="n">
+      <c r="AF26" t="n">
         <v>1.95</v>
       </c>
-      <c r="AG25" t="n">
+      <c r="AG26" t="n">
         <v>1.22</v>
       </c>
-      <c r="AH25" t="n">
+      <c r="AH26" t="n">
         <v>1.74</v>
       </c>
-      <c r="AI25" s="3" t="n">
+      <c r="AI26" s="3" t="n">
         <v>45987.79166666666</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>45987</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Chile Primera B</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Concepción</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" s="3" t="n">
+        <v>45987.85416666666</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="M2" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="N2" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="O2" t="n">
         <v>3.4</v>
@@ -781,70 +781,70 @@
         <v>2.8</v>
       </c>
       <c r="M3" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="N3" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="O3" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="P3" t="n">
         <v>1.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.25</v>
+        <v>3.09</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45987.375</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45987.41666666666</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="M6" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="N6" t="n">
-        <v>3.9</v>
+        <v>3.58</v>
       </c>
       <c r="O6" t="n">
         <v>2.76</v>
@@ -1180,10 +1180,10 @@
         <v>2.35</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="AC6" t="n">
         <v>4.1</v>
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45987.54166666666</v>
@@ -1382,31 +1382,31 @@
         <v>2.3</v>
       </c>
       <c r="O8" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P8" t="n">
         <v>1.85</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="R8" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S8" t="n">
         <v>2.3</v>
       </c>
       <c r="T8" t="n">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="U8" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="V8" t="n">
         <v>12</v>
       </c>
       <c r="W8" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X8" t="n">
         <v>1.11</v>
@@ -1424,10 +1424,10 @@
         <v>1.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.4</v>
+        <v>5.35</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AE8" t="n">
         <v>2.21</v>
@@ -1516,7 +1516,7 @@
         <v>2.4</v>
       </c>
       <c r="T9" t="n">
-        <v>3.75</v>
+        <v>3.68</v>
       </c>
       <c r="U9" t="n">
         <v>1.25</v>
@@ -1525,7 +1525,7 @@
         <v>11</v>
       </c>
       <c r="W9" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
         <v>1.08</v>
@@ -1537,25 +1537,25 @@
         <v>2.1</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="AB9" t="n">
         <v>1.44</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="AF9" t="n">
         <v>1.65</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="AH9" t="n">
         <v>1.22</v>
@@ -1629,28 +1629,28 @@
         <v>7</v>
       </c>
       <c r="R10" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="S10" t="n">
-        <v>3.58</v>
+        <v>3.54</v>
       </c>
       <c r="T10" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="U10" t="n">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="V10" t="n">
-        <v>4.95</v>
+        <v>4.75</v>
       </c>
       <c r="W10" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X10" t="n">
         <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="Z10" t="n">
         <v>5</v>
@@ -1671,13 +1671,13 @@
         <v>1.75</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45987.61458333334</v>
@@ -1739,13 +1739,13 @@
         <v>1.6</v>
       </c>
       <c r="O11" t="n">
-        <v>4.31</v>
+        <v>5.1</v>
       </c>
       <c r="P11" t="n">
         <v>2.53</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="R11" t="n">
         <v>1.32</v>
@@ -1769,7 +1769,7 @@
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z11" t="n">
         <v>4.15</v>
@@ -1790,13 +1790,13 @@
         <v>1.68</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45987.61458333334</v>
@@ -1858,7 +1858,7 @@
         <v>3.2</v>
       </c>
       <c r="O12" t="n">
-        <v>2.58</v>
+        <v>2.45</v>
       </c>
       <c r="P12" t="n">
         <v>2.2</v>
@@ -1891,7 +1891,7 @@
         <v>1.18</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.6</v>
+        <v>4.25</v>
       </c>
       <c r="AA12" t="n">
         <v>1.65</v>
@@ -1903,19 +1903,19 @@
         <v>2.45</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AE12" t="n">
         <v>1.53</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45987.625</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,22 +1968,22 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.77</v>
+        <v>2.07</v>
       </c>
       <c r="M13" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="N13" t="n">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="O13" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="P13" t="n">
         <v>2.15</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="R13" t="n">
         <v>1.42</v>
@@ -1992,13 +1992,13 @@
         <v>2.65</v>
       </c>
       <c r="T13" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="U13" t="n">
         <v>1.36</v>
       </c>
       <c r="V13" t="n">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="W13" t="n">
         <v>1.04</v>
@@ -2007,34 +2007,34 @@
         <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="AA13" t="n">
         <v>1.98</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.99</v>
+        <v>1.64</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.55</v>
+        <v>1.61</v>
       </c>
       <c r="M14" t="n">
-        <v>3.21</v>
+        <v>3.63</v>
       </c>
       <c r="N14" t="n">
-        <v>2.6</v>
+        <v>5.8</v>
       </c>
       <c r="O14" t="n">
-        <v>3.26</v>
+        <v>2.2</v>
       </c>
       <c r="P14" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.35</v>
+        <v>5.78</v>
       </c>
       <c r="R14" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S14" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="T14" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="U14" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
         <v>1.33</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.14</v>
+        <v>1.87</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.63</v>
+        <v>3.61</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.79</v>
+        <v>2.01</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.5</v>
+        <v>2.17</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,22 +2206,22 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.12</v>
+        <v>1.81</v>
       </c>
       <c r="M15" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="N15" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="O15" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="P15" t="n">
         <v>2.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="R15" t="n">
         <v>1.42</v>
@@ -2230,13 +2230,13 @@
         <v>2.65</v>
       </c>
       <c r="T15" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="U15" t="n">
         <v>1.36</v>
       </c>
       <c r="V15" t="n">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="W15" t="n">
         <v>1.04</v>
@@ -2245,34 +2245,34 @@
         <v>1.02</v>
       </c>
       <c r="Y15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG15" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH15" t="n">
-        <v>1.64</v>
+        <v>1.99</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.48</v>
+        <v>2.44</v>
       </c>
       <c r="M16" t="n">
-        <v>3.85</v>
+        <v>3.31</v>
       </c>
       <c r="N16" t="n">
-        <v>4.79</v>
+        <v>2.8</v>
       </c>
       <c r="O16" t="n">
-        <v>2.2</v>
+        <v>3.26</v>
       </c>
       <c r="P16" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.78</v>
+        <v>3.35</v>
       </c>
       <c r="R16" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S16" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="T16" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="U16" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V16" t="n">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y16" t="n">
         <v>1.33</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.61</v>
+        <v>3.63</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.01</v>
+        <v>1.79</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.17</v>
+        <v>1.5</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.07</v>
+        <v>2.52</v>
       </c>
       <c r="M17" t="n">
-        <v>3.56</v>
+        <v>3.13</v>
       </c>
       <c r="N17" t="n">
-        <v>3.27</v>
+        <v>2.83</v>
       </c>
       <c r="O17" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="P17" t="n">
-        <v>2.18</v>
+        <v>1.91</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="R17" t="n">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="S17" t="n">
-        <v>3.32</v>
+        <v>2.57</v>
       </c>
       <c r="T17" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="U17" t="n">
-        <v>1.52</v>
+        <v>1.3</v>
       </c>
       <c r="V17" t="n">
-        <v>5.75</v>
+        <v>8.1</v>
       </c>
       <c r="W17" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="Z17" t="n">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.79</v>
+        <v>2.28</v>
       </c>
       <c r="AB17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE17" t="n">
         <v>1.91</v>
       </c>
-      <c r="AC17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.64</v>
-      </c>
       <c r="AF17" t="n">
-        <v>2.2</v>
+        <v>1.82</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.31</v>
+        <v>1.45</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.71</v>
+        <v>1.44</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.43</v>
+        <v>1.71</v>
       </c>
       <c r="M18" t="n">
-        <v>4.6</v>
+        <v>3.92</v>
       </c>
       <c r="N18" t="n">
-        <v>6.6</v>
+        <v>4.33</v>
       </c>
       <c r="O18" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="P18" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.5</v>
+        <v>4.2</v>
       </c>
       <c r="R18" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S18" t="n">
-        <v>3.66</v>
+        <v>3.5</v>
       </c>
       <c r="T18" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="U18" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V18" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AA18" t="n">
         <v>1.65</v>
       </c>
-      <c r="V18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.49</v>
-      </c>
       <c r="AB18" t="n">
-        <v>2.51</v>
+        <v>2.2</v>
       </c>
       <c r="AC18" t="n">
         <v>2.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.1</v>
+        <v>2.47</v>
       </c>
       <c r="AG18" t="n">
         <v>1.18</v>
       </c>
       <c r="AH18" t="n">
-        <v>3</v>
+        <v>2.15</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.29</v>
+        <v>1.26</v>
       </c>
       <c r="M19" t="n">
-        <v>3.39</v>
+        <v>6</v>
       </c>
       <c r="N19" t="n">
-        <v>2.95</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>2.8</v>
+        <v>1.73</v>
       </c>
       <c r="P19" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.3</v>
+        <v>5.8</v>
       </c>
       <c r="R19" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="S19" t="n">
-        <v>3.02</v>
+        <v>4.7</v>
       </c>
       <c r="T19" t="n">
-        <v>2.62</v>
+        <v>2.01</v>
       </c>
       <c r="U19" t="n">
-        <v>1.48</v>
+        <v>1.9</v>
       </c>
       <c r="V19" t="n">
-        <v>6.1</v>
+        <v>3.75</v>
       </c>
       <c r="W19" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="X19" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.8</v>
+        <v>7.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.79</v>
+        <v>1.33</v>
       </c>
       <c r="AB19" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AD19" t="n">
         <v>1.95</v>
       </c>
-      <c r="AC19" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AE19" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.67</v>
+        <v>3.4</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.26</v>
+        <v>2.63</v>
       </c>
       <c r="M20" t="n">
-        <v>6</v>
+        <v>3.51</v>
       </c>
       <c r="N20" t="n">
-        <v>8.800000000000001</v>
+        <v>2.47</v>
       </c>
       <c r="O20" t="n">
-        <v>1.66</v>
+        <v>3.16</v>
       </c>
       <c r="P20" t="n">
-        <v>2.7</v>
+        <v>2.15</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.8</v>
+        <v>3</v>
       </c>
       <c r="R20" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="S20" t="n">
-        <v>4.55</v>
+        <v>3.36</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>2.39</v>
       </c>
       <c r="U20" t="n">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="V20" t="n">
-        <v>3.75</v>
+        <v>5.45</v>
       </c>
       <c r="W20" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="X20" t="n">
         <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.04</v>
+        <v>1.19</v>
       </c>
       <c r="Z20" t="n">
-        <v>7.5</v>
+        <v>4.45</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.33</v>
+        <v>1.63</v>
       </c>
       <c r="AB20" t="n">
-        <v>3.15</v>
+        <v>2.25</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.76</v>
+        <v>2.46</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.95</v>
+        <v>1.47</v>
       </c>
       <c r="AE20" t="n">
         <v>1.53</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AH20" t="n">
-        <v>3.4</v>
+        <v>1.44</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>6.9</v>
+        <v>1.43</v>
       </c>
       <c r="M21" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="N21" t="n">
-        <v>1.38</v>
+        <v>6.6</v>
       </c>
       <c r="O21" t="n">
-        <v>6</v>
+        <v>1.79</v>
       </c>
       <c r="P21" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.83</v>
+        <v>5.5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="S21" t="n">
-        <v>3.75</v>
+        <v>3.62</v>
       </c>
       <c r="T21" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="U21" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="V21" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="W21" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="Z21" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.63</v>
+        <v>1.49</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.25</v>
+        <v>2.51</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.13</v>
+        <v>3</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,55 +3039,55 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.71</v>
+        <v>2.07</v>
       </c>
       <c r="M22" t="n">
-        <v>3.92</v>
+        <v>3.56</v>
       </c>
       <c r="N22" t="n">
-        <v>4.33</v>
+        <v>3.27</v>
       </c>
       <c r="O22" t="n">
-        <v>2.2</v>
+        <v>2.53</v>
       </c>
       <c r="P22" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="R22" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="S22" t="n">
-        <v>3.5</v>
+        <v>3.32</v>
       </c>
       <c r="T22" t="n">
-        <v>2.2</v>
+        <v>2.47</v>
       </c>
       <c r="U22" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="V22" t="n">
-        <v>5.05</v>
+        <v>5.75</v>
       </c>
       <c r="W22" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="X22" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="Z22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AC22" t="n">
         <v>2.3</v>
@@ -3096,16 +3096,16 @@
         <v>1.6</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.49</v>
+        <v>2.2</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.32</v>
+        <v>1.7</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.63</v>
+        <v>2.29</v>
       </c>
       <c r="M23" t="n">
-        <v>3.51</v>
+        <v>3.39</v>
       </c>
       <c r="N23" t="n">
-        <v>2.47</v>
+        <v>2.95</v>
       </c>
       <c r="O23" t="n">
-        <v>3.25</v>
+        <v>2.85</v>
       </c>
       <c r="P23" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V23" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF23" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q23" t="n">
-        <v>3</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V23" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>2.64</v>
-      </c>
       <c r="AG23" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.72</v>
+        <v>6.9</v>
       </c>
       <c r="M24" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="N24" t="n">
-        <v>2.65</v>
+        <v>1.38</v>
       </c>
       <c r="O24" t="n">
-        <v>3.4</v>
+        <v>5.03</v>
       </c>
       <c r="P24" t="n">
-        <v>1.91</v>
+        <v>2.45</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.25</v>
+        <v>1.83</v>
       </c>
       <c r="R24" t="n">
-        <v>1.49</v>
+        <v>1.25</v>
       </c>
       <c r="S24" t="n">
-        <v>2.57</v>
+        <v>3.75</v>
       </c>
       <c r="T24" t="n">
-        <v>3.3</v>
+        <v>2.25</v>
       </c>
       <c r="U24" t="n">
-        <v>1.3</v>
+        <v>1.67</v>
       </c>
       <c r="V24" t="n">
-        <v>8.1</v>
+        <v>4.9</v>
       </c>
       <c r="W24" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X24" t="n">
         <v>1.02</v>
       </c>
-      <c r="X24" t="n">
-        <v>1.09</v>
-      </c>
       <c r="Y24" t="n">
-        <v>1.43</v>
+        <v>1.15</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.75</v>
+        <v>5</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.38</v>
+        <v>1.63</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.57</v>
+        <v>2.25</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.05</v>
+        <v>2.35</v>
       </c>
       <c r="AD24" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG24" t="n">
         <v>1.18</v>
       </c>
-      <c r="AE24" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AH24" t="n">
-        <v>1.44</v>
+        <v>1.11</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="M25" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="N25" t="n">
-        <v>3.13</v>
+        <v>2.85</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3524,28 +3524,28 @@
         <v>3.31</v>
       </c>
       <c r="O26" t="n">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="P26" t="n">
         <v>2.16</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="R26" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="S26" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="T26" t="n">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="U26" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="V26" t="n">
-        <v>5.9</v>
+        <v>5.95</v>
       </c>
       <c r="W26" t="n">
         <v>1.07</v>
@@ -3557,7 +3557,7 @@
         <v>1.22</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.52</v>
+        <v>3.6</v>
       </c>
       <c r="AA26" t="n">
         <v>1.85</v>
@@ -3572,16 +3572,16 @@
         <v>1.33</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45987.79166666666</v>
@@ -3637,10 +3637,10 @@
         <v>2.45</v>
       </c>
       <c r="M27" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="N27" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -1135,58 +1135,58 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="M6" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="N6" t="n">
-        <v>3.58</v>
+        <v>3.75</v>
       </c>
       <c r="O6" t="n">
         <v>2.76</v>
       </c>
       <c r="P6" t="n">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.33</v>
+        <v>4.68</v>
       </c>
       <c r="R6" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S6" t="n">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="T6" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="U6" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="V6" t="n">
-        <v>9.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W6" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
         <v>1.06</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.35</v>
+        <v>2.56</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AD6" t="n">
         <v>1.18</v>
@@ -1195,13 +1195,13 @@
         <v>1.97</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45987.45833333334</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="M8" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="O8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q8" t="n">
         <v>2.75</v>
       </c>
-      <c r="N8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.96</v>
-      </c>
       <c r="R8" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="S8" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="T8" t="n">
-        <v>3.74</v>
+        <v>3.8</v>
       </c>
       <c r="U8" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="V8" t="n">
         <v>12</v>
       </c>
       <c r="W8" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="AB8" t="n">
         <v>1.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.35</v>
+        <v>5.45</v>
       </c>
       <c r="AD8" t="n">
         <v>1.13</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.4</v>
+        <v>1.71</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45987.60416666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="M9" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="O9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q9" t="n">
         <v>2.9</v>
       </c>
-      <c r="N9" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="O9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.75</v>
-      </c>
       <c r="R9" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="S9" t="n">
-        <v>2.4</v>
+        <v>2.16</v>
       </c>
       <c r="T9" t="n">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="U9" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="V9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W9" t="n">
         <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.2</v>
+        <v>5.35</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG9" t="n">
         <v>1.4</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45987.60416666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,22 +1968,22 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.07</v>
+        <v>2.44</v>
       </c>
       <c r="M13" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q13" t="n">
         <v>3.35</v>
-      </c>
-      <c r="N13" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O13" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>3.75</v>
       </c>
       <c r="R13" t="n">
         <v>1.42</v>
@@ -1992,25 +1992,25 @@
         <v>2.65</v>
       </c>
       <c r="T13" t="n">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="U13" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V13" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AA13" t="n">
         <v>1.98</v>
@@ -2019,22 +2019,22 @@
         <v>1.77</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.38</v>
+        <v>3.63</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.61</v>
+        <v>2.07</v>
       </c>
       <c r="M14" t="n">
-        <v>3.63</v>
+        <v>3.35</v>
       </c>
       <c r="N14" t="n">
-        <v>5.8</v>
+        <v>3.45</v>
       </c>
       <c r="O14" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="P14" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.78</v>
+        <v>3.75</v>
       </c>
       <c r="R14" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S14" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="T14" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="U14" t="n">
         <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="W14" t="n">
         <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG14" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z14" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AH14" t="n">
-        <v>2.17</v>
+        <v>1.64</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,28 +2206,28 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.81</v>
+        <v>1.61</v>
       </c>
       <c r="M15" t="n">
-        <v>3.45</v>
+        <v>3.63</v>
       </c>
       <c r="N15" t="n">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="O15" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="P15" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.6</v>
+        <v>5.78</v>
       </c>
       <c r="R15" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S15" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="T15" t="n">
         <v>2.88</v>
@@ -2236,43 +2236,43 @@
         <v>1.36</v>
       </c>
       <c r="V15" t="n">
-        <v>6.75</v>
+        <v>7.1</v>
       </c>
       <c r="W15" t="n">
         <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.35</v>
+        <v>3.61</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="AF15" t="n">
         <v>1.85</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.99</v>
+        <v>2.17</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,22 +2325,22 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.44</v>
+        <v>1.81</v>
       </c>
       <c r="M16" t="n">
-        <v>3.31</v>
+        <v>3.45</v>
       </c>
       <c r="N16" t="n">
-        <v>2.8</v>
+        <v>4.4</v>
       </c>
       <c r="O16" t="n">
-        <v>3.26</v>
+        <v>2.4</v>
       </c>
       <c r="P16" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.35</v>
+        <v>4.6</v>
       </c>
       <c r="R16" t="n">
         <v>1.42</v>
@@ -2349,25 +2349,25 @@
         <v>2.65</v>
       </c>
       <c r="T16" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="U16" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V16" t="n">
-        <v>7.4</v>
+        <v>6.75</v>
       </c>
       <c r="W16" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA16" t="n">
         <v>1.98</v>
@@ -2376,22 +2376,22 @@
         <v>1.77</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.63</v>
+        <v>3.35</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AF16" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.5</v>
+        <v>1.99</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.52</v>
+        <v>6.9</v>
       </c>
       <c r="M17" t="n">
-        <v>3.13</v>
+        <v>5</v>
       </c>
       <c r="N17" t="n">
-        <v>2.83</v>
+        <v>1.38</v>
       </c>
       <c r="O17" t="n">
-        <v>3.4</v>
+        <v>5.03</v>
       </c>
       <c r="P17" t="n">
-        <v>1.91</v>
+        <v>2.45</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.25</v>
+        <v>1.83</v>
       </c>
       <c r="R17" t="n">
-        <v>1.49</v>
+        <v>1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>2.57</v>
+        <v>3.75</v>
       </c>
       <c r="T17" t="n">
-        <v>3.3</v>
+        <v>2.25</v>
       </c>
       <c r="U17" t="n">
-        <v>1.3</v>
+        <v>1.67</v>
       </c>
       <c r="V17" t="n">
-        <v>8.1</v>
+        <v>4.9</v>
       </c>
       <c r="W17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X17" t="n">
         <v>1.02</v>
       </c>
-      <c r="X17" t="n">
-        <v>1.09</v>
-      </c>
       <c r="Y17" t="n">
-        <v>1.43</v>
+        <v>1.15</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.75</v>
+        <v>5</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.28</v>
+        <v>1.63</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.55</v>
+        <v>2.25</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.05</v>
+        <v>2.35</v>
       </c>
       <c r="AD17" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG17" t="n">
         <v>1.18</v>
       </c>
-      <c r="AE17" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AH17" t="n">
-        <v>1.44</v>
+        <v>1.11</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.71</v>
+        <v>1.26</v>
       </c>
       <c r="M18" t="n">
-        <v>3.92</v>
+        <v>6</v>
       </c>
       <c r="N18" t="n">
-        <v>4.33</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="P18" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="R18" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="S18" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="T18" t="n">
-        <v>2.3</v>
+        <v>2.01</v>
       </c>
       <c r="U18" t="n">
-        <v>1.64</v>
+        <v>1.9</v>
       </c>
       <c r="V18" t="n">
-        <v>5.05</v>
+        <v>3.75</v>
       </c>
       <c r="W18" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="X18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y18" t="n">
         <v>1.04</v>
       </c>
-      <c r="Y18" t="n">
-        <v>1.13</v>
-      </c>
       <c r="Z18" t="n">
-        <v>4.55</v>
+        <v>7.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.2</v>
+        <v>3.15</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.3</v>
+        <v>1.76</v>
       </c>
       <c r="AD18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE18" t="n">
         <v>1.53</v>
       </c>
-      <c r="AE18" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AF18" t="n">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,61 +2682,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.26</v>
+        <v>2.63</v>
       </c>
       <c r="M19" t="n">
-        <v>6</v>
+        <v>3.51</v>
       </c>
       <c r="N19" t="n">
-        <v>8.800000000000001</v>
+        <v>2.47</v>
       </c>
       <c r="O19" t="n">
-        <v>1.73</v>
+        <v>3.16</v>
       </c>
       <c r="P19" t="n">
-        <v>2.7</v>
+        <v>2.15</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.8</v>
+        <v>3</v>
       </c>
       <c r="R19" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="S19" t="n">
-        <v>4.7</v>
+        <v>3.36</v>
       </c>
       <c r="T19" t="n">
-        <v>2.01</v>
+        <v>2.39</v>
       </c>
       <c r="U19" t="n">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="V19" t="n">
-        <v>3.75</v>
+        <v>5.45</v>
       </c>
       <c r="W19" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="X19" t="n">
         <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.04</v>
+        <v>1.19</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.5</v>
+        <v>4.45</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.33</v>
+        <v>1.63</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.15</v>
+        <v>2.25</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.76</v>
+        <v>2.46</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.95</v>
+        <v>1.47</v>
       </c>
       <c r="AE19" t="n">
         <v>1.53</v>
@@ -2745,10 +2745,10 @@
         <v>2.4</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.4</v>
+        <v>1.44</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.63</v>
+        <v>2.29</v>
       </c>
       <c r="M20" t="n">
-        <v>3.51</v>
+        <v>3.39</v>
       </c>
       <c r="N20" t="n">
-        <v>2.47</v>
+        <v>2.95</v>
       </c>
       <c r="O20" t="n">
-        <v>3.16</v>
+        <v>2.85</v>
       </c>
       <c r="P20" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V20" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF20" t="n">
         <v>2.15</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V20" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2.4</v>
       </c>
       <c r="AG20" t="n">
         <v>1.3</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,55 +2920,55 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.43</v>
+        <v>2.07</v>
       </c>
       <c r="M21" t="n">
-        <v>4.6</v>
+        <v>3.56</v>
       </c>
       <c r="N21" t="n">
-        <v>6.6</v>
+        <v>3.27</v>
       </c>
       <c r="O21" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V21" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA21" t="n">
         <v>1.79</v>
       </c>
-      <c r="P21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="V21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.49</v>
-      </c>
       <c r="AB21" t="n">
-        <v>2.51</v>
+        <v>1.91</v>
       </c>
       <c r="AC21" t="n">
         <v>2.3</v>
@@ -2977,16 +2977,16 @@
         <v>1.6</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AH21" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.07</v>
+        <v>1.71</v>
       </c>
       <c r="M22" t="n">
-        <v>3.56</v>
+        <v>3.92</v>
       </c>
       <c r="N22" t="n">
-        <v>3.27</v>
+        <v>4.33</v>
       </c>
       <c r="O22" t="n">
-        <v>2.53</v>
+        <v>2.2</v>
       </c>
       <c r="P22" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="R22" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="S22" t="n">
-        <v>3.32</v>
+        <v>3.5</v>
       </c>
       <c r="T22" t="n">
-        <v>2.47</v>
+        <v>2.3</v>
       </c>
       <c r="U22" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="V22" t="n">
-        <v>5.75</v>
+        <v>5.05</v>
       </c>
       <c r="W22" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="X22" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="Z22" t="n">
-        <v>4</v>
+        <v>4.55</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AC22" t="n">
         <v>2.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.2</v>
+        <v>2.47</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.29</v>
+        <v>2.52</v>
       </c>
       <c r="M23" t="n">
-        <v>3.39</v>
+        <v>3.13</v>
       </c>
       <c r="N23" t="n">
-        <v>2.95</v>
+        <v>2.83</v>
       </c>
       <c r="O23" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="P23" t="n">
-        <v>2.12</v>
+        <v>1.91</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="R23" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="S23" t="n">
-        <v>2.97</v>
+        <v>2.57</v>
       </c>
       <c r="T23" t="n">
-        <v>2.72</v>
+        <v>3.3</v>
       </c>
       <c r="U23" t="n">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="V23" t="n">
-        <v>6.25</v>
+        <v>8.1</v>
       </c>
       <c r="W23" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X23" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.8</v>
+        <v>2.75</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.79</v>
+        <v>2.28</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.95</v>
+        <v>1.55</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.02</v>
+        <v>4.05</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.15</v>
+        <v>1.82</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>6.9</v>
+        <v>1.43</v>
       </c>
       <c r="M24" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="N24" t="n">
-        <v>1.38</v>
+        <v>6.6</v>
       </c>
       <c r="O24" t="n">
-        <v>5.03</v>
+        <v>1.79</v>
       </c>
       <c r="P24" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.83</v>
+        <v>5.5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S24" t="n">
-        <v>3.75</v>
+        <v>3.62</v>
       </c>
       <c r="T24" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="U24" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="V24" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="W24" t="n">
         <v>1.16</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="Z24" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.63</v>
+        <v>1.49</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.25</v>
+        <v>2.51</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG24" t="n">
         <v>1.18</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.11</v>
+        <v>3</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45987.70833333334</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -659,10 +659,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="M2" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="N2" t="n">
         <v>2.8</v>
@@ -698,16 +698,16 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA2" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -778,10 +778,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="M3" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="N3" t="n">
         <v>2.6</v>
@@ -823,10 +823,10 @@
         <v>2.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.09</v>
+        <v>3.15</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AC3" t="n">
         <v>6.25</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45987.41666666666</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45987.41666666666</v>
@@ -1611,61 +1611,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="M10" t="n">
         <v>5</v>
       </c>
       <c r="N10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O10" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="P10" t="n">
-        <v>2.63</v>
+        <v>2.57</v>
       </c>
       <c r="Q10" t="n">
         <v>7</v>
       </c>
       <c r="R10" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S10" t="n">
-        <v>3.54</v>
+        <v>3.38</v>
       </c>
       <c r="T10" t="n">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
       <c r="U10" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="V10" t="n">
-        <v>4.75</v>
+        <v>4.85</v>
       </c>
       <c r="W10" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X10" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z10" t="n">
         <v>5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AE10" t="n">
         <v>1.75</v>
@@ -1730,22 +1730,22 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>5.1</v>
+        <v>5.15</v>
       </c>
       <c r="M11" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="N11" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="O11" t="n">
-        <v>5.1</v>
+        <v>4.95</v>
       </c>
       <c r="P11" t="n">
         <v>2.53</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="R11" t="n">
         <v>1.32</v>
@@ -1760,7 +1760,7 @@
         <v>1.57</v>
       </c>
       <c r="V11" t="n">
-        <v>5.3</v>
+        <v>5.35</v>
       </c>
       <c r="W11" t="n">
         <v>1.12</v>
@@ -1769,16 +1769,16 @@
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z11" t="n">
         <v>4.15</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="AC11" t="n">
         <v>2.55</v>
@@ -1787,10 +1787,10 @@
         <v>1.44</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AG11" t="n">
         <v>1.25</v>
@@ -1849,10 +1849,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="M12" t="n">
-        <v>3.36</v>
+        <v>3.75</v>
       </c>
       <c r="N12" t="n">
         <v>3.2</v>
@@ -1861,10 +1861,10 @@
         <v>2.45</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="R12" t="n">
         <v>1.29</v>
@@ -1873,10 +1873,10 @@
         <v>3.28</v>
       </c>
       <c r="T12" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="U12" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="V12" t="n">
         <v>5</v>
@@ -1885,31 +1885,31 @@
         <v>1.11</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
         <v>1.18</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.25</v>
+        <v>4.6</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AE12" t="n">
         <v>1.53</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="AG12" t="n">
         <v>1.29</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.44</v>
+        <v>1.48</v>
       </c>
       <c r="M13" t="n">
-        <v>3.31</v>
+        <v>3.85</v>
       </c>
       <c r="N13" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="O13" t="n">
-        <v>3.26</v>
+        <v>2.2</v>
       </c>
       <c r="P13" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.35</v>
+        <v>5.79</v>
       </c>
       <c r="R13" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>2.65</v>
+        <v>2.92</v>
       </c>
       <c r="T13" t="n">
         <v>2.8</v>
       </c>
       <c r="U13" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="V13" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.63</v>
+        <v>3.55</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AF13" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.5</v>
+        <v>2.15</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.07</v>
+        <v>1.77</v>
       </c>
       <c r="M14" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="N14" t="n">
-        <v>3.45</v>
+        <v>4.6</v>
       </c>
       <c r="O14" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="P14" t="n">
         <v>2.15</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="R14" t="n">
         <v>1.42</v>
       </c>
       <c r="S14" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="T14" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="U14" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="V14" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG14" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH14" t="n">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,43 +2206,43 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.61</v>
+        <v>2.55</v>
       </c>
       <c r="M15" t="n">
-        <v>3.63</v>
+        <v>3.3</v>
       </c>
       <c r="N15" t="n">
-        <v>5.8</v>
+        <v>2.62</v>
       </c>
       <c r="O15" t="n">
-        <v>2.2</v>
+        <v>3.21</v>
       </c>
       <c r="P15" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.78</v>
+        <v>3.25</v>
       </c>
       <c r="R15" t="n">
         <v>1.41</v>
       </c>
       <c r="S15" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="T15" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="U15" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V15" t="n">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
         <v>1.33</v>
@@ -2251,28 +2251,28 @@
         <v>3.34</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.87</v>
+        <v>2.14</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.61</v>
+        <v>3.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.01</v>
+        <v>1.75</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.17</v>
+        <v>1.5</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,22 +2325,22 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.81</v>
+        <v>2.22</v>
       </c>
       <c r="M16" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N16" t="n">
-        <v>4.4</v>
+        <v>3.05</v>
       </c>
       <c r="O16" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="P16" t="n">
         <v>2.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="R16" t="n">
         <v>1.42</v>
@@ -2349,13 +2349,13 @@
         <v>2.65</v>
       </c>
       <c r="T16" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="U16" t="n">
         <v>1.36</v>
       </c>
       <c r="V16" t="n">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="W16" t="n">
         <v>1.04</v>
@@ -2364,34 +2364,34 @@
         <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.5</v>
+        <v>2.99</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.99</v>
+        <v>1.65</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>6.9</v>
+        <v>2.72</v>
       </c>
       <c r="M17" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>1.38</v>
+        <v>2.8</v>
       </c>
       <c r="O17" t="n">
-        <v>5.03</v>
+        <v>3.4</v>
       </c>
       <c r="P17" t="n">
-        <v>2.45</v>
+        <v>1.91</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.83</v>
+        <v>3.25</v>
       </c>
       <c r="R17" t="n">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="S17" t="n">
-        <v>3.75</v>
+        <v>2.42</v>
       </c>
       <c r="T17" t="n">
-        <v>2.25</v>
+        <v>3.3</v>
       </c>
       <c r="U17" t="n">
-        <v>1.67</v>
+        <v>1.28</v>
       </c>
       <c r="V17" t="n">
-        <v>4.9</v>
+        <v>8.1</v>
       </c>
       <c r="W17" t="n">
-        <v>1.16</v>
+        <v>1.02</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.15</v>
+        <v>1.46</v>
       </c>
       <c r="Z17" t="n">
-        <v>5</v>
+        <v>2.77</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.63</v>
+        <v>2.37</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.25</v>
+        <v>1.55</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.35</v>
+        <v>4.33</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.52</v>
+        <v>1.18</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.11</v>
+        <v>1.44</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.26</v>
+        <v>1.68</v>
       </c>
       <c r="M18" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="N18" t="n">
-        <v>8.800000000000001</v>
+        <v>4.6</v>
       </c>
       <c r="O18" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="P18" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="R18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG18" t="n">
         <v>1.18</v>
       </c>
-      <c r="S18" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="V18" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AH18" t="n">
-        <v>3.4</v>
+        <v>2.25</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.63</v>
+        <v>1.97</v>
       </c>
       <c r="M19" t="n">
-        <v>3.51</v>
+        <v>3.3</v>
       </c>
       <c r="N19" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T19" t="n">
         <v>2.47</v>
       </c>
-      <c r="O19" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>3</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.39</v>
-      </c>
       <c r="U19" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="V19" t="n">
-        <v>5.45</v>
+        <v>5.75</v>
       </c>
       <c r="W19" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.46</v>
+        <v>2.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AG19" t="n">
         <v>1.3</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.29</v>
+        <v>1.25</v>
       </c>
       <c r="M20" t="n">
-        <v>3.39</v>
+        <v>5.5</v>
       </c>
       <c r="N20" t="n">
-        <v>2.95</v>
+        <v>7</v>
       </c>
       <c r="O20" t="n">
-        <v>2.85</v>
+        <v>1.73</v>
       </c>
       <c r="P20" t="n">
-        <v>2.12</v>
+        <v>2.69</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.65</v>
+        <v>5.8</v>
       </c>
       <c r="R20" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="S20" t="n">
-        <v>2.97</v>
+        <v>4.6</v>
       </c>
       <c r="T20" t="n">
-        <v>2.72</v>
+        <v>1.98</v>
       </c>
       <c r="U20" t="n">
-        <v>1.46</v>
+        <v>1.88</v>
       </c>
       <c r="V20" t="n">
-        <v>6.25</v>
+        <v>3.75</v>
       </c>
       <c r="W20" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="X20" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.8</v>
+        <v>6.75</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.79</v>
+        <v>1.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.95</v>
+        <v>3.35</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.02</v>
+        <v>1.82</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.36</v>
+        <v>2.05</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.62</v>
+        <v>3.4</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.07</v>
+        <v>2.3</v>
       </c>
       <c r="M21" t="n">
-        <v>3.56</v>
+        <v>3.3</v>
       </c>
       <c r="N21" t="n">
-        <v>3.27</v>
+        <v>3.06</v>
       </c>
       <c r="O21" t="n">
-        <v>2.53</v>
+        <v>2.8</v>
       </c>
       <c r="P21" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="R21" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S21" t="n">
-        <v>3.32</v>
+        <v>3.22</v>
       </c>
       <c r="T21" t="n">
-        <v>2.47</v>
+        <v>2.72</v>
       </c>
       <c r="U21" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="V21" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="W21" t="n">
         <v>1.09</v>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="Z21" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.3</v>
+        <v>2.92</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AG21" t="n">
         <v>1.3</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.71</v>
+        <v>2.62</v>
       </c>
       <c r="M22" t="n">
-        <v>3.92</v>
+        <v>3.5</v>
       </c>
       <c r="N22" t="n">
-        <v>4.33</v>
+        <v>2.4</v>
       </c>
       <c r="O22" t="n">
-        <v>2.2</v>
+        <v>3.18</v>
       </c>
       <c r="P22" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.2</v>
+        <v>3.04</v>
       </c>
       <c r="R22" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="S22" t="n">
-        <v>3.5</v>
+        <v>3.36</v>
       </c>
       <c r="T22" t="n">
         <v>2.3</v>
       </c>
       <c r="U22" t="n">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="V22" t="n">
-        <v>5.05</v>
+        <v>5.55</v>
       </c>
       <c r="W22" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X22" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.55</v>
+        <v>4.75</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.3</v>
+        <v>2.59</v>
       </c>
       <c r="AD22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE22" t="n">
         <v>1.53</v>
       </c>
-      <c r="AE22" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AF22" t="n">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.15</v>
+        <v>1.44</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.52</v>
+        <v>7</v>
       </c>
       <c r="M23" t="n">
-        <v>3.13</v>
+        <v>4.8</v>
       </c>
       <c r="N23" t="n">
-        <v>2.83</v>
+        <v>1.43</v>
       </c>
       <c r="O23" t="n">
-        <v>3.4</v>
+        <v>5.13</v>
       </c>
       <c r="P23" t="n">
-        <v>1.91</v>
+        <v>2.45</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.25</v>
+        <v>1.87</v>
       </c>
       <c r="R23" t="n">
-        <v>1.49</v>
+        <v>1.22</v>
       </c>
       <c r="S23" t="n">
-        <v>2.57</v>
+        <v>3.75</v>
       </c>
       <c r="T23" t="n">
-        <v>3.3</v>
+        <v>2.33</v>
       </c>
       <c r="U23" t="n">
-        <v>1.3</v>
+        <v>1.67</v>
       </c>
       <c r="V23" t="n">
-        <v>8.1</v>
+        <v>4.95</v>
       </c>
       <c r="W23" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X23" t="n">
         <v>1.02</v>
       </c>
-      <c r="X23" t="n">
-        <v>1.09</v>
-      </c>
       <c r="Y23" t="n">
-        <v>1.43</v>
+        <v>1.15</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.75</v>
+        <v>5</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.28</v>
+        <v>1.48</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.55</v>
+        <v>2.59</v>
       </c>
       <c r="AC23" t="n">
-        <v>4.05</v>
+        <v>2.38</v>
       </c>
       <c r="AD23" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG23" t="n">
         <v>1.18</v>
       </c>
-      <c r="AE23" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AH23" t="n">
-        <v>1.44</v>
+        <v>1.11</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3277,16 +3277,16 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="M24" t="n">
-        <v>4.6</v>
+        <v>5.27</v>
       </c>
       <c r="N24" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="O24" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="P24" t="n">
         <v>2.5</v>
@@ -3301,13 +3301,13 @@
         <v>3.62</v>
       </c>
       <c r="T24" t="n">
-        <v>2.19</v>
+        <v>2.02</v>
       </c>
       <c r="U24" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="V24" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="W24" t="n">
         <v>1.16</v>
@@ -3316,19 +3316,19 @@
         <v>1.03</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z24" t="n">
         <v>4.9</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AD24" t="n">
         <v>1.6</v>
@@ -3337,13 +3337,13 @@
         <v>1.8</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AH24" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3396,22 +3396,22 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="M25" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N25" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3515,22 +3515,22 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="M26" t="n">
         <v>3.25</v>
       </c>
       <c r="N26" t="n">
-        <v>3.31</v>
+        <v>3.8</v>
       </c>
       <c r="O26" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="P26" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="R26" t="n">
         <v>1.35</v>
@@ -3545,34 +3545,34 @@
         <v>1.44</v>
       </c>
       <c r="V26" t="n">
-        <v>5.95</v>
+        <v>5.85</v>
       </c>
       <c r="W26" t="n">
         <v>1.07</v>
       </c>
       <c r="X26" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y26" t="n">
         <v>1.22</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC26" t="n">
         <v>2.85</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AF26" t="n">
         <v>2.05</v>
@@ -3634,22 +3634,22 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="M27" t="n">
-        <v>3.05</v>
+        <v>3.16</v>
       </c>
       <c r="N27" t="n">
-        <v>2.75</v>
+        <v>2.99</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45987.41666666666</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45987.41666666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.37</v>
+        <v>4.35</v>
       </c>
       <c r="M10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O10" t="n">
         <v>5</v>
       </c>
-      <c r="N10" t="n">
-        <v>10</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.75</v>
-      </c>
       <c r="P10" t="n">
-        <v>2.57</v>
+        <v>2.53</v>
       </c>
       <c r="Q10" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="R10" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="S10" t="n">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="T10" t="n">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="U10" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="V10" t="n">
-        <v>4.85</v>
+        <v>5.35</v>
       </c>
       <c r="W10" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="X10" t="n">
         <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="Z10" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.25</v>
+        <v>1.17</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45987.61458333334</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>5.15</v>
+        <v>1.35</v>
       </c>
       <c r="M11" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="N11" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>7</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V11" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA11" t="n">
         <v>1.61</v>
       </c>
-      <c r="O11" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V11" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AB11" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.25</v>
+        <v>1.84</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.18</v>
+        <v>3.25</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45987.61458333334</v>
@@ -1977,46 +1977,46 @@
         <v>5</v>
       </c>
       <c r="O13" t="n">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.79</v>
+        <v>5</v>
       </c>
       <c r="R13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="U13" t="n">
         <v>1.4</v>
       </c>
-      <c r="S13" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.38</v>
-      </c>
       <c r="V13" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="W13" t="n">
         <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z13" t="n">
         <v>3.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AC13" t="n">
         <v>3.55</v>
@@ -2025,7 +2025,7 @@
         <v>1.25</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AF13" t="n">
         <v>1.85</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.77</v>
+        <v>2.26</v>
       </c>
       <c r="M14" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="N14" t="n">
-        <v>4.6</v>
+        <v>3.22</v>
       </c>
       <c r="O14" t="n">
-        <v>2.4</v>
+        <v>2.79</v>
       </c>
       <c r="P14" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.6</v>
+        <v>3.96</v>
       </c>
       <c r="R14" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="T14" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="U14" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AD14" t="n">
         <v>1.28</v>
       </c>
-      <c r="Z14" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AE14" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.55</v>
+        <v>1.8</v>
       </c>
       <c r="M15" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="N15" t="n">
-        <v>2.62</v>
+        <v>4.4</v>
       </c>
       <c r="O15" t="n">
-        <v>3.21</v>
+        <v>2.35</v>
       </c>
       <c r="P15" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.25</v>
+        <v>4.35</v>
       </c>
       <c r="R15" t="n">
         <v>1.41</v>
       </c>
       <c r="S15" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="T15" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="U15" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V15" t="n">
-        <v>7.4</v>
+        <v>6.65</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X15" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.14</v>
+        <v>1.98</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AF15" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH15" t="n">
         <v>2</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.5</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.22</v>
+        <v>2.47</v>
       </c>
       <c r="M16" t="n">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="N16" t="n">
-        <v>3.05</v>
+        <v>2.62</v>
       </c>
       <c r="O16" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="R16" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S16" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="T16" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="U16" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AB16" t="n">
         <v>1.76</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.38</v>
+        <v>3.66</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.72</v>
+        <v>1.6</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="N17" t="n">
-        <v>2.8</v>
+        <v>4.8</v>
       </c>
       <c r="O17" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S17" t="n">
         <v>3.4</v>
       </c>
-      <c r="P17" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.42</v>
-      </c>
       <c r="T17" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="U17" t="n">
-        <v>1.28</v>
+        <v>1.64</v>
       </c>
       <c r="V17" t="n">
-        <v>8.1</v>
+        <v>5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.02</v>
+        <v>1.16</v>
       </c>
       <c r="X17" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.46</v>
+        <v>1.17</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.77</v>
+        <v>5.75</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.37</v>
+        <v>1.52</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.55</v>
+        <v>2.45</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.33</v>
+        <v>2.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.18</v>
+        <v>1.6</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.91</v>
+        <v>1.59</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.44</v>
+        <v>2.32</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.68</v>
+        <v>2.57</v>
       </c>
       <c r="M18" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>4.6</v>
+        <v>2.73</v>
       </c>
       <c r="O18" t="n">
-        <v>2.2</v>
+        <v>3.55</v>
       </c>
       <c r="P18" t="n">
-        <v>2.45</v>
+        <v>1.91</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="R18" t="n">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="S18" t="n">
-        <v>3.5</v>
+        <v>2.42</v>
       </c>
       <c r="T18" t="n">
-        <v>2.28</v>
+        <v>3.25</v>
       </c>
       <c r="U18" t="n">
-        <v>1.65</v>
+        <v>1.3</v>
       </c>
       <c r="V18" t="n">
-        <v>4.8</v>
+        <v>8.1</v>
       </c>
       <c r="W18" t="n">
-        <v>1.16</v>
+        <v>1.02</v>
       </c>
       <c r="X18" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.6</v>
+        <v>2.7</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.52</v>
+        <v>2.25</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.35</v>
+        <v>1.57</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.3</v>
+        <v>4.33</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.53</v>
+        <v>1.17</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.57</v>
+        <v>2.04</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.3</v>
+        <v>1.81</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.25</v>
+        <v>1.44</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2682,7 +2682,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.97</v>
+        <v>2.23</v>
       </c>
       <c r="M19" t="n">
         <v>3.3</v>
@@ -2691,34 +2691,34 @@
         <v>3.15</v>
       </c>
       <c r="O19" t="n">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="P19" t="n">
-        <v>2.38</v>
+        <v>2.17</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.65</v>
+        <v>3.68</v>
       </c>
       <c r="R19" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S19" t="n">
-        <v>3.35</v>
+        <v>3.29</v>
       </c>
       <c r="T19" t="n">
-        <v>2.47</v>
+        <v>2.67</v>
       </c>
       <c r="U19" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="V19" t="n">
-        <v>5.75</v>
+        <v>5.6</v>
       </c>
       <c r="W19" t="n">
         <v>1.09</v>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y19" t="n">
         <v>1.21</v>
@@ -2727,22 +2727,22 @@
         <v>4.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AG19" t="n">
         <v>1.3</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>6</v>
+      </c>
+      <c r="M20" t="n">
+        <v>5</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="O20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="R20" t="n">
         <v>1.25</v>
       </c>
-      <c r="M20" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="N20" t="n">
-        <v>7</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.18</v>
-      </c>
       <c r="S20" t="n">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="T20" t="n">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="U20" t="n">
-        <v>1.88</v>
+        <v>1.61</v>
       </c>
       <c r="V20" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="X20" t="n">
         <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="Z20" t="n">
-        <v>6.75</v>
+        <v>4.9</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AB20" t="n">
-        <v>3.35</v>
+        <v>2.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.82</v>
+        <v>2.38</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.05</v>
+        <v>1.63</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.14</v>
+        <v>2.65</v>
       </c>
       <c r="AH20" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="M21" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N21" t="n">
-        <v>3.06</v>
+        <v>2.4</v>
       </c>
       <c r="O21" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="P21" t="n">
         <v>2.25</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="R21" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="S21" t="n">
-        <v>3.22</v>
+        <v>3.36</v>
       </c>
       <c r="T21" t="n">
-        <v>2.72</v>
+        <v>2.4</v>
       </c>
       <c r="U21" t="n">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="V21" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="W21" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X21" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.92</v>
+        <v>2.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.62</v>
+        <v>1.3</v>
       </c>
       <c r="M22" t="n">
-        <v>3.5</v>
+        <v>6.2</v>
       </c>
       <c r="N22" t="n">
-        <v>2.4</v>
+        <v>8.4</v>
       </c>
       <c r="O22" t="n">
-        <v>3.18</v>
+        <v>1.75</v>
       </c>
       <c r="P22" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.04</v>
+        <v>6.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="S22" t="n">
-        <v>3.36</v>
+        <v>4.6</v>
       </c>
       <c r="T22" t="n">
-        <v>2.3</v>
+        <v>1.97</v>
       </c>
       <c r="U22" t="n">
-        <v>1.56</v>
+        <v>1.91</v>
       </c>
       <c r="V22" t="n">
-        <v>5.55</v>
+        <v>3.7</v>
       </c>
       <c r="W22" t="n">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="X22" t="n">
         <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.75</v>
+        <v>8</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.66</v>
+        <v>1.32</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.31</v>
+        <v>3.42</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.59</v>
+        <v>1.81</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.44</v>
+        <v>3.4</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>7</v>
+        <v>1.36</v>
       </c>
       <c r="M23" t="n">
-        <v>4.8</v>
+        <v>5.25</v>
       </c>
       <c r="N23" t="n">
-        <v>1.43</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O23" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q23" t="n">
         <v>5.13</v>
       </c>
-      <c r="P23" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1.87</v>
-      </c>
       <c r="R23" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S23" t="n">
-        <v>3.75</v>
+        <v>3.62</v>
       </c>
       <c r="T23" t="n">
-        <v>2.33</v>
+        <v>2.18</v>
       </c>
       <c r="U23" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="V23" t="n">
-        <v>4.95</v>
+        <v>4.6</v>
       </c>
       <c r="W23" t="n">
         <v>1.16</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="Z23" t="n">
         <v>5</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.11</v>
+        <v>3.1</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O24" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V24" t="n">
+        <v>6</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AG24" t="n">
         <v>1.3</v>
       </c>
-      <c r="M24" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="N24" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="V24" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AH24" t="n">
-        <v>3.1</v>
+        <v>1.65</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45987.70833333334</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45987.41666666666</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45987.41666666666</v>
@@ -1135,70 +1135,70 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P6" t="n">
         <v>2</v>
       </c>
-      <c r="M6" t="n">
-        <v>3</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O6" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.87</v>
-      </c>
       <c r="Q6" t="n">
-        <v>4.68</v>
+        <v>4.33</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S6" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="T6" t="n">
         <v>3.28</v>
       </c>
       <c r="U6" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="V6" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
         <v>1.06</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.56</v>
+        <v>2.35</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AH6" t="n">
         <v>1.7</v>
@@ -1373,70 +1373,70 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="M8" t="n">
         <v>2.9</v>
       </c>
       <c r="N8" t="n">
-        <v>2.11</v>
+        <v>1.91</v>
       </c>
       <c r="O8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="P8" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="R8" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="S8" t="n">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="T8" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="U8" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="V8" t="n">
-        <v>12</v>
+        <v>9.1</v>
       </c>
       <c r="W8" t="n">
         <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Y8" t="n">
         <v>1.65</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.45</v>
+        <v>5.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.15</v>
+        <v>2.51</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.71</v>
+        <v>1.33</v>
       </c>
       <c r="AH8" t="n">
         <v>1.22</v>
@@ -1492,31 +1492,31 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.4</v>
+        <v>3.79</v>
       </c>
       <c r="M9" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="N9" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="O9" t="n">
         <v>4.2</v>
       </c>
       <c r="P9" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="S9" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="T9" t="n">
-        <v>3.7</v>
+        <v>3.74</v>
       </c>
       <c r="U9" t="n">
         <v>1.19</v>
@@ -1528,37 +1528,37 @@
         <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="Z9" t="n">
         <v>2.25</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="AB9" t="n">
         <v>1.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.35</v>
+        <v>5.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.21</v>
+        <v>2.29</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AG9" t="n">
         <v>1.4</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45987.60416666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.48</v>
+        <v>2.47</v>
       </c>
       <c r="M13" t="n">
-        <v>3.85</v>
+        <v>3.22</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>2.62</v>
       </c>
       <c r="O13" t="n">
-        <v>2.29</v>
+        <v>3</v>
       </c>
       <c r="P13" t="n">
-        <v>2.31</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>5</v>
+        <v>3.55</v>
       </c>
       <c r="R13" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S13" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="T13" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="U13" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="V13" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AA13" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF13" t="n">
         <v>2</v>
       </c>
-      <c r="AB13" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AG13" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.15</v>
+        <v>1.47</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.26</v>
+        <v>1.8</v>
       </c>
       <c r="M14" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="N14" t="n">
-        <v>3.22</v>
+        <v>4.4</v>
       </c>
       <c r="O14" t="n">
-        <v>2.79</v>
+        <v>2.35</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.96</v>
+        <v>4.35</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S14" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="T14" t="n">
-        <v>2.95</v>
+        <v>3.07</v>
       </c>
       <c r="U14" t="n">
         <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>6.9</v>
+        <v>6.65</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X14" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y14" t="n">
         <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.38</v>
+        <v>3.35</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.01</v>
+        <v>1.96</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.8</v>
+        <v>2.26</v>
       </c>
       <c r="M15" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="N15" t="n">
-        <v>4.4</v>
+        <v>3.22</v>
       </c>
       <c r="O15" t="n">
-        <v>2.35</v>
+        <v>2.79</v>
       </c>
       <c r="P15" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.35</v>
+        <v>3.96</v>
       </c>
       <c r="R15" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="T15" t="n">
-        <v>3.07</v>
+        <v>2.95</v>
       </c>
       <c r="U15" t="n">
         <v>1.36</v>
       </c>
       <c r="V15" t="n">
-        <v>6.65</v>
+        <v>6.9</v>
       </c>
       <c r="W15" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
         <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.96</v>
+        <v>2.01</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.47</v>
+        <v>1.48</v>
       </c>
       <c r="M16" t="n">
-        <v>3.22</v>
+        <v>3.85</v>
       </c>
       <c r="N16" t="n">
-        <v>2.62</v>
+        <v>5</v>
       </c>
       <c r="O16" t="n">
-        <v>3</v>
+        <v>2.29</v>
       </c>
       <c r="P16" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>5</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA16" t="n">
         <v>2</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="AB16" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AC16" t="n">
         <v>3.55</v>
       </c>
-      <c r="R16" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V16" t="n">
-        <v>8</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.66</v>
-      </c>
       <c r="AD16" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="AF16" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.47</v>
+        <v>2.15</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.6</v>
+        <v>2.57</v>
       </c>
       <c r="M17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N17" t="n">
-        <v>4.8</v>
+        <v>2.73</v>
       </c>
       <c r="O17" t="n">
-        <v>2.19</v>
+        <v>3.55</v>
       </c>
       <c r="P17" t="n">
-        <v>2.45</v>
+        <v>1.91</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.06</v>
+        <v>3.25</v>
       </c>
       <c r="R17" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="S17" t="n">
-        <v>3.4</v>
+        <v>2.42</v>
       </c>
       <c r="T17" t="n">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="U17" t="n">
-        <v>1.64</v>
+        <v>1.3</v>
       </c>
       <c r="V17" t="n">
-        <v>5</v>
+        <v>8.1</v>
       </c>
       <c r="W17" t="n">
-        <v>1.16</v>
+        <v>1.02</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AD17" t="n">
         <v>1.17</v>
       </c>
-      <c r="Z17" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AE17" t="n">
-        <v>1.59</v>
+        <v>2.04</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.3</v>
+        <v>1.81</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.32</v>
+        <v>1.44</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.57</v>
+        <v>1.36</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>5.25</v>
       </c>
       <c r="N18" t="n">
-        <v>2.73</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>3.55</v>
+        <v>1.75</v>
       </c>
       <c r="P18" t="n">
-        <v>1.91</v>
+        <v>2.75</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.25</v>
+        <v>5.13</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="S18" t="n">
-        <v>2.42</v>
+        <v>3.62</v>
       </c>
       <c r="T18" t="n">
-        <v>3.25</v>
+        <v>2.18</v>
       </c>
       <c r="U18" t="n">
-        <v>1.3</v>
+        <v>1.65</v>
       </c>
       <c r="V18" t="n">
-        <v>8.1</v>
+        <v>4.6</v>
       </c>
       <c r="W18" t="n">
-        <v>1.02</v>
+        <v>1.16</v>
       </c>
       <c r="X18" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.4</v>
+        <v>1.12</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.7</v>
+        <v>5</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.25</v>
+        <v>1.44</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.57</v>
+        <v>2.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.33</v>
+        <v>2.27</v>
       </c>
       <c r="AD18" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG18" t="n">
         <v>1.17</v>
       </c>
-      <c r="AE18" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AH18" t="n">
-        <v>1.44</v>
+        <v>3.1</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.23</v>
+        <v>1.3</v>
       </c>
       <c r="M19" t="n">
-        <v>3.3</v>
+        <v>6.2</v>
       </c>
       <c r="N19" t="n">
-        <v>3.15</v>
+        <v>8.4</v>
       </c>
       <c r="O19" t="n">
-        <v>2.75</v>
+        <v>1.75</v>
       </c>
       <c r="P19" t="n">
-        <v>2.17</v>
+        <v>2.9</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.68</v>
+        <v>6.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="S19" t="n">
-        <v>3.29</v>
+        <v>4.6</v>
       </c>
       <c r="T19" t="n">
-        <v>2.67</v>
+        <v>1.97</v>
       </c>
       <c r="U19" t="n">
-        <v>1.48</v>
+        <v>1.91</v>
       </c>
       <c r="V19" t="n">
-        <v>5.6</v>
+        <v>3.7</v>
       </c>
       <c r="W19" t="n">
-        <v>1.09</v>
+        <v>1.24</v>
       </c>
       <c r="X19" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.72</v>
+        <v>1.32</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.14</v>
+        <v>3.42</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.88</v>
+        <v>1.81</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.43</v>
+        <v>2</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.65</v>
+        <v>3.4</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,34 +2801,34 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>6</v>
+        <v>1.6</v>
       </c>
       <c r="M20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N20" t="n">
-        <v>1.44</v>
+        <v>4.8</v>
       </c>
       <c r="O20" t="n">
-        <v>5.5</v>
+        <v>2.19</v>
       </c>
       <c r="P20" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.85</v>
+        <v>4.06</v>
       </c>
       <c r="R20" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S20" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="T20" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="U20" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="V20" t="n">
         <v>5</v>
@@ -2837,37 +2837,37 @@
         <v>1.16</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.9</v>
+        <v>5.75</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.65</v>
+        <v>1.22</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.1</v>
+        <v>2.32</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.45</v>
+        <v>2.31</v>
       </c>
       <c r="M21" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N21" t="n">
-        <v>2.4</v>
+        <v>3.05</v>
       </c>
       <c r="O21" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="P21" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.1</v>
+        <v>3.76</v>
       </c>
       <c r="R21" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="S21" t="n">
-        <v>3.36</v>
+        <v>2.93</v>
       </c>
       <c r="T21" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="U21" t="n">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="V21" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="W21" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="AA21" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE21" t="n">
         <v>1.65</v>
       </c>
-      <c r="AB21" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AF21" t="n">
-        <v>2.6</v>
+        <v>2.21</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.3</v>
+        <v>6</v>
       </c>
       <c r="M22" t="n">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="N22" t="n">
-        <v>8.4</v>
+        <v>1.44</v>
       </c>
       <c r="O22" t="n">
-        <v>1.75</v>
+        <v>5.5</v>
       </c>
       <c r="P22" t="n">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="Q22" t="n">
-        <v>6.5</v>
+        <v>1.85</v>
       </c>
       <c r="R22" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="T22" t="n">
-        <v>1.97</v>
+        <v>2.25</v>
       </c>
       <c r="U22" t="n">
-        <v>1.91</v>
+        <v>1.61</v>
       </c>
       <c r="V22" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="X22" t="n">
         <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="Z22" t="n">
-        <v>8</v>
+        <v>4.9</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.32</v>
+        <v>1.48</v>
       </c>
       <c r="AB22" t="n">
-        <v>3.42</v>
+        <v>2.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.81</v>
+        <v>2.38</v>
       </c>
       <c r="AD22" t="n">
-        <v>2</v>
+        <v>1.63</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.34</v>
+        <v>2.15</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.11</v>
+        <v>2.65</v>
       </c>
       <c r="AH22" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.36</v>
+        <v>2.23</v>
       </c>
       <c r="M23" t="n">
-        <v>5.25</v>
+        <v>3.3</v>
       </c>
       <c r="N23" t="n">
-        <v>8.800000000000001</v>
+        <v>3.15</v>
       </c>
       <c r="O23" t="n">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
       <c r="P23" t="n">
-        <v>2.75</v>
+        <v>2.17</v>
       </c>
       <c r="Q23" t="n">
-        <v>5.13</v>
+        <v>3.68</v>
       </c>
       <c r="R23" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="S23" t="n">
-        <v>3.62</v>
+        <v>3.29</v>
       </c>
       <c r="T23" t="n">
-        <v>2.18</v>
+        <v>2.67</v>
       </c>
       <c r="U23" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V23" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH23" t="n">
         <v>1.65</v>
-      </c>
-      <c r="V23" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>3.1</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="M24" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N24" t="n">
-        <v>3.05</v>
+        <v>2.4</v>
       </c>
       <c r="O24" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="P24" t="n">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.76</v>
+        <v>3.1</v>
       </c>
       <c r="R24" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="S24" t="n">
-        <v>2.93</v>
+        <v>3.36</v>
       </c>
       <c r="T24" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="U24" t="n">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="V24" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="W24" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AG24" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z24" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH24" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3515,22 +3515,22 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="M26" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="N26" t="n">
         <v>3.8</v>
       </c>
       <c r="O26" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="P26" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="R26" t="n">
         <v>1.35</v>
@@ -3539,25 +3539,25 @@
         <v>2.94</v>
       </c>
       <c r="T26" t="n">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="U26" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="V26" t="n">
-        <v>5.85</v>
+        <v>6.25</v>
       </c>
       <c r="W26" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X26" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AA26" t="n">
         <v>1.75</v>
@@ -3566,19 +3566,19 @@
         <v>1.95</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AE26" t="n">
         <v>1.7</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AH26" t="n">
         <v>1.8</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -659,10 +659,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="M2" t="n">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="N2" t="n">
         <v>2.8</v>
@@ -704,10 +704,10 @@
         <v>2.1</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="M3" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="N3" t="n">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="O3" t="n">
-        <v>4</v>
+        <v>4.41</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R3" t="n">
         <v>1.68</v>
       </c>
       <c r="S3" t="n">
-        <v>2.08</v>
+        <v>2.03</v>
       </c>
       <c r="T3" t="n">
         <v>4</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="V3" t="n">
         <v>10</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Y3" t="n">
         <v>1.67</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AC3" t="n">
-        <v>6.25</v>
+        <v>6.75</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.33</v>
+        <v>2.39</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45987.375</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45987.41666666666</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45987.41666666666</v>
@@ -1263,64 +1263,64 @@
         <v>3.1</v>
       </c>
       <c r="O7" t="n">
-        <v>3.12</v>
+        <v>3.82</v>
       </c>
       <c r="P7" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.3</v>
+        <v>3.44</v>
       </c>
       <c r="R7" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="S7" t="n">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="T7" t="n">
-        <v>3.88</v>
+        <v>4.1</v>
       </c>
       <c r="U7" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="V7" t="n">
-        <v>9.6</v>
+        <v>9.9</v>
       </c>
       <c r="W7" t="n">
         <v>1.02</v>
       </c>
       <c r="X7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="AD7" t="n">
         <v>1.06</v>
       </c>
-      <c r="Y7" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AB7" t="n">
+      <c r="AE7" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG7" t="n">
         <v>1.35</v>
       </c>
-      <c r="AC7" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AG7" t="n">
+      <c r="AH7" t="n">
         <v>1.32</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.49</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45987.54166666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.47</v>
+        <v>1.61</v>
       </c>
       <c r="M13" t="n">
-        <v>3.22</v>
+        <v>3.63</v>
       </c>
       <c r="N13" t="n">
-        <v>2.62</v>
+        <v>5.8</v>
       </c>
       <c r="O13" t="n">
-        <v>3</v>
+        <v>2.29</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.55</v>
+        <v>5.83</v>
       </c>
       <c r="R13" t="n">
         <v>1.41</v>
       </c>
       <c r="S13" t="n">
-        <v>2.62</v>
+        <v>2.99</v>
       </c>
       <c r="T13" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="U13" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.06</v>
+        <v>1.87</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.66</v>
+        <v>3.57</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="AF13" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.47</v>
+        <v>2.15</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="M14" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="N14" t="n">
         <v>4.4</v>
@@ -2099,28 +2099,28 @@
         <v>2.35</v>
       </c>
       <c r="P14" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="Q14" t="n">
         <v>4.35</v>
       </c>
       <c r="R14" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S14" t="n">
-        <v>2.69</v>
+        <v>2.81</v>
       </c>
       <c r="T14" t="n">
-        <v>3.07</v>
+        <v>3.1</v>
       </c>
       <c r="U14" t="n">
         <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>6.65</v>
+        <v>6.7</v>
       </c>
       <c r="W14" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
         <v>1.06</v>
@@ -2135,22 +2135,22 @@
         <v>1.98</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE14" t="n">
         <v>1.87</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH14" t="n">
         <v>2</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,22 +2206,22 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.26</v>
+        <v>2.44</v>
       </c>
       <c r="M15" t="n">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
       <c r="N15" t="n">
-        <v>3.22</v>
+        <v>2.8</v>
       </c>
       <c r="O15" t="n">
-        <v>2.79</v>
+        <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.96</v>
+        <v>3.55</v>
       </c>
       <c r="R15" t="n">
         <v>1.4</v>
@@ -2230,49 +2230,49 @@
         <v>2.65</v>
       </c>
       <c r="T15" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="U15" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V15" t="n">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z15" t="n">
         <v>3.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.38</v>
+        <v>3.66</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AG15" t="n">
         <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.48</v>
+        <v>2.07</v>
       </c>
       <c r="M16" t="n">
-        <v>3.85</v>
+        <v>3.35</v>
       </c>
       <c r="N16" t="n">
-        <v>5</v>
+        <v>3.45</v>
       </c>
       <c r="O16" t="n">
-        <v>2.29</v>
+        <v>2.83</v>
       </c>
       <c r="P16" t="n">
-        <v>2.31</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="R16" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S16" t="n">
-        <v>2.65</v>
+        <v>2.89</v>
       </c>
       <c r="T16" t="n">
-        <v>2.89</v>
+        <v>2.95</v>
       </c>
       <c r="U16" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="V16" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="W16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X16" t="n">
         <v>1.04</v>
       </c>
-      <c r="X16" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y16" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z16" t="n">
         <v>3.25</v>
       </c>
       <c r="AA16" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.55</v>
+        <v>3.38</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE16" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.15</v>
+        <v>1.63</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.57</v>
+        <v>2.23</v>
       </c>
       <c r="M17" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="N17" t="n">
-        <v>2.73</v>
+        <v>3.15</v>
       </c>
       <c r="O17" t="n">
-        <v>3.55</v>
+        <v>2.75</v>
       </c>
       <c r="P17" t="n">
-        <v>1.91</v>
+        <v>2.17</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.25</v>
+        <v>3.68</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="S17" t="n">
-        <v>2.42</v>
+        <v>3.29</v>
       </c>
       <c r="T17" t="n">
-        <v>3.25</v>
+        <v>2.67</v>
       </c>
       <c r="U17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V17" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AG17" t="n">
         <v>1.3</v>
       </c>
-      <c r="V17" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AH17" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="M18" t="n">
-        <v>5.25</v>
+        <v>6.2</v>
       </c>
       <c r="N18" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="O18" t="n">
         <v>1.75</v>
       </c>
       <c r="P18" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.13</v>
+        <v>6.5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="S18" t="n">
-        <v>3.62</v>
+        <v>4.6</v>
       </c>
       <c r="T18" t="n">
-        <v>2.18</v>
+        <v>1.97</v>
       </c>
       <c r="U18" t="n">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="V18" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="W18" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="Z18" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.5</v>
+        <v>3.42</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.27</v>
+        <v>1.81</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.1</v>
+        <v>2.34</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.3</v>
+        <v>2.45</v>
       </c>
       <c r="M19" t="n">
-        <v>6.2</v>
+        <v>3.35</v>
       </c>
       <c r="N19" t="n">
-        <v>8.4</v>
+        <v>2.4</v>
       </c>
       <c r="O19" t="n">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="P19" t="n">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.5</v>
+        <v>3.1</v>
       </c>
       <c r="R19" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="S19" t="n">
-        <v>4.6</v>
+        <v>3.36</v>
       </c>
       <c r="T19" t="n">
-        <v>1.97</v>
+        <v>2.4</v>
       </c>
       <c r="U19" t="n">
-        <v>1.91</v>
+        <v>1.56</v>
       </c>
       <c r="V19" t="n">
-        <v>3.7</v>
+        <v>5.8</v>
       </c>
       <c r="W19" t="n">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="X19" t="n">
         <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>8</v>
+        <v>4.33</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.32</v>
+        <v>1.65</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.42</v>
+        <v>2.25</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.81</v>
+        <v>2.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.34</v>
+        <v>2.6</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.4</v>
+        <v>1.44</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,34 +2801,34 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.6</v>
+        <v>6</v>
       </c>
       <c r="M20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N20" t="n">
-        <v>4.8</v>
+        <v>1.44</v>
       </c>
       <c r="O20" t="n">
-        <v>2.19</v>
+        <v>5.5</v>
       </c>
       <c r="P20" t="n">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.06</v>
+        <v>1.85</v>
       </c>
       <c r="R20" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S20" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="T20" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="U20" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="V20" t="n">
         <v>5</v>
@@ -2837,37 +2837,37 @@
         <v>1.16</v>
       </c>
       <c r="X20" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.75</v>
+        <v>4.9</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.22</v>
+        <v>2.65</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.32</v>
+        <v>1.1</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.31</v>
+        <v>1.36</v>
       </c>
       <c r="M21" t="n">
-        <v>3.3</v>
+        <v>5.25</v>
       </c>
       <c r="N21" t="n">
-        <v>3.05</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>2.85</v>
+        <v>1.75</v>
       </c>
       <c r="P21" t="n">
-        <v>2.31</v>
+        <v>2.75</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.76</v>
+        <v>5.13</v>
       </c>
       <c r="R21" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="S21" t="n">
-        <v>2.93</v>
+        <v>3.62</v>
       </c>
       <c r="T21" t="n">
-        <v>2.55</v>
+        <v>2.18</v>
       </c>
       <c r="U21" t="n">
-        <v>1.42</v>
+        <v>1.65</v>
       </c>
       <c r="V21" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.9</v>
+        <v>1.44</v>
       </c>
       <c r="AB21" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.13</v>
+        <v>2.27</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.38</v>
+        <v>1.71</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.65</v>
+        <v>3.1</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,34 +3039,34 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>6</v>
+        <v>1.6</v>
       </c>
       <c r="M22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N22" t="n">
-        <v>1.44</v>
+        <v>4.8</v>
       </c>
       <c r="O22" t="n">
-        <v>5.5</v>
+        <v>2.19</v>
       </c>
       <c r="P22" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.85</v>
+        <v>4.06</v>
       </c>
       <c r="R22" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S22" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="T22" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="U22" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="V22" t="n">
         <v>5</v>
@@ -3075,37 +3075,37 @@
         <v>1.16</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.9</v>
+        <v>5.75</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.65</v>
+        <v>1.22</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.1</v>
+        <v>2.32</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,67 +3158,67 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.23</v>
+        <v>2.31</v>
       </c>
       <c r="M23" t="n">
         <v>3.3</v>
       </c>
       <c r="N23" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="O23" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="P23" t="n">
-        <v>2.17</v>
+        <v>2.31</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.68</v>
+        <v>3.76</v>
       </c>
       <c r="R23" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="S23" t="n">
-        <v>3.29</v>
+        <v>2.93</v>
       </c>
       <c r="T23" t="n">
-        <v>2.67</v>
+        <v>2.55</v>
       </c>
       <c r="U23" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="V23" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="W23" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.88</v>
+        <v>3.13</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="AG23" t="n">
         <v>1.3</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.45</v>
+        <v>2.52</v>
       </c>
       <c r="M24" t="n">
-        <v>3.35</v>
+        <v>3.13</v>
       </c>
       <c r="N24" t="n">
-        <v>2.4</v>
+        <v>2.83</v>
       </c>
       <c r="O24" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="P24" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="R24" t="n">
-        <v>1.27</v>
+        <v>1.46</v>
       </c>
       <c r="S24" t="n">
-        <v>3.36</v>
+        <v>2.42</v>
       </c>
       <c r="T24" t="n">
-        <v>2.4</v>
+        <v>3.28</v>
       </c>
       <c r="U24" t="n">
-        <v>1.56</v>
+        <v>1.29</v>
       </c>
       <c r="V24" t="n">
-        <v>5.8</v>
+        <v>8.1</v>
       </c>
       <c r="W24" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="Z24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC24" t="n">
         <v>4.33</v>
       </c>
-      <c r="AA24" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AD24" t="n">
-        <v>1.5</v>
+        <v>1.23</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.53</v>
+        <v>2.01</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.6</v>
+        <v>1.89</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45987.70833333334</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -659,10 +659,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="M2" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="N2" t="n">
         <v>2.8</v>
@@ -704,10 +704,10 @@
         <v>2.1</v>
       </c>
       <c r="AA2" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="M3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N3" t="n">
         <v>2.65</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2.48</v>
       </c>
       <c r="O3" t="n">
         <v>4.41</v>
@@ -817,16 +817,16 @@
         <v>1.1</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AC3" t="n">
         <v>6.75</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>9.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45987.41666666666</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45987.41666666666</v>
@@ -1156,13 +1156,13 @@
         <v>1.51</v>
       </c>
       <c r="S6" t="n">
-        <v>2.29</v>
+        <v>2.47</v>
       </c>
       <c r="T6" t="n">
         <v>3.28</v>
       </c>
       <c r="U6" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="V6" t="n">
         <v>8.300000000000001</v>
@@ -1171,7 +1171,7 @@
         <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y6" t="n">
         <v>1.43</v>
@@ -1198,7 +1198,7 @@
         <v>1.73</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="AH6" t="n">
         <v>1.7</v>
@@ -1382,61 +1382,61 @@
         <v>1.91</v>
       </c>
       <c r="O8" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="P8" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q8" t="n">
         <v>2.8</v>
       </c>
       <c r="R8" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="S8" t="n">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="T8" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="U8" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="V8" t="n">
-        <v>9.1</v>
+        <v>12</v>
       </c>
       <c r="W8" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X8" t="n">
         <v>1.14</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.6</v>
+        <v>3.06</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH8" t="n">
         <v>1.22</v>
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.79</v>
+        <v>3.4</v>
       </c>
       <c r="M9" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="N9" t="n">
         <v>2.1</v>
@@ -1507,7 +1507,7 @@
         <v>1.83</v>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="R9" t="n">
         <v>1.6</v>
@@ -1522,7 +1522,7 @@
         <v>1.19</v>
       </c>
       <c r="V9" t="n">
-        <v>12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W9" t="n">
         <v>1.03</v>
@@ -1531,7 +1531,7 @@
         <v>1.13</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="Z9" t="n">
         <v>2.25</v>
@@ -1540,25 +1540,25 @@
         <v>2.88</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AC9" t="n">
         <v>5.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AE9" t="n">
         <v>2.29</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AG9" t="n">
         <v>1.4</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45987.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.35</v>
+        <v>1.32</v>
       </c>
       <c r="M10" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="N10" t="n">
-        <v>1.6</v>
+        <v>9</v>
       </c>
       <c r="O10" t="n">
-        <v>5</v>
+        <v>1.78</v>
       </c>
       <c r="P10" t="n">
-        <v>2.53</v>
+        <v>2.57</v>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R10" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S10" t="n">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="T10" t="n">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="U10" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="V10" t="n">
-        <v>5.35</v>
+        <v>5.05</v>
       </c>
       <c r="W10" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.51</v>
+        <v>1.65</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.17</v>
+        <v>3.25</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45987.61458333334</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.35</v>
+        <v>5.1</v>
       </c>
       <c r="M11" t="n">
-        <v>5.25</v>
+        <v>4.1</v>
       </c>
       <c r="N11" t="n">
-        <v>9.5</v>
+        <v>1.6</v>
       </c>
       <c r="O11" t="n">
-        <v>1.77</v>
+        <v>4.75</v>
       </c>
       <c r="P11" t="n">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="Q11" t="n">
-        <v>7</v>
+        <v>2.1</v>
       </c>
       <c r="R11" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S11" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="T11" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V11" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AG11" t="n">
         <v>2.25</v>
       </c>
-      <c r="U11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V11" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y11" t="n">
+      <c r="AH11" t="n">
         <v>1.17</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>3.25</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45987.61458333334</v>
@@ -1849,28 +1849,28 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="M12" t="n">
-        <v>3.75</v>
+        <v>3.36</v>
       </c>
       <c r="N12" t="n">
         <v>3.2</v>
       </c>
       <c r="O12" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="P12" t="n">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="R12" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S12" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="T12" t="n">
         <v>2.3</v>
@@ -1885,37 +1885,37 @@
         <v>1.11</v>
       </c>
       <c r="X12" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z12" t="n">
         <v>4.6</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.36</v>
+        <v>2.1</v>
       </c>
       <c r="AC12" t="n">
         <v>2.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AE12" t="n">
         <v>1.53</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45987.625</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.61</v>
+        <v>2.44</v>
       </c>
       <c r="M13" t="n">
-        <v>3.63</v>
+        <v>3.31</v>
       </c>
       <c r="N13" t="n">
-        <v>5.8</v>
+        <v>2.8</v>
       </c>
       <c r="O13" t="n">
-        <v>2.29</v>
+        <v>3</v>
       </c>
       <c r="P13" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.83</v>
+        <v>3.55</v>
       </c>
       <c r="R13" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>2.99</v>
+        <v>2.65</v>
       </c>
       <c r="T13" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="U13" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V13" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.57</v>
+        <v>3.66</v>
       </c>
       <c r="AD13" t="n">
         <v>1.25</v>
       </c>
       <c r="AE13" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF13" t="n">
         <v>2</v>
       </c>
-      <c r="AF13" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AG13" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.15</v>
+        <v>1.5</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.81</v>
+        <v>1.61</v>
       </c>
       <c r="M14" t="n">
-        <v>3.45</v>
+        <v>3.63</v>
       </c>
       <c r="N14" t="n">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="O14" t="n">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="P14" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.35</v>
+        <v>5.83</v>
       </c>
       <c r="R14" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="S14" t="n">
-        <v>2.81</v>
+        <v>2.99</v>
       </c>
       <c r="T14" t="n">
-        <v>3.1</v>
+        <v>2.89</v>
       </c>
       <c r="U14" t="n">
         <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
         <v>1.06</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.4</v>
+        <v>3.57</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AF14" t="n">
         <v>1.85</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH14" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,49 +2206,49 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.44</v>
+        <v>2.07</v>
       </c>
       <c r="M15" t="n">
-        <v>3.31</v>
+        <v>3.35</v>
       </c>
       <c r="N15" t="n">
-        <v>2.8</v>
+        <v>3.45</v>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S15" t="n">
-        <v>2.65</v>
+        <v>2.89</v>
       </c>
       <c r="T15" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="U15" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="V15" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AA15" t="n">
         <v>1.98</v>
@@ -2257,22 +2257,22 @@
         <v>1.77</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.66</v>
+        <v>3.38</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AF15" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,49 +2325,49 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.07</v>
+        <v>1.81</v>
       </c>
       <c r="M16" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="N16" t="n">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="O16" t="n">
-        <v>2.83</v>
+        <v>2.35</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.75</v>
+        <v>4.35</v>
       </c>
       <c r="R16" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S16" t="n">
-        <v>2.89</v>
+        <v>2.81</v>
       </c>
       <c r="T16" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="U16" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="V16" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="W16" t="n">
         <v>1.05</v>
       </c>
       <c r="X16" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
         <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AA16" t="n">
         <v>1.98</v>
@@ -2376,22 +2376,22 @@
         <v>1.77</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.01</v>
+        <v>1.85</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.63</v>
+        <v>2</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.23</v>
+        <v>2.52</v>
       </c>
       <c r="M17" t="n">
-        <v>3.3</v>
+        <v>3.13</v>
       </c>
       <c r="N17" t="n">
-        <v>3.15</v>
+        <v>2.83</v>
       </c>
       <c r="O17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V17" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z17" t="n">
         <v>2.75</v>
       </c>
-      <c r="P17" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V17" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AA17" t="n">
-        <v>1.72</v>
+        <v>2.28</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.14</v>
+        <v>1.55</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.88</v>
+        <v>4.33</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.43</v>
+        <v>1.23</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.6</v>
+        <v>2.01</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.28</v>
+        <v>1.89</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.65</v>
+        <v>1.42</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.3</v>
+        <v>2.29</v>
       </c>
       <c r="M18" t="n">
-        <v>6.2</v>
+        <v>3.39</v>
       </c>
       <c r="N18" t="n">
-        <v>8.4</v>
+        <v>2.95</v>
       </c>
       <c r="O18" t="n">
-        <v>1.75</v>
+        <v>2.8</v>
       </c>
       <c r="P18" t="n">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.5</v>
+        <v>3.78</v>
       </c>
       <c r="R18" t="n">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="S18" t="n">
-        <v>4.6</v>
+        <v>3.14</v>
       </c>
       <c r="T18" t="n">
-        <v>1.97</v>
+        <v>2.64</v>
       </c>
       <c r="U18" t="n">
-        <v>1.91</v>
+        <v>1.44</v>
       </c>
       <c r="V18" t="n">
-        <v>3.7</v>
+        <v>6</v>
       </c>
       <c r="W18" t="n">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="Z18" t="n">
-        <v>8</v>
+        <v>3.6</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.32</v>
+        <v>1.79</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.42</v>
+        <v>1.95</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.81</v>
+        <v>3.13</v>
       </c>
       <c r="AD18" t="n">
-        <v>2</v>
+        <v>1.35</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.11</v>
+        <v>1.34</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.4</v>
+        <v>1.66</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.45</v>
+        <v>1.43</v>
       </c>
       <c r="M19" t="n">
-        <v>3.35</v>
+        <v>4.6</v>
       </c>
       <c r="N19" t="n">
-        <v>2.4</v>
+        <v>6.6</v>
       </c>
       <c r="O19" t="n">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="P19" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="Q19" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH19" t="n">
         <v>3.1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V19" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.44</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>6</v>
+        <v>2.63</v>
       </c>
       <c r="M20" t="n">
-        <v>5</v>
+        <v>3.51</v>
       </c>
       <c r="N20" t="n">
-        <v>1.44</v>
+        <v>2.47</v>
       </c>
       <c r="O20" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V20" t="n">
         <v>5.5</v>
       </c>
-      <c r="P20" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V20" t="n">
-        <v>5</v>
-      </c>
       <c r="W20" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="X20" t="n">
         <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.9</v>
+        <v>4.33</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.48</v>
+        <v>1.63</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.65</v>
+        <v>1.32</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.1</v>
+        <v>1.53</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.36</v>
+        <v>6.9</v>
       </c>
       <c r="M21" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="N21" t="n">
-        <v>8.800000000000001</v>
+        <v>1.38</v>
       </c>
       <c r="O21" t="n">
-        <v>1.75</v>
+        <v>5.5</v>
       </c>
       <c r="P21" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.13</v>
+        <v>1.85</v>
       </c>
       <c r="R21" t="n">
         <v>1.25</v>
       </c>
       <c r="S21" t="n">
-        <v>3.62</v>
+        <v>3.75</v>
       </c>
       <c r="T21" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="U21" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="V21" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="W21" t="n">
         <v>1.16</v>
       </c>
       <c r="X21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z21" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.27</v>
+        <v>2.35</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.71</v>
+        <v>1.52</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AH21" t="n">
-        <v>3.1</v>
+        <v>1.13</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,55 +3039,55 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.6</v>
+        <v>2.07</v>
       </c>
       <c r="M22" t="n">
-        <v>4</v>
+        <v>3.56</v>
       </c>
       <c r="N22" t="n">
-        <v>4.8</v>
+        <v>3.27</v>
       </c>
       <c r="O22" t="n">
-        <v>2.19</v>
+        <v>2.75</v>
       </c>
       <c r="P22" t="n">
-        <v>2.45</v>
+        <v>2.12</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.06</v>
+        <v>3.68</v>
       </c>
       <c r="R22" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="S22" t="n">
-        <v>3.4</v>
+        <v>3.33</v>
       </c>
       <c r="T22" t="n">
-        <v>2.3</v>
+        <v>2.67</v>
       </c>
       <c r="U22" t="n">
-        <v>1.64</v>
+        <v>1.48</v>
       </c>
       <c r="V22" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="W22" t="n">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="X22" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.75</v>
+        <v>4.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.52</v>
+        <v>1.77</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.45</v>
+        <v>1.98</v>
       </c>
       <c r="AC22" t="n">
         <v>2.3</v>
@@ -3096,16 +3096,16 @@
         <v>1.6</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.32</v>
+        <v>1.7</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.31</v>
+        <v>1.71</v>
       </c>
       <c r="M23" t="n">
-        <v>3.3</v>
+        <v>3.92</v>
       </c>
       <c r="N23" t="n">
-        <v>3.05</v>
+        <v>4.33</v>
       </c>
       <c r="O23" t="n">
-        <v>2.85</v>
+        <v>2.19</v>
       </c>
       <c r="P23" t="n">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.76</v>
+        <v>4.2</v>
       </c>
       <c r="R23" t="n">
-        <v>1.37</v>
+        <v>1.23</v>
       </c>
       <c r="S23" t="n">
-        <v>2.93</v>
+        <v>3.5</v>
       </c>
       <c r="T23" t="n">
-        <v>2.55</v>
+        <v>2.36</v>
       </c>
       <c r="U23" t="n">
-        <v>1.42</v>
+        <v>1.59</v>
       </c>
       <c r="V23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AB23" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.13</v>
+        <v>2.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.21</v>
+        <v>2.46</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.65</v>
+        <v>2.24</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.52</v>
+        <v>1.26</v>
       </c>
       <c r="M24" t="n">
-        <v>3.13</v>
+        <v>6</v>
       </c>
       <c r="N24" t="n">
-        <v>2.83</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>3.4</v>
+        <v>1.72</v>
       </c>
       <c r="P24" t="n">
-        <v>1.91</v>
+        <v>2.91</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.25</v>
+        <v>6.5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.46</v>
+        <v>1.18</v>
       </c>
       <c r="S24" t="n">
-        <v>2.42</v>
+        <v>4.6</v>
       </c>
       <c r="T24" t="n">
-        <v>3.28</v>
+        <v>1.94</v>
       </c>
       <c r="U24" t="n">
-        <v>1.29</v>
+        <v>1.88</v>
       </c>
       <c r="V24" t="n">
-        <v>8.1</v>
+        <v>3.7</v>
       </c>
       <c r="W24" t="n">
-        <v>1.02</v>
+        <v>1.24</v>
       </c>
       <c r="X24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y24" t="n">
         <v>1.08</v>
       </c>
-      <c r="Y24" t="n">
-        <v>1.4</v>
-      </c>
       <c r="Z24" t="n">
-        <v>2.75</v>
+        <v>7.5</v>
       </c>
       <c r="AA24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF24" t="n">
         <v>2.28</v>
       </c>
-      <c r="AB24" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.89</v>
-      </c>
       <c r="AG24" t="n">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.42</v>
+        <v>3.5</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="M25" t="n">
-        <v>3</v>
+        <v>3.38</v>
       </c>
       <c r="N25" t="n">
-        <v>2.75</v>
+        <v>3.08</v>
       </c>
       <c r="O25" t="n">
         <v>2.75</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3515,19 +3515,19 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="M26" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="N26" t="n">
-        <v>3.8</v>
+        <v>3.31</v>
       </c>
       <c r="O26" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="P26" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q26" t="n">
         <v>4</v>
@@ -3539,49 +3539,49 @@
         <v>2.94</v>
       </c>
       <c r="T26" t="n">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="U26" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="V26" t="n">
         <v>6.25</v>
       </c>
       <c r="W26" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X26" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AC26" t="n">
         <v>2.9</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AE26" t="n">
         <v>1.7</v>
       </c>
       <c r="AF26" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45987.79166666666</v>
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="M27" t="n">
-        <v>3.16</v>
+        <v>3.23</v>
       </c>
       <c r="N27" t="n">
-        <v>2.99</v>
+        <v>2.58</v>
       </c>
       <c r="O27" t="n">
         <v>3.2</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45987.41666666666</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>9.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45987.41666666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.61</v>
+        <v>2.07</v>
       </c>
       <c r="M14" t="n">
-        <v>3.63</v>
+        <v>3.35</v>
       </c>
       <c r="N14" t="n">
-        <v>5.8</v>
+        <v>3.45</v>
       </c>
       <c r="O14" t="n">
-        <v>2.29</v>
+        <v>2.83</v>
       </c>
       <c r="P14" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.83</v>
+        <v>3.75</v>
       </c>
       <c r="R14" t="n">
         <v>1.41</v>
       </c>
       <c r="S14" t="n">
-        <v>2.99</v>
+        <v>2.89</v>
       </c>
       <c r="T14" t="n">
-        <v>2.89</v>
+        <v>2.95</v>
       </c>
       <c r="U14" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="V14" t="n">
         <v>7</v>
       </c>
       <c r="W14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X14" t="n">
         <v>1.04</v>
       </c>
-      <c r="X14" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y14" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
         <v>3.25</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.57</v>
+        <v>3.38</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE14" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.15</v>
+        <v>1.63</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,49 +2206,49 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.07</v>
+        <v>1.81</v>
       </c>
       <c r="M15" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="N15" t="n">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="O15" t="n">
-        <v>2.83</v>
+        <v>2.35</v>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.75</v>
+        <v>4.35</v>
       </c>
       <c r="R15" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S15" t="n">
-        <v>2.89</v>
+        <v>2.81</v>
       </c>
       <c r="T15" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="U15" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="V15" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="W15" t="n">
         <v>1.05</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
         <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AA15" t="n">
         <v>1.98</v>
@@ -2257,22 +2257,22 @@
         <v>1.77</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.01</v>
+        <v>1.85</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.63</v>
+        <v>2</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.81</v>
+        <v>1.61</v>
       </c>
       <c r="M16" t="n">
-        <v>3.45</v>
+        <v>3.63</v>
       </c>
       <c r="N16" t="n">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="O16" t="n">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="P16" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.35</v>
+        <v>5.83</v>
       </c>
       <c r="R16" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="S16" t="n">
-        <v>2.81</v>
+        <v>2.99</v>
       </c>
       <c r="T16" t="n">
-        <v>3.1</v>
+        <v>2.89</v>
       </c>
       <c r="U16" t="n">
         <v>1.36</v>
       </c>
       <c r="V16" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="W16" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
         <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.4</v>
+        <v>3.57</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AF16" t="n">
         <v>1.85</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.52</v>
+        <v>2.07</v>
       </c>
       <c r="M17" t="n">
-        <v>3.13</v>
+        <v>3.56</v>
       </c>
       <c r="N17" t="n">
-        <v>2.83</v>
+        <v>3.27</v>
       </c>
       <c r="O17" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="P17" t="n">
-        <v>1.91</v>
+        <v>2.12</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.25</v>
+        <v>3.68</v>
       </c>
       <c r="R17" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="S17" t="n">
-        <v>2.42</v>
+        <v>3.33</v>
       </c>
       <c r="T17" t="n">
-        <v>3.28</v>
+        <v>2.67</v>
       </c>
       <c r="U17" t="n">
-        <v>1.29</v>
+        <v>1.48</v>
       </c>
       <c r="V17" t="n">
-        <v>8.1</v>
+        <v>5.6</v>
       </c>
       <c r="W17" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="X17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
       <c r="AA17" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF17" t="n">
         <v>2.28</v>
       </c>
-      <c r="AB17" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.89</v>
-      </c>
       <c r="AG17" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.42</v>
+        <v>1.7</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.29</v>
+        <v>2.52</v>
       </c>
       <c r="M18" t="n">
-        <v>3.39</v>
+        <v>3.13</v>
       </c>
       <c r="N18" t="n">
-        <v>2.95</v>
+        <v>2.83</v>
       </c>
       <c r="O18" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="P18" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.78</v>
+        <v>3.25</v>
       </c>
       <c r="R18" t="n">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="S18" t="n">
-        <v>3.14</v>
+        <v>2.42</v>
       </c>
       <c r="T18" t="n">
-        <v>2.64</v>
+        <v>3.28</v>
       </c>
       <c r="U18" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="V18" t="n">
-        <v>6</v>
+        <v>8.1</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.79</v>
+        <v>2.28</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.95</v>
+        <v>1.55</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.13</v>
+        <v>4.33</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.71</v>
+        <v>2.01</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.2</v>
+        <v>1.89</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.66</v>
+        <v>1.42</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.43</v>
+        <v>1.26</v>
       </c>
       <c r="M19" t="n">
+        <v>6</v>
+      </c>
+      <c r="N19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S19" t="n">
         <v>4.6</v>
       </c>
-      <c r="N19" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>5.32</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.54</v>
-      </c>
       <c r="T19" t="n">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="U19" t="n">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="V19" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="W19" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="Z19" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.51</v>
+        <v>3.15</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.3</v>
+        <v>1.76</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="AF19" t="n">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,49 +2801,49 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="M20" t="n">
+        <v>5</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="O20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="P20" t="n">
         <v>2.63</v>
       </c>
-      <c r="M20" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="N20" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="O20" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.25</v>
-      </c>
       <c r="Q20" t="n">
-        <v>3.1</v>
+        <v>1.85</v>
       </c>
       <c r="R20" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="S20" t="n">
-        <v>3.36</v>
+        <v>3.75</v>
       </c>
       <c r="T20" t="n">
-        <v>2.42</v>
+        <v>2.26</v>
       </c>
       <c r="U20" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="V20" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="X20" t="n">
         <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.33</v>
+        <v>4.9</v>
       </c>
       <c r="AA20" t="n">
         <v>1.63</v>
@@ -2852,22 +2852,22 @@
         <v>2.25</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.53</v>
+        <v>1.13</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>6.9</v>
+        <v>1.71</v>
       </c>
       <c r="M21" t="n">
-        <v>5</v>
+        <v>3.92</v>
       </c>
       <c r="N21" t="n">
-        <v>1.38</v>
+        <v>4.33</v>
       </c>
       <c r="O21" t="n">
-        <v>5.5</v>
+        <v>2.19</v>
       </c>
       <c r="P21" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.85</v>
+        <v>4.2</v>
       </c>
       <c r="R21" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="S21" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="T21" t="n">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="U21" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="V21" t="n">
         <v>5</v>
       </c>
       <c r="W21" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.15</v>
+        <v>2.46</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.13</v>
+        <v>2.24</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.07</v>
+        <v>2.29</v>
       </c>
       <c r="M22" t="n">
-        <v>3.56</v>
+        <v>3.39</v>
       </c>
       <c r="N22" t="n">
-        <v>3.27</v>
+        <v>2.95</v>
       </c>
       <c r="O22" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="P22" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.68</v>
+        <v>3.78</v>
       </c>
       <c r="R22" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="S22" t="n">
-        <v>3.33</v>
+        <v>3.14</v>
       </c>
       <c r="T22" t="n">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="U22" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="V22" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="W22" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X22" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.3</v>
+        <v>3.13</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.6</v>
+        <v>1.35</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.71</v>
+        <v>2.63</v>
       </c>
       <c r="M23" t="n">
-        <v>3.92</v>
+        <v>3.51</v>
       </c>
       <c r="N23" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="O23" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V23" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z23" t="n">
         <v>4.33</v>
       </c>
-      <c r="O23" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="V23" t="n">
-        <v>5</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>4.6</v>
-      </c>
       <c r="AA23" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.24</v>
+        <v>1.53</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.26</v>
+        <v>1.43</v>
       </c>
       <c r="M24" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="N24" t="n">
-        <v>8.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="O24" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="P24" t="n">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="Q24" t="n">
-        <v>6.5</v>
+        <v>5.32</v>
       </c>
       <c r="R24" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="S24" t="n">
-        <v>4.6</v>
+        <v>3.54</v>
       </c>
       <c r="T24" t="n">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="U24" t="n">
-        <v>1.88</v>
+        <v>1.65</v>
       </c>
       <c r="V24" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="W24" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Z24" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="AB24" t="n">
-        <v>3.15</v>
+        <v>2.51</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.76</v>
+        <v>2.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.28</v>
+        <v>2</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AH24" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45987.70833333334</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -642,30 +642,30 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="M2" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="N2" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="O2" t="n">
         <v>3.4</v>
@@ -704,10 +704,10 @@
         <v>2.1</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -778,19 +778,19 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="M3" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="N3" t="n">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="O3" t="n">
-        <v>4.41</v>
+        <v>3.8</v>
       </c>
       <c r="P3" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="Q3" t="n">
         <v>3.4</v>
@@ -802,7 +802,7 @@
         <v>2.03</v>
       </c>
       <c r="T3" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="U3" t="n">
         <v>1.15</v>
@@ -814,19 +814,19 @@
         <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Y3" t="n">
         <v>1.68</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" t="n">
         <v>6.75</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>9.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45987.41666666666</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45987.41666666666</v>
@@ -1269,55 +1269,55 @@
         <v>1.75</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="R7" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="S7" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="T7" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="U7" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="V7" t="n">
-        <v>9.9</v>
+        <v>13</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
         <v>1.08</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AC7" t="n">
-        <v>6.3</v>
+        <v>6.35</v>
       </c>
       <c r="AD7" t="n">
         <v>1.06</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AH7" t="n">
         <v>1.32</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.44</v>
+        <v>1.61</v>
       </c>
       <c r="M13" t="n">
-        <v>3.31</v>
+        <v>3.63</v>
       </c>
       <c r="N13" t="n">
-        <v>2.8</v>
+        <v>5.8</v>
       </c>
       <c r="O13" t="n">
-        <v>3</v>
+        <v>2.29</v>
       </c>
       <c r="P13" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.55</v>
+        <v>5.83</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S13" t="n">
-        <v>2.65</v>
+        <v>2.99</v>
       </c>
       <c r="T13" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="U13" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V13" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.66</v>
+        <v>3.57</v>
       </c>
       <c r="AD13" t="n">
         <v>1.25</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="AF13" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.5</v>
+        <v>2.15</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,49 +2087,49 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.07</v>
+        <v>1.81</v>
       </c>
       <c r="M14" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="N14" t="n">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="O14" t="n">
-        <v>2.83</v>
+        <v>2.35</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.75</v>
+        <v>4.35</v>
       </c>
       <c r="R14" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S14" t="n">
-        <v>2.89</v>
+        <v>2.81</v>
       </c>
       <c r="T14" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="U14" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="W14" t="n">
         <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y14" t="n">
         <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AA14" t="n">
         <v>1.98</v>
@@ -2138,22 +2138,22 @@
         <v>1.77</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.01</v>
+        <v>1.85</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.63</v>
+        <v>2</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,49 +2206,49 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.81</v>
+        <v>2.07</v>
       </c>
       <c r="M15" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N15" t="n">
         <v>3.45</v>
       </c>
-      <c r="N15" t="n">
-        <v>4.4</v>
-      </c>
       <c r="O15" t="n">
-        <v>2.35</v>
+        <v>2.83</v>
       </c>
       <c r="P15" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.35</v>
+        <v>3.75</v>
       </c>
       <c r="R15" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="S15" t="n">
-        <v>2.81</v>
+        <v>2.89</v>
       </c>
       <c r="T15" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="U15" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="V15" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="W15" t="n">
         <v>1.05</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
         <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AA15" t="n">
         <v>1.98</v>
@@ -2257,22 +2257,22 @@
         <v>1.77</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AH15" t="n">
-        <v>2</v>
+        <v>1.63</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.61</v>
+        <v>2.44</v>
       </c>
       <c r="M16" t="n">
-        <v>3.63</v>
+        <v>3.31</v>
       </c>
       <c r="N16" t="n">
-        <v>5.8</v>
+        <v>2.8</v>
       </c>
       <c r="O16" t="n">
-        <v>2.29</v>
+        <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.83</v>
+        <v>3.55</v>
       </c>
       <c r="R16" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>2.99</v>
+        <v>2.65</v>
       </c>
       <c r="T16" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="U16" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V16" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X16" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.57</v>
+        <v>3.66</v>
       </c>
       <c r="AD16" t="n">
         <v>1.25</v>
       </c>
       <c r="AE16" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF16" t="n">
         <v>2</v>
       </c>
-      <c r="AF16" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AG16" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.15</v>
+        <v>1.5</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.07</v>
+        <v>2.52</v>
       </c>
       <c r="M17" t="n">
-        <v>3.56</v>
+        <v>3.13</v>
       </c>
       <c r="N17" t="n">
-        <v>3.27</v>
+        <v>2.83</v>
       </c>
       <c r="O17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V17" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z17" t="n">
         <v>2.75</v>
       </c>
-      <c r="P17" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V17" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AA17" t="n">
-        <v>1.77</v>
+        <v>2.28</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.98</v>
+        <v>1.55</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.3</v>
+        <v>4.33</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.6</v>
+        <v>1.23</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.67</v>
+        <v>2.01</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.28</v>
+        <v>1.89</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.7</v>
+        <v>1.42</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.52</v>
+        <v>2.29</v>
       </c>
       <c r="M18" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V18" t="n">
+        <v>6</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC18" t="n">
         <v>3.13</v>
       </c>
-      <c r="N18" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="O18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V18" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>4.33</v>
-      </c>
       <c r="AD18" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.01</v>
+        <v>1.71</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.42</v>
+        <v>1.66</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.26</v>
+        <v>1.43</v>
       </c>
       <c r="M19" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="N19" t="n">
-        <v>8.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="O19" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="P19" t="n">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.5</v>
+        <v>5.32</v>
       </c>
       <c r="R19" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="S19" t="n">
-        <v>4.6</v>
+        <v>3.54</v>
       </c>
       <c r="T19" t="n">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="U19" t="n">
-        <v>1.88</v>
+        <v>1.65</v>
       </c>
       <c r="V19" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="W19" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.15</v>
+        <v>2.51</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.76</v>
+        <v>2.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.28</v>
+        <v>2</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>6.9</v>
+        <v>1.71</v>
       </c>
       <c r="M20" t="n">
-        <v>5</v>
+        <v>3.92</v>
       </c>
       <c r="N20" t="n">
-        <v>1.38</v>
+        <v>4.33</v>
       </c>
       <c r="O20" t="n">
-        <v>5.5</v>
+        <v>2.19</v>
       </c>
       <c r="P20" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.85</v>
+        <v>4.2</v>
       </c>
       <c r="R20" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="S20" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="T20" t="n">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="U20" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="V20" t="n">
         <v>5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.15</v>
+        <v>2.46</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.13</v>
+        <v>2.24</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.71</v>
+        <v>2.63</v>
       </c>
       <c r="M21" t="n">
-        <v>3.92</v>
+        <v>3.51</v>
       </c>
       <c r="N21" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="O21" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z21" t="n">
         <v>4.33</v>
       </c>
-      <c r="O21" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="V21" t="n">
-        <v>5</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>4.6</v>
-      </c>
       <c r="AA21" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.24</v>
+        <v>1.53</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.29</v>
+        <v>6.9</v>
       </c>
       <c r="M22" t="n">
-        <v>3.39</v>
+        <v>5</v>
       </c>
       <c r="N22" t="n">
-        <v>2.95</v>
+        <v>1.38</v>
       </c>
       <c r="O22" t="n">
-        <v>2.8</v>
+        <v>5.5</v>
       </c>
       <c r="P22" t="n">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.78</v>
+        <v>1.85</v>
       </c>
       <c r="R22" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>3.14</v>
+        <v>3.75</v>
       </c>
       <c r="T22" t="n">
-        <v>2.64</v>
+        <v>2.26</v>
       </c>
       <c r="U22" t="n">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="V22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="X22" t="n">
         <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.79</v>
+        <v>1.63</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.13</v>
+        <v>2.35</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.35</v>
+        <v>1.52</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.66</v>
+        <v>1.13</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.63</v>
+        <v>1.26</v>
       </c>
       <c r="M23" t="n">
-        <v>3.51</v>
+        <v>6</v>
       </c>
       <c r="N23" t="n">
-        <v>2.47</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O23" t="n">
-        <v>3.16</v>
+        <v>1.72</v>
       </c>
       <c r="P23" t="n">
-        <v>2.25</v>
+        <v>2.91</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.1</v>
+        <v>6.5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="S23" t="n">
-        <v>3.36</v>
+        <v>4.6</v>
       </c>
       <c r="T23" t="n">
-        <v>2.42</v>
+        <v>1.94</v>
       </c>
       <c r="U23" t="n">
-        <v>1.56</v>
+        <v>1.88</v>
       </c>
       <c r="V23" t="n">
-        <v>5.5</v>
+        <v>3.7</v>
       </c>
       <c r="W23" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="X23" t="n">
         <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.33</v>
+        <v>7.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.25</v>
+        <v>3.15</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.7</v>
+        <v>1.76</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.5</v>
+        <v>1.95</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.6</v>
+        <v>2.28</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.53</v>
+        <v>3.5</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,55 +3277,55 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.43</v>
+        <v>2.07</v>
       </c>
       <c r="M24" t="n">
-        <v>4.6</v>
+        <v>3.56</v>
       </c>
       <c r="N24" t="n">
-        <v>6.6</v>
+        <v>3.27</v>
       </c>
       <c r="O24" t="n">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
       <c r="P24" t="n">
-        <v>2.75</v>
+        <v>2.12</v>
       </c>
       <c r="Q24" t="n">
-        <v>5.32</v>
+        <v>3.68</v>
       </c>
       <c r="R24" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="S24" t="n">
-        <v>3.54</v>
+        <v>3.33</v>
       </c>
       <c r="T24" t="n">
-        <v>2.2</v>
+        <v>2.67</v>
       </c>
       <c r="U24" t="n">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="V24" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="W24" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="X24" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="Z24" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.49</v>
+        <v>1.77</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.51</v>
+        <v>1.98</v>
       </c>
       <c r="AC24" t="n">
         <v>2.3</v>
@@ -3334,16 +3334,16 @@
         <v>1.6</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AF24" t="n">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="AH24" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45987.70833333334</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -774,7 +774,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -893,7 +893,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -1144,19 +1144,19 @@
         <v>3.58</v>
       </c>
       <c r="O6" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.33</v>
+        <v>4.55</v>
       </c>
       <c r="R6" t="n">
         <v>1.51</v>
       </c>
       <c r="S6" t="n">
-        <v>2.47</v>
+        <v>2.29</v>
       </c>
       <c r="T6" t="n">
         <v>3.28</v>
@@ -1171,7 +1171,7 @@
         <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y6" t="n">
         <v>1.43</v>
@@ -1186,22 +1186,22 @@
         <v>1.57</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AE6" t="n">
         <v>1.99</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45987.45833333334</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="M8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="O8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q8" t="n">
         <v>2.9</v>
       </c>
-      <c r="N8" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="O8" t="n">
-        <v>5</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.8</v>
-      </c>
       <c r="R8" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="S8" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="T8" t="n">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="U8" t="n">
         <v>1.19</v>
       </c>
       <c r="V8" t="n">
-        <v>12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W8" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.06</v>
+        <v>2.78</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AC8" t="n">
         <v>5.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.49</v>
+        <v>2.29</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG8" t="n">
         <v>1.4</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45987.60416666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="M9" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="N9" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="O9" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="P9" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.02</v>
+        <v>2.63</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="S9" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="T9" t="n">
-        <v>3.74</v>
+        <v>3.9</v>
       </c>
       <c r="U9" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="V9" t="n">
-        <v>8.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="W9" t="n">
         <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AA9" t="n">
         <v>2.88</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.29</v>
+        <v>2.48</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45987.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,49 +1611,49 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O10" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R10" t="n">
         <v>1.32</v>
       </c>
-      <c r="M10" t="n">
-        <v>5</v>
-      </c>
-      <c r="N10" t="n">
-        <v>9</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>7</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.27</v>
-      </c>
       <c r="S10" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="T10" t="n">
-        <v>2.43</v>
+        <v>2.39</v>
       </c>
       <c r="U10" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="V10" t="n">
-        <v>5.05</v>
+        <v>5.35</v>
       </c>
       <c r="W10" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.8</v>
+        <v>4.15</v>
       </c>
       <c r="AA10" t="n">
         <v>1.58</v>
@@ -1662,22 +1662,22 @@
         <v>2.35</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.91</v>
+        <v>2.14</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.25</v>
+        <v>1.16</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45987.61458333334</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,49 +1730,49 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>5.1</v>
+        <v>1.32</v>
       </c>
       <c r="M11" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="N11" t="n">
-        <v>1.6</v>
+        <v>9</v>
       </c>
       <c r="O11" t="n">
-        <v>4.75</v>
+        <v>1.75</v>
       </c>
       <c r="P11" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.1</v>
+        <v>7</v>
       </c>
       <c r="R11" t="n">
         <v>1.26</v>
       </c>
       <c r="S11" t="n">
-        <v>3.36</v>
+        <v>3.55</v>
       </c>
       <c r="T11" t="n">
-        <v>2.51</v>
+        <v>2.42</v>
       </c>
       <c r="U11" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="V11" t="n">
-        <v>5.35</v>
+        <v>5.05</v>
       </c>
       <c r="W11" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA11" t="n">
         <v>1.58</v>
@@ -1781,22 +1781,22 @@
         <v>2.35</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.13</v>
+        <v>1.83</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.25</v>
+        <v>1.17</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.17</v>
+        <v>3.25</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45987.61458333334</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.61</v>
+        <v>1.81</v>
       </c>
       <c r="M13" t="n">
-        <v>3.63</v>
+        <v>3.45</v>
       </c>
       <c r="N13" t="n">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="O13" t="n">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="P13" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.83</v>
+        <v>4.55</v>
       </c>
       <c r="R13" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>2.99</v>
+        <v>2.73</v>
       </c>
       <c r="T13" t="n">
-        <v>2.89</v>
+        <v>2.96</v>
       </c>
       <c r="U13" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="V13" t="n">
-        <v>7</v>
+        <v>6.45</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.57</v>
+        <v>3.26</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AE13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH13" t="n">
         <v>2</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>2.15</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,49 +2087,49 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.81</v>
+        <v>2.07</v>
       </c>
       <c r="M14" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N14" t="n">
         <v>3.45</v>
       </c>
-      <c r="N14" t="n">
-        <v>4.4</v>
-      </c>
       <c r="O14" t="n">
-        <v>2.35</v>
+        <v>2.99</v>
       </c>
       <c r="P14" t="n">
         <v>2.15</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.35</v>
+        <v>3.5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="S14" t="n">
-        <v>2.81</v>
+        <v>2.69</v>
       </c>
       <c r="T14" t="n">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="U14" t="n">
         <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
         <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AA14" t="n">
         <v>1.98</v>
@@ -2138,22 +2138,22 @@
         <v>1.77</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AD14" t="n">
         <v>1.29</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,49 +2206,49 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.07</v>
+        <v>2.44</v>
       </c>
       <c r="M15" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q15" t="n">
         <v>3.35</v>
       </c>
-      <c r="N15" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O15" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3.75</v>
-      </c>
       <c r="R15" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
-        <v>2.89</v>
+        <v>2.62</v>
       </c>
       <c r="T15" t="n">
         <v>2.95</v>
       </c>
       <c r="U15" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="V15" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.25</v>
+        <v>2.99</v>
       </c>
       <c r="AA15" t="n">
         <v>1.98</v>
@@ -2257,22 +2257,22 @@
         <v>1.77</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.38</v>
+        <v>3.73</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.63</v>
+        <v>1.43</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.44</v>
+        <v>1.61</v>
       </c>
       <c r="M16" t="n">
-        <v>3.31</v>
+        <v>3.63</v>
       </c>
       <c r="N16" t="n">
-        <v>2.8</v>
+        <v>5.8</v>
       </c>
       <c r="O16" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="P16" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.55</v>
+        <v>5.79</v>
       </c>
       <c r="R16" t="n">
         <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="T16" t="n">
-        <v>2.94</v>
+        <v>3.03</v>
       </c>
       <c r="U16" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V16" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="W16" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.66</v>
+        <v>3.63</v>
       </c>
       <c r="AD16" t="n">
         <v>1.25</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.81</v>
+        <v>1.98</v>
       </c>
       <c r="AF16" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.5</v>
+        <v>2.15</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.52</v>
+        <v>2.07</v>
       </c>
       <c r="M17" t="n">
-        <v>3.13</v>
+        <v>3.56</v>
       </c>
       <c r="N17" t="n">
-        <v>2.83</v>
+        <v>3.27</v>
       </c>
       <c r="O17" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="P17" t="n">
-        <v>1.91</v>
+        <v>2.13</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.25</v>
+        <v>3.72</v>
       </c>
       <c r="R17" t="n">
-        <v>1.46</v>
+        <v>1.34</v>
       </c>
       <c r="S17" t="n">
-        <v>2.42</v>
+        <v>3.3</v>
       </c>
       <c r="T17" t="n">
-        <v>3.28</v>
+        <v>2.53</v>
       </c>
       <c r="U17" t="n">
-        <v>1.29</v>
+        <v>1.48</v>
       </c>
       <c r="V17" t="n">
-        <v>8.1</v>
+        <v>5.8</v>
       </c>
       <c r="W17" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="X17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.75</v>
+        <v>4.35</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.28</v>
+        <v>1.77</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.55</v>
+        <v>1.98</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.33</v>
+        <v>2.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.23</v>
+        <v>1.6</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.01</v>
+        <v>1.62</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.89</v>
+        <v>2.29</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.42</v>
+        <v>1.71</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.29</v>
+        <v>1.26</v>
       </c>
       <c r="M18" t="n">
-        <v>3.39</v>
+        <v>6</v>
       </c>
       <c r="N18" t="n">
-        <v>2.95</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>2.8</v>
+        <v>1.67</v>
       </c>
       <c r="P18" t="n">
-        <v>2.25</v>
+        <v>2.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.78</v>
+        <v>6</v>
       </c>
       <c r="R18" t="n">
-        <v>1.37</v>
+        <v>1.16</v>
       </c>
       <c r="S18" t="n">
-        <v>3.14</v>
+        <v>4.85</v>
       </c>
       <c r="T18" t="n">
-        <v>2.64</v>
+        <v>1.86</v>
       </c>
       <c r="U18" t="n">
-        <v>1.44</v>
+        <v>1.98</v>
       </c>
       <c r="V18" t="n">
-        <v>6</v>
+        <v>3.58</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.24</v>
+        <v>1.03</v>
       </c>
       <c r="Z18" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AH18" t="n">
         <v>3.6</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.66</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.43</v>
+        <v>2.29</v>
       </c>
       <c r="M19" t="n">
-        <v>4.6</v>
+        <v>3.39</v>
       </c>
       <c r="N19" t="n">
-        <v>6.6</v>
+        <v>2.95</v>
       </c>
       <c r="O19" t="n">
-        <v>1.75</v>
+        <v>2.8</v>
       </c>
       <c r="P19" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.32</v>
+        <v>3.35</v>
       </c>
       <c r="R19" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="S19" t="n">
-        <v>3.54</v>
+        <v>2.93</v>
       </c>
       <c r="T19" t="n">
-        <v>2.2</v>
+        <v>2.64</v>
       </c>
       <c r="U19" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="V19" t="n">
-        <v>4.7</v>
+        <v>6.05</v>
       </c>
       <c r="W19" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.12</v>
+        <v>1.27</v>
       </c>
       <c r="Z19" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.49</v>
+        <v>1.79</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.51</v>
+        <v>1.95</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.3</v>
+        <v>3.16</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AF19" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.17</v>
+        <v>1.35</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.1</v>
+        <v>1.62</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,55 +2801,55 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.71</v>
+        <v>1.43</v>
       </c>
       <c r="M20" t="n">
-        <v>3.92</v>
+        <v>4.6</v>
       </c>
       <c r="N20" t="n">
-        <v>4.33</v>
+        <v>6.6</v>
       </c>
       <c r="O20" t="n">
-        <v>2.19</v>
+        <v>1.89</v>
       </c>
       <c r="P20" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.2</v>
+        <v>5.42</v>
       </c>
       <c r="R20" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="S20" t="n">
-        <v>3.5</v>
+        <v>3.32</v>
       </c>
       <c r="T20" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="U20" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="V20" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="W20" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y20" t="n">
         <v>1.15</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.13</v>
       </c>
       <c r="Z20" t="n">
         <v>4.6</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.65</v>
+        <v>1.49</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.2</v>
+        <v>2.51</v>
       </c>
       <c r="AC20" t="n">
         <v>2.3</v>
@@ -2858,16 +2858,16 @@
         <v>1.6</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.58</v>
+        <v>1.87</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.46</v>
+        <v>1.9</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.24</v>
+        <v>3.01</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.63</v>
+        <v>2.52</v>
       </c>
       <c r="M21" t="n">
-        <v>3.51</v>
+        <v>3.13</v>
       </c>
       <c r="N21" t="n">
-        <v>2.47</v>
+        <v>2.83</v>
       </c>
       <c r="O21" t="n">
-        <v>3.16</v>
+        <v>3.4</v>
       </c>
       <c r="P21" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="R21" t="n">
-        <v>1.32</v>
+        <v>1.47</v>
       </c>
       <c r="S21" t="n">
-        <v>3.36</v>
+        <v>2.42</v>
       </c>
       <c r="T21" t="n">
-        <v>2.42</v>
+        <v>3.28</v>
       </c>
       <c r="U21" t="n">
-        <v>1.56</v>
+        <v>1.29</v>
       </c>
       <c r="V21" t="n">
-        <v>5.5</v>
+        <v>8.1</v>
       </c>
       <c r="W21" t="n">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="Z21" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC21" t="n">
         <v>4.33</v>
       </c>
-      <c r="AA21" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.7</v>
-      </c>
       <c r="AD21" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.53</v>
+        <v>2.04</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.6</v>
+        <v>1.82</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>6.9</v>
+        <v>1.71</v>
       </c>
       <c r="M22" t="n">
-        <v>5</v>
+        <v>3.92</v>
       </c>
       <c r="N22" t="n">
-        <v>1.38</v>
+        <v>4.33</v>
       </c>
       <c r="O22" t="n">
-        <v>5.5</v>
+        <v>2.1</v>
       </c>
       <c r="P22" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.85</v>
+        <v>5.35</v>
       </c>
       <c r="R22" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="S22" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="T22" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="U22" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="V22" t="n">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="W22" t="n">
         <v>1.16</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.13</v>
+        <v>2.3</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.26</v>
+        <v>6.9</v>
       </c>
       <c r="M23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N23" t="n">
-        <v>8.800000000000001</v>
+        <v>1.38</v>
       </c>
       <c r="O23" t="n">
-        <v>1.72</v>
+        <v>5.55</v>
       </c>
       <c r="P23" t="n">
-        <v>2.91</v>
+        <v>2.6</v>
       </c>
       <c r="Q23" t="n">
-        <v>6.5</v>
+        <v>1.91</v>
       </c>
       <c r="R23" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="S23" t="n">
-        <v>4.6</v>
+        <v>3.66</v>
       </c>
       <c r="T23" t="n">
-        <v>1.94</v>
+        <v>2.31</v>
       </c>
       <c r="U23" t="n">
-        <v>1.88</v>
+        <v>1.65</v>
       </c>
       <c r="V23" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="Z23" t="n">
-        <v>7.5</v>
+        <v>5.25</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.33</v>
+        <v>1.63</v>
       </c>
       <c r="AB23" t="n">
-        <v>3.15</v>
+        <v>2.25</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.76</v>
+        <v>2.35</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.95</v>
+        <v>1.52</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AH23" t="n">
-        <v>3.5</v>
+        <v>1.13</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.07</v>
+        <v>2.63</v>
       </c>
       <c r="M24" t="n">
-        <v>3.56</v>
+        <v>3.51</v>
       </c>
       <c r="N24" t="n">
-        <v>3.27</v>
+        <v>2.47</v>
       </c>
       <c r="O24" t="n">
-        <v>2.75</v>
+        <v>3.18</v>
       </c>
       <c r="P24" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.68</v>
+        <v>3.1</v>
       </c>
       <c r="R24" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S24" t="n">
-        <v>3.33</v>
+        <v>3.36</v>
       </c>
       <c r="T24" t="n">
-        <v>2.67</v>
+        <v>2.56</v>
       </c>
       <c r="U24" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="V24" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="W24" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X24" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.77</v>
+        <v>1.63</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3524,37 +3524,37 @@
         <v>3.31</v>
       </c>
       <c r="O26" t="n">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="P26" t="n">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>4.54</v>
       </c>
       <c r="R26" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="S26" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="T26" t="n">
         <v>2.57</v>
       </c>
       <c r="U26" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="V26" t="n">
         <v>6.25</v>
       </c>
       <c r="W26" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X26" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z26" t="n">
         <v>3.8</v>
@@ -3566,10 +3566,10 @@
         <v>1.85</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE26" t="n">
         <v>1.7</v>
@@ -3578,10 +3578,10 @@
         <v>2.02</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45987.79166666666</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,19 +871,19 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -893,77 +893,77 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45987.41666666666</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1012,77 +1012,77 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>9.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45987.41666666666</v>
@@ -1118,20 +1118,20 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1237,20 +1237,20 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -1263,67 +1263,67 @@
         <v>3.1</v>
       </c>
       <c r="O7" t="n">
-        <v>3.82</v>
+        <v>3.88</v>
       </c>
       <c r="P7" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.4</v>
+        <v>3.46</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="S7" t="n">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="T7" t="n">
-        <v>3.9</v>
+        <v>4.15</v>
       </c>
       <c r="U7" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="V7" t="n">
-        <v>13</v>
+        <v>9.9</v>
       </c>
       <c r="W7" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
         <v>1.08</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="AA7" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AC7" t="n">
-        <v>6.35</v>
+        <v>6.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="AF7" t="n">
         <v>1.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AI7" s="3" t="n">
-        <v>45987.54166666666</v>
+        <v>45987.5</v>
       </c>
     </row>
     <row r="8">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,49 +1968,49 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.81</v>
+        <v>2.44</v>
       </c>
       <c r="M13" t="n">
-        <v>3.45</v>
+        <v>3.31</v>
       </c>
       <c r="N13" t="n">
-        <v>4.4</v>
+        <v>2.8</v>
       </c>
       <c r="O13" t="n">
-        <v>2.35</v>
+        <v>3.05</v>
       </c>
       <c r="P13" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.55</v>
+        <v>3.35</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S13" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="T13" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="U13" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="V13" t="n">
-        <v>6.45</v>
+        <v>7.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.24</v>
+        <v>2.99</v>
       </c>
       <c r="AA13" t="n">
         <v>1.98</v>
@@ -2019,22 +2019,22 @@
         <v>1.77</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.26</v>
+        <v>3.73</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AH13" t="n">
-        <v>2</v>
+        <v>1.43</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,49 +2087,49 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.07</v>
+        <v>1.81</v>
       </c>
       <c r="M14" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="N14" t="n">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="O14" t="n">
-        <v>2.99</v>
+        <v>2.35</v>
       </c>
       <c r="P14" t="n">
         <v>2.15</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.5</v>
+        <v>4.55</v>
       </c>
       <c r="R14" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="T14" t="n">
-        <v>3.07</v>
+        <v>2.96</v>
       </c>
       <c r="U14" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="V14" t="n">
-        <v>6.9</v>
+        <v>6.45</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y14" t="n">
         <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="AA14" t="n">
         <v>1.98</v>
@@ -2138,22 +2138,22 @@
         <v>1.77</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.5</v>
+        <v>3.26</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.44</v>
+        <v>1.61</v>
       </c>
       <c r="M15" t="n">
-        <v>3.31</v>
+        <v>3.63</v>
       </c>
       <c r="N15" t="n">
-        <v>2.8</v>
+        <v>5.8</v>
       </c>
       <c r="O15" t="n">
-        <v>3.05</v>
+        <v>2.2</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.35</v>
+        <v>5.79</v>
       </c>
       <c r="R15" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="T15" t="n">
-        <v>2.95</v>
+        <v>3.03</v>
       </c>
       <c r="U15" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="V15" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.99</v>
+        <v>3.25</v>
       </c>
       <c r="AA15" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE15" t="n">
         <v>1.98</v>
       </c>
-      <c r="AB15" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AF15" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.43</v>
+        <v>2.15</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,43 +2325,43 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.61</v>
+        <v>2.07</v>
       </c>
       <c r="M16" t="n">
-        <v>3.63</v>
+        <v>3.35</v>
       </c>
       <c r="N16" t="n">
-        <v>5.8</v>
+        <v>3.45</v>
       </c>
       <c r="O16" t="n">
-        <v>2.2</v>
+        <v>2.99</v>
       </c>
       <c r="P16" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.79</v>
+        <v>3.5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S16" t="n">
         <v>2.69</v>
       </c>
       <c r="T16" t="n">
-        <v>3.03</v>
+        <v>3.07</v>
       </c>
       <c r="U16" t="n">
         <v>1.36</v>
       </c>
       <c r="V16" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="W16" t="n">
         <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
         <v>1.3</v>
@@ -2370,28 +2370,28 @@
         <v>3.25</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.63</v>
+        <v>3.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.15</v>
+        <v>1.57</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,55 +2444,55 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.07</v>
+        <v>1.43</v>
       </c>
       <c r="M17" t="n">
-        <v>3.56</v>
+        <v>4.6</v>
       </c>
       <c r="N17" t="n">
-        <v>3.27</v>
+        <v>6.6</v>
       </c>
       <c r="O17" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="P17" t="n">
         <v>2.75</v>
       </c>
-      <c r="P17" t="n">
-        <v>2.13</v>
-      </c>
       <c r="Q17" t="n">
-        <v>3.72</v>
+        <v>5.42</v>
       </c>
       <c r="R17" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="S17" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="T17" t="n">
-        <v>2.53</v>
+        <v>2.34</v>
       </c>
       <c r="U17" t="n">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="V17" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="W17" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X17" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.35</v>
+        <v>4.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.77</v>
+        <v>1.49</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.98</v>
+        <v>2.51</v>
       </c>
       <c r="AC17" t="n">
         <v>2.3</v>
@@ -2501,16 +2501,16 @@
         <v>1.6</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.62</v>
+        <v>1.87</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.29</v>
+        <v>1.9</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.71</v>
+        <v>3.01</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.26</v>
+        <v>1.71</v>
       </c>
       <c r="M18" t="n">
-        <v>6</v>
+        <v>3.92</v>
       </c>
       <c r="N18" t="n">
-        <v>8.800000000000001</v>
+        <v>4.33</v>
       </c>
       <c r="O18" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="P18" t="n">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="Q18" t="n">
-        <v>6</v>
+        <v>5.35</v>
       </c>
       <c r="R18" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V18" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="W18" t="n">
         <v>1.16</v>
       </c>
-      <c r="S18" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="V18" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.27</v>
-      </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="Z18" t="n">
-        <v>8</v>
+        <v>4.6</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.33</v>
+        <v>1.65</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.76</v>
+        <v>2.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.29</v>
+        <v>2.07</v>
       </c>
       <c r="M19" t="n">
-        <v>3.39</v>
+        <v>3.56</v>
       </c>
       <c r="N19" t="n">
-        <v>2.95</v>
+        <v>3.27</v>
       </c>
       <c r="O19" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="P19" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.35</v>
+        <v>3.72</v>
       </c>
       <c r="R19" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="S19" t="n">
-        <v>2.93</v>
+        <v>3.3</v>
       </c>
       <c r="T19" t="n">
-        <v>2.64</v>
+        <v>2.53</v>
       </c>
       <c r="U19" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="V19" t="n">
-        <v>6.05</v>
+        <v>5.8</v>
       </c>
       <c r="W19" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X19" t="n">
         <v>1.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.5</v>
+        <v>4.35</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.16</v>
+        <v>2.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.43</v>
+        <v>1.26</v>
       </c>
       <c r="M20" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="N20" t="n">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>1.89</v>
+        <v>1.67</v>
       </c>
       <c r="P20" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.42</v>
+        <v>6</v>
       </c>
       <c r="R20" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="S20" t="n">
-        <v>3.32</v>
+        <v>4.85</v>
       </c>
       <c r="T20" t="n">
-        <v>2.34</v>
+        <v>1.86</v>
       </c>
       <c r="U20" t="n">
-        <v>1.58</v>
+        <v>1.98</v>
       </c>
       <c r="V20" t="n">
-        <v>5.1</v>
+        <v>3.58</v>
       </c>
       <c r="W20" t="n">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
       <c r="X20" t="n">
         <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.6</v>
+        <v>8</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.51</v>
+        <v>3.15</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.3</v>
+        <v>1.76</v>
       </c>
       <c r="AD20" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE20" t="n">
         <v>1.6</v>
       </c>
-      <c r="AE20" t="n">
-        <v>1.87</v>
-      </c>
       <c r="AF20" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AH20" t="n">
-        <v>3.01</v>
+        <v>3.6</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.52</v>
+        <v>2.29</v>
       </c>
       <c r="M21" t="n">
-        <v>3.13</v>
+        <v>3.39</v>
       </c>
       <c r="N21" t="n">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="O21" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="P21" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="R21" t="n">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="S21" t="n">
-        <v>2.42</v>
+        <v>2.93</v>
       </c>
       <c r="T21" t="n">
-        <v>3.28</v>
+        <v>2.64</v>
       </c>
       <c r="U21" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="V21" t="n">
-        <v>8.1</v>
+        <v>6.05</v>
       </c>
       <c r="W21" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X21" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.28</v>
+        <v>1.79</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.55</v>
+        <v>1.95</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.33</v>
+        <v>3.16</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.04</v>
+        <v>1.67</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.82</v>
+        <v>2.15</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.46</v>
+        <v>1.62</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.71</v>
+        <v>6.9</v>
       </c>
       <c r="M22" t="n">
-        <v>3.92</v>
+        <v>5</v>
       </c>
       <c r="N22" t="n">
-        <v>4.33</v>
+        <v>1.38</v>
       </c>
       <c r="O22" t="n">
-        <v>2.1</v>
+        <v>5.55</v>
       </c>
       <c r="P22" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.35</v>
+        <v>1.91</v>
       </c>
       <c r="R22" t="n">
         <v>1.23</v>
       </c>
       <c r="S22" t="n">
-        <v>3.5</v>
+        <v>3.66</v>
       </c>
       <c r="T22" t="n">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="U22" t="n">
         <v>1.65</v>
       </c>
       <c r="V22" t="n">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="W22" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y22" t="n">
         <v>1.16</v>
       </c>
-      <c r="X22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.17</v>
-      </c>
       <c r="Z22" t="n">
-        <v>4.6</v>
+        <v>5.25</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.3</v>
+        <v>1.13</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,49 +3158,49 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>6.9</v>
+        <v>2.63</v>
       </c>
       <c r="M23" t="n">
-        <v>5</v>
+        <v>3.51</v>
       </c>
       <c r="N23" t="n">
-        <v>1.38</v>
+        <v>2.47</v>
       </c>
       <c r="O23" t="n">
-        <v>5.55</v>
+        <v>3.18</v>
       </c>
       <c r="P23" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.91</v>
+        <v>3.1</v>
       </c>
       <c r="R23" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="S23" t="n">
-        <v>3.66</v>
+        <v>3.36</v>
       </c>
       <c r="T23" t="n">
-        <v>2.31</v>
+        <v>2.56</v>
       </c>
       <c r="U23" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="V23" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="W23" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z23" t="n">
-        <v>5.25</v>
+        <v>4.4</v>
       </c>
       <c r="AA23" t="n">
         <v>1.63</v>
@@ -3209,22 +3209,22 @@
         <v>2.25</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.13</v>
+        <v>1.44</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.63</v>
+        <v>2.52</v>
       </c>
       <c r="M24" t="n">
-        <v>3.51</v>
+        <v>3.13</v>
       </c>
       <c r="N24" t="n">
-        <v>2.47</v>
+        <v>2.83</v>
       </c>
       <c r="O24" t="n">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="P24" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="R24" t="n">
-        <v>1.32</v>
+        <v>1.47</v>
       </c>
       <c r="S24" t="n">
-        <v>3.36</v>
+        <v>2.42</v>
       </c>
       <c r="T24" t="n">
-        <v>2.56</v>
+        <v>3.28</v>
       </c>
       <c r="U24" t="n">
-        <v>1.57</v>
+        <v>1.29</v>
       </c>
       <c r="V24" t="n">
-        <v>5.2</v>
+        <v>8.1</v>
       </c>
       <c r="W24" t="n">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AD24" t="n">
         <v>1.2</v>
       </c>
-      <c r="Z24" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AE24" t="n">
-        <v>1.53</v>
+        <v>2.04</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.4</v>
+        <v>1.82</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45987.70833333334</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -1369,17 +1369,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="M8" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="N8" t="n">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="O8" t="n">
         <v>4.2</v>
@@ -1388,19 +1388,19 @@
         <v>1.83</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="S8" t="n">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="T8" t="n">
-        <v>3.78</v>
+        <v>3.74</v>
       </c>
       <c r="U8" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="V8" t="n">
         <v>8.800000000000001</v>
@@ -1421,10 +1421,10 @@
         <v>2.78</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="AD8" t="n">
         <v>1.13</v>
@@ -1433,7 +1433,7 @@
         <v>2.29</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG8" t="n">
         <v>1.4</v>
@@ -1492,34 +1492,34 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="M9" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="N9" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="P9" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="R9" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="S9" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="T9" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="U9" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="V9" t="n">
         <v>13</v>
@@ -1531,34 +1531,34 @@
         <v>1.15</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AB9" t="n">
         <v>1.36</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.75</v>
+        <v>6.78</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45987.60416666666</v>
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5.1</v>
+        <v>5.75</v>
       </c>
       <c r="M10" t="n">
-        <v>4.1</v>
+        <v>4.42</v>
       </c>
       <c r="N10" t="n">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="O10" t="n">
-        <v>4.51</v>
+        <v>5</v>
       </c>
       <c r="P10" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="R10" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S10" t="n">
-        <v>3.36</v>
+        <v>3.2</v>
       </c>
       <c r="T10" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="U10" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="V10" t="n">
-        <v>5.35</v>
+        <v>5.65</v>
       </c>
       <c r="W10" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.58</v>
+        <v>1.74</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.35</v>
+        <v>2.18</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.14</v>
+        <v>1.96</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45987.61458333334</v>
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="M11" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="N11" t="n">
-        <v>9</v>
+        <v>11.9</v>
       </c>
       <c r="O11" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="P11" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R11" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="T11" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="U11" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="V11" t="n">
-        <v>5.05</v>
+        <v>5.25</v>
       </c>
       <c r="W11" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.1</v>
+        <v>2.62</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.91</v>
+        <v>2.09</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.25</v>
+        <v>3.61</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45987.61458333334</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,49 +2087,49 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.81</v>
+        <v>2.07</v>
       </c>
       <c r="M14" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N14" t="n">
         <v>3.45</v>
       </c>
-      <c r="N14" t="n">
-        <v>4.4</v>
-      </c>
       <c r="O14" t="n">
-        <v>2.35</v>
+        <v>2.99</v>
       </c>
       <c r="P14" t="n">
         <v>2.15</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.55</v>
+        <v>3.5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S14" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="T14" t="n">
-        <v>2.96</v>
+        <v>3.07</v>
       </c>
       <c r="U14" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>6.45</v>
+        <v>6.9</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
         <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="AA14" t="n">
         <v>1.98</v>
@@ -2138,22 +2138,22 @@
         <v>1.77</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.26</v>
+        <v>3.5</v>
       </c>
       <c r="AD14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG14" t="n">
         <v>1.33</v>
       </c>
-      <c r="AE14" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH14" t="n">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.61</v>
+        <v>1.81</v>
       </c>
       <c r="M15" t="n">
-        <v>3.63</v>
+        <v>3.45</v>
       </c>
       <c r="N15" t="n">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="O15" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.79</v>
+        <v>4.55</v>
       </c>
       <c r="R15" t="n">
         <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="T15" t="n">
-        <v>3.03</v>
+        <v>2.96</v>
       </c>
       <c r="U15" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="V15" t="n">
-        <v>7</v>
+        <v>6.45</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
         <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.63</v>
+        <v>3.26</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,43 +2325,43 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.07</v>
+        <v>1.61</v>
       </c>
       <c r="M16" t="n">
-        <v>3.35</v>
+        <v>3.63</v>
       </c>
       <c r="N16" t="n">
-        <v>3.45</v>
+        <v>5.8</v>
       </c>
       <c r="O16" t="n">
-        <v>2.99</v>
+        <v>2.2</v>
       </c>
       <c r="P16" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.5</v>
+        <v>5.79</v>
       </c>
       <c r="R16" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
         <v>2.69</v>
       </c>
       <c r="T16" t="n">
-        <v>3.07</v>
+        <v>3.03</v>
       </c>
       <c r="U16" t="n">
         <v>1.36</v>
       </c>
       <c r="V16" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="W16" t="n">
         <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
         <v>1.3</v>
@@ -2370,28 +2370,28 @@
         <v>3.25</v>
       </c>
       <c r="AA16" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE16" t="n">
         <v>1.98</v>
       </c>
-      <c r="AB16" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AF16" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.57</v>
+        <v>2.15</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.43</v>
+        <v>2.52</v>
       </c>
       <c r="M17" t="n">
-        <v>4.6</v>
+        <v>3.13</v>
       </c>
       <c r="N17" t="n">
-        <v>6.6</v>
+        <v>2.83</v>
       </c>
       <c r="O17" t="n">
-        <v>1.89</v>
+        <v>3.4</v>
       </c>
       <c r="P17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V17" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z17" t="n">
         <v>2.75</v>
       </c>
-      <c r="Q17" t="n">
-        <v>5.42</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V17" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>4.6</v>
-      </c>
       <c r="AA17" t="n">
-        <v>1.49</v>
+        <v>2.28</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.51</v>
+        <v>1.55</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.3</v>
+        <v>4.33</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.87</v>
+        <v>2.04</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.21</v>
+        <v>1.39</v>
       </c>
       <c r="AH17" t="n">
-        <v>3.01</v>
+        <v>1.46</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.71</v>
+        <v>4.9</v>
       </c>
       <c r="M18" t="n">
-        <v>3.92</v>
+        <v>4.5</v>
       </c>
       <c r="N18" t="n">
-        <v>4.33</v>
+        <v>1.6</v>
       </c>
       <c r="O18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="Q18" t="n">
         <v>2.1</v>
       </c>
-      <c r="P18" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>5.35</v>
-      </c>
       <c r="R18" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S18" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="T18" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="U18" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="V18" t="n">
-        <v>4.95</v>
+        <v>4.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X18" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AF18" t="n">
         <v>2.32</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.3</v>
+        <v>1.17</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.07</v>
+        <v>1.3</v>
       </c>
       <c r="M19" t="n">
-        <v>3.56</v>
+        <v>6.75</v>
       </c>
       <c r="N19" t="n">
-        <v>3.27</v>
+        <v>8.5</v>
       </c>
       <c r="O19" t="n">
-        <v>2.75</v>
+        <v>1.62</v>
       </c>
       <c r="P19" t="n">
-        <v>2.13</v>
+        <v>3</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.72</v>
+        <v>6.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.34</v>
+        <v>1.17</v>
       </c>
       <c r="S19" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="T19" t="n">
-        <v>2.53</v>
+        <v>1.8</v>
       </c>
       <c r="U19" t="n">
-        <v>1.48</v>
+        <v>2.06</v>
       </c>
       <c r="V19" t="n">
-        <v>5.8</v>
+        <v>3.6</v>
       </c>
       <c r="W19" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="X19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y19" t="n">
         <v>1.05</v>
       </c>
-      <c r="Y19" t="n">
-        <v>1.21</v>
-      </c>
       <c r="Z19" t="n">
-        <v>4.35</v>
+        <v>9.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.77</v>
+        <v>1.26</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.98</v>
+        <v>3.8</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.3</v>
+        <v>1.68</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.6</v>
+        <v>2.15</v>
       </c>
       <c r="AE19" t="n">
         <v>1.62</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.29</v>
+        <v>2.37</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.71</v>
+        <v>3.8</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.26</v>
+        <v>2.18</v>
       </c>
       <c r="M20" t="n">
-        <v>6</v>
+        <v>3.25</v>
       </c>
       <c r="N20" t="n">
-        <v>8.800000000000001</v>
+        <v>2.77</v>
       </c>
       <c r="O20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V20" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE20" t="n">
         <v>1.67</v>
       </c>
-      <c r="P20" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>6</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="S20" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="V20" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA20" t="n">
+      <c r="AF20" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AG20" t="n">
         <v>1.33</v>
       </c>
-      <c r="AB20" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE20" t="n">
+      <c r="AH20" t="n">
         <v>1.6</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>3.6</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="M21" t="n">
-        <v>3.39</v>
+        <v>3.5</v>
       </c>
       <c r="N21" t="n">
-        <v>2.95</v>
+        <v>2.36</v>
       </c>
       <c r="O21" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="P21" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="R21" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="S21" t="n">
-        <v>2.93</v>
+        <v>3.1</v>
       </c>
       <c r="T21" t="n">
-        <v>2.64</v>
+        <v>2.4</v>
       </c>
       <c r="U21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V21" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH21" t="n">
         <v>1.44</v>
-      </c>
-      <c r="V21" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.62</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>6.9</v>
+        <v>2.08</v>
       </c>
       <c r="M22" t="n">
-        <v>5</v>
+        <v>3.35</v>
       </c>
       <c r="N22" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V22" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AD22" t="n">
         <v>1.38</v>
       </c>
-      <c r="O22" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V22" t="n">
-        <v>5</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.52</v>
-      </c>
       <c r="AE22" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.13</v>
+        <v>1.74</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,37 +3158,37 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M23" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="N23" t="n">
+        <v>7</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="P23" t="n">
         <v>2.63</v>
       </c>
-      <c r="M23" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="N23" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="O23" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.25</v>
-      </c>
       <c r="Q23" t="n">
-        <v>3.1</v>
+        <v>5.7</v>
       </c>
       <c r="R23" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="S23" t="n">
-        <v>3.36</v>
+        <v>3.5</v>
       </c>
       <c r="T23" t="n">
-        <v>2.56</v>
+        <v>2.35</v>
       </c>
       <c r="U23" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="V23" t="n">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="W23" t="n">
         <v>1.12</v>
@@ -3197,34 +3197,34 @@
         <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AB23" t="n">
         <v>2.25</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.4</v>
+        <v>1.89</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.3</v>
+        <v>1.07</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.44</v>
+        <v>3</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.52</v>
+        <v>1.55</v>
       </c>
       <c r="M24" t="n">
-        <v>3.13</v>
+        <v>4.7</v>
       </c>
       <c r="N24" t="n">
-        <v>2.83</v>
+        <v>5.75</v>
       </c>
       <c r="O24" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>5</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S24" t="n">
         <v>3.4</v>
       </c>
-      <c r="P24" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.42</v>
-      </c>
       <c r="T24" t="n">
-        <v>3.28</v>
+        <v>2.25</v>
       </c>
       <c r="U24" t="n">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="V24" t="n">
-        <v>8.1</v>
+        <v>5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="X24" t="n">
         <v>1.04</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.75</v>
+        <v>5</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.28</v>
+        <v>1.54</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.55</v>
+        <v>2.38</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.33</v>
+        <v>2.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.04</v>
+        <v>1.67</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.82</v>
+        <v>2.3</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.39</v>
+        <v>1.17</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.46</v>
+        <v>2.71</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45987.70833333334</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -1347,99 +1347,99 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="M8" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="N8" t="n">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="O8" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="P8" t="n">
         <v>1.83</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="S8" t="n">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="T8" t="n">
-        <v>3.74</v>
+        <v>3.85</v>
       </c>
       <c r="U8" t="n">
         <v>1.22</v>
       </c>
       <c r="V8" t="n">
-        <v>8.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="W8" t="n">
         <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.75</v>
+        <v>6.78</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="AF8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG8" t="n">
         <v>1.6</v>
       </c>
-      <c r="AG8" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AH8" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45987.60416666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1488,77 +1488,77 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="O9" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="P9" t="n">
         <v>1.83</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="S9" t="n">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="T9" t="n">
-        <v>3.85</v>
+        <v>3.74</v>
       </c>
       <c r="U9" t="n">
         <v>1.22</v>
       </c>
       <c r="V9" t="n">
-        <v>13</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W9" t="n">
         <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AA9" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AC9" t="n">
-        <v>6.78</v>
+        <v>5.75</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45987.60416666666</v>
@@ -1594,20 +1594,20 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -1713,20 +1713,20 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -1832,30 +1832,30 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="M12" t="n">
-        <v>3.36</v>
+        <v>3.58</v>
       </c>
       <c r="N12" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="O12" t="n">
         <v>2.5</v>
@@ -1864,58 +1864,58 @@
         <v>2.36</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="R12" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S12" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="T12" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="U12" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="V12" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
         <v>1.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AE12" t="n">
         <v>1.53</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45987.625</v>
@@ -1942,19 +1942,19 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1964,77 +1964,77 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="M13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q13" t="n">
         <v>3.31</v>
-      </c>
-      <c r="N13" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O13" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>3.35</v>
       </c>
       <c r="R13" t="n">
         <v>1.42</v>
       </c>
       <c r="S13" t="n">
-        <v>2.62</v>
+        <v>2.85</v>
       </c>
       <c r="T13" t="n">
         <v>2.95</v>
       </c>
       <c r="U13" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="V13" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.99</v>
+        <v>3.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AB13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE13" t="n">
         <v>1.77</v>
       </c>
-      <c r="AC13" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AF13" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2061,99 +2061,99 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.07</v>
+        <v>2.48</v>
       </c>
       <c r="M14" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N14" t="n">
-        <v>3.45</v>
+        <v>2.7</v>
       </c>
       <c r="O14" t="n">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="P14" t="n">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R14" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="S14" t="n">
-        <v>2.69</v>
+        <v>2.55</v>
       </c>
       <c r="T14" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="U14" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V14" t="n">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X14" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.5</v>
+        <v>3.72</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG14" t="n">
         <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2180,16 +2180,16 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -2202,77 +2202,77 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.81</v>
+        <v>1.48</v>
       </c>
       <c r="M15" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="N15" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="O15" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="P15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V15" t="n">
+        <v>7</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH15" t="n">
         <v>2.15</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V15" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>2</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2299,99 +2299,99 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="M16" t="n">
-        <v>3.63</v>
+        <v>3.8</v>
       </c>
       <c r="N16" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="O16" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="P16" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.79</v>
+        <v>4.7</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="S16" t="n">
-        <v>2.69</v>
+        <v>3</v>
       </c>
       <c r="T16" t="n">
-        <v>3.03</v>
+        <v>2.7</v>
       </c>
       <c r="U16" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="V16" t="n">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X16" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.63</v>
+        <v>3.17</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.85</v>
+        <v>1.99</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.52</v>
+        <v>1.3</v>
       </c>
       <c r="M17" t="n">
-        <v>3.13</v>
+        <v>4.83</v>
       </c>
       <c r="N17" t="n">
-        <v>2.83</v>
+        <v>7</v>
       </c>
       <c r="O17" t="n">
-        <v>3.4</v>
+        <v>1.93</v>
       </c>
       <c r="P17" t="n">
-        <v>1.91</v>
+        <v>2.63</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.25</v>
+        <v>5.7</v>
       </c>
       <c r="R17" t="n">
-        <v>1.47</v>
+        <v>1.29</v>
       </c>
       <c r="S17" t="n">
-        <v>2.42</v>
+        <v>3.5</v>
       </c>
       <c r="T17" t="n">
-        <v>3.28</v>
+        <v>2.35</v>
       </c>
       <c r="U17" t="n">
-        <v>1.29</v>
+        <v>1.53</v>
       </c>
       <c r="V17" t="n">
-        <v>8.1</v>
+        <v>5.25</v>
       </c>
       <c r="W17" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.4</v>
+        <v>1.16</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.28</v>
+        <v>1.62</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.55</v>
+        <v>2.25</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.33</v>
+        <v>2.62</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.2</v>
+        <v>1.56</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.04</v>
+        <v>1.83</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.39</v>
+        <v>1.07</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.46</v>
+        <v>3</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>4.9</v>
+        <v>2.08</v>
       </c>
       <c r="M18" t="n">
-        <v>4.5</v>
+        <v>3.35</v>
       </c>
       <c r="N18" t="n">
-        <v>1.6</v>
+        <v>3.44</v>
       </c>
       <c r="O18" t="n">
-        <v>4.6</v>
+        <v>2.6</v>
       </c>
       <c r="P18" t="n">
-        <v>2.61</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="R18" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="S18" t="n">
-        <v>3.9</v>
+        <v>2.88</v>
       </c>
       <c r="T18" t="n">
-        <v>2.16</v>
+        <v>2.45</v>
       </c>
       <c r="U18" t="n">
-        <v>1.7</v>
+        <v>1.42</v>
       </c>
       <c r="V18" t="n">
-        <v>4.5</v>
+        <v>5.75</v>
       </c>
       <c r="W18" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.5</v>
+        <v>3.75</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.45</v>
+        <v>1.77</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.75</v>
+        <v>2</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.18</v>
+        <v>2.95</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.7</v>
+        <v>1.38</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.17</v>
+        <v>1.74</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.3</v>
+        <v>2.18</v>
       </c>
       <c r="M19" t="n">
-        <v>6.75</v>
+        <v>3.25</v>
       </c>
       <c r="N19" t="n">
-        <v>8.5</v>
+        <v>2.77</v>
       </c>
       <c r="O19" t="n">
-        <v>1.62</v>
+        <v>2.8</v>
       </c>
       <c r="P19" t="n">
-        <v>3</v>
+        <v>2.15</v>
       </c>
       <c r="Q19" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V19" t="n">
         <v>6.5</v>
       </c>
-      <c r="R19" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="V19" t="n">
-        <v>3.6</v>
-      </c>
       <c r="W19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y19" t="n">
         <v>1.25</v>
       </c>
-      <c r="X19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Z19" t="n">
-        <v>9.5</v>
+        <v>3.95</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.26</v>
+        <v>1.85</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.8</v>
+        <v>1.9</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.68</v>
+        <v>3.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.15</v>
+        <v>1.33</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.37</v>
+        <v>2.23</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.8</v>
+        <v>1.6</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.18</v>
+        <v>2.75</v>
       </c>
       <c r="M20" t="n">
+        <v>3</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q20" t="n">
         <v>3.25</v>
       </c>
-      <c r="N20" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="O20" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3.55</v>
-      </c>
       <c r="R20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V20" t="n">
+        <v>8</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y20" t="n">
         <v>1.4</v>
       </c>
-      <c r="S20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V20" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.25</v>
-      </c>
       <c r="Z20" t="n">
-        <v>3.95</v>
+        <v>2.64</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.67</v>
+        <v>1.97</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.23</v>
+        <v>1.83</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="M21" t="n">
-        <v>3.5</v>
+        <v>6.75</v>
       </c>
       <c r="N21" t="n">
-        <v>2.36</v>
+        <v>8.5</v>
       </c>
       <c r="O21" t="n">
-        <v>2.9</v>
+        <v>1.62</v>
       </c>
       <c r="P21" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AD21" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q21" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V21" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AE21" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.55</v>
+        <v>1.13</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.44</v>
+        <v>3.8</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3013,19 +3013,19 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -3035,77 +3035,77 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.08</v>
+        <v>2.5</v>
       </c>
       <c r="M22" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="N22" t="n">
-        <v>3.44</v>
+        <v>2.36</v>
       </c>
       <c r="O22" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V22" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AC22" t="n">
         <v>2.6</v>
       </c>
-      <c r="P22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V22" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.95</v>
-      </c>
       <c r="AD22" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.26</v>
+        <v>1.55</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.74</v>
+        <v>1.44</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.3</v>
+        <v>4.9</v>
       </c>
       <c r="M23" t="n">
-        <v>4.83</v>
+        <v>4.5</v>
       </c>
       <c r="N23" t="n">
-        <v>7</v>
+        <v>1.6</v>
       </c>
       <c r="O23" t="n">
-        <v>1.93</v>
+        <v>4.6</v>
       </c>
       <c r="P23" t="n">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="Q23" t="n">
-        <v>5.7</v>
+        <v>2.1</v>
       </c>
       <c r="R23" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="S23" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="T23" t="n">
-        <v>2.35</v>
+        <v>2.16</v>
       </c>
       <c r="U23" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="V23" t="n">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="X23" t="n">
         <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.62</v>
+        <v>1.45</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.62</v>
+        <v>2.18</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.89</v>
+        <v>2.32</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AH23" t="n">
-        <v>3</v>
+        <v>1.17</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.09</v>
+        <v>2.6</v>
       </c>
       <c r="M25" t="n">
-        <v>3.38</v>
+        <v>2.95</v>
       </c>
       <c r="N25" t="n">
-        <v>3.08</v>
+        <v>2.75</v>
       </c>
       <c r="O25" t="n">
         <v>2.75</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="M26" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="N26" t="n">
-        <v>3.31</v>
+        <v>4</v>
       </c>
       <c r="O26" t="n">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="P26" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.54</v>
+        <v>4</v>
       </c>
       <c r="R26" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="S26" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="T26" t="n">
-        <v>2.57</v>
+        <v>2.85</v>
       </c>
       <c r="U26" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="V26" t="n">
         <v>6.25</v>
       </c>
       <c r="W26" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X26" t="n">
         <v>1.05</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.8</v>
+        <v>3.44</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE26" t="n">
         <v>1.7</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45987.79166666666</v>
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.48</v>
+        <v>2.2</v>
       </c>
       <c r="M27" t="n">
-        <v>3.23</v>
+        <v>3.1</v>
       </c>
       <c r="N27" t="n">
-        <v>2.58</v>
+        <v>3.25</v>
       </c>
       <c r="O27" t="n">
         <v>3.2</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>

--- a/jogos_2025-11-26.xlsx
+++ b/jogos_2025-11-26.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,19 +871,19 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -893,77 +893,77 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>9.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45987.41666666666</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,19 +990,19 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1012,77 +1012,77 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45987.41666666666</v>
@@ -1347,99 +1347,99 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="N8" t="n">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="O8" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="P8" t="n">
         <v>1.83</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="S8" t="n">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="T8" t="n">
-        <v>3.85</v>
+        <v>3.74</v>
       </c>
       <c r="U8" t="n">
         <v>1.22</v>
       </c>
       <c r="V8" t="n">
-        <v>13</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W8" t="n">
         <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AA8" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AC8" t="n">
-        <v>6.78</v>
+        <v>5.75</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45987.60416666666</v>
@@ -1466,99 +1466,99 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="M9" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="N9" t="n">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="P9" t="n">
         <v>1.83</v>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="S9" t="n">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="T9" t="n">
-        <v>3.74</v>
+        <v>3.85</v>
       </c>
       <c r="U9" t="n">
         <v>1.22</v>
       </c>
       <c r="V9" t="n">
-        <v>8.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="W9" t="n">
         <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.75</v>
+        <v>6.78</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="AF9" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG9" t="n">
         <v>1.6</v>
       </c>
-      <c r="AG9" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AH9" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45987.60416666666</v>
@@ -1942,19 +1942,19 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.45</v>
+        <v>1.48</v>
       </c>
       <c r="M13" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="N13" t="n">
-        <v>2.85</v>
+        <v>4.7</v>
       </c>
       <c r="O13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T13" t="n">
         <v>2.94</v>
       </c>
-      <c r="P13" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.95</v>
-      </c>
       <c r="U13" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="V13" t="n">
         <v>7</v>
       </c>
       <c r="W13" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.25</v>
+        <v>3.36</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.77</v>
+        <v>1.98</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.08</v>
+        <v>1.82</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.63</v>
+        <v>2.15</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2061,16 +2061,16 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.48</v>
+        <v>1.72</v>
       </c>
       <c r="M14" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="N14" t="n">
+        <v>5</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="n">
         <v>2.7</v>
       </c>
-      <c r="O14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P14" t="n">
+      <c r="U14" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V14" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF14" t="n">
         <v>1.99</v>
       </c>
-      <c r="Q14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V14" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2</v>
-      </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.48</v>
+        <v>2.1</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2180,22 +2180,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.48</v>
+        <v>2.48</v>
       </c>
       <c r="M15" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="N15" t="n">
-        <v>4.7</v>
+        <v>2.7</v>
       </c>
       <c r="O15" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2</v>
+        <v>1.99</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.66</v>
+        <v>3.3</v>
       </c>
       <c r="R15" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S15" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="T15" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="W15" t="n">
         <v>1.06</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.36</v>
+        <v>3.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.68</v>
+        <v>3.72</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.98</v>
+        <v>1.81</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.15</v>
+        <v>1.48</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2299,22 +2299,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.72</v>
+        <v>2.45</v>
       </c>
       <c r="M16" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>5</v>
+        <v>2.85</v>
       </c>
       <c r="O16" t="n">
-        <v>2.25</v>
+        <v>2.94</v>
       </c>
       <c r="P16" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.7</v>
+        <v>3.31</v>
       </c>
       <c r="R16" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="T16" t="n">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="U16" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="V16" t="n">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="W16" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X16" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AD16" t="n">
         <v>1.28</v>
       </c>
-      <c r="Z16" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AE16" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.1</v>
+        <v>1.63</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45987.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,99 +2418,99 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.3</v>
+        <v>2.75</v>
       </c>
       <c r="M17" t="n">
-        <v>4.83</v>
+        <v>3</v>
       </c>
       <c r="N17" t="n">
-        <v>7</v>
+        <v>2.69</v>
       </c>
       <c r="O17" t="n">
-        <v>1.93</v>
+        <v>3.4</v>
       </c>
       <c r="P17" t="n">
-        <v>2.63</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.7</v>
+        <v>3.25</v>
       </c>
       <c r="R17" t="n">
-        <v>1.29</v>
+        <v>1.52</v>
       </c>
       <c r="S17" t="n">
-        <v>3.5</v>
+        <v>2.35</v>
       </c>
       <c r="T17" t="n">
-        <v>2.35</v>
+        <v>3.4</v>
       </c>
       <c r="U17" t="n">
-        <v>1.53</v>
+        <v>1.28</v>
       </c>
       <c r="V17" t="n">
-        <v>5.25</v>
+        <v>8</v>
       </c>
       <c r="W17" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.16</v>
+        <v>1.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.5</v>
+        <v>2.64</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.62</v>
+        <v>4</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.56</v>
+        <v>1.2</v>
       </c>
       <c r="AE17" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF17" t="n">
         <v>1.83</v>
       </c>
-      <c r="AF17" t="n">
-        <v>1.89</v>
-      </c>
       <c r="AG17" t="n">
-        <v>1.07</v>
+        <v>1.39</v>
       </c>
       <c r="AH17" t="n">
-        <v>3</v>
+        <v>1.42</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2546,20 +2546,20 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -2656,19 +2656,19 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -2678,77 +2678,77 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="M19" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>2.77</v>
+        <v>2.36</v>
       </c>
       <c r="O19" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="P19" t="n">
         <v>2.15</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S19" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="T19" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="U19" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V19" t="n">
-        <v>6.5</v>
+        <v>5.25</v>
       </c>
       <c r="W19" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X19" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.95</v>
+        <v>4.9</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.9</v>
+        <v>2.27</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,99 +2775,99 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.75</v>
+        <v>1.55</v>
       </c>
       <c r="M20" t="n">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="N20" t="n">
-        <v>2.69</v>
+        <v>5.75</v>
       </c>
       <c r="O20" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>5</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S20" t="n">
         <v>3.4</v>
       </c>
-      <c r="P20" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.35</v>
-      </c>
       <c r="T20" t="n">
-        <v>3.4</v>
+        <v>2.25</v>
       </c>
       <c r="U20" t="n">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="V20" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="X20" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.64</v>
+        <v>5</v>
       </c>
       <c r="AA20" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AC20" t="n">
         <v>2.3</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="AD20" t="n">
         <v>1.6</v>
       </c>
-      <c r="AC20" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AE20" t="n">
-        <v>1.97</v>
+        <v>1.67</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.39</v>
+        <v>1.17</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.42</v>
+        <v>2.71</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45987.70833333334</v>
@@ -2903,20 +2903,20 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -3013,25 +3013,25 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H22" t="n">
         <v>3</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -3039,34 +3039,34 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="M22" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="N22" t="n">
+        <v>7</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S22" t="n">
         <v>3.5</v>
       </c>
-      <c r="N22" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="O22" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.1</v>
-      </c>
       <c r="T22" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="U22" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="V22" t="n">
         <v>5.25</v>
@@ -3075,37 +3075,37 @@
         <v>1.12</v>
       </c>
       <c r="X22" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.4</v>
+        <v>1.89</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.55</v>
+        <v>1.07</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.44</v>
+        <v>3</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3132,99 +3132,99 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>4.9</v>
+        <v>2.18</v>
       </c>
       <c r="M23" t="n">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="N23" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V23" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH23" t="n">
         <v>1.6</v>
-      </c>
-      <c r="O23" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V23" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.17</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3251,99 +3251,99 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.55</v>
+        <v>4.9</v>
       </c>
       <c r="M24" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="N24" t="n">
-        <v>5.75</v>
+        <v>1.6</v>
       </c>
       <c r="O24" t="n">
-        <v>1.97</v>
+        <v>4.6</v>
       </c>
       <c r="P24" t="n">
-        <v>2.5</v>
+        <v>2.61</v>
       </c>
       <c r="Q24" t="n">
-        <v>5</v>
+        <v>2.1</v>
       </c>
       <c r="R24" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="S24" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="T24" t="n">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="U24" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="V24" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="W24" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y24" t="n">
         <v>1.14</v>
       </c>
-      <c r="X24" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y24" t="n">
+      <c r="Z24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH24" t="n">
         <v>1.17</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>2.71</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45987.70833333334</v>
@@ -3379,20 +3379,20 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -3501,7 +3501,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L26" t="n">
